--- a/outputs/daily/hr_rankings_2026-08-22_full.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-22_full.xlsx
@@ -45363,27 +45363,27 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>666126</t>
+          <t>573262</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Carlos Cortes</t>
+          <t>Mike Yastrzemski</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>2026-08-22T23:10:00Z</t>
+          <t>2026-08-22T18:10:00Z</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -45393,17 +45393,17 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>Hunter Brown</t>
+          <t>Logan Henderson</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>686613</t>
+          <t>701656</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
@@ -45412,7 +45412,7 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>39.5</v>
+        <v>39.4</v>
       </c>
       <c r="M165" t="inlineStr">
         <is>
@@ -45430,22 +45430,22 @@
         </is>
       </c>
       <c r="P165" t="n">
-        <v>30.7</v>
+        <v>35.8</v>
       </c>
       <c r="Q165" t="n">
-        <v>22.7</v>
+        <v>35</v>
       </c>
       <c r="R165" t="n">
         <v>27.6</v>
       </c>
       <c r="S165" t="n">
-        <v>71.7</v>
+        <v>40.2</v>
       </c>
       <c r="T165" t="n">
         <v>80</v>
       </c>
       <c r="U165" t="n">
-        <v>50</v>
+        <v>44.5</v>
       </c>
       <c r="V165" t="inlineStr">
         <is>
@@ -45459,7 +45459,7 @@
       </c>
       <c r="X165" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y165" t="inlineStr">
@@ -45496,32 +45496,32 @@
       </c>
       <c r="AG165" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AH165" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI165" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
         <is>
-          <t>Recent form unavailable</t>
+          <t>Last 7 games: 5/17, 1 HR</t>
         </is>
       </c>
       <c r="AL165" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.2% barrel, 11.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.6% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AM165" t="inlineStr">
@@ -45531,104 +45531,104 @@
       </c>
       <c r="AN165" t="inlineStr">
         <is>
-          <t>7.24</t>
+          <t>7.59</t>
         </is>
       </c>
       <c r="AO165" t="inlineStr">
         <is>
-          <t>39.59</t>
+          <t>43.23</t>
         </is>
       </c>
       <c r="AP165" t="inlineStr">
         <is>
-          <t>89.38</t>
+          <t>90.73</t>
         </is>
       </c>
       <c r="AQ165" t="inlineStr">
         <is>
-          <t>99.6817</t>
+          <t>99.7769</t>
         </is>
       </c>
       <c r="AR165" t="inlineStr">
         <is>
-          <t>0.408</t>
+          <t>0.3861</t>
         </is>
       </c>
       <c r="AS165" t="inlineStr">
         <is>
-          <t>0.1483</t>
+          <t>0.1491</t>
         </is>
       </c>
       <c r="AT165" t="inlineStr">
         <is>
-          <t>0.3189</t>
+          <t>0.3185</t>
         </is>
       </c>
       <c r="AU165" t="inlineStr">
         <is>
-          <t>70.76</t>
+          <t>71.31</t>
         </is>
       </c>
       <c r="AV165" t="inlineStr">
         <is>
-          <t>14.41</t>
+          <t>8.44</t>
         </is>
       </c>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>30.48</t>
+          <t>46.04</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>31.12</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>11.4</t>
         </is>
       </c>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>0.1717</t>
+          <t>0.1623</t>
         </is>
       </c>
       <c r="BA165" t="inlineStr">
         <is>
-          <t>6.18</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="BB165" t="inlineStr">
         <is>
-          <t>35.63</t>
+          <t>36.09</t>
         </is>
       </c>
       <c r="BC165" t="inlineStr">
         <is>
-          <t>85.96</t>
+          <t>88.38</t>
         </is>
       </c>
       <c r="BD165" t="inlineStr">
         <is>
-          <t>0.3397</t>
+          <t>0.352</t>
         </is>
       </c>
       <c r="BE165" t="inlineStr">
         <is>
-          <t>0.1304</t>
+          <t>0.1393</t>
         </is>
       </c>
       <c r="BF165" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BG165" t="inlineStr"/>
       <c r="BH165" t="inlineStr"/>
       <c r="BI165" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ165" t="inlineStr"/>
@@ -45639,27 +45639,27 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>573262</t>
+          <t>702284</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Mike Yastrzemski</t>
+          <t>Cole Young</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-08-22T18:10:00Z</t>
+          <t>2026-08-22T23:15:00Z</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -45669,22 +45669,22 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>Logan Henderson</t>
+          <t>David Peterson</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>701656</t>
+          <t>656849</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L166" t="n">
@@ -45702,26 +45702,26 @@
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P166" t="n">
-        <v>35.8</v>
+        <v>24.2</v>
       </c>
       <c r="Q166" t="n">
-        <v>35</v>
+        <v>35.9</v>
       </c>
       <c r="R166" t="n">
-        <v>27.6</v>
+        <v>25.4</v>
       </c>
       <c r="S166" t="n">
-        <v>40.2</v>
+        <v>95.5</v>
       </c>
       <c r="T166" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U166" t="n">
-        <v>44.5</v>
+        <v>21.8</v>
       </c>
       <c r="V166" t="inlineStr">
         <is>
@@ -45735,7 +45735,7 @@
       </c>
       <c r="X166" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y166" t="inlineStr">
@@ -45777,12 +45777,12 @@
       </c>
       <c r="AH166" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI166" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ166" t="inlineStr">
@@ -45792,12 +45792,12 @@
       </c>
       <c r="AK166" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/17, 1 HR</t>
+          <t>Last 7 games: 4/28, 1 HR</t>
         </is>
       </c>
       <c r="AL166" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.6% barrel, 7.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.4% barrel, 11.0 HR allowed</t>
         </is>
       </c>
       <c r="AM166" t="inlineStr">
@@ -45807,104 +45807,104 @@
       </c>
       <c r="AN166" t="inlineStr">
         <is>
-          <t>7.59</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AO166" t="inlineStr">
         <is>
-          <t>43.23</t>
+          <t>36.28</t>
         </is>
       </c>
       <c r="AP166" t="inlineStr">
         <is>
-          <t>90.73</t>
+          <t>88.37</t>
         </is>
       </c>
       <c r="AQ166" t="inlineStr">
         <is>
-          <t>99.7769</t>
+          <t>98.9567</t>
         </is>
       </c>
       <c r="AR166" t="inlineStr">
         <is>
-          <t>0.3861</t>
+          <t>0.3879</t>
         </is>
       </c>
       <c r="AS166" t="inlineStr">
         <is>
-          <t>0.1491</t>
+          <t>0.1324</t>
         </is>
       </c>
       <c r="AT166" t="inlineStr">
         <is>
-          <t>0.3185</t>
+          <t>0.3145</t>
         </is>
       </c>
       <c r="AU166" t="inlineStr">
         <is>
-          <t>71.31</t>
+          <t>71.44</t>
         </is>
       </c>
       <c r="AV166" t="inlineStr">
         <is>
-          <t>8.44</t>
+          <t>21.16</t>
         </is>
       </c>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>46.04</t>
+          <t>41.84</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>31.12</t>
+          <t>27.29</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr">
         <is>
-          <t>11.4</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>0.1623</t>
+          <t>0.1262</t>
         </is>
       </c>
       <c r="BA166" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="BB166" t="inlineStr">
         <is>
-          <t>36.09</t>
+          <t>42.64</t>
         </is>
       </c>
       <c r="BC166" t="inlineStr">
         <is>
-          <t>88.38</t>
+          <t>89.69</t>
         </is>
       </c>
       <c r="BD166" t="inlineStr">
         <is>
-          <t>0.352</t>
+          <t>0.414</t>
         </is>
       </c>
       <c r="BE166" t="inlineStr">
         <is>
-          <t>0.1393</t>
+          <t>0.1405</t>
         </is>
       </c>
       <c r="BF166" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>19.71</t>
         </is>
       </c>
       <c r="BG166" t="inlineStr"/>
       <c r="BH166" t="inlineStr"/>
       <c r="BI166" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ166" t="inlineStr"/>
@@ -45915,27 +45915,27 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>702284</t>
+          <t>667472</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Cole Young</t>
+          <t>Dane Myers</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>2026-08-22T23:15:00Z</t>
+          <t>2026-08-23T00:10:00Z</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -45945,22 +45945,22 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>David Peterson</t>
+          <t>Michael Soroka</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>656849</t>
+          <t>647336</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L167" t="n">
@@ -45978,26 +45978,26 @@
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P167" t="n">
-        <v>24.2</v>
+        <v>27.8</v>
       </c>
       <c r="Q167" t="n">
-        <v>35.9</v>
+        <v>33.7</v>
       </c>
       <c r="R167" t="n">
-        <v>25.4</v>
+        <v>28.2</v>
       </c>
       <c r="S167" t="n">
-        <v>95.5</v>
+        <v>71.7</v>
       </c>
       <c r="T167" t="n">
         <v>50</v>
       </c>
       <c r="U167" t="n">
-        <v>21.8</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="V167" t="inlineStr">
         <is>
@@ -46011,7 +46011,7 @@
       </c>
       <c r="X167" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y167" t="inlineStr">
@@ -46053,27 +46053,27 @@
       </c>
       <c r="AH167" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI167" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/28, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL167" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.4% barrel, 11.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.6% barrel, 7.8 HR allowed</t>
         </is>
       </c>
       <c r="AM167" t="inlineStr">
@@ -46083,104 +46083,104 @@
       </c>
       <c r="AN167" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="AO167" t="inlineStr">
         <is>
-          <t>36.28</t>
+          <t>37.94</t>
         </is>
       </c>
       <c r="AP167" t="inlineStr">
         <is>
-          <t>88.37</t>
+          <t>89.86</t>
         </is>
       </c>
       <c r="AQ167" t="inlineStr">
         <is>
-          <t>98.9567</t>
+          <t>99.3259</t>
         </is>
       </c>
       <c r="AR167" t="inlineStr">
         <is>
-          <t>0.3879</t>
+          <t>0.3748</t>
         </is>
       </c>
       <c r="AS167" t="inlineStr">
         <is>
-          <t>0.1324</t>
+          <t>0.1358</t>
         </is>
       </c>
       <c r="AT167" t="inlineStr">
         <is>
-          <t>0.3145</t>
+          <t>0.3138</t>
         </is>
       </c>
       <c r="AU167" t="inlineStr">
         <is>
-          <t>71.44</t>
+          <t>71.25</t>
         </is>
       </c>
       <c r="AV167" t="inlineStr">
         <is>
-          <t>21.16</t>
+          <t>19.38</t>
         </is>
       </c>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>41.84</t>
+          <t>25.97</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>27.29</t>
+          <t>25.52</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>0.1262</t>
+          <t>0.1043</t>
         </is>
       </c>
       <c r="BA167" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>7.61</t>
         </is>
       </c>
       <c r="BB167" t="inlineStr">
         <is>
-          <t>42.64</t>
+          <t>34.94</t>
         </is>
       </c>
       <c r="BC167" t="inlineStr">
         <is>
-          <t>89.69</t>
+          <t>88.08</t>
         </is>
       </c>
       <c r="BD167" t="inlineStr">
         <is>
-          <t>0.414</t>
+          <t>0.3902</t>
         </is>
       </c>
       <c r="BE167" t="inlineStr">
         <is>
-          <t>0.1405</t>
+          <t>0.1497</t>
         </is>
       </c>
       <c r="BF167" t="inlineStr">
         <is>
-          <t>19.71</t>
+          <t>28.36</t>
         </is>
       </c>
       <c r="BG167" t="inlineStr"/>
       <c r="BH167" t="inlineStr"/>
       <c r="BI167" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BJ167" t="inlineStr"/>
@@ -46191,27 +46191,27 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>667472</t>
+          <t>689414</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Dane Myers</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>2026-08-23T00:10:00Z</t>
+          <t>2026-08-22T23:05:00Z</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -46221,17 +46221,17 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>Michael Soroka</t>
+          <t>Brandon Young</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>647336</t>
+          <t>687064</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
@@ -46240,7 +46240,7 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>39.4</v>
+        <v>39.1</v>
       </c>
       <c r="M168" t="inlineStr">
         <is>
@@ -46254,26 +46254,26 @@
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P168" t="n">
-        <v>27.8</v>
+        <v>8.5</v>
       </c>
       <c r="Q168" t="n">
-        <v>33.7</v>
+        <v>43.6</v>
       </c>
       <c r="R168" t="n">
-        <v>28.2</v>
+        <v>32.1</v>
       </c>
       <c r="S168" t="n">
-        <v>71.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T168" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U168" t="n">
-        <v>66.40000000000001</v>
+        <v>48.1</v>
       </c>
       <c r="V168" t="inlineStr">
         <is>
@@ -46287,7 +46287,7 @@
       </c>
       <c r="X168" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y168" t="inlineStr">
@@ -46339,17 +46339,17 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 7/22, 1 HR</t>
         </is>
       </c>
       <c r="AL168" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.6% barrel, 7.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.9% barrel, 14.1 HR allowed</t>
         </is>
       </c>
       <c r="AM168" t="inlineStr">
@@ -46359,104 +46359,104 @@
       </c>
       <c r="AN168" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="AO168" t="inlineStr">
         <is>
-          <t>37.94</t>
+          <t>27.98</t>
         </is>
       </c>
       <c r="AP168" t="inlineStr">
         <is>
-          <t>89.86</t>
+          <t>84.81</t>
         </is>
       </c>
       <c r="AQ168" t="inlineStr">
         <is>
-          <t>99.3259</t>
+          <t>96.2084</t>
         </is>
       </c>
       <c r="AR168" t="inlineStr">
         <is>
-          <t>0.3748</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AS168" t="inlineStr">
         <is>
-          <t>0.1358</t>
+          <t>0.1004</t>
         </is>
       </c>
       <c r="AT168" t="inlineStr">
         <is>
-          <t>0.3138</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AU168" t="inlineStr">
         <is>
-          <t>71.25</t>
+          <t>68.03</t>
         </is>
       </c>
       <c r="AV168" t="inlineStr">
         <is>
-          <t>19.38</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>25.97</t>
+          <t>42.1</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>25.52</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AZ168" t="inlineStr">
         <is>
-          <t>0.1043</t>
+          <t>0.1389</t>
         </is>
       </c>
       <c r="BA168" t="inlineStr">
         <is>
-          <t>7.61</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="BB168" t="inlineStr">
         <is>
-          <t>34.94</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="BC168" t="inlineStr">
         <is>
-          <t>88.08</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="BD168" t="inlineStr">
         <is>
-          <t>0.3902</t>
+          <t>0.4201</t>
         </is>
       </c>
       <c r="BE168" t="inlineStr">
         <is>
-          <t>0.1497</t>
+          <t>0.1672</t>
         </is>
       </c>
       <c r="BF168" t="inlineStr">
         <is>
-          <t>28.36</t>
+          <t>27.43</t>
         </is>
       </c>
       <c r="BG168" t="inlineStr"/>
       <c r="BH168" t="inlineStr"/>
       <c r="BI168" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ168" t="inlineStr"/>
@@ -46467,27 +46467,27 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>689414</t>
+          <t>650333</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Liam Hicks</t>
+          <t>Luis Arraez</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>2026-08-22T23:05:00Z</t>
+          <t>2026-08-22T22:05:00Z</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -46497,26 +46497,14 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>Brandon Young</t>
-        </is>
-      </c>
-      <c r="J169" t="inlineStr">
-        <is>
-          <t>687064</t>
-        </is>
-      </c>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr"/>
       <c r="L169" t="n">
-        <v>39.1</v>
+        <v>38.8</v>
       </c>
       <c r="M169" t="inlineStr">
         <is>
@@ -46530,26 +46518,26 @@
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P169" t="n">
-        <v>8.5</v>
+        <v>7.7</v>
       </c>
       <c r="Q169" t="n">
-        <v>43.6</v>
+        <v>41.2</v>
       </c>
       <c r="R169" t="n">
-        <v>32.1</v>
+        <v>34.3</v>
       </c>
       <c r="S169" t="n">
-        <v>81.90000000000001</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T169" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U169" t="n">
-        <v>48.1</v>
+        <v>63.3</v>
       </c>
       <c r="V169" t="inlineStr">
         <is>
@@ -46563,7 +46551,7 @@
       </c>
       <c r="X169" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y169" t="inlineStr">
@@ -46588,7 +46576,7 @@
       </c>
       <c r="AC169" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD169" t="inlineStr"/>
@@ -46605,12 +46593,12 @@
       </c>
       <c r="AH169" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AI169" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AJ169" t="inlineStr">
@@ -46620,12 +46608,12 @@
       </c>
       <c r="AK169" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/22, 1 HR</t>
+          <t>Contact streak: 14/31 over last 7 games</t>
         </is>
       </c>
       <c r="AL169" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.9% barrel, 14.1 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM169" t="inlineStr">
@@ -46635,104 +46623,80 @@
       </c>
       <c r="AN169" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AO169" t="inlineStr">
         <is>
-          <t>27.98</t>
+          <t>19.08</t>
         </is>
       </c>
       <c r="AP169" t="inlineStr">
         <is>
-          <t>84.81</t>
+          <t>86.59</t>
         </is>
       </c>
       <c r="AQ169" t="inlineStr">
         <is>
-          <t>96.2084</t>
+          <t>94.0058</t>
         </is>
       </c>
       <c r="AR169" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.3777</t>
         </is>
       </c>
       <c r="AS169" t="inlineStr">
         <is>
-          <t>0.1004</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AT169" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.3072</t>
         </is>
       </c>
       <c r="AU169" t="inlineStr">
         <is>
-          <t>68.03</t>
+          <t>62.99</t>
         </is>
       </c>
       <c r="AV169" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>30.24</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>28.52</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="AZ169" t="inlineStr">
         <is>
-          <t>0.1389</t>
-        </is>
-      </c>
-      <c r="BA169" t="inlineStr">
-        <is>
-          <t>7.89</t>
-        </is>
-      </c>
-      <c r="BB169" t="inlineStr">
-        <is>
-          <t>41.43</t>
-        </is>
-      </c>
-      <c r="BC169" t="inlineStr">
-        <is>
-          <t>89.4</t>
-        </is>
-      </c>
-      <c r="BD169" t="inlineStr">
-        <is>
-          <t>0.4201</t>
-        </is>
-      </c>
-      <c r="BE169" t="inlineStr">
-        <is>
-          <t>0.1672</t>
-        </is>
-      </c>
-      <c r="BF169" t="inlineStr">
-        <is>
-          <t>27.43</t>
-        </is>
-      </c>
+          <t>0.1154</t>
+        </is>
+      </c>
+      <c r="BA169" t="inlineStr"/>
+      <c r="BB169" t="inlineStr"/>
+      <c r="BC169" t="inlineStr"/>
+      <c r="BD169" t="inlineStr"/>
+      <c r="BE169" t="inlineStr"/>
+      <c r="BF169" t="inlineStr"/>
       <c r="BG169" t="inlineStr"/>
       <c r="BH169" t="inlineStr"/>
       <c r="BI169" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BJ169" t="inlineStr"/>
@@ -46743,27 +46707,27 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>650333</t>
+          <t>691720</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Luis Arraez</t>
+          <t>Kyle Karros</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>2026-08-22T22:05:00Z</t>
+          <t>2026-08-23T00:10:00Z</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -46773,12 +46737,24 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr"/>
-      <c r="J170" t="inlineStr"/>
-      <c r="K170" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Tanner Bibee</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>676440</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L170" t="n">
         <v>38.8</v>
       </c>
@@ -46794,26 +46770,26 @@
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P170" t="n">
-        <v>7.7</v>
+        <v>24.2</v>
       </c>
       <c r="Q170" t="n">
-        <v>41.2</v>
+        <v>43.8</v>
       </c>
       <c r="R170" t="n">
-        <v>34.3</v>
+        <v>38.7</v>
       </c>
       <c r="S170" t="n">
-        <v>90.40000000000001</v>
+        <v>59.8</v>
       </c>
       <c r="T170" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U170" t="n">
-        <v>63.3</v>
+        <v>32.9</v>
       </c>
       <c r="V170" t="inlineStr">
         <is>
@@ -46827,7 +46803,7 @@
       </c>
       <c r="X170" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y170" t="inlineStr">
@@ -46852,7 +46828,7 @@
       </c>
       <c r="AC170" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD170" t="inlineStr"/>
@@ -46869,12 +46845,12 @@
       </c>
       <c r="AH170" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI170" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ170" t="inlineStr">
@@ -46884,12 +46860,12 @@
       </c>
       <c r="AK170" t="inlineStr">
         <is>
-          <t>Contact streak: 14/31 over last 7 games</t>
+          <t>Last 7 games: 5/23, 1 HR</t>
         </is>
       </c>
       <c r="AL170" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.2% barrel, 25.6 HR allowed</t>
         </is>
       </c>
       <c r="AM170" t="inlineStr">
@@ -46899,80 +46875,104 @@
       </c>
       <c r="AN170" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="AO170" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>39.09</t>
         </is>
       </c>
       <c r="AP170" t="inlineStr">
         <is>
-          <t>86.59</t>
+          <t>89.02</t>
         </is>
       </c>
       <c r="AQ170" t="inlineStr">
         <is>
-          <t>94.0058</t>
+          <t>99.598</t>
         </is>
       </c>
       <c r="AR170" t="inlineStr">
         <is>
-          <t>0.3777</t>
+          <t>0.3614</t>
         </is>
       </c>
       <c r="AS170" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.1201</t>
         </is>
       </c>
       <c r="AT170" t="inlineStr">
         <is>
-          <t>0.3072</t>
+          <t>0.3147</t>
         </is>
       </c>
       <c r="AU170" t="inlineStr">
         <is>
-          <t>62.99</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="AV170" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>30.24</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>28.52</t>
+          <t>24.13</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AZ170" t="inlineStr">
         <is>
-          <t>0.1154</t>
-        </is>
-      </c>
-      <c r="BA170" t="inlineStr"/>
-      <c r="BB170" t="inlineStr"/>
-      <c r="BC170" t="inlineStr"/>
-      <c r="BD170" t="inlineStr"/>
-      <c r="BE170" t="inlineStr"/>
-      <c r="BF170" t="inlineStr"/>
+          <t>0.1252</t>
+        </is>
+      </c>
+      <c r="BA170" t="inlineStr">
+        <is>
+          <t>8.24</t>
+        </is>
+      </c>
+      <c r="BB170" t="inlineStr">
+        <is>
+          <t>38.49</t>
+        </is>
+      </c>
+      <c r="BC170" t="inlineStr">
+        <is>
+          <t>89.13</t>
+        </is>
+      </c>
+      <c r="BD170" t="inlineStr">
+        <is>
+          <t>0.4116</t>
+        </is>
+      </c>
+      <c r="BE170" t="inlineStr">
+        <is>
+          <t>0.1674</t>
+        </is>
+      </c>
+      <c r="BF170" t="inlineStr">
+        <is>
+          <t>27.62</t>
+        </is>
+      </c>
       <c r="BG170" t="inlineStr"/>
       <c r="BH170" t="inlineStr"/>
       <c r="BI170" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ170" t="inlineStr"/>
@@ -46983,27 +46983,27 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>691720</t>
+          <t>676391</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Kyle Karros</t>
+          <t>Ernie Clement</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-08-23T00:10:00Z</t>
+          <t>2026-08-22T17:35:00Z</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -47013,26 +47013,26 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>Tanner Bibee</t>
+          <t>Ryan Weathers</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>676440</t>
+          <t>677960</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L171" t="n">
-        <v>38.8</v>
+        <v>38.7</v>
       </c>
       <c r="M171" t="inlineStr">
         <is>
@@ -47046,26 +47046,26 @@
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P171" t="n">
-        <v>24.2</v>
+        <v>5.5</v>
       </c>
       <c r="Q171" t="n">
-        <v>43.8</v>
+        <v>45.5</v>
       </c>
       <c r="R171" t="n">
-        <v>38.7</v>
+        <v>38.2</v>
       </c>
       <c r="S171" t="n">
-        <v>59.8</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T171" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U171" t="n">
-        <v>32.9</v>
+        <v>34.2</v>
       </c>
       <c r="V171" t="inlineStr">
         <is>
@@ -47079,7 +47079,7 @@
       </c>
       <c r="X171" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y171" t="inlineStr">
@@ -47121,7 +47121,7 @@
       </c>
       <c r="AH171" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI171" t="inlineStr">
@@ -47131,17 +47131,17 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/23, 1 HR</t>
+          <t>Contact streak: 8/23 over last 7 games</t>
         </is>
       </c>
       <c r="AL171" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.2% barrel, 25.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 14.7 HR allowed</t>
         </is>
       </c>
       <c r="AM171" t="inlineStr">
@@ -47151,104 +47151,104 @@
       </c>
       <c r="AN171" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="AO171" t="inlineStr">
         <is>
-          <t>39.09</t>
+          <t>22.08</t>
         </is>
       </c>
       <c r="AP171" t="inlineStr">
         <is>
-          <t>89.02</t>
+          <t>85.13</t>
         </is>
       </c>
       <c r="AQ171" t="inlineStr">
         <is>
-          <t>99.598</t>
+          <t>94.7039</t>
         </is>
       </c>
       <c r="AR171" t="inlineStr">
         <is>
-          <t>0.3614</t>
+          <t>0.3415</t>
         </is>
       </c>
       <c r="AS171" t="inlineStr">
         <is>
-          <t>0.1201</t>
+          <t>0.0867</t>
         </is>
       </c>
       <c r="AT171" t="inlineStr">
         <is>
-          <t>0.3147</t>
+          <t>0.2757</t>
         </is>
       </c>
       <c r="AU171" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>67.46</t>
         </is>
       </c>
       <c r="AV171" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>24.13</t>
+          <t>27.83</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AZ171" t="inlineStr">
         <is>
-          <t>0.1252</t>
+          <t>0.1189</t>
         </is>
       </c>
       <c r="BA171" t="inlineStr">
         <is>
-          <t>8.24</t>
+          <t>8.76</t>
         </is>
       </c>
       <c r="BB171" t="inlineStr">
         <is>
-          <t>38.49</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="BC171" t="inlineStr">
         <is>
-          <t>89.13</t>
+          <t>89.46</t>
         </is>
       </c>
       <c r="BD171" t="inlineStr">
         <is>
-          <t>0.4116</t>
+          <t>0.4173</t>
         </is>
       </c>
       <c r="BE171" t="inlineStr">
         <is>
-          <t>0.1674</t>
+          <t>0.1708</t>
         </is>
       </c>
       <c r="BF171" t="inlineStr">
         <is>
-          <t>27.62</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="BG171" t="inlineStr"/>
       <c r="BH171" t="inlineStr"/>
       <c r="BI171" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ171" t="inlineStr"/>
@@ -47259,27 +47259,27 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>676391</t>
+          <t>701675</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Ernie Clement</t>
+          <t>Nathan Church</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>2026-08-22T17:35:00Z</t>
+          <t>2026-08-22T22:05:00Z</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -47289,26 +47289,26 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>Ryan Weathers</t>
+          <t>Andrew Painter</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>677960</t>
+          <t>691725</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L172" t="n">
-        <v>38.7</v>
+        <v>38.4</v>
       </c>
       <c r="M172" t="inlineStr">
         <is>
@@ -47326,22 +47326,22 @@
         </is>
       </c>
       <c r="P172" t="n">
-        <v>5.5</v>
+        <v>16</v>
       </c>
       <c r="Q172" t="n">
-        <v>45.5</v>
+        <v>41.4</v>
       </c>
       <c r="R172" t="n">
-        <v>38.2</v>
+        <v>34.3</v>
       </c>
       <c r="S172" t="n">
-        <v>81.90000000000001</v>
+        <v>71.7</v>
       </c>
       <c r="T172" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U172" t="n">
-        <v>34.2</v>
+        <v>16.6</v>
       </c>
       <c r="V172" t="inlineStr">
         <is>
@@ -47355,7 +47355,7 @@
       </c>
       <c r="X172" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y172" t="inlineStr">
@@ -47380,7 +47380,7 @@
       </c>
       <c r="AC172" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD172" t="inlineStr"/>
@@ -47397,12 +47397,12 @@
       </c>
       <c r="AH172" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI172" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AJ172" t="inlineStr">
@@ -47412,12 +47412,12 @@
       </c>
       <c r="AK172" t="inlineStr">
         <is>
-          <t>Contact streak: 8/23 over last 7 games</t>
+          <t>Last 7 games: 3/13, 0 HR</t>
         </is>
       </c>
       <c r="AL172" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 14.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.4% barrel, 17.0 HR allowed</t>
         </is>
       </c>
       <c r="AM172" t="inlineStr">
@@ -47427,104 +47427,104 @@
       </c>
       <c r="AN172" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="AO172" t="inlineStr">
         <is>
-          <t>22.08</t>
+          <t>33.59</t>
         </is>
       </c>
       <c r="AP172" t="inlineStr">
         <is>
-          <t>85.13</t>
+          <t>86.9</t>
         </is>
       </c>
       <c r="AQ172" t="inlineStr">
         <is>
-          <t>94.7039</t>
+          <t>97.7451</t>
         </is>
       </c>
       <c r="AR172" t="inlineStr">
         <is>
-          <t>0.3415</t>
+          <t>0.3357</t>
         </is>
       </c>
       <c r="AS172" t="inlineStr">
         <is>
-          <t>0.0867</t>
+          <t>0.1088</t>
         </is>
       </c>
       <c r="AT172" t="inlineStr">
         <is>
-          <t>0.2757</t>
+          <t>0.2736</t>
         </is>
       </c>
       <c r="AU172" t="inlineStr">
         <is>
-          <t>67.46</t>
+          <t>69.6</t>
         </is>
       </c>
       <c r="AV172" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>8.62</t>
         </is>
       </c>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>34.78</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>27.83</t>
+          <t>21.46</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="AZ172" t="inlineStr">
         <is>
-          <t>0.1189</t>
+          <t>0.1053</t>
         </is>
       </c>
       <c r="BA172" t="inlineStr">
         <is>
-          <t>8.76</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="BB172" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>35.5</t>
         </is>
       </c>
       <c r="BC172" t="inlineStr">
         <is>
-          <t>89.46</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="BD172" t="inlineStr">
         <is>
-          <t>0.4173</t>
+          <t>0.445</t>
         </is>
       </c>
       <c r="BE172" t="inlineStr">
         <is>
-          <t>0.1708</t>
+          <t>0.178</t>
         </is>
       </c>
       <c r="BF172" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="BG172" t="inlineStr"/>
       <c r="BH172" t="inlineStr"/>
       <c r="BI172" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BJ172" t="inlineStr"/>
@@ -47535,27 +47535,27 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>701675</t>
+          <t>670623</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Nathan Church</t>
+          <t>Isaac Paredes</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2026-08-22T22:05:00Z</t>
+          <t>2026-08-22T23:10:00Z</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -47565,22 +47565,22 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>Andrew Painter</t>
+          <t>Jacob Lopez</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>691725</t>
+          <t>682052</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L173" t="n">
@@ -47598,26 +47598,26 @@
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P173" t="n">
-        <v>16</v>
+        <v>18.1</v>
       </c>
       <c r="Q173" t="n">
-        <v>41.4</v>
+        <v>21.9</v>
       </c>
       <c r="R173" t="n">
-        <v>34.3</v>
+        <v>27.6</v>
       </c>
       <c r="S173" t="n">
-        <v>71.7</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T173" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U173" t="n">
-        <v>16.6</v>
+        <v>62.8</v>
       </c>
       <c r="V173" t="inlineStr">
         <is>
@@ -47631,7 +47631,7 @@
       </c>
       <c r="X173" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y173" t="inlineStr">
@@ -47656,7 +47656,7 @@
       </c>
       <c r="AC173" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD173" t="inlineStr"/>
@@ -47673,134 +47673,134 @@
       </c>
       <c r="AH173" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI173" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/13, 0 HR</t>
+          <t>Contact streak: 10/24 over last 7 games</t>
         </is>
       </c>
       <c r="AL173" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.4% barrel, 17.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.7% barrel, 15.0 HR allowed</t>
         </is>
       </c>
       <c r="AM173" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN173" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="AO173" t="inlineStr">
         <is>
-          <t>33.59</t>
+          <t>29.89</t>
         </is>
       </c>
       <c r="AP173" t="inlineStr">
         <is>
-          <t>86.9</t>
+          <t>86.42</t>
         </is>
       </c>
       <c r="AQ173" t="inlineStr">
         <is>
-          <t>97.7451</t>
+          <t>96.9173</t>
         </is>
       </c>
       <c r="AR173" t="inlineStr">
         <is>
-          <t>0.3357</t>
+          <t>0.3779</t>
         </is>
       </c>
       <c r="AS173" t="inlineStr">
         <is>
-          <t>0.1088</t>
+          <t>0.132</t>
         </is>
       </c>
       <c r="AT173" t="inlineStr">
         <is>
-          <t>0.2736</t>
+          <t>0.3235</t>
         </is>
       </c>
       <c r="AU173" t="inlineStr">
         <is>
-          <t>69.6</t>
+          <t>67.74</t>
         </is>
       </c>
       <c r="AV173" t="inlineStr">
         <is>
-          <t>8.62</t>
+          <t>7.57</t>
         </is>
       </c>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>34.78</t>
+          <t>52.14</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>21.46</t>
+          <t>30.59</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>0.1053</t>
+          <t>0.176</t>
         </is>
       </c>
       <c r="BA173" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>5.69</t>
         </is>
       </c>
       <c r="BB173" t="inlineStr">
         <is>
-          <t>35.5</t>
+          <t>30.19</t>
         </is>
       </c>
       <c r="BC173" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>85.29</t>
         </is>
       </c>
       <c r="BD173" t="inlineStr">
         <is>
-          <t>0.445</t>
+          <t>0.3424</t>
         </is>
       </c>
       <c r="BE173" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>0.1338</t>
         </is>
       </c>
       <c r="BF173" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>32.48</t>
         </is>
       </c>
       <c r="BG173" t="inlineStr"/>
       <c r="BH173" t="inlineStr"/>
       <c r="BI173" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ173" t="inlineStr"/>
@@ -47811,27 +47811,27 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>670623</t>
+          <t>660688</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Isaac Paredes</t>
+          <t>Keibert Ruiz</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2026-08-22T23:10:00Z</t>
+          <t>2026-08-22T20:10:00Z</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -47841,26 +47841,26 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>Jacob Lopez</t>
+          <t>Eury Pérez</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>682052</t>
+          <t>691587</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L174" t="n">
-        <v>38.4</v>
+        <v>38.3</v>
       </c>
       <c r="M174" t="inlineStr">
         <is>
@@ -47874,26 +47874,26 @@
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P174" t="n">
-        <v>18.1</v>
+        <v>16.4</v>
       </c>
       <c r="Q174" t="n">
-        <v>21.9</v>
+        <v>41.7</v>
       </c>
       <c r="R174" t="n">
-        <v>27.6</v>
+        <v>21.5</v>
       </c>
       <c r="S174" t="n">
-        <v>92.09999999999999</v>
+        <v>71.7</v>
       </c>
       <c r="T174" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U174" t="n">
-        <v>62.8</v>
+        <v>56.6</v>
       </c>
       <c r="V174" t="inlineStr">
         <is>
@@ -47907,7 +47907,7 @@
       </c>
       <c r="X174" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y174" t="inlineStr">
@@ -47949,7 +47949,7 @@
       </c>
       <c r="AH174" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI174" t="inlineStr">
@@ -47964,12 +47964,12 @@
       </c>
       <c r="AK174" t="inlineStr">
         <is>
-          <t>Contact streak: 10/24 over last 7 games</t>
+          <t>Contact streak: 9/24 over last 7 games</t>
         </is>
       </c>
       <c r="AL174" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.7% barrel, 15.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.1% barrel, 12.7 HR allowed</t>
         </is>
       </c>
       <c r="AM174" t="inlineStr">
@@ -47979,104 +47979,104 @@
       </c>
       <c r="AN174" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>4.16</t>
         </is>
       </c>
       <c r="AO174" t="inlineStr">
         <is>
-          <t>29.89</t>
+          <t>35.59</t>
         </is>
       </c>
       <c r="AP174" t="inlineStr">
         <is>
-          <t>86.42</t>
+          <t>87.67</t>
         </is>
       </c>
       <c r="AQ174" t="inlineStr">
         <is>
-          <t>96.9173</t>
+          <t>97.6467</t>
         </is>
       </c>
       <c r="AR174" t="inlineStr">
         <is>
-          <t>0.3779</t>
+          <t>0.3587</t>
         </is>
       </c>
       <c r="AS174" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>0.108</t>
         </is>
       </c>
       <c r="AT174" t="inlineStr">
         <is>
-          <t>0.3235</t>
+          <t>0.2835</t>
         </is>
       </c>
       <c r="AU174" t="inlineStr">
         <is>
-          <t>67.74</t>
+          <t>67.22</t>
         </is>
       </c>
       <c r="AV174" t="inlineStr">
         <is>
-          <t>7.57</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>52.14</t>
+          <t>53.98</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>30.59</t>
+          <t>25.51</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="AZ174" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>0.1375</t>
         </is>
       </c>
       <c r="BA174" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>9.14</t>
         </is>
       </c>
       <c r="BB174" t="inlineStr">
         <is>
-          <t>30.19</t>
+          <t>41.81</t>
         </is>
       </c>
       <c r="BC174" t="inlineStr">
         <is>
-          <t>85.29</t>
+          <t>88.96</t>
         </is>
       </c>
       <c r="BD174" t="inlineStr">
         <is>
-          <t>0.3424</t>
+          <t>0.3618</t>
         </is>
       </c>
       <c r="BE174" t="inlineStr">
         <is>
-          <t>0.1338</t>
+          <t>0.1553</t>
         </is>
       </c>
       <c r="BF174" t="inlineStr">
         <is>
-          <t>32.48</t>
+          <t>30.45</t>
         </is>
       </c>
       <c r="BG174" t="inlineStr"/>
       <c r="BH174" t="inlineStr"/>
       <c r="BI174" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>loanDepot park</t>
         </is>
       </c>
       <c r="BJ174" t="inlineStr"/>
@@ -48087,24 +48087,24 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>660688</t>
+          <t>665923</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Keibert Ruiz</t>
+          <t>Esteury Ruiz</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
           <t>WSH</t>
         </is>
       </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>MIA</t>
-        </is>
-      </c>
       <c r="F175" t="inlineStr">
         <is>
           <t>2026-08-22T20:10:00Z</t>
@@ -48117,17 +48117,17 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>Eury Pérez</t>
+          <t>Jake Irvin</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>691587</t>
+          <t>663623</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -48150,26 +48150,26 @@
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P175" t="n">
-        <v>16.4</v>
+        <v>18.5</v>
       </c>
       <c r="Q175" t="n">
-        <v>41.7</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="R175" t="n">
         <v>21.5</v>
       </c>
       <c r="S175" t="n">
-        <v>71.7</v>
+        <v>59.8</v>
       </c>
       <c r="T175" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U175" t="n">
-        <v>56.6</v>
+        <v>13.6</v>
       </c>
       <c r="V175" t="inlineStr">
         <is>
@@ -48183,7 +48183,7 @@
       </c>
       <c r="X175" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y175" t="inlineStr">
@@ -48225,27 +48225,27 @@
       </c>
       <c r="AH175" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI175" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
         <is>
-          <t>Contact streak: 9/24 over last 7 games</t>
+          <t>Last 7 games: 4/19, 0 HR</t>
         </is>
       </c>
       <c r="AL175" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.1% barrel, 12.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 12.2% barrel, 19.8 HR allowed</t>
         </is>
       </c>
       <c r="AM175" t="inlineStr">
@@ -48255,97 +48255,97 @@
       </c>
       <c r="AN175" t="inlineStr">
         <is>
-          <t>4.16</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="AO175" t="inlineStr">
         <is>
-          <t>35.59</t>
+          <t>27.16</t>
         </is>
       </c>
       <c r="AP175" t="inlineStr">
         <is>
-          <t>87.67</t>
+          <t>84.37</t>
         </is>
       </c>
       <c r="AQ175" t="inlineStr">
         <is>
-          <t>97.6467</t>
+          <t>96.2826</t>
         </is>
       </c>
       <c r="AR175" t="inlineStr">
         <is>
-          <t>0.3587</t>
+          <t>0.3335</t>
         </is>
       </c>
       <c r="AS175" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>0.1435</t>
         </is>
       </c>
       <c r="AT175" t="inlineStr">
         <is>
-          <t>0.2835</t>
+          <t>0.2882</t>
         </is>
       </c>
       <c r="AU175" t="inlineStr">
         <is>
-          <t>67.22</t>
+          <t>71.31</t>
         </is>
       </c>
       <c r="AV175" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>17.82</t>
         </is>
       </c>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>53.98</t>
+          <t>45.78</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>25.51</t>
+          <t>24.99</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AZ175" t="inlineStr">
         <is>
-          <t>0.1375</t>
+          <t>0.1829</t>
         </is>
       </c>
       <c r="BA175" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>12.21</t>
         </is>
       </c>
       <c r="BB175" t="inlineStr">
         <is>
-          <t>41.81</t>
+          <t>44.79</t>
         </is>
       </c>
       <c r="BC175" t="inlineStr">
         <is>
-          <t>88.96</t>
+          <t>89.28</t>
         </is>
       </c>
       <c r="BD175" t="inlineStr">
         <is>
-          <t>0.3618</t>
+          <t>0.4742</t>
         </is>
       </c>
       <c r="BE175" t="inlineStr">
         <is>
-          <t>0.1553</t>
+          <t>0.2197</t>
         </is>
       </c>
       <c r="BF175" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>30.07</t>
         </is>
       </c>
       <c r="BG175" t="inlineStr"/>
@@ -48363,27 +48363,27 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>665923</t>
+          <t>553869</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Esteury Ruiz</t>
+          <t>Elias Diaz</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>2026-08-22T20:10:00Z</t>
+          <t>2026-08-22T23:05:00Z</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -48398,12 +48398,12 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>Jake Irvin</t>
+          <t>Ryan Johnson</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>663623</t>
+          <t>696270</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
@@ -48412,7 +48412,7 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>38.3</v>
+        <v>38.2</v>
       </c>
       <c r="M176" t="inlineStr">
         <is>
@@ -48430,13 +48430,13 @@
         </is>
       </c>
       <c r="P176" t="n">
-        <v>18.5</v>
+        <v>26.7</v>
       </c>
       <c r="Q176" t="n">
-        <v>64.40000000000001</v>
+        <v>50.2</v>
       </c>
       <c r="R176" t="n">
-        <v>21.5</v>
+        <v>27.6</v>
       </c>
       <c r="S176" t="n">
         <v>59.8</v>
@@ -48445,7 +48445,7 @@
         <v>50</v>
       </c>
       <c r="U176" t="n">
-        <v>13.6</v>
+        <v>5.7</v>
       </c>
       <c r="V176" t="inlineStr">
         <is>
@@ -48501,7 +48501,7 @@
       </c>
       <c r="AH176" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI176" t="inlineStr">
@@ -48516,12 +48516,12 @@
       </c>
       <c r="AK176" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/19, 0 HR</t>
+          <t>Last 7 games: 3/19, 0 HR</t>
         </is>
       </c>
       <c r="AL176" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 12.2% barrel, 19.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.4% barrel, 12.4 HR allowed</t>
         </is>
       </c>
       <c r="AM176" t="inlineStr">
@@ -48531,104 +48531,104 @@
       </c>
       <c r="AN176" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>6.76</t>
         </is>
       </c>
       <c r="AO176" t="inlineStr">
         <is>
-          <t>27.16</t>
+          <t>38.49</t>
         </is>
       </c>
       <c r="AP176" t="inlineStr">
         <is>
-          <t>84.37</t>
+          <t>87.21</t>
         </is>
       </c>
       <c r="AQ176" t="inlineStr">
         <is>
-          <t>96.2826</t>
+          <t>99.945</t>
         </is>
       </c>
       <c r="AR176" t="inlineStr">
         <is>
-          <t>0.3335</t>
+          <t>0.3501</t>
         </is>
       </c>
       <c r="AS176" t="inlineStr">
         <is>
-          <t>0.1435</t>
+          <t>0.1306</t>
         </is>
       </c>
       <c r="AT176" t="inlineStr">
         <is>
-          <t>0.2882</t>
+          <t>0.2624</t>
         </is>
       </c>
       <c r="AU176" t="inlineStr">
         <is>
-          <t>71.31</t>
+          <t>74.27</t>
         </is>
       </c>
       <c r="AV176" t="inlineStr">
         <is>
-          <t>17.82</t>
+          <t>43.44</t>
         </is>
       </c>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>45.78</t>
+          <t>37.93</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>27.59</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="AZ176" t="inlineStr">
         <is>
-          <t>0.1829</t>
+          <t>0.1445</t>
         </is>
       </c>
       <c r="BA176" t="inlineStr">
         <is>
-          <t>12.21</t>
+          <t>10.39</t>
         </is>
       </c>
       <c r="BB176" t="inlineStr">
         <is>
-          <t>44.79</t>
+          <t>36.84</t>
         </is>
       </c>
       <c r="BC176" t="inlineStr">
         <is>
-          <t>89.28</t>
+          <t>87.82</t>
         </is>
       </c>
       <c r="BD176" t="inlineStr">
         <is>
-          <t>0.4742</t>
+          <t>0.4535</t>
         </is>
       </c>
       <c r="BE176" t="inlineStr">
         <is>
-          <t>0.2197</t>
+          <t>0.1945</t>
         </is>
       </c>
       <c r="BF176" t="inlineStr">
         <is>
-          <t>30.07</t>
+          <t>33.95</t>
         </is>
       </c>
       <c r="BG176" t="inlineStr"/>
       <c r="BH176" t="inlineStr"/>
       <c r="BI176" t="inlineStr">
         <is>
-          <t>loanDepot park</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ176" t="inlineStr"/>
@@ -48639,27 +48639,27 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>553869</t>
+          <t>666126</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Elias Diaz</t>
+          <t>Carlos Cortes</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>2026-08-22T23:05:00Z</t>
+          <t>2026-08-22T23:10:00Z</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -48669,17 +48669,17 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>Ryan Johnson</t>
+          <t>Hunter Brown</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>696270</t>
+          <t>686613</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
@@ -48702,26 +48702,26 @@
       </c>
       <c r="O177" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P177" t="n">
-        <v>26.7</v>
+        <v>30.7</v>
       </c>
       <c r="Q177" t="n">
-        <v>50.2</v>
+        <v>22.7</v>
       </c>
       <c r="R177" t="n">
         <v>27.6</v>
       </c>
       <c r="S177" t="n">
-        <v>59.8</v>
+        <v>71.7</v>
       </c>
       <c r="T177" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U177" t="n">
-        <v>5.7</v>
+        <v>24.9</v>
       </c>
       <c r="V177" t="inlineStr">
         <is>
@@ -48735,7 +48735,7 @@
       </c>
       <c r="X177" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y177" t="inlineStr">
@@ -48777,12 +48777,12 @@
       </c>
       <c r="AH177" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI177" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ177" t="inlineStr">
@@ -48792,119 +48792,119 @@
       </c>
       <c r="AK177" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/19, 0 HR</t>
+          <t>Last 7 games: 6/21, 0 HR</t>
         </is>
       </c>
       <c r="AL177" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.4% barrel, 12.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.2% barrel, 11.4 HR allowed</t>
         </is>
       </c>
       <c r="AM177" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN177" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>7.24</t>
         </is>
       </c>
       <c r="AO177" t="inlineStr">
         <is>
-          <t>38.49</t>
+          <t>39.59</t>
         </is>
       </c>
       <c r="AP177" t="inlineStr">
         <is>
-          <t>87.21</t>
+          <t>89.38</t>
         </is>
       </c>
       <c r="AQ177" t="inlineStr">
         <is>
-          <t>99.945</t>
+          <t>99.6817</t>
         </is>
       </c>
       <c r="AR177" t="inlineStr">
         <is>
-          <t>0.3501</t>
+          <t>0.408</t>
         </is>
       </c>
       <c r="AS177" t="inlineStr">
         <is>
-          <t>0.1306</t>
+          <t>0.1483</t>
         </is>
       </c>
       <c r="AT177" t="inlineStr">
         <is>
-          <t>0.2624</t>
+          <t>0.3189</t>
         </is>
       </c>
       <c r="AU177" t="inlineStr">
         <is>
-          <t>74.27</t>
+          <t>70.76</t>
         </is>
       </c>
       <c r="AV177" t="inlineStr">
         <is>
-          <t>43.44</t>
+          <t>14.41</t>
         </is>
       </c>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>37.93</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>27.59</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>0.1445</t>
+          <t>0.1717</t>
         </is>
       </c>
       <c r="BA177" t="inlineStr">
         <is>
-          <t>10.39</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="BB177" t="inlineStr">
         <is>
-          <t>36.84</t>
+          <t>35.63</t>
         </is>
       </c>
       <c r="BC177" t="inlineStr">
         <is>
-          <t>87.82</t>
+          <t>85.96</t>
         </is>
       </c>
       <c r="BD177" t="inlineStr">
         <is>
-          <t>0.4535</t>
+          <t>0.3397</t>
         </is>
       </c>
       <c r="BE177" t="inlineStr">
         <is>
-          <t>0.1945</t>
+          <t>0.1304</t>
         </is>
       </c>
       <c r="BF177" t="inlineStr">
         <is>
-          <t>33.95</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="BG177" t="inlineStr"/>
       <c r="BH177" t="inlineStr"/>
       <c r="BI177" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ177" t="inlineStr"/>

--- a/outputs/daily/hr_rankings_2026-08-22_full.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-22_full.xlsx
@@ -47331,47 +47331,47 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>694497</t>
+          <t>669224</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Evan Carter</t>
+          <t>Austin Wells</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>2026-08-22T23:05:00Z</t>
+          <t>2026-08-22T17:35:00Z</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>Ryan Johnson</t>
+          <t>Dylan Cease</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>696270</t>
+          <t>656302</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
@@ -47380,7 +47380,7 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>38.6</v>
+        <v>38.5</v>
       </c>
       <c r="M172" t="inlineStr">
         <is>
@@ -47394,62 +47394,58 @@
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P172" t="n">
-        <v>21.5</v>
+        <v>35.8</v>
       </c>
       <c r="Q172" t="n">
-        <v>50.2</v>
+        <v>20.3</v>
       </c>
       <c r="R172" t="n">
-        <v>27.6</v>
+        <v>48.2</v>
       </c>
       <c r="S172" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T172" t="n">
         <v>80</v>
       </c>
       <c r="U172" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="V172" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W172" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X172" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y172" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z172" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W172" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X172" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y172" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z172" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA172" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB172" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB172" t="inlineStr"/>
       <c r="AC172" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -47464,139 +47460,147 @@
       </c>
       <c r="AG172" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AH172" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI172" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AJ172" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AH172" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI172" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ172" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK172" t="inlineStr">
         <is>
-          <t>Recent form unavailable</t>
+          <t>Last 7 games: 2/18, 0 HR</t>
         </is>
       </c>
       <c r="AL172" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.4% barrel, 12.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM172" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN172" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>7.61</t>
         </is>
       </c>
       <c r="AO172" t="inlineStr">
         <is>
-          <t>35.65</t>
+          <t>43.24</t>
         </is>
       </c>
       <c r="AP172" t="inlineStr">
         <is>
-          <t>87.54</t>
+          <t>89.48</t>
         </is>
       </c>
       <c r="AQ172" t="inlineStr">
         <is>
-          <t>98.6524</t>
+          <t>100.5968</t>
         </is>
       </c>
       <c r="AR172" t="inlineStr">
         <is>
-          <t>0.3348</t>
+          <t>0.3683</t>
         </is>
       </c>
       <c r="AS172" t="inlineStr">
         <is>
-          <t>0.1218</t>
+          <t>0.1591</t>
         </is>
       </c>
       <c r="AT172" t="inlineStr">
         <is>
-          <t>0.2912</t>
+          <t>0.2899</t>
         </is>
       </c>
       <c r="AU172" t="inlineStr">
         <is>
-          <t>70.95</t>
+          <t>72.98</t>
         </is>
       </c>
       <c r="AV172" t="inlineStr">
         <is>
-          <t>17.51</t>
+          <t>27.39</t>
         </is>
       </c>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>38.56</t>
+          <t>46.38</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>28.05</t>
+          <t>32.93</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="AZ172" t="inlineStr">
         <is>
-          <t>0.1331</t>
+          <t>0.147</t>
         </is>
       </c>
       <c r="BA172" t="inlineStr">
         <is>
-          <t>10.39</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="BB172" t="inlineStr">
         <is>
-          <t>36.84</t>
+          <t>33.93</t>
         </is>
       </c>
       <c r="BC172" t="inlineStr">
         <is>
-          <t>87.82</t>
+          <t>86.73</t>
         </is>
       </c>
       <c r="BD172" t="inlineStr">
         <is>
-          <t>0.4535</t>
+          <t>0.3009</t>
         </is>
       </c>
       <c r="BE172" t="inlineStr">
         <is>
-          <t>0.1945</t>
+          <t>0.1086</t>
         </is>
       </c>
       <c r="BF172" t="inlineStr">
         <is>
-          <t>33.95</t>
-        </is>
-      </c>
-      <c r="BG172" t="inlineStr"/>
-      <c r="BH172" t="inlineStr"/>
+          <t>25.47</t>
+        </is>
+      </c>
+      <c r="BG172" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH172" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
       <c r="BI172" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ172" t="inlineStr"/>
@@ -47607,47 +47611,47 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>669224</t>
+          <t>701675</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Austin Wells</t>
+          <t>Nathan Church</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2026-08-22T17:35:00Z</t>
+          <t>2026-08-22T22:05:00Z</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>Dylan Cease</t>
+          <t>Andrew Painter</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>656302</t>
+          <t>691725</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
@@ -47656,7 +47660,7 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>38.5</v>
+        <v>38.4</v>
       </c>
       <c r="M173" t="inlineStr">
         <is>
@@ -47670,61 +47674,65 @@
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P173" t="n">
-        <v>35.8</v>
+        <v>16</v>
       </c>
       <c r="Q173" t="n">
-        <v>20.3</v>
+        <v>41.4</v>
       </c>
       <c r="R173" t="n">
-        <v>48.2</v>
+        <v>34.3</v>
       </c>
       <c r="S173" t="n">
-        <v>52.4</v>
+        <v>71.7</v>
       </c>
       <c r="T173" t="n">
         <v>80</v>
       </c>
       <c r="U173" t="n">
-        <v>0</v>
+        <v>16.6</v>
       </c>
       <c r="V173" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W173" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X173" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y173" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W173" t="inlineStr">
+      <c r="Z173" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X173" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y173" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z173" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB173" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB173" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC173" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD173" t="inlineStr"/>
@@ -47741,12 +47749,12 @@
       </c>
       <c r="AH173" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI173" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AJ173" t="inlineStr">
@@ -47756,12 +47764,12 @@
       </c>
       <c r="AK173" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/18, 0 HR</t>
+          <t>Last 7 games: 3/13, 0 HR</t>
         </is>
       </c>
       <c r="AL173" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.0% barrel, 12.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.4% barrel, 17.0 HR allowed</t>
         </is>
       </c>
       <c r="AM173" t="inlineStr">
@@ -47771,112 +47779,104 @@
       </c>
       <c r="AN173" t="inlineStr">
         <is>
-          <t>7.61</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="AO173" t="inlineStr">
         <is>
-          <t>43.24</t>
+          <t>33.59</t>
         </is>
       </c>
       <c r="AP173" t="inlineStr">
         <is>
-          <t>89.48</t>
+          <t>86.9</t>
         </is>
       </c>
       <c r="AQ173" t="inlineStr">
         <is>
-          <t>100.5968</t>
+          <t>97.7451</t>
         </is>
       </c>
       <c r="AR173" t="inlineStr">
         <is>
-          <t>0.3683</t>
+          <t>0.3357</t>
         </is>
       </c>
       <c r="AS173" t="inlineStr">
         <is>
-          <t>0.1591</t>
+          <t>0.1088</t>
         </is>
       </c>
       <c r="AT173" t="inlineStr">
         <is>
-          <t>0.2899</t>
+          <t>0.2736</t>
         </is>
       </c>
       <c r="AU173" t="inlineStr">
         <is>
-          <t>72.98</t>
+          <t>69.6</t>
         </is>
       </c>
       <c r="AV173" t="inlineStr">
         <is>
-          <t>27.39</t>
+          <t>8.62</t>
         </is>
       </c>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>46.38</t>
+          <t>34.78</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>32.93</t>
+          <t>21.46</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>0.1053</t>
         </is>
       </c>
       <c r="BA173" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="BB173" t="inlineStr">
         <is>
-          <t>33.93</t>
+          <t>35.5</t>
         </is>
       </c>
       <c r="BC173" t="inlineStr">
         <is>
-          <t>86.73</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="BD173" t="inlineStr">
         <is>
-          <t>0.3009</t>
+          <t>0.445</t>
         </is>
       </c>
       <c r="BE173" t="inlineStr">
         <is>
-          <t>0.1086</t>
+          <t>0.178</t>
         </is>
       </c>
       <c r="BF173" t="inlineStr">
         <is>
-          <t>25.47</t>
-        </is>
-      </c>
-      <c r="BG173" t="inlineStr">
-        <is>
-          <t>In From CF</t>
-        </is>
-      </c>
-      <c r="BH173" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
+          <t>27.1</t>
+        </is>
+      </c>
+      <c r="BG173" t="inlineStr"/>
+      <c r="BH173" t="inlineStr"/>
       <c r="BI173" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BJ173" t="inlineStr"/>
@@ -47887,27 +47887,27 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>701675</t>
+          <t>670623</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Nathan Church</t>
+          <t>Isaac Paredes</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2026-08-22T22:05:00Z</t>
+          <t>2026-08-22T23:10:00Z</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -47917,22 +47917,22 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>Andrew Painter</t>
+          <t>Jacob Lopez</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>691725</t>
+          <t>682052</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L174" t="n">
@@ -47950,26 +47950,26 @@
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P174" t="n">
-        <v>16</v>
+        <v>18.1</v>
       </c>
       <c r="Q174" t="n">
-        <v>41.4</v>
+        <v>21.9</v>
       </c>
       <c r="R174" t="n">
-        <v>34.3</v>
+        <v>27.6</v>
       </c>
       <c r="S174" t="n">
-        <v>71.7</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T174" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U174" t="n">
-        <v>16.6</v>
+        <v>62.8</v>
       </c>
       <c r="V174" t="inlineStr">
         <is>
@@ -47983,7 +47983,7 @@
       </c>
       <c r="X174" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y174" t="inlineStr">
@@ -48008,7 +48008,7 @@
       </c>
       <c r="AC174" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD174" t="inlineStr"/>
@@ -48025,134 +48025,134 @@
       </c>
       <c r="AH174" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI174" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/13, 0 HR</t>
+          <t>Contact streak: 10/24 over last 7 games</t>
         </is>
       </c>
       <c r="AL174" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.4% barrel, 17.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.7% barrel, 15.0 HR allowed</t>
         </is>
       </c>
       <c r="AM174" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN174" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="AO174" t="inlineStr">
         <is>
-          <t>33.59</t>
+          <t>29.89</t>
         </is>
       </c>
       <c r="AP174" t="inlineStr">
         <is>
-          <t>86.9</t>
+          <t>86.42</t>
         </is>
       </c>
       <c r="AQ174" t="inlineStr">
         <is>
-          <t>97.7451</t>
+          <t>96.9173</t>
         </is>
       </c>
       <c r="AR174" t="inlineStr">
         <is>
-          <t>0.3357</t>
+          <t>0.3779</t>
         </is>
       </c>
       <c r="AS174" t="inlineStr">
         <is>
-          <t>0.1088</t>
+          <t>0.132</t>
         </is>
       </c>
       <c r="AT174" t="inlineStr">
         <is>
-          <t>0.2736</t>
+          <t>0.3235</t>
         </is>
       </c>
       <c r="AU174" t="inlineStr">
         <is>
-          <t>69.6</t>
+          <t>67.74</t>
         </is>
       </c>
       <c r="AV174" t="inlineStr">
         <is>
-          <t>8.62</t>
+          <t>7.57</t>
         </is>
       </c>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>34.78</t>
+          <t>52.14</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>21.46</t>
+          <t>30.59</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="AZ174" t="inlineStr">
         <is>
-          <t>0.1053</t>
+          <t>0.176</t>
         </is>
       </c>
       <c r="BA174" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>5.69</t>
         </is>
       </c>
       <c r="BB174" t="inlineStr">
         <is>
-          <t>35.5</t>
+          <t>30.19</t>
         </is>
       </c>
       <c r="BC174" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>85.29</t>
         </is>
       </c>
       <c r="BD174" t="inlineStr">
         <is>
-          <t>0.445</t>
+          <t>0.3424</t>
         </is>
       </c>
       <c r="BE174" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>0.1338</t>
         </is>
       </c>
       <c r="BF174" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>32.48</t>
         </is>
       </c>
       <c r="BG174" t="inlineStr"/>
       <c r="BH174" t="inlineStr"/>
       <c r="BI174" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ174" t="inlineStr"/>
@@ -48163,27 +48163,27 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>670623</t>
+          <t>660688</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Isaac Paredes</t>
+          <t>Keibert Ruiz</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>2026-08-22T23:10:00Z</t>
+          <t>2026-08-22T20:10:00Z</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -48193,26 +48193,26 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>Jacob Lopez</t>
+          <t>Eury Pérez</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>682052</t>
+          <t>691587</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L175" t="n">
-        <v>38.4</v>
+        <v>38.3</v>
       </c>
       <c r="M175" t="inlineStr">
         <is>
@@ -48226,26 +48226,26 @@
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P175" t="n">
-        <v>18.1</v>
+        <v>16.4</v>
       </c>
       <c r="Q175" t="n">
-        <v>21.9</v>
+        <v>41.7</v>
       </c>
       <c r="R175" t="n">
-        <v>27.6</v>
+        <v>21.5</v>
       </c>
       <c r="S175" t="n">
-        <v>92.09999999999999</v>
+        <v>71.7</v>
       </c>
       <c r="T175" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U175" t="n">
-        <v>62.8</v>
+        <v>56.6</v>
       </c>
       <c r="V175" t="inlineStr">
         <is>
@@ -48259,7 +48259,7 @@
       </c>
       <c r="X175" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y175" t="inlineStr">
@@ -48301,7 +48301,7 @@
       </c>
       <c r="AH175" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI175" t="inlineStr">
@@ -48316,12 +48316,12 @@
       </c>
       <c r="AK175" t="inlineStr">
         <is>
-          <t>Contact streak: 10/24 over last 7 games</t>
+          <t>Contact streak: 9/24 over last 7 games</t>
         </is>
       </c>
       <c r="AL175" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.7% barrel, 15.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.1% barrel, 12.7 HR allowed</t>
         </is>
       </c>
       <c r="AM175" t="inlineStr">
@@ -48331,104 +48331,104 @@
       </c>
       <c r="AN175" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>4.16</t>
         </is>
       </c>
       <c r="AO175" t="inlineStr">
         <is>
-          <t>29.89</t>
+          <t>35.59</t>
         </is>
       </c>
       <c r="AP175" t="inlineStr">
         <is>
-          <t>86.42</t>
+          <t>87.67</t>
         </is>
       </c>
       <c r="AQ175" t="inlineStr">
         <is>
-          <t>96.9173</t>
+          <t>97.6467</t>
         </is>
       </c>
       <c r="AR175" t="inlineStr">
         <is>
-          <t>0.3779</t>
+          <t>0.3587</t>
         </is>
       </c>
       <c r="AS175" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>0.108</t>
         </is>
       </c>
       <c r="AT175" t="inlineStr">
         <is>
-          <t>0.3235</t>
+          <t>0.2835</t>
         </is>
       </c>
       <c r="AU175" t="inlineStr">
         <is>
-          <t>67.74</t>
+          <t>67.22</t>
         </is>
       </c>
       <c r="AV175" t="inlineStr">
         <is>
-          <t>7.57</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>52.14</t>
+          <t>53.98</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>30.59</t>
+          <t>25.51</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="AZ175" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>0.1375</t>
         </is>
       </c>
       <c r="BA175" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>9.14</t>
         </is>
       </c>
       <c r="BB175" t="inlineStr">
         <is>
-          <t>30.19</t>
+          <t>41.81</t>
         </is>
       </c>
       <c r="BC175" t="inlineStr">
         <is>
-          <t>85.29</t>
+          <t>88.96</t>
         </is>
       </c>
       <c r="BD175" t="inlineStr">
         <is>
-          <t>0.3424</t>
+          <t>0.3618</t>
         </is>
       </c>
       <c r="BE175" t="inlineStr">
         <is>
-          <t>0.1338</t>
+          <t>0.1553</t>
         </is>
       </c>
       <c r="BF175" t="inlineStr">
         <is>
-          <t>32.48</t>
+          <t>30.45</t>
         </is>
       </c>
       <c r="BG175" t="inlineStr"/>
       <c r="BH175" t="inlineStr"/>
       <c r="BI175" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>loanDepot park</t>
         </is>
       </c>
       <c r="BJ175" t="inlineStr"/>
@@ -48439,24 +48439,24 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>660688</t>
+          <t>665923</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Keibert Ruiz</t>
+          <t>Esteury Ruiz</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
           <t>WSH</t>
         </is>
       </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>MIA</t>
-        </is>
-      </c>
       <c r="F176" t="inlineStr">
         <is>
           <t>2026-08-22T20:10:00Z</t>
@@ -48469,17 +48469,17 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>Eury Pérez</t>
+          <t>Jake Irvin</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>691587</t>
+          <t>663623</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
@@ -48502,26 +48502,26 @@
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P176" t="n">
-        <v>16.4</v>
+        <v>18.5</v>
       </c>
       <c r="Q176" t="n">
-        <v>41.7</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="R176" t="n">
         <v>21.5</v>
       </c>
       <c r="S176" t="n">
-        <v>71.7</v>
+        <v>59.8</v>
       </c>
       <c r="T176" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U176" t="n">
-        <v>56.6</v>
+        <v>13.6</v>
       </c>
       <c r="V176" t="inlineStr">
         <is>
@@ -48535,7 +48535,7 @@
       </c>
       <c r="X176" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y176" t="inlineStr">
@@ -48577,27 +48577,27 @@
       </c>
       <c r="AH176" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI176" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK176" t="inlineStr">
         <is>
-          <t>Contact streak: 9/24 over last 7 games</t>
+          <t>Last 7 games: 4/19, 0 HR</t>
         </is>
       </c>
       <c r="AL176" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.1% barrel, 12.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 12.2% barrel, 19.8 HR allowed</t>
         </is>
       </c>
       <c r="AM176" t="inlineStr">
@@ -48607,97 +48607,97 @@
       </c>
       <c r="AN176" t="inlineStr">
         <is>
-          <t>4.16</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="AO176" t="inlineStr">
         <is>
-          <t>35.59</t>
+          <t>27.16</t>
         </is>
       </c>
       <c r="AP176" t="inlineStr">
         <is>
-          <t>87.67</t>
+          <t>84.37</t>
         </is>
       </c>
       <c r="AQ176" t="inlineStr">
         <is>
-          <t>97.6467</t>
+          <t>96.2826</t>
         </is>
       </c>
       <c r="AR176" t="inlineStr">
         <is>
-          <t>0.3587</t>
+          <t>0.3335</t>
         </is>
       </c>
       <c r="AS176" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>0.1435</t>
         </is>
       </c>
       <c r="AT176" t="inlineStr">
         <is>
-          <t>0.2835</t>
+          <t>0.2882</t>
         </is>
       </c>
       <c r="AU176" t="inlineStr">
         <is>
-          <t>67.22</t>
+          <t>71.31</t>
         </is>
       </c>
       <c r="AV176" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>17.82</t>
         </is>
       </c>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>53.98</t>
+          <t>45.78</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>25.51</t>
+          <t>24.99</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AZ176" t="inlineStr">
         <is>
-          <t>0.1375</t>
+          <t>0.1829</t>
         </is>
       </c>
       <c r="BA176" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>12.21</t>
         </is>
       </c>
       <c r="BB176" t="inlineStr">
         <is>
-          <t>41.81</t>
+          <t>44.79</t>
         </is>
       </c>
       <c r="BC176" t="inlineStr">
         <is>
-          <t>88.96</t>
+          <t>89.28</t>
         </is>
       </c>
       <c r="BD176" t="inlineStr">
         <is>
-          <t>0.3618</t>
+          <t>0.4742</t>
         </is>
       </c>
       <c r="BE176" t="inlineStr">
         <is>
-          <t>0.1553</t>
+          <t>0.2197</t>
         </is>
       </c>
       <c r="BF176" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>30.07</t>
         </is>
       </c>
       <c r="BG176" t="inlineStr"/>
@@ -48715,27 +48715,27 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>665923</t>
+          <t>553869</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Esteury Ruiz</t>
+          <t>Elias Diaz</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>2026-08-22T20:10:00Z</t>
+          <t>2026-08-22T23:05:00Z</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -48750,12 +48750,12 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>Jake Irvin</t>
+          <t>Ryan Johnson</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>663623</t>
+          <t>696270</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
@@ -48764,7 +48764,7 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>38.3</v>
+        <v>38.2</v>
       </c>
       <c r="M177" t="inlineStr">
         <is>
@@ -48782,13 +48782,13 @@
         </is>
       </c>
       <c r="P177" t="n">
-        <v>18.5</v>
+        <v>26.7</v>
       </c>
       <c r="Q177" t="n">
-        <v>64.40000000000001</v>
+        <v>50.2</v>
       </c>
       <c r="R177" t="n">
-        <v>21.5</v>
+        <v>27.6</v>
       </c>
       <c r="S177" t="n">
         <v>59.8</v>
@@ -48797,7 +48797,7 @@
         <v>50</v>
       </c>
       <c r="U177" t="n">
-        <v>13.6</v>
+        <v>5.7</v>
       </c>
       <c r="V177" t="inlineStr">
         <is>
@@ -48853,7 +48853,7 @@
       </c>
       <c r="AH177" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI177" t="inlineStr">
@@ -48868,12 +48868,12 @@
       </c>
       <c r="AK177" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/19, 0 HR</t>
+          <t>Last 7 games: 3/19, 0 HR</t>
         </is>
       </c>
       <c r="AL177" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 12.2% barrel, 19.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.4% barrel, 12.4 HR allowed</t>
         </is>
       </c>
       <c r="AM177" t="inlineStr">
@@ -48883,104 +48883,104 @@
       </c>
       <c r="AN177" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>6.76</t>
         </is>
       </c>
       <c r="AO177" t="inlineStr">
         <is>
-          <t>27.16</t>
+          <t>38.49</t>
         </is>
       </c>
       <c r="AP177" t="inlineStr">
         <is>
-          <t>84.37</t>
+          <t>87.21</t>
         </is>
       </c>
       <c r="AQ177" t="inlineStr">
         <is>
-          <t>96.2826</t>
+          <t>99.945</t>
         </is>
       </c>
       <c r="AR177" t="inlineStr">
         <is>
-          <t>0.3335</t>
+          <t>0.3501</t>
         </is>
       </c>
       <c r="AS177" t="inlineStr">
         <is>
-          <t>0.1435</t>
+          <t>0.1306</t>
         </is>
       </c>
       <c r="AT177" t="inlineStr">
         <is>
-          <t>0.2882</t>
+          <t>0.2624</t>
         </is>
       </c>
       <c r="AU177" t="inlineStr">
         <is>
-          <t>71.31</t>
+          <t>74.27</t>
         </is>
       </c>
       <c r="AV177" t="inlineStr">
         <is>
-          <t>17.82</t>
+          <t>43.44</t>
         </is>
       </c>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>45.78</t>
+          <t>37.93</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>27.59</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>0.1829</t>
+          <t>0.1445</t>
         </is>
       </c>
       <c r="BA177" t="inlineStr">
         <is>
-          <t>12.21</t>
+          <t>10.39</t>
         </is>
       </c>
       <c r="BB177" t="inlineStr">
         <is>
-          <t>44.79</t>
+          <t>36.84</t>
         </is>
       </c>
       <c r="BC177" t="inlineStr">
         <is>
-          <t>89.28</t>
+          <t>87.82</t>
         </is>
       </c>
       <c r="BD177" t="inlineStr">
         <is>
-          <t>0.4742</t>
+          <t>0.4535</t>
         </is>
       </c>
       <c r="BE177" t="inlineStr">
         <is>
-          <t>0.2197</t>
+          <t>0.1945</t>
         </is>
       </c>
       <c r="BF177" t="inlineStr">
         <is>
-          <t>30.07</t>
+          <t>33.95</t>
         </is>
       </c>
       <c r="BG177" t="inlineStr"/>
       <c r="BH177" t="inlineStr"/>
       <c r="BI177" t="inlineStr">
         <is>
-          <t>loanDepot park</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ177" t="inlineStr"/>
@@ -48991,27 +48991,27 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>553869</t>
+          <t>666126</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Elias Diaz</t>
+          <t>Carlos Cortes</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>2026-08-22T23:05:00Z</t>
+          <t>2026-08-22T23:10:00Z</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -49021,17 +49021,17 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>Ryan Johnson</t>
+          <t>Hunter Brown</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>696270</t>
+          <t>686613</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
@@ -49054,26 +49054,26 @@
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P178" t="n">
-        <v>26.7</v>
+        <v>30.7</v>
       </c>
       <c r="Q178" t="n">
-        <v>50.2</v>
+        <v>22.7</v>
       </c>
       <c r="R178" t="n">
         <v>27.6</v>
       </c>
       <c r="S178" t="n">
-        <v>59.8</v>
+        <v>71.7</v>
       </c>
       <c r="T178" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U178" t="n">
-        <v>5.7</v>
+        <v>24.9</v>
       </c>
       <c r="V178" t="inlineStr">
         <is>
@@ -49087,7 +49087,7 @@
       </c>
       <c r="X178" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y178" t="inlineStr">
@@ -49129,12 +49129,12 @@
       </c>
       <c r="AH178" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI178" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ178" t="inlineStr">
@@ -49144,119 +49144,119 @@
       </c>
       <c r="AK178" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/19, 0 HR</t>
+          <t>Last 7 games: 6/21, 0 HR</t>
         </is>
       </c>
       <c r="AL178" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.4% barrel, 12.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.2% barrel, 11.4 HR allowed</t>
         </is>
       </c>
       <c r="AM178" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN178" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>7.24</t>
         </is>
       </c>
       <c r="AO178" t="inlineStr">
         <is>
-          <t>38.49</t>
+          <t>39.59</t>
         </is>
       </c>
       <c r="AP178" t="inlineStr">
         <is>
-          <t>87.21</t>
+          <t>89.38</t>
         </is>
       </c>
       <c r="AQ178" t="inlineStr">
         <is>
-          <t>99.945</t>
+          <t>99.6817</t>
         </is>
       </c>
       <c r="AR178" t="inlineStr">
         <is>
-          <t>0.3501</t>
+          <t>0.408</t>
         </is>
       </c>
       <c r="AS178" t="inlineStr">
         <is>
-          <t>0.1306</t>
+          <t>0.1483</t>
         </is>
       </c>
       <c r="AT178" t="inlineStr">
         <is>
-          <t>0.2624</t>
+          <t>0.3189</t>
         </is>
       </c>
       <c r="AU178" t="inlineStr">
         <is>
-          <t>74.27</t>
+          <t>70.76</t>
         </is>
       </c>
       <c r="AV178" t="inlineStr">
         <is>
-          <t>43.44</t>
+          <t>14.41</t>
         </is>
       </c>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>37.93</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>27.59</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="AZ178" t="inlineStr">
         <is>
-          <t>0.1445</t>
+          <t>0.1717</t>
         </is>
       </c>
       <c r="BA178" t="inlineStr">
         <is>
-          <t>10.39</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="BB178" t="inlineStr">
         <is>
-          <t>36.84</t>
+          <t>35.63</t>
         </is>
       </c>
       <c r="BC178" t="inlineStr">
         <is>
-          <t>87.82</t>
+          <t>85.96</t>
         </is>
       </c>
       <c r="BD178" t="inlineStr">
         <is>
-          <t>0.4535</t>
+          <t>0.3397</t>
         </is>
       </c>
       <c r="BE178" t="inlineStr">
         <is>
-          <t>0.1945</t>
+          <t>0.1304</t>
         </is>
       </c>
       <c r="BF178" t="inlineStr">
         <is>
-          <t>33.95</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="BG178" t="inlineStr"/>
       <c r="BH178" t="inlineStr"/>
       <c r="BI178" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ178" t="inlineStr"/>
@@ -49267,27 +49267,27 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>666126</t>
+          <t>669134</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Carlos Cortes</t>
+          <t>Luis Campusano</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>2026-08-22T23:10:00Z</t>
+          <t>2026-08-23T00:40:00Z</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -49302,12 +49302,12 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>Hunter Brown</t>
+          <t>Dean Kremer</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>686613</t>
+          <t>665152</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
@@ -49330,26 +49330,26 @@
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P179" t="n">
-        <v>30.7</v>
+        <v>24.8</v>
       </c>
       <c r="Q179" t="n">
-        <v>22.7</v>
+        <v>41.7</v>
       </c>
       <c r="R179" t="n">
-        <v>27.6</v>
+        <v>22.6</v>
       </c>
       <c r="S179" t="n">
         <v>71.7</v>
       </c>
       <c r="T179" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U179" t="n">
-        <v>24.9</v>
+        <v>41.2</v>
       </c>
       <c r="V179" t="inlineStr">
         <is>
@@ -49410,129 +49410,129 @@
       </c>
       <c r="AI179" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 0 HR</t>
+          <t>Last 7 games: 6/22, 1 HR</t>
         </is>
       </c>
       <c r="AL179" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.2% barrel, 11.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.8% barrel, 15.7 HR allowed</t>
         </is>
       </c>
       <c r="AM179" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN179" t="inlineStr">
         <is>
-          <t>7.24</t>
+          <t>7.07</t>
         </is>
       </c>
       <c r="AO179" t="inlineStr">
         <is>
-          <t>39.59</t>
+          <t>39.8</t>
         </is>
       </c>
       <c r="AP179" t="inlineStr">
         <is>
-          <t>89.38</t>
+          <t>88.36</t>
         </is>
       </c>
       <c r="AQ179" t="inlineStr">
         <is>
-          <t>99.6817</t>
+          <t>99.034</t>
         </is>
       </c>
       <c r="AR179" t="inlineStr">
         <is>
-          <t>0.408</t>
+          <t>0.3179</t>
         </is>
       </c>
       <c r="AS179" t="inlineStr">
         <is>
-          <t>0.1483</t>
+          <t>0.1162</t>
         </is>
       </c>
       <c r="AT179" t="inlineStr">
         <is>
-          <t>0.3189</t>
+          <t>0.3081</t>
         </is>
       </c>
       <c r="AU179" t="inlineStr">
         <is>
-          <t>70.76</t>
+          <t>72.68</t>
         </is>
       </c>
       <c r="AV179" t="inlineStr">
         <is>
-          <t>14.41</t>
+          <t>27.26</t>
         </is>
       </c>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>30.48</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AZ179" t="inlineStr">
         <is>
-          <t>0.1717</t>
+          <t>0.1365</t>
         </is>
       </c>
       <c r="BA179" t="inlineStr">
         <is>
-          <t>6.18</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="BB179" t="inlineStr">
         <is>
-          <t>35.63</t>
+          <t>34.4</t>
         </is>
       </c>
       <c r="BC179" t="inlineStr">
         <is>
-          <t>85.96</t>
+          <t>87.33</t>
         </is>
       </c>
       <c r="BD179" t="inlineStr">
         <is>
-          <t>0.3397</t>
+          <t>0.4319</t>
         </is>
       </c>
       <c r="BE179" t="inlineStr">
         <is>
-          <t>0.1304</t>
+          <t>0.1953</t>
         </is>
       </c>
       <c r="BF179" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BG179" t="inlineStr"/>
       <c r="BH179" t="inlineStr"/>
       <c r="BI179" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ179" t="inlineStr"/>
@@ -49543,27 +49543,27 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>669134</t>
+          <t>691458</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Luis Campusano</t>
+          <t>Blaze Jordan</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>2026-08-23T00:40:00Z</t>
+          <t>2026-08-22T22:05:00Z</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -49573,17 +49573,17 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>Dean Kremer</t>
+          <t>Andrew Painter</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>665152</t>
+          <t>691725</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
@@ -49592,7 +49592,7 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>38.2</v>
+        <v>38</v>
       </c>
       <c r="M180" t="inlineStr">
         <is>
@@ -49610,22 +49610,22 @@
         </is>
       </c>
       <c r="P180" t="n">
-        <v>24.8</v>
+        <v>33.4</v>
       </c>
       <c r="Q180" t="n">
-        <v>41.7</v>
+        <v>41.4</v>
       </c>
       <c r="R180" t="n">
-        <v>22.6</v>
+        <v>34.3</v>
       </c>
       <c r="S180" t="n">
-        <v>71.7</v>
+        <v>47.9</v>
       </c>
       <c r="T180" t="n">
         <v>50</v>
       </c>
       <c r="U180" t="n">
-        <v>41.2</v>
+        <v>14.1</v>
       </c>
       <c r="V180" t="inlineStr">
         <is>
@@ -49639,7 +49639,7 @@
       </c>
       <c r="X180" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y180" t="inlineStr">
@@ -49664,7 +49664,7 @@
       </c>
       <c r="AC180" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026</t>
         </is>
       </c>
       <c r="AD180" t="inlineStr"/>
@@ -49686,129 +49686,129 @@
       </c>
       <c r="AI180" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/22, 1 HR</t>
+          <t>Last 7 games: 6/28, 0 HR</t>
         </is>
       </c>
       <c r="AL180" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.8% barrel, 15.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.4% barrel, 17.0 HR allowed</t>
         </is>
       </c>
       <c r="AM180" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN180" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="AO180" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="AP180" t="inlineStr">
         <is>
-          <t>88.36</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AQ180" t="inlineStr">
         <is>
-          <t>99.034</t>
+          <t>99.8323</t>
         </is>
       </c>
       <c r="AR180" t="inlineStr">
         <is>
-          <t>0.3179</t>
+          <t>0.407</t>
         </is>
       </c>
       <c r="AS180" t="inlineStr">
         <is>
-          <t>0.1162</t>
+          <t>0.146</t>
         </is>
       </c>
       <c r="AT180" t="inlineStr">
         <is>
-          <t>0.3081</t>
+          <t>0.308</t>
         </is>
       </c>
       <c r="AU180" t="inlineStr">
         <is>
-          <t>72.68</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AV180" t="inlineStr">
         <is>
-          <t>27.26</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>0.1365</t>
+          <t>0.121</t>
         </is>
       </c>
       <c r="BA180" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="BB180" t="inlineStr">
         <is>
-          <t>34.4</t>
+          <t>35.5</t>
         </is>
       </c>
       <c r="BC180" t="inlineStr">
         <is>
-          <t>87.33</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="BD180" t="inlineStr">
         <is>
-          <t>0.4319</t>
+          <t>0.445</t>
         </is>
       </c>
       <c r="BE180" t="inlineStr">
         <is>
-          <t>0.1953</t>
+          <t>0.178</t>
         </is>
       </c>
       <c r="BF180" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="BG180" t="inlineStr"/>
       <c r="BH180" t="inlineStr"/>
       <c r="BI180" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BJ180" t="inlineStr"/>
@@ -49819,27 +49819,27 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>691458</t>
+          <t>701358</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Blaze Jordan</t>
+          <t>Cam Smith</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>2026-08-22T22:05:00Z</t>
+          <t>2026-08-22T23:10:00Z</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -49854,17 +49854,17 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>Andrew Painter</t>
+          <t>Jacob Lopez</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>691725</t>
+          <t>682052</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L181" t="n">
@@ -49882,26 +49882,26 @@
       </c>
       <c r="O181" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P181" t="n">
-        <v>33.4</v>
+        <v>42.2</v>
       </c>
       <c r="Q181" t="n">
-        <v>41.4</v>
+        <v>21.9</v>
       </c>
       <c r="R181" t="n">
-        <v>34.3</v>
+        <v>27.6</v>
       </c>
       <c r="S181" t="n">
         <v>47.9</v>
       </c>
       <c r="T181" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U181" t="n">
-        <v>14.1</v>
+        <v>18.3</v>
       </c>
       <c r="V181" t="inlineStr">
         <is>
@@ -49940,7 +49940,7 @@
       </c>
       <c r="AC181" t="inlineStr">
         <is>
-          <t>H:2026 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD181" t="inlineStr"/>
@@ -49957,134 +49957,134 @@
       </c>
       <c r="AH181" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI181" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/28, 0 HR</t>
+          <t>Last 7 games: 2/20, 1 HR</t>
         </is>
       </c>
       <c r="AL181" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.4% barrel, 17.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.7% barrel, 15.0 HR allowed</t>
         </is>
       </c>
       <c r="AM181" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN181" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="AO181" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>43.46</t>
         </is>
       </c>
       <c r="AP181" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>88.88</t>
         </is>
       </c>
       <c r="AQ181" t="inlineStr">
         <is>
-          <t>99.8323</t>
+          <t>101.626</t>
         </is>
       </c>
       <c r="AR181" t="inlineStr">
         <is>
-          <t>0.407</t>
+          <t>0.4173</t>
         </is>
       </c>
       <c r="AS181" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>0.176</t>
         </is>
       </c>
       <c r="AT181" t="inlineStr">
         <is>
-          <t>0.308</t>
+          <t>0.3194</t>
         </is>
       </c>
       <c r="AU181" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>76.74</t>
         </is>
       </c>
       <c r="AV181" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>67.97</t>
         </is>
       </c>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>37.98</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>25.21</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>14.6</t>
         </is>
       </c>
       <c r="AZ181" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>0.1591</t>
         </is>
       </c>
       <c r="BA181" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>5.69</t>
         </is>
       </c>
       <c r="BB181" t="inlineStr">
         <is>
-          <t>35.5</t>
+          <t>30.19</t>
         </is>
       </c>
       <c r="BC181" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>85.29</t>
         </is>
       </c>
       <c r="BD181" t="inlineStr">
         <is>
-          <t>0.445</t>
+          <t>0.3424</t>
         </is>
       </c>
       <c r="BE181" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>0.1338</t>
         </is>
       </c>
       <c r="BF181" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>32.48</t>
         </is>
       </c>
       <c r="BG181" t="inlineStr"/>
       <c r="BH181" t="inlineStr"/>
       <c r="BI181" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ181" t="inlineStr"/>
@@ -50095,27 +50095,27 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>701358</t>
+          <t>693304</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Cam Smith</t>
+          <t>Nick Gonzales</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>2026-08-22T23:10:00Z</t>
+          <t>2026-08-22T23:15:00Z</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -50125,17 +50125,17 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>Jacob Lopez</t>
+          <t>Tarik Skubal</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>682052</t>
+          <t>669373</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
@@ -50158,26 +50158,26 @@
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P182" t="n">
-        <v>42.2</v>
+        <v>16</v>
       </c>
       <c r="Q182" t="n">
-        <v>21.9</v>
+        <v>28.8</v>
       </c>
       <c r="R182" t="n">
         <v>27.6</v>
       </c>
       <c r="S182" t="n">
-        <v>47.9</v>
+        <v>88.7</v>
       </c>
       <c r="T182" t="n">
         <v>78</v>
       </c>
       <c r="U182" t="n">
-        <v>18.3</v>
+        <v>43.4</v>
       </c>
       <c r="V182" t="inlineStr">
         <is>
@@ -50191,7 +50191,7 @@
       </c>
       <c r="X182" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y182" t="inlineStr">
@@ -50233,134 +50233,134 @@
       </c>
       <c r="AH182" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI182" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK182" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/20, 1 HR</t>
+          <t>Contact streak: 9/22 over last 7 games</t>
         </is>
       </c>
       <c r="AL182" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.7% barrel, 15.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.5% barrel, 13.8 HR allowed</t>
         </is>
       </c>
       <c r="AM182" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN182" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="AO182" t="inlineStr">
         <is>
-          <t>43.46</t>
+          <t>36.14</t>
         </is>
       </c>
       <c r="AP182" t="inlineStr">
         <is>
-          <t>88.88</t>
+          <t>87.05</t>
         </is>
       </c>
       <c r="AQ182" t="inlineStr">
         <is>
-          <t>101.626</t>
+          <t>98.2813</t>
         </is>
       </c>
       <c r="AR182" t="inlineStr">
         <is>
-          <t>0.4173</t>
+          <t>0.3813</t>
         </is>
       </c>
       <c r="AS182" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>0.1063</t>
         </is>
       </c>
       <c r="AT182" t="inlineStr">
         <is>
-          <t>0.3194</t>
+          <t>0.3141</t>
         </is>
       </c>
       <c r="AU182" t="inlineStr">
         <is>
-          <t>76.74</t>
+          <t>70.71</t>
         </is>
       </c>
       <c r="AV182" t="inlineStr">
         <is>
-          <t>67.97</t>
+          <t>12.66</t>
         </is>
       </c>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>37.98</t>
+          <t>37.64</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>25.21</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr">
         <is>
-          <t>14.6</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="AZ182" t="inlineStr">
         <is>
-          <t>0.1591</t>
+          <t>0.0957</t>
         </is>
       </c>
       <c r="BA182" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>7.54</t>
         </is>
       </c>
       <c r="BB182" t="inlineStr">
         <is>
-          <t>30.19</t>
+          <t>35.38</t>
         </is>
       </c>
       <c r="BC182" t="inlineStr">
         <is>
-          <t>85.29</t>
+          <t>86.94</t>
         </is>
       </c>
       <c r="BD182" t="inlineStr">
         <is>
-          <t>0.3424</t>
+          <t>0.3433</t>
         </is>
       </c>
       <c r="BE182" t="inlineStr">
         <is>
-          <t>0.1338</t>
+          <t>0.1233</t>
         </is>
       </c>
       <c r="BF182" t="inlineStr">
         <is>
-          <t>32.48</t>
+          <t>26.32</t>
         </is>
       </c>
       <c r="BG182" t="inlineStr"/>
       <c r="BH182" t="inlineStr"/>
       <c r="BI182" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ182" t="inlineStr"/>
@@ -50371,27 +50371,27 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>693304</t>
+          <t>592663</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Nick Gonzales</t>
+          <t>J.T. Realmuto</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>2026-08-22T23:15:00Z</t>
+          <t>2026-08-22T22:05:00Z</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -50401,26 +50401,14 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I183" t="inlineStr">
-        <is>
-          <t>Tarik Skubal</t>
-        </is>
-      </c>
-      <c r="J183" t="inlineStr">
-        <is>
-          <t>669373</t>
-        </is>
-      </c>
-      <c r="K183" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr"/>
+      <c r="J183" t="inlineStr"/>
+      <c r="K183" t="inlineStr"/>
       <c r="L183" t="n">
-        <v>38</v>
+        <v>37.7</v>
       </c>
       <c r="M183" t="inlineStr">
         <is>
@@ -50434,26 +50422,26 @@
       </c>
       <c r="O183" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P183" t="n">
-        <v>16</v>
+        <v>30.5</v>
       </c>
       <c r="Q183" t="n">
-        <v>28.8</v>
+        <v>41.2</v>
       </c>
       <c r="R183" t="n">
-        <v>27.6</v>
+        <v>34.3</v>
       </c>
       <c r="S183" t="n">
-        <v>88.7</v>
+        <v>47.9</v>
       </c>
       <c r="T183" t="n">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="U183" t="n">
-        <v>43.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="V183" t="inlineStr">
         <is>
@@ -50467,7 +50455,7 @@
       </c>
       <c r="X183" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y183" t="inlineStr">
@@ -50492,7 +50480,7 @@
       </c>
       <c r="AC183" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD183" t="inlineStr"/>
@@ -50509,7 +50497,7 @@
       </c>
       <c r="AH183" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI183" t="inlineStr">
@@ -50524,12 +50512,12 @@
       </c>
       <c r="AK183" t="inlineStr">
         <is>
-          <t>Contact streak: 9/22 over last 7 games</t>
+          <t>Last 7 games: 4/22, 0 HR</t>
         </is>
       </c>
       <c r="AL183" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.5% barrel, 13.8 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM183" t="inlineStr">
@@ -50539,104 +50527,80 @@
       </c>
       <c r="AN183" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>5.79</t>
         </is>
       </c>
       <c r="AO183" t="inlineStr">
         <is>
-          <t>36.14</t>
+          <t>41.86</t>
         </is>
       </c>
       <c r="AP183" t="inlineStr">
         <is>
-          <t>87.05</t>
+          <t>89.79</t>
         </is>
       </c>
       <c r="AQ183" t="inlineStr">
         <is>
-          <t>98.2813</t>
+          <t>100.1831</t>
         </is>
       </c>
       <c r="AR183" t="inlineStr">
         <is>
-          <t>0.3813</t>
+          <t>0.3935</t>
         </is>
       </c>
       <c r="AS183" t="inlineStr">
         <is>
-          <t>0.1063</t>
+          <t>0.137</t>
         </is>
       </c>
       <c r="AT183" t="inlineStr">
         <is>
-          <t>0.3141</t>
+          <t>0.3202</t>
         </is>
       </c>
       <c r="AU183" t="inlineStr">
         <is>
-          <t>70.71</t>
+          <t>72.84</t>
         </is>
       </c>
       <c r="AV183" t="inlineStr">
         <is>
-          <t>12.66</t>
+          <t>32.15</t>
         </is>
       </c>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>37.64</t>
+          <t>41.25</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="AZ183" t="inlineStr">
         <is>
-          <t>0.0957</t>
-        </is>
-      </c>
-      <c r="BA183" t="inlineStr">
-        <is>
-          <t>7.54</t>
-        </is>
-      </c>
-      <c r="BB183" t="inlineStr">
-        <is>
-          <t>35.38</t>
-        </is>
-      </c>
-      <c r="BC183" t="inlineStr">
-        <is>
-          <t>86.94</t>
-        </is>
-      </c>
-      <c r="BD183" t="inlineStr">
-        <is>
-          <t>0.3433</t>
-        </is>
-      </c>
-      <c r="BE183" t="inlineStr">
-        <is>
-          <t>0.1233</t>
-        </is>
-      </c>
-      <c r="BF183" t="inlineStr">
-        <is>
-          <t>26.32</t>
-        </is>
-      </c>
+          <t>0.1263</t>
+        </is>
+      </c>
+      <c r="BA183" t="inlineStr"/>
+      <c r="BB183" t="inlineStr"/>
+      <c r="BC183" t="inlineStr"/>
+      <c r="BD183" t="inlineStr"/>
+      <c r="BE183" t="inlineStr"/>
+      <c r="BF183" t="inlineStr"/>
       <c r="BG183" t="inlineStr"/>
       <c r="BH183" t="inlineStr"/>
       <c r="BI183" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BJ183" t="inlineStr"/>
@@ -50647,27 +50611,27 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>592663</t>
+          <t>676439</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>J.T. Realmuto</t>
+          <t>Hunter Feduccia</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>2026-08-22T22:05:00Z</t>
+          <t>2026-08-22T23:15:00Z</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -50677,12 +50641,24 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr"/>
-      <c r="J184" t="inlineStr"/>
-      <c r="K184" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>Jared Jones</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>683003</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L184" t="n">
         <v>37.7</v>
       </c>
@@ -50698,26 +50674,26 @@
       </c>
       <c r="O184" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P184" t="n">
-        <v>30.5</v>
+        <v>30.3</v>
       </c>
       <c r="Q184" t="n">
-        <v>41.2</v>
+        <v>42.6</v>
       </c>
       <c r="R184" t="n">
-        <v>34.3</v>
+        <v>27.6</v>
       </c>
       <c r="S184" t="n">
-        <v>47.9</v>
+        <v>40.2</v>
       </c>
       <c r="T184" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U184" t="n">
-        <v>9.300000000000001</v>
+        <v>10.1</v>
       </c>
       <c r="V184" t="inlineStr">
         <is>
@@ -50731,7 +50707,7 @@
       </c>
       <c r="X184" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y184" t="inlineStr">
@@ -50756,7 +50732,7 @@
       </c>
       <c r="AC184" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD184" t="inlineStr"/>
@@ -50773,12 +50749,12 @@
       </c>
       <c r="AH184" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI184" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ184" t="inlineStr">
@@ -50788,12 +50764,12 @@
       </c>
       <c r="AK184" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/22, 0 HR</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AL184" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.6% barrel, 11.0 HR allowed</t>
         </is>
       </c>
       <c r="AM184" t="inlineStr">
@@ -50803,80 +50779,104 @@
       </c>
       <c r="AN184" t="inlineStr">
         <is>
-          <t>5.79</t>
+          <t>8.55</t>
         </is>
       </c>
       <c r="AO184" t="inlineStr">
         <is>
-          <t>41.86</t>
+          <t>37.63</t>
         </is>
       </c>
       <c r="AP184" t="inlineStr">
         <is>
-          <t>89.79</t>
+          <t>89.49</t>
         </is>
       </c>
       <c r="AQ184" t="inlineStr">
         <is>
-          <t>100.1831</t>
+          <t>99.0908</t>
         </is>
       </c>
       <c r="AR184" t="inlineStr">
         <is>
-          <t>0.3935</t>
+          <t>0.3601</t>
         </is>
       </c>
       <c r="AS184" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>0.1304</t>
         </is>
       </c>
       <c r="AT184" t="inlineStr">
         <is>
-          <t>0.3202</t>
+          <t>0.3058</t>
         </is>
       </c>
       <c r="AU184" t="inlineStr">
         <is>
-          <t>72.84</t>
+          <t>70.71</t>
         </is>
       </c>
       <c r="AV184" t="inlineStr">
         <is>
-          <t>32.15</t>
+          <t>12.7</t>
         </is>
       </c>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>41.25</t>
+          <t>31.89</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="AZ184" t="inlineStr">
         <is>
-          <t>0.1263</t>
-        </is>
-      </c>
-      <c r="BA184" t="inlineStr"/>
-      <c r="BB184" t="inlineStr"/>
-      <c r="BC184" t="inlineStr"/>
-      <c r="BD184" t="inlineStr"/>
-      <c r="BE184" t="inlineStr"/>
-      <c r="BF184" t="inlineStr"/>
+          <t>0.0983</t>
+        </is>
+      </c>
+      <c r="BA184" t="inlineStr">
+        <is>
+          <t>8.6</t>
+        </is>
+      </c>
+      <c r="BB184" t="inlineStr">
+        <is>
+          <t>39.1</t>
+        </is>
+      </c>
+      <c r="BC184" t="inlineStr">
+        <is>
+          <t>89.6</t>
+        </is>
+      </c>
+      <c r="BD184" t="inlineStr">
+        <is>
+          <t>0.392</t>
+        </is>
+      </c>
+      <c r="BE184" t="inlineStr">
+        <is>
+          <t>0.173</t>
+        </is>
+      </c>
+      <c r="BF184" t="inlineStr">
+        <is>
+          <t>27.0</t>
+        </is>
+      </c>
       <c r="BG184" t="inlineStr"/>
       <c r="BH184" t="inlineStr"/>
       <c r="BI184" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ184" t="inlineStr"/>
@@ -50887,27 +50887,27 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>676439</t>
+          <t>800325</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Hunter Feduccia</t>
+          <t>Luis Lara</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>2026-08-22T23:15:00Z</t>
+          <t>2026-08-22T18:10:00Z</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -50917,26 +50917,26 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>Jared Jones</t>
+          <t>Martín Pérez</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>683003</t>
+          <t>527048</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L185" t="n">
-        <v>37.7</v>
+        <v>37.6</v>
       </c>
       <c r="M185" t="inlineStr">
         <is>
@@ -50954,22 +50954,22 @@
         </is>
       </c>
       <c r="P185" t="n">
-        <v>30.3</v>
+        <v>22.4</v>
       </c>
       <c r="Q185" t="n">
-        <v>42.6</v>
+        <v>37</v>
       </c>
       <c r="R185" t="n">
         <v>27.6</v>
       </c>
       <c r="S185" t="n">
-        <v>40.2</v>
+        <v>59.8</v>
       </c>
       <c r="T185" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U185" t="n">
-        <v>10.1</v>
+        <v>41.7</v>
       </c>
       <c r="V185" t="inlineStr">
         <is>
@@ -50983,7 +50983,7 @@
       </c>
       <c r="X185" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y185" t="inlineStr">
@@ -51008,7 +51008,7 @@
       </c>
       <c r="AC185" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD185" t="inlineStr"/>
@@ -51025,27 +51025,27 @@
       </c>
       <c r="AH185" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI185" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/16, 0 HR</t>
+          <t>Last 7 games: 8/29, 1 HR</t>
         </is>
       </c>
       <c r="AL185" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.6% barrel, 11.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.1% barrel, 9.5 HR allowed</t>
         </is>
       </c>
       <c r="AM185" t="inlineStr">
@@ -51055,104 +51055,104 @@
       </c>
       <c r="AN185" t="inlineStr">
         <is>
-          <t>8.55</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="AO185" t="inlineStr">
         <is>
-          <t>37.63</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="AP185" t="inlineStr">
         <is>
-          <t>89.49</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AQ185" t="inlineStr">
         <is>
-          <t>99.0908</t>
+          <t>98.8151</t>
         </is>
       </c>
       <c r="AR185" t="inlineStr">
         <is>
-          <t>0.3601</t>
+          <t>0.366</t>
         </is>
       </c>
       <c r="AS185" t="inlineStr">
         <is>
-          <t>0.1304</t>
+          <t>0.092</t>
         </is>
       </c>
       <c r="AT185" t="inlineStr">
         <is>
-          <t>0.3058</t>
+          <t>0.319</t>
         </is>
       </c>
       <c r="AU185" t="inlineStr">
         <is>
-          <t>70.71</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="AV185" t="inlineStr">
         <is>
-          <t>12.7</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>31.89</t>
+          <t>32.1</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ185" t="inlineStr">
         <is>
-          <t>0.0983</t>
+          <t>0.108</t>
         </is>
       </c>
       <c r="BA185" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.14</t>
         </is>
       </c>
       <c r="BB185" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>37.86</t>
         </is>
       </c>
       <c r="BC185" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>88.13</t>
         </is>
       </c>
       <c r="BD185" t="inlineStr">
         <is>
-          <t>0.392</t>
+          <t>0.4171</t>
         </is>
       </c>
       <c r="BE185" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="BF185" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="BG185" t="inlineStr"/>
       <c r="BH185" t="inlineStr"/>
       <c r="BI185" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ185" t="inlineStr"/>
@@ -51163,27 +51163,27 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>800325</t>
+          <t>665804</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Luis Lara</t>
+          <t>Miguel Amaya</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>2026-08-22T18:10:00Z</t>
+          <t>2026-08-22T23:15:00Z</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -51193,17 +51193,17 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>Martín Pérez</t>
+          <t>Kade Anderson</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>527048</t>
+          <t>807739</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
@@ -51230,22 +51230,22 @@
         </is>
       </c>
       <c r="P186" t="n">
-        <v>22.4</v>
+        <v>24.9</v>
       </c>
       <c r="Q186" t="n">
-        <v>37</v>
+        <v>41.2</v>
       </c>
       <c r="R186" t="n">
-        <v>27.6</v>
+        <v>25.4</v>
       </c>
       <c r="S186" t="n">
-        <v>59.8</v>
+        <v>40.2</v>
       </c>
       <c r="T186" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="U186" t="n">
-        <v>41.7</v>
+        <v>60.3</v>
       </c>
       <c r="V186" t="inlineStr">
         <is>
@@ -51259,7 +51259,7 @@
       </c>
       <c r="X186" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y186" t="inlineStr">
@@ -51284,7 +51284,7 @@
       </c>
       <c r="AC186" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD186" t="inlineStr"/>
@@ -51301,27 +51301,27 @@
       </c>
       <c r="AH186" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI186" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK186" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/29, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL186" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.1% barrel, 9.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM186" t="inlineStr">
@@ -51331,104 +51331,80 @@
       </c>
       <c r="AN186" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>7.09</t>
         </is>
       </c>
       <c r="AO186" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>35.28</t>
         </is>
       </c>
       <c r="AP186" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>87.38</t>
         </is>
       </c>
       <c r="AQ186" t="inlineStr">
         <is>
-          <t>98.8151</t>
+          <t>97.8095</t>
         </is>
       </c>
       <c r="AR186" t="inlineStr">
         <is>
-          <t>0.366</t>
+          <t>0.3447</t>
         </is>
       </c>
       <c r="AS186" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>0.1294</t>
         </is>
       </c>
       <c r="AT186" t="inlineStr">
         <is>
-          <t>0.319</t>
+          <t>0.2936</t>
         </is>
       </c>
       <c r="AU186" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>71.01</t>
         </is>
       </c>
       <c r="AV186" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>13.87</t>
         </is>
       </c>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>32.1</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>32.09</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="AZ186" t="inlineStr">
         <is>
-          <t>0.108</t>
-        </is>
-      </c>
-      <c r="BA186" t="inlineStr">
-        <is>
-          <t>8.14</t>
-        </is>
-      </c>
-      <c r="BB186" t="inlineStr">
-        <is>
-          <t>37.86</t>
-        </is>
-      </c>
-      <c r="BC186" t="inlineStr">
-        <is>
-          <t>88.13</t>
-        </is>
-      </c>
-      <c r="BD186" t="inlineStr">
-        <is>
-          <t>0.4171</t>
-        </is>
-      </c>
-      <c r="BE186" t="inlineStr">
-        <is>
-          <t>0.1618</t>
-        </is>
-      </c>
-      <c r="BF186" t="inlineStr">
-        <is>
-          <t>24.2</t>
-        </is>
-      </c>
+          <t>0.1609</t>
+        </is>
+      </c>
+      <c r="BA186" t="inlineStr"/>
+      <c r="BB186" t="inlineStr"/>
+      <c r="BC186" t="inlineStr"/>
+      <c r="BD186" t="inlineStr"/>
+      <c r="BE186" t="inlineStr"/>
+      <c r="BF186" t="inlineStr"/>
       <c r="BG186" t="inlineStr"/>
       <c r="BH186" t="inlineStr"/>
       <c r="BI186" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ186" t="inlineStr"/>
@@ -51439,22 +51415,22 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>665804</t>
+          <t>678545</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Miguel Amaya</t>
+          <t>Osleivis Basabe</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -51469,17 +51445,17 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>Kade Anderson</t>
+          <t>Patrick Sandoval</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>807739</t>
+          <t>663776</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
@@ -51506,22 +51482,22 @@
         </is>
       </c>
       <c r="P187" t="n">
-        <v>24.9</v>
+        <v>35.1</v>
       </c>
       <c r="Q187" t="n">
-        <v>41.2</v>
+        <v>23.7</v>
       </c>
       <c r="R187" t="n">
-        <v>25.4</v>
+        <v>28.7</v>
       </c>
       <c r="S187" t="n">
-        <v>40.2</v>
+        <v>59.8</v>
       </c>
       <c r="T187" t="n">
         <v>78</v>
       </c>
       <c r="U187" t="n">
-        <v>60.3</v>
+        <v>12</v>
       </c>
       <c r="V187" t="inlineStr">
         <is>
@@ -51535,7 +51511,7 @@
       </c>
       <c r="X187" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y187" t="inlineStr">
@@ -51560,7 +51536,7 @@
       </c>
       <c r="AC187" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026 P:2026</t>
         </is>
       </c>
       <c r="AD187" t="inlineStr"/>
@@ -51582,105 +51558,129 @@
       </c>
       <c r="AI187" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL187" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.6% barrel, 3.0 HR allowed</t>
         </is>
       </c>
       <c r="AM187" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN187" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="AO187" t="inlineStr">
         <is>
-          <t>35.28</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="AP187" t="inlineStr">
         <is>
-          <t>87.38</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AQ187" t="inlineStr">
         <is>
-          <t>97.8095</t>
+          <t>99.2819</t>
         </is>
       </c>
       <c r="AR187" t="inlineStr">
         <is>
-          <t>0.3447</t>
+          <t>0.374</t>
         </is>
       </c>
       <c r="AS187" t="inlineStr">
         <is>
-          <t>0.1294</t>
+          <t>0.143</t>
         </is>
       </c>
       <c r="AT187" t="inlineStr">
         <is>
-          <t>0.2936</t>
+          <t>0.275</t>
         </is>
       </c>
       <c r="AU187" t="inlineStr">
         <is>
-          <t>71.01</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="AV187" t="inlineStr">
         <is>
-          <t>13.87</t>
+          <t>32.5</t>
         </is>
       </c>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>32.09</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ187" t="inlineStr">
         <is>
-          <t>0.1609</t>
-        </is>
-      </c>
-      <c r="BA187" t="inlineStr"/>
-      <c r="BB187" t="inlineStr"/>
-      <c r="BC187" t="inlineStr"/>
-      <c r="BD187" t="inlineStr"/>
-      <c r="BE187" t="inlineStr"/>
-      <c r="BF187" t="inlineStr"/>
+          <t>0.162</t>
+        </is>
+      </c>
+      <c r="BA187" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
+      </c>
+      <c r="BB187" t="inlineStr">
+        <is>
+          <t>32.4</t>
+        </is>
+      </c>
+      <c r="BC187" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="BD187" t="inlineStr">
+        <is>
+          <t>0.412</t>
+        </is>
+      </c>
+      <c r="BE187" t="inlineStr">
+        <is>
+          <t>0.135</t>
+        </is>
+      </c>
+      <c r="BF187" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
       <c r="BG187" t="inlineStr"/>
       <c r="BH187" t="inlineStr"/>
       <c r="BI187" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>Fenway Park</t>
         </is>
       </c>
       <c r="BJ187" t="inlineStr"/>
@@ -51691,27 +51691,27 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>678545</t>
+          <t>694197</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Osleivis Basabe</t>
+          <t>Angel Genao</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>2026-08-22T23:15:00Z</t>
+          <t>2026-08-23T00:10:00Z</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -51726,17 +51726,17 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>Patrick Sandoval</t>
+          <t>Gabriel Hughes</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>663776</t>
+          <t>687312</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L188" t="n">
@@ -51758,22 +51758,22 @@
         </is>
       </c>
       <c r="P188" t="n">
-        <v>35.1</v>
+        <v>36</v>
       </c>
       <c r="Q188" t="n">
-        <v>23.7</v>
+        <v>14</v>
       </c>
       <c r="R188" t="n">
-        <v>28.7</v>
+        <v>38.7</v>
       </c>
       <c r="S188" t="n">
         <v>59.8</v>
       </c>
       <c r="T188" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U188" t="n">
-        <v>12</v>
+        <v>28.2</v>
       </c>
       <c r="V188" t="inlineStr">
         <is>
@@ -51829,12 +51829,12 @@
       </c>
       <c r="AH188" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI188" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ188" t="inlineStr">
@@ -51844,107 +51844,107 @@
       </c>
       <c r="AK188" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Last 7 games: 8/26, 0 HR</t>
         </is>
       </c>
       <c r="AL188" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.6% barrel, 3.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 4.3% barrel, 3.0 HR allowed</t>
         </is>
       </c>
       <c r="AM188" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN188" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="AO188" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="AP188" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>92.6</t>
         </is>
       </c>
       <c r="AQ188" t="inlineStr">
         <is>
-          <t>99.2819</t>
+          <t>101.0112</t>
         </is>
       </c>
       <c r="AR188" t="inlineStr">
         <is>
-          <t>0.374</t>
+          <t>0.395</t>
         </is>
       </c>
       <c r="AS188" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>0.118</t>
         </is>
       </c>
       <c r="AT188" t="inlineStr">
         <is>
-          <t>0.275</t>
+          <t>0.327</t>
         </is>
       </c>
       <c r="AU188" t="inlineStr">
         <is>
-          <t>73.4</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AV188" t="inlineStr">
         <is>
-          <t>32.5</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>31.1</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>15.6</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ188" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="BA188" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="BB188" t="inlineStr">
         <is>
-          <t>32.4</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="BC188" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="BD188" t="inlineStr">
         <is>
-          <t>0.412</t>
+          <t>0.338</t>
         </is>
       </c>
       <c r="BE188" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>0.106</t>
         </is>
       </c>
       <c r="BF188" t="inlineStr">
@@ -51956,7 +51956,7 @@
       <c r="BH188" t="inlineStr"/>
       <c r="BI188" t="inlineStr">
         <is>
-          <t>Fenway Park</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ188" t="inlineStr"/>
@@ -51967,27 +51967,27 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>694197</t>
+          <t>678882</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Angel Genao</t>
+          <t>Ceddanne Rafaela</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>2026-08-23T00:10:00Z</t>
+          <t>2026-08-22T23:15:00Z</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -51997,17 +51997,17 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>Gabriel Hughes</t>
+          <t>Blade Tidwell</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>687312</t>
+          <t>694918</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
@@ -52016,7 +52016,7 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>37.6</v>
+        <v>37.2</v>
       </c>
       <c r="M189" t="inlineStr">
         <is>
@@ -52030,26 +52030,26 @@
       </c>
       <c r="O189" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P189" t="n">
-        <v>36</v>
+        <v>22.9</v>
       </c>
       <c r="Q189" t="n">
-        <v>14</v>
+        <v>26.2</v>
       </c>
       <c r="R189" t="n">
-        <v>38.7</v>
+        <v>28.7</v>
       </c>
       <c r="S189" t="n">
-        <v>59.8</v>
+        <v>95.5</v>
       </c>
       <c r="T189" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U189" t="n">
-        <v>28.2</v>
+        <v>22.9</v>
       </c>
       <c r="V189" t="inlineStr">
         <is>
@@ -52063,7 +52063,7 @@
       </c>
       <c r="X189" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y189" t="inlineStr">
@@ -52088,7 +52088,7 @@
       </c>
       <c r="AC189" t="inlineStr">
         <is>
-          <t>H:2026 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD189" t="inlineStr"/>
@@ -52105,12 +52105,12 @@
       </c>
       <c r="AH189" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI189" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AJ189" t="inlineStr">
@@ -52120,119 +52120,119 @@
       </c>
       <c r="AK189" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/26, 0 HR</t>
+          <t>Last 7 games: 9/33, 0 HR</t>
         </is>
       </c>
       <c r="AL189" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 4.3% barrel, 3.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.5% barrel, 2.6 HR allowed</t>
         </is>
       </c>
       <c r="AM189" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN189" t="inlineStr">
         <is>
-          <t>6.7</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="AO189" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>34.08</t>
         </is>
       </c>
       <c r="AP189" t="inlineStr">
         <is>
-          <t>92.6</t>
+          <t>86.97</t>
         </is>
       </c>
       <c r="AQ189" t="inlineStr">
         <is>
-          <t>101.0112</t>
+          <t>97.8319</t>
         </is>
       </c>
       <c r="AR189" t="inlineStr">
         <is>
-          <t>0.395</t>
+          <t>0.3796</t>
         </is>
       </c>
       <c r="AS189" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>0.1334</t>
         </is>
       </c>
       <c r="AT189" t="inlineStr">
         <is>
-          <t>0.327</t>
+          <t>0.291</t>
         </is>
       </c>
       <c r="AU189" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>70.02</t>
         </is>
       </c>
       <c r="AV189" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>8.83</t>
         </is>
       </c>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>31.1</t>
+          <t>35.43</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>15.6</t>
+          <t>26.14</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="AZ189" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.1734</t>
         </is>
       </c>
       <c r="BA189" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>6.51</t>
         </is>
       </c>
       <c r="BB189" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>36.64</t>
         </is>
       </c>
       <c r="BC189" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.78</t>
         </is>
       </c>
       <c r="BD189" t="inlineStr">
         <is>
-          <t>0.338</t>
+          <t>0.3849</t>
         </is>
       </c>
       <c r="BE189" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>0.125</t>
         </is>
       </c>
       <c r="BF189" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>21.73</t>
         </is>
       </c>
       <c r="BG189" t="inlineStr"/>
       <c r="BH189" t="inlineStr"/>
       <c r="BI189" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Fenway Park</t>
         </is>
       </c>
       <c r="BJ189" t="inlineStr"/>
@@ -52243,27 +52243,27 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>678882</t>
+          <t>694497</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Ceddanne Rafaela</t>
+          <t>Evan Carter</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>2026-08-22T23:15:00Z</t>
+          <t>2026-08-22T23:05:00Z</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -52273,17 +52273,17 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>Blade Tidwell</t>
+          <t>Ryan Johnson</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>694918</t>
+          <t>696270</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
@@ -52292,7 +52292,7 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>37.2</v>
+        <v>37.1</v>
       </c>
       <c r="M190" t="inlineStr">
         <is>
@@ -52306,26 +52306,26 @@
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P190" t="n">
-        <v>22.9</v>
+        <v>21.5</v>
       </c>
       <c r="Q190" t="n">
-        <v>26.2</v>
+        <v>50.2</v>
       </c>
       <c r="R190" t="n">
-        <v>28.7</v>
+        <v>27.6</v>
       </c>
       <c r="S190" t="n">
-        <v>95.5</v>
+        <v>40.2</v>
       </c>
       <c r="T190" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U190" t="n">
-        <v>22.9</v>
+        <v>19.5</v>
       </c>
       <c r="V190" t="inlineStr">
         <is>
@@ -52339,7 +52339,7 @@
       </c>
       <c r="X190" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y190" t="inlineStr">
@@ -52381,12 +52381,12 @@
       </c>
       <c r="AH190" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI190" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ190" t="inlineStr">
@@ -52396,119 +52396,119 @@
       </c>
       <c r="AK190" t="inlineStr">
         <is>
-          <t>Last 7 games: 9/33, 0 HR</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AL190" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.5% barrel, 2.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.4% barrel, 12.4 HR allowed</t>
         </is>
       </c>
       <c r="AM190" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN190" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>5.69</t>
         </is>
       </c>
       <c r="AO190" t="inlineStr">
         <is>
-          <t>34.08</t>
+          <t>35.65</t>
         </is>
       </c>
       <c r="AP190" t="inlineStr">
         <is>
-          <t>86.97</t>
+          <t>87.54</t>
         </is>
       </c>
       <c r="AQ190" t="inlineStr">
         <is>
-          <t>97.8319</t>
+          <t>98.6524</t>
         </is>
       </c>
       <c r="AR190" t="inlineStr">
         <is>
-          <t>0.3796</t>
+          <t>0.3348</t>
         </is>
       </c>
       <c r="AS190" t="inlineStr">
         <is>
-          <t>0.1334</t>
+          <t>0.1218</t>
         </is>
       </c>
       <c r="AT190" t="inlineStr">
         <is>
-          <t>0.291</t>
+          <t>0.2912</t>
         </is>
       </c>
       <c r="AU190" t="inlineStr">
         <is>
-          <t>70.02</t>
+          <t>70.95</t>
         </is>
       </c>
       <c r="AV190" t="inlineStr">
         <is>
-          <t>8.83</t>
+          <t>17.51</t>
         </is>
       </c>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>35.43</t>
+          <t>38.56</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>26.14</t>
+          <t>28.05</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="AZ190" t="inlineStr">
         <is>
-          <t>0.1734</t>
+          <t>0.1331</t>
         </is>
       </c>
       <c r="BA190" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>10.39</t>
         </is>
       </c>
       <c r="BB190" t="inlineStr">
         <is>
-          <t>36.64</t>
+          <t>36.84</t>
         </is>
       </c>
       <c r="BC190" t="inlineStr">
         <is>
-          <t>87.78</t>
+          <t>87.82</t>
         </is>
       </c>
       <c r="BD190" t="inlineStr">
         <is>
-          <t>0.3849</t>
+          <t>0.4535</t>
         </is>
       </c>
       <c r="BE190" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>0.1945</t>
         </is>
       </c>
       <c r="BF190" t="inlineStr">
         <is>
-          <t>21.73</t>
+          <t>33.95</t>
         </is>
       </c>
       <c r="BG190" t="inlineStr"/>
       <c r="BH190" t="inlineStr"/>
       <c r="BI190" t="inlineStr">
         <is>
-          <t>Fenway Park</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ190" t="inlineStr"/>
@@ -65195,22 +65195,22 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>500743</t>
+          <t>678011</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Miguel Rojas</t>
+          <t>Anthony Seigler</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -65225,17 +65225,17 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>Jared Jones</t>
+          <t>Blade Tidwell</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>683003</t>
+          <t>694918</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
@@ -65244,7 +65244,7 @@
         </is>
       </c>
       <c r="L237" t="n">
-        <v>32</v>
+        <v>32.1</v>
       </c>
       <c r="M237" t="inlineStr">
         <is>
@@ -65258,27 +65258,27 @@
       </c>
       <c r="O237" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P237" t="n">
-        <v>18.8</v>
+        <v>20.2</v>
       </c>
       <c r="Q237" t="n">
-        <v>42.6</v>
+        <v>25.9</v>
       </c>
       <c r="R237" t="n">
-        <v>27.6</v>
+        <v>28.7</v>
       </c>
       <c r="S237" t="n">
-        <v>47.9</v>
+        <v>40.2</v>
       </c>
       <c r="T237" t="n">
+        <v>75</v>
+      </c>
+      <c r="U237" t="n">
         <v>50</v>
       </c>
-      <c r="U237" t="n">
-        <v>5.1</v>
-      </c>
       <c r="V237" t="inlineStr">
         <is>
           <t>No</t>
@@ -65291,7 +65291,7 @@
       </c>
       <c r="X237" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y237" t="inlineStr">
@@ -65316,7 +65316,7 @@
       </c>
       <c r="AC237" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD237" t="inlineStr"/>
@@ -65328,17 +65328,17 @@
       </c>
       <c r="AG237" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AH237" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AI237" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AJ237" t="inlineStr">
@@ -65348,12 +65348,12 @@
       </c>
       <c r="AK237" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/13, 0 HR</t>
+          <t>Recent form unavailable</t>
         </is>
       </c>
       <c r="AL237" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.6% barrel, 11.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.5% barrel, 2.6 HR allowed</t>
         </is>
       </c>
       <c r="AM237" t="inlineStr">
@@ -65363,104 +65363,104 @@
       </c>
       <c r="AN237" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="AO237" t="inlineStr">
         <is>
-          <t>35.47</t>
+          <t>36.38</t>
         </is>
       </c>
       <c r="AP237" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>88.11</t>
         </is>
       </c>
       <c r="AQ237" t="inlineStr">
         <is>
-          <t>98.1355</t>
+          <t>97.283</t>
         </is>
       </c>
       <c r="AR237" t="inlineStr">
         <is>
-          <t>0.3881</t>
+          <t>0.3677</t>
         </is>
       </c>
       <c r="AS237" t="inlineStr">
         <is>
-          <t>0.1118</t>
+          <t>0.1258</t>
         </is>
       </c>
       <c r="AT237" t="inlineStr">
         <is>
-          <t>0.3133</t>
+          <t>0.3079</t>
         </is>
       </c>
       <c r="AU237" t="inlineStr">
         <is>
-          <t>68.94</t>
+          <t>67.08</t>
         </is>
       </c>
       <c r="AV237" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>36.99</t>
+          <t>33.93</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>27.8</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="AZ237" t="inlineStr">
         <is>
-          <t>0.1252</t>
+          <t>0.1105</t>
         </is>
       </c>
       <c r="BA237" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>6.51</t>
         </is>
       </c>
       <c r="BB237" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>36.64</t>
         </is>
       </c>
       <c r="BC237" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>87.78</t>
         </is>
       </c>
       <c r="BD237" t="inlineStr">
         <is>
-          <t>0.392</t>
+          <t>0.3849</t>
         </is>
       </c>
       <c r="BE237" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>0.125</t>
         </is>
       </c>
       <c r="BF237" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>21.73</t>
         </is>
       </c>
       <c r="BG237" t="inlineStr"/>
       <c r="BH237" t="inlineStr"/>
       <c r="BI237" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Fenway Park</t>
         </is>
       </c>
       <c r="BJ237" t="inlineStr"/>
@@ -65471,22 +65471,22 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>664728</t>
+          <t>500743</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Kyle Isbel</t>
+          <t>Miguel Rojas</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -65501,17 +65501,17 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>Drew Anderson</t>
+          <t>Jared Jones</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>623454</t>
+          <t>683003</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
@@ -65520,7 +65520,7 @@
         </is>
       </c>
       <c r="L238" t="n">
-        <v>31.6</v>
+        <v>32</v>
       </c>
       <c r="M238" t="inlineStr">
         <is>
@@ -65534,26 +65534,26 @@
       </c>
       <c r="O238" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P238" t="n">
-        <v>13.1</v>
+        <v>18.8</v>
       </c>
       <c r="Q238" t="n">
-        <v>36.8</v>
+        <v>42.6</v>
       </c>
       <c r="R238" t="n">
-        <v>23.2</v>
+        <v>27.6</v>
       </c>
       <c r="S238" t="n">
-        <v>40.2</v>
+        <v>47.9</v>
       </c>
       <c r="T238" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U238" t="n">
-        <v>43.2</v>
+        <v>5.1</v>
       </c>
       <c r="V238" t="inlineStr">
         <is>
@@ -65567,7 +65567,7 @@
       </c>
       <c r="X238" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y238" t="inlineStr">
@@ -65609,27 +65609,27 @@
       </c>
       <c r="AH238" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI238" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AJ238" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK238" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 1 HR</t>
+          <t>Last 7 games: 2/13, 0 HR</t>
         </is>
       </c>
       <c r="AL238" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.3% barrel, 11.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.6% barrel, 11.0 HR allowed</t>
         </is>
       </c>
       <c r="AM238" t="inlineStr">
@@ -65639,104 +65639,104 @@
       </c>
       <c r="AN238" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="AO238" t="inlineStr">
         <is>
-          <t>34.84</t>
+          <t>35.47</t>
         </is>
       </c>
       <c r="AP238" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="AQ238" t="inlineStr">
         <is>
-          <t>99.1019</t>
+          <t>98.1355</t>
         </is>
       </c>
       <c r="AR238" t="inlineStr">
         <is>
-          <t>0.3089</t>
+          <t>0.3881</t>
         </is>
       </c>
       <c r="AS238" t="inlineStr">
         <is>
-          <t>0.0798</t>
+          <t>0.1118</t>
         </is>
       </c>
       <c r="AT238" t="inlineStr">
         <is>
-          <t>0.2629</t>
+          <t>0.3133</t>
         </is>
       </c>
       <c r="AU238" t="inlineStr">
         <is>
-          <t>71.24</t>
+          <t>68.94</t>
         </is>
       </c>
       <c r="AV238" t="inlineStr">
         <is>
-          <t>14.11</t>
+          <t>5.35</t>
         </is>
       </c>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>32.74</t>
+          <t>36.99</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>17.89</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="AZ238" t="inlineStr">
         <is>
-          <t>0.1134</t>
+          <t>0.1252</t>
         </is>
       </c>
       <c r="BA238" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="BB238" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="BC238" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="BD238" t="inlineStr">
         <is>
-          <t>0.354</t>
+          <t>0.392</t>
         </is>
       </c>
       <c r="BE238" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>0.173</t>
         </is>
       </c>
       <c r="BF238" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="BG238" t="inlineStr"/>
       <c r="BH238" t="inlineStr"/>
       <c r="BI238" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ238" t="inlineStr"/>
@@ -65747,22 +65747,22 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>678011</t>
+          <t>664728</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Anthony Seigler</t>
+          <t>Kyle Isbel</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -65782,12 +65782,12 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>Blade Tidwell</t>
+          <t>Drew Anderson</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>694918</t>
+          <t>623454</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
@@ -65814,22 +65814,22 @@
         </is>
       </c>
       <c r="P239" t="n">
-        <v>20.2</v>
+        <v>13.1</v>
       </c>
       <c r="Q239" t="n">
-        <v>25.9</v>
+        <v>36.8</v>
       </c>
       <c r="R239" t="n">
-        <v>28.7</v>
+        <v>23.2</v>
       </c>
       <c r="S239" t="n">
         <v>40.2</v>
       </c>
       <c r="T239" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U239" t="n">
-        <v>40.3</v>
+        <v>43.2</v>
       </c>
       <c r="V239" t="inlineStr">
         <is>
@@ -65868,7 +65868,7 @@
       </c>
       <c r="AC239" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD239" t="inlineStr"/>
@@ -65885,27 +65885,27 @@
       </c>
       <c r="AH239" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI239" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
         <is>
-          <t>Contact streak: 7/18 over last 7 games</t>
+          <t>Last 7 games: 6/21, 1 HR</t>
         </is>
       </c>
       <c r="AL239" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.5% barrel, 2.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 11.0 HR allowed</t>
         </is>
       </c>
       <c r="AM239" t="inlineStr">
@@ -65915,104 +65915,104 @@
       </c>
       <c r="AN239" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AO239" t="inlineStr">
         <is>
-          <t>36.38</t>
+          <t>34.84</t>
         </is>
       </c>
       <c r="AP239" t="inlineStr">
         <is>
-          <t>88.11</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AQ239" t="inlineStr">
         <is>
-          <t>97.283</t>
+          <t>99.1019</t>
         </is>
       </c>
       <c r="AR239" t="inlineStr">
         <is>
-          <t>0.3677</t>
+          <t>0.3089</t>
         </is>
       </c>
       <c r="AS239" t="inlineStr">
         <is>
-          <t>0.1258</t>
+          <t>0.0798</t>
         </is>
       </c>
       <c r="AT239" t="inlineStr">
         <is>
-          <t>0.3079</t>
+          <t>0.2629</t>
         </is>
       </c>
       <c r="AU239" t="inlineStr">
         <is>
-          <t>67.08</t>
+          <t>71.24</t>
         </is>
       </c>
       <c r="AV239" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>14.11</t>
         </is>
       </c>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>33.93</t>
+          <t>32.74</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>27.8</t>
+          <t>17.89</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="AZ239" t="inlineStr">
         <is>
-          <t>0.1105</t>
+          <t>0.1134</t>
         </is>
       </c>
       <c r="BA239" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="BB239" t="inlineStr">
         <is>
-          <t>36.64</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="BC239" t="inlineStr">
         <is>
-          <t>87.78</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="BD239" t="inlineStr">
         <is>
-          <t>0.3849</t>
+          <t>0.354</t>
         </is>
       </c>
       <c r="BE239" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>0.137</t>
         </is>
       </c>
       <c r="BF239" t="inlineStr">
         <is>
-          <t>21.73</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="BG239" t="inlineStr"/>
       <c r="BH239" t="inlineStr"/>
       <c r="BI239" t="inlineStr">
         <is>
-          <t>Fenway Park</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ239" t="inlineStr"/>

--- a/outputs/daily/hr_rankings_2026-08-22_full.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-22_full.xlsx
@@ -61607,27 +61607,27 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>695720</t>
+          <t>681508</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Tommy White</t>
+          <t>Mickey Gasper</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>2026-08-22T23:10:00Z</t>
+          <t>2026-08-22T23:15:00Z</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
@@ -61637,17 +61637,17 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>Hunter Brown</t>
+          <t>Blade Tidwell</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>686613</t>
+          <t>694918</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
@@ -61656,7 +61656,7 @@
         </is>
       </c>
       <c r="L224" t="n">
-        <v>33.5</v>
+        <v>33.7</v>
       </c>
       <c r="M224" t="inlineStr">
         <is>
@@ -61670,26 +61670,26 @@
       </c>
       <c r="O224" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P224" t="n">
-        <v>15.3</v>
+        <v>22.4</v>
       </c>
       <c r="Q224" t="n">
-        <v>22.7</v>
+        <v>25.9</v>
       </c>
       <c r="R224" t="n">
-        <v>27.6</v>
+        <v>28.7</v>
       </c>
       <c r="S224" t="n">
-        <v>81.90000000000001</v>
+        <v>40.2</v>
       </c>
       <c r="T224" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U224" t="n">
-        <v>57.8</v>
+        <v>67</v>
       </c>
       <c r="V224" t="inlineStr">
         <is>
@@ -61703,7 +61703,7 @@
       </c>
       <c r="X224" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y224" t="inlineStr">
@@ -61728,7 +61728,7 @@
       </c>
       <c r="AC224" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD224" t="inlineStr"/>
@@ -61745,27 +61745,27 @@
       </c>
       <c r="AH224" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI224" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL224" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.2% barrel, 11.4 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.5% barrel, 2.6 HR allowed</t>
         </is>
       </c>
       <c r="AM224" t="inlineStr">
@@ -61775,42 +61775,42 @@
       </c>
       <c r="AN224" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="AO224" t="inlineStr">
         <is>
-          <t>31.2</t>
+          <t>33.86</t>
         </is>
       </c>
       <c r="AP224" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>88.15</t>
         </is>
       </c>
       <c r="AQ224" t="inlineStr">
         <is>
-          <t>96.7187</t>
+          <t>98.2082</t>
         </is>
       </c>
       <c r="AR224" t="inlineStr">
         <is>
-          <t>0.365</t>
+          <t>0.3446</t>
         </is>
       </c>
       <c r="AS224" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.1251</t>
         </is>
       </c>
       <c r="AT224" t="inlineStr">
         <is>
-          <t>0.282</t>
+          <t>0.2899</t>
         </is>
       </c>
       <c r="AU224" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>71.58</t>
         </is>
       </c>
       <c r="AV224" t="inlineStr">
@@ -61820,59 +61820,59 @@
       </c>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>31.2</t>
+          <t>40.24</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>31.06</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="AZ224" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>0.1153</t>
         </is>
       </c>
       <c r="BA224" t="inlineStr">
         <is>
-          <t>6.18</t>
+          <t>6.51</t>
         </is>
       </c>
       <c r="BB224" t="inlineStr">
         <is>
-          <t>35.63</t>
+          <t>36.64</t>
         </is>
       </c>
       <c r="BC224" t="inlineStr">
         <is>
-          <t>85.96</t>
+          <t>87.78</t>
         </is>
       </c>
       <c r="BD224" t="inlineStr">
         <is>
-          <t>0.3397</t>
+          <t>0.3849</t>
         </is>
       </c>
       <c r="BE224" t="inlineStr">
         <is>
-          <t>0.1304</t>
+          <t>0.125</t>
         </is>
       </c>
       <c r="BF224" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>21.73</t>
         </is>
       </c>
       <c r="BG224" t="inlineStr"/>
       <c r="BH224" t="inlineStr"/>
       <c r="BI224" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Fenway Park</t>
         </is>
       </c>
       <c r="BJ224" t="inlineStr"/>
@@ -61883,12 +61883,12 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>691777</t>
+          <t>695720</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Max Muncy</t>
+          <t>Tommy White</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -61913,7 +61913,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -61946,11 +61946,11 @@
       </c>
       <c r="O225" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P225" t="n">
-        <v>36.8</v>
+        <v>15.3</v>
       </c>
       <c r="Q225" t="n">
         <v>22.7</v>
@@ -61959,13 +61959,13 @@
         <v>27.6</v>
       </c>
       <c r="S225" t="n">
-        <v>40.2</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T225" t="n">
         <v>50</v>
       </c>
       <c r="U225" t="n">
-        <v>31.9</v>
+        <v>57.8</v>
       </c>
       <c r="V225" t="inlineStr">
         <is>
@@ -61979,7 +61979,7 @@
       </c>
       <c r="X225" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y225" t="inlineStr">
@@ -62004,7 +62004,7 @@
       </c>
       <c r="AC225" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD225" t="inlineStr"/>
@@ -62021,22 +62021,22 @@
       </c>
       <c r="AH225" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI225" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/19, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL225" t="inlineStr">
@@ -62051,67 +62051,67 @@
       </c>
       <c r="AN225" t="inlineStr">
         <is>
-          <t>10.73</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AO225" t="inlineStr">
         <is>
-          <t>40.59</t>
+          <t>31.2</t>
         </is>
       </c>
       <c r="AP225" t="inlineStr">
         <is>
-          <t>89.48</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="AQ225" t="inlineStr">
         <is>
-          <t>100.9026</t>
+          <t>96.7187</t>
         </is>
       </c>
       <c r="AR225" t="inlineStr">
         <is>
-          <t>0.3558</t>
+          <t>0.365</t>
         </is>
       </c>
       <c r="AS225" t="inlineStr">
         <is>
-          <t>0.1479</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AT225" t="inlineStr">
         <is>
-          <t>0.2796</t>
+          <t>0.282</t>
         </is>
       </c>
       <c r="AU225" t="inlineStr">
         <is>
-          <t>73.94</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="AV225" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>13.4</t>
         </is>
       </c>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>41.91</t>
+          <t>31.2</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>23.77</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ225" t="inlineStr">
         <is>
-          <t>0.1601</t>
+          <t>0.071</t>
         </is>
       </c>
       <c r="BA225" t="inlineStr">
@@ -62159,27 +62159,27 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>656716</t>
+          <t>691777</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Zach McKinstry</t>
+          <t>Max Muncy</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>2026-08-22T23:15:00Z</t>
+          <t>2026-08-22T23:10:00Z</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
@@ -62189,17 +62189,17 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>Michael Wacha</t>
+          <t>Hunter Brown</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>608379</t>
+          <t>686613</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
@@ -62222,26 +62222,26 @@
       </c>
       <c r="O226" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P226" t="n">
-        <v>7.1</v>
+        <v>36.8</v>
       </c>
       <c r="Q226" t="n">
-        <v>39.3</v>
+        <v>22.7</v>
       </c>
       <c r="R226" t="n">
-        <v>23.2</v>
+        <v>27.6</v>
       </c>
       <c r="S226" t="n">
-        <v>71.7</v>
+        <v>40.2</v>
       </c>
       <c r="T226" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U226" t="n">
-        <v>21.5</v>
+        <v>31.9</v>
       </c>
       <c r="V226" t="inlineStr">
         <is>
@@ -62255,7 +62255,7 @@
       </c>
       <c r="X226" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y226" t="inlineStr">
@@ -62297,7 +62297,7 @@
       </c>
       <c r="AH226" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI226" t="inlineStr">
@@ -62307,17 +62307,17 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK226" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/19, 0 HR</t>
+          <t>Last 7 games: 4/19, 1 HR</t>
         </is>
       </c>
       <c r="AL226" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.2% barrel, 19.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.2% barrel, 11.4 HR allowed</t>
         </is>
       </c>
       <c r="AM226" t="inlineStr">
@@ -62327,104 +62327,104 @@
       </c>
       <c r="AN226" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>10.73</t>
         </is>
       </c>
       <c r="AO226" t="inlineStr">
         <is>
-          <t>25.11</t>
+          <t>40.59</t>
         </is>
       </c>
       <c r="AP226" t="inlineStr">
         <is>
-          <t>85.63</t>
+          <t>89.48</t>
         </is>
       </c>
       <c r="AQ226" t="inlineStr">
         <is>
-          <t>95.716</t>
+          <t>100.9026</t>
         </is>
       </c>
       <c r="AR226" t="inlineStr">
         <is>
-          <t>0.3335</t>
+          <t>0.3558</t>
         </is>
       </c>
       <c r="AS226" t="inlineStr">
         <is>
-          <t>0.0928</t>
+          <t>0.1479</t>
         </is>
       </c>
       <c r="AT226" t="inlineStr">
         <is>
-          <t>0.2945</t>
+          <t>0.2796</t>
         </is>
       </c>
       <c r="AU226" t="inlineStr">
         <is>
-          <t>67.99</t>
+          <t>73.94</t>
         </is>
       </c>
       <c r="AV226" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>40.54</t>
+          <t>41.91</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>26.53</t>
+          <t>23.77</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>0.1286</t>
+          <t>0.1601</t>
         </is>
       </c>
       <c r="BA226" t="inlineStr">
         <is>
-          <t>7.19</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="BB226" t="inlineStr">
         <is>
-          <t>36.35</t>
+          <t>35.63</t>
         </is>
       </c>
       <c r="BC226" t="inlineStr">
         <is>
-          <t>88.34</t>
+          <t>85.96</t>
         </is>
       </c>
       <c r="BD226" t="inlineStr">
         <is>
-          <t>0.4182</t>
+          <t>0.3397</t>
         </is>
       </c>
       <c r="BE226" t="inlineStr">
         <is>
-          <t>0.1661</t>
+          <t>0.1304</t>
         </is>
       </c>
       <c r="BF226" t="inlineStr">
         <is>
-          <t>28.88</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="BG226" t="inlineStr"/>
       <c r="BH226" t="inlineStr"/>
       <c r="BI226" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ226" t="inlineStr"/>
@@ -62435,24 +62435,24 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>686555</t>
+          <t>656716</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Isaac Collins</t>
+          <t>Zach McKinstry</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
           <t>KC</t>
         </is>
       </c>
-      <c r="E227" t="inlineStr">
-        <is>
-          <t>DET</t>
-        </is>
-      </c>
       <c r="F227" t="inlineStr">
         <is>
           <t>2026-08-22T23:15:00Z</t>
@@ -62465,17 +62465,17 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>Drew Anderson</t>
+          <t>Michael Wacha</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>623454</t>
+          <t>608379</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
@@ -62484,7 +62484,7 @@
         </is>
       </c>
       <c r="L227" t="n">
-        <v>33.3</v>
+        <v>33.5</v>
       </c>
       <c r="M227" t="inlineStr">
         <is>
@@ -62502,22 +62502,22 @@
         </is>
       </c>
       <c r="P227" t="n">
-        <v>23.8</v>
+        <v>7.1</v>
       </c>
       <c r="Q227" t="n">
-        <v>35.6</v>
+        <v>39.3</v>
       </c>
       <c r="R227" t="n">
         <v>23.2</v>
       </c>
       <c r="S227" t="n">
-        <v>47.9</v>
+        <v>71.7</v>
       </c>
       <c r="T227" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U227" t="n">
-        <v>0</v>
+        <v>21.5</v>
       </c>
       <c r="V227" t="inlineStr">
         <is>
@@ -62531,7 +62531,7 @@
       </c>
       <c r="X227" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y227" t="inlineStr">
@@ -62556,7 +62556,7 @@
       </c>
       <c r="AC227" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD227" t="inlineStr"/>
@@ -62573,12 +62573,12 @@
       </c>
       <c r="AH227" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI227" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ227" t="inlineStr">
@@ -62588,12 +62588,12 @@
       </c>
       <c r="AK227" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/18, 0 HR</t>
+          <t>Last 7 games: 5/19, 0 HR</t>
         </is>
       </c>
       <c r="AL227" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.3% barrel, 11.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.2% barrel, 19.2 HR allowed</t>
         </is>
       </c>
       <c r="AM227" t="inlineStr">
@@ -62603,97 +62603,97 @@
       </c>
       <c r="AN227" t="inlineStr">
         <is>
-          <t>5.53</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="AO227" t="inlineStr">
         <is>
-          <t>39.81</t>
+          <t>25.11</t>
         </is>
       </c>
       <c r="AP227" t="inlineStr">
         <is>
-          <t>88.73</t>
+          <t>85.63</t>
         </is>
       </c>
       <c r="AQ227" t="inlineStr">
         <is>
-          <t>99.9594</t>
+          <t>95.716</t>
         </is>
       </c>
       <c r="AR227" t="inlineStr">
         <is>
-          <t>0.3331</t>
+          <t>0.3335</t>
         </is>
       </c>
       <c r="AS227" t="inlineStr">
         <is>
-          <t>0.0997</t>
+          <t>0.0928</t>
         </is>
       </c>
       <c r="AT227" t="inlineStr">
         <is>
-          <t>0.3073</t>
+          <t>0.2945</t>
         </is>
       </c>
       <c r="AU227" t="inlineStr">
         <is>
-          <t>73.33</t>
+          <t>67.99</t>
         </is>
       </c>
       <c r="AV227" t="inlineStr">
         <is>
-          <t>30.41</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>39.98</t>
+          <t>40.54</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>26.53</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AZ227" t="inlineStr">
         <is>
-          <t>0.1291</t>
+          <t>0.1286</t>
         </is>
       </c>
       <c r="BA227" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>7.19</t>
         </is>
       </c>
       <c r="BB227" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>36.35</t>
         </is>
       </c>
       <c r="BC227" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.34</t>
         </is>
       </c>
       <c r="BD227" t="inlineStr">
         <is>
-          <t>0.354</t>
+          <t>0.4182</t>
         </is>
       </c>
       <c r="BE227" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>0.1661</t>
         </is>
       </c>
       <c r="BF227" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>28.88</t>
         </is>
       </c>
       <c r="BG227" t="inlineStr"/>
@@ -62711,27 +62711,27 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>686797</t>
+          <t>686555</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Brooks Lee</t>
+          <t>Isaac Collins</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>2026-08-23T00:40:00Z</t>
+          <t>2026-08-22T23:15:00Z</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
@@ -62746,12 +62746,12 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>Casey Mize</t>
+          <t>Drew Anderson</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>663554</t>
+          <t>623454</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
@@ -62778,13 +62778,13 @@
         </is>
       </c>
       <c r="P228" t="n">
-        <v>18.6</v>
+        <v>23.8</v>
       </c>
       <c r="Q228" t="n">
-        <v>37.8</v>
+        <v>35.6</v>
       </c>
       <c r="R228" t="n">
-        <v>22.6</v>
+        <v>23.2</v>
       </c>
       <c r="S228" t="n">
         <v>47.9</v>
@@ -62793,7 +62793,7 @@
         <v>75</v>
       </c>
       <c r="U228" t="n">
-        <v>24.3</v>
+        <v>0</v>
       </c>
       <c r="V228" t="inlineStr">
         <is>
@@ -62832,7 +62832,7 @@
       </c>
       <c r="AC228" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD228" t="inlineStr"/>
@@ -62849,134 +62849,134 @@
       </c>
       <c r="AH228" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI228" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK228" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/25, 1 HR</t>
+          <t>Last 7 games: 2/18, 0 HR</t>
         </is>
       </c>
       <c r="AL228" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.2% barrel, 11.2 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.3% barrel, 11.0 HR allowed</t>
         </is>
       </c>
       <c r="AM228" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN228" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>5.53</t>
         </is>
       </c>
       <c r="AO228" t="inlineStr">
         <is>
-          <t>34.23</t>
+          <t>39.81</t>
         </is>
       </c>
       <c r="AP228" t="inlineStr">
         <is>
-          <t>88.04</t>
+          <t>88.73</t>
         </is>
       </c>
       <c r="AQ228" t="inlineStr">
         <is>
-          <t>97.4526</t>
+          <t>99.9594</t>
         </is>
       </c>
       <c r="AR228" t="inlineStr">
         <is>
-          <t>0.3432</t>
+          <t>0.3331</t>
         </is>
       </c>
       <c r="AS228" t="inlineStr">
         <is>
-          <t>0.1162</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AT228" t="inlineStr">
         <is>
-          <t>0.2764</t>
+          <t>0.3073</t>
         </is>
       </c>
       <c r="AU228" t="inlineStr">
         <is>
-          <t>69.92</t>
+          <t>73.33</t>
         </is>
       </c>
       <c r="AV228" t="inlineStr">
         <is>
-          <t>8.21</t>
+          <t>30.41</t>
         </is>
       </c>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>39.98</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="AZ228" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>0.1291</t>
         </is>
       </c>
       <c r="BA228" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="BB228" t="inlineStr">
         <is>
-          <t>38.58</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="BC228" t="inlineStr">
         <is>
-          <t>89.16</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="BD228" t="inlineStr">
         <is>
-          <t>0.3763</t>
+          <t>0.354</t>
         </is>
       </c>
       <c r="BE228" t="inlineStr">
         <is>
-          <t>0.1455</t>
+          <t>0.137</t>
         </is>
       </c>
       <c r="BF228" t="inlineStr">
         <is>
-          <t>30.46</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="BG228" t="inlineStr"/>
       <c r="BH228" t="inlineStr"/>
       <c r="BI228" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ228" t="inlineStr"/>
@@ -62987,12 +62987,12 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>701785</t>
+          <t>686797</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Kaelen Culpepper</t>
+          <t>Brooks Lee</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -63017,7 +63017,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -63036,7 +63036,7 @@
         </is>
       </c>
       <c r="L229" t="n">
-        <v>33.2</v>
+        <v>33.3</v>
       </c>
       <c r="M229" t="inlineStr">
         <is>
@@ -63050,26 +63050,26 @@
       </c>
       <c r="O229" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P229" t="n">
-        <v>26</v>
+        <v>18.6</v>
       </c>
       <c r="Q229" t="n">
-        <v>39</v>
+        <v>37.8</v>
       </c>
       <c r="R229" t="n">
         <v>22.6</v>
       </c>
       <c r="S229" t="n">
-        <v>40.2</v>
+        <v>47.9</v>
       </c>
       <c r="T229" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U229" t="n">
-        <v>36</v>
+        <v>24.3</v>
       </c>
       <c r="V229" t="inlineStr">
         <is>
@@ -63083,7 +63083,7 @@
       </c>
       <c r="X229" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y229" t="inlineStr">
@@ -63108,7 +63108,7 @@
       </c>
       <c r="AC229" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD229" t="inlineStr"/>
@@ -63125,7 +63125,7 @@
       </c>
       <c r="AH229" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI229" t="inlineStr">
@@ -63135,17 +63135,17 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
         <is>
-          <t>Contact streak: 9/25 over last 7 games</t>
+          <t>Last 7 games: 4/25, 1 HR</t>
         </is>
       </c>
       <c r="AL229" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.2% barrel, 11.2 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.2% barrel, 11.2 HR allowed</t>
         </is>
       </c>
       <c r="AM229" t="inlineStr">
@@ -63155,67 +63155,67 @@
       </c>
       <c r="AN229" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="AO229" t="inlineStr">
         <is>
-          <t>42.3</t>
+          <t>34.23</t>
         </is>
       </c>
       <c r="AP229" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>88.04</t>
         </is>
       </c>
       <c r="AQ229" t="inlineStr">
         <is>
-          <t>98.8632</t>
+          <t>97.4526</t>
         </is>
       </c>
       <c r="AR229" t="inlineStr">
         <is>
-          <t>0.365</t>
+          <t>0.3432</t>
         </is>
       </c>
       <c r="AS229" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>0.1162</t>
         </is>
       </c>
       <c r="AT229" t="inlineStr">
         <is>
-          <t>0.303</t>
+          <t>0.2764</t>
         </is>
       </c>
       <c r="AU229" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>69.92</t>
         </is>
       </c>
       <c r="AV229" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>8.21</t>
         </is>
       </c>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="AZ229" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>0.162</t>
         </is>
       </c>
       <c r="BA229" t="inlineStr">
@@ -63263,24 +63263,24 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>650859</t>
+          <t>701785</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Luis Rengifo</t>
+          <t>Kaelen Culpepper</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="E230" t="inlineStr">
-        <is>
-          <t>MIN</t>
-        </is>
-      </c>
       <c r="F230" t="inlineStr">
         <is>
           <t>2026-08-23T00:40:00Z</t>
@@ -63298,12 +63298,12 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>Dean Kremer</t>
+          <t>Casey Mize</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>665152</t>
+          <t>663554</t>
         </is>
       </c>
       <c r="K230" t="inlineStr">
@@ -63312,7 +63312,7 @@
         </is>
       </c>
       <c r="L230" t="n">
-        <v>33.1</v>
+        <v>33.2</v>
       </c>
       <c r="M230" t="inlineStr">
         <is>
@@ -63326,14 +63326,14 @@
       </c>
       <c r="O230" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P230" t="n">
-        <v>16.3</v>
+        <v>26</v>
       </c>
       <c r="Q230" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="R230" t="n">
         <v>22.6</v>
@@ -63342,10 +63342,10 @@
         <v>40.2</v>
       </c>
       <c r="T230" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U230" t="n">
-        <v>46.5</v>
+        <v>36</v>
       </c>
       <c r="V230" t="inlineStr">
         <is>
@@ -63384,7 +63384,7 @@
       </c>
       <c r="AC230" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD230" t="inlineStr"/>
@@ -63401,27 +63401,27 @@
       </c>
       <c r="AH230" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI230" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ230" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK230" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/26, 1 HR</t>
+          <t>Contact streak: 9/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL230" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 7.8% barrel, 15.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.2% barrel, 11.2 HR allowed</t>
         </is>
       </c>
       <c r="AM230" t="inlineStr">
@@ -63431,97 +63431,97 @@
       </c>
       <c r="AN230" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AO230" t="inlineStr">
         <is>
-          <t>33.61</t>
+          <t>42.3</t>
         </is>
       </c>
       <c r="AP230" t="inlineStr">
         <is>
-          <t>87.52</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="AQ230" t="inlineStr">
         <is>
-          <t>97.8176</t>
+          <t>98.8632</t>
         </is>
       </c>
       <c r="AR230" t="inlineStr">
         <is>
-          <t>0.3568</t>
+          <t>0.365</t>
         </is>
       </c>
       <c r="AS230" t="inlineStr">
         <is>
-          <t>0.1003</t>
+          <t>0.114</t>
         </is>
       </c>
       <c r="AT230" t="inlineStr">
         <is>
-          <t>0.3062</t>
+          <t>0.303</t>
         </is>
       </c>
       <c r="AU230" t="inlineStr">
         <is>
-          <t>70.76</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AV230" t="inlineStr">
         <is>
-          <t>14.23</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>18.01</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ230" t="inlineStr">
         <is>
-          <t>0.0837</t>
+          <t>0.106</t>
         </is>
       </c>
       <c r="BA230" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="BB230" t="inlineStr">
         <is>
-          <t>34.4</t>
+          <t>38.58</t>
         </is>
       </c>
       <c r="BC230" t="inlineStr">
         <is>
-          <t>87.33</t>
+          <t>89.16</t>
         </is>
       </c>
       <c r="BD230" t="inlineStr">
         <is>
-          <t>0.4319</t>
+          <t>0.3763</t>
         </is>
       </c>
       <c r="BE230" t="inlineStr">
         <is>
-          <t>0.1953</t>
+          <t>0.1455</t>
         </is>
       </c>
       <c r="BF230" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>30.46</t>
         </is>
       </c>
       <c r="BG230" t="inlineStr"/>
@@ -63539,27 +63539,27 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>699302</t>
+          <t>650859</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Hector Rodriguez</t>
+          <t>Luis Rengifo</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>2026-08-23T00:10:00Z</t>
+          <t>2026-08-23T00:40:00Z</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
@@ -63569,17 +63569,17 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>Michael Soroka</t>
+          <t>Dean Kremer</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>647336</t>
+          <t>665152</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
@@ -63588,7 +63588,7 @@
         </is>
       </c>
       <c r="L231" t="n">
-        <v>32.4</v>
+        <v>33.1</v>
       </c>
       <c r="M231" t="inlineStr">
         <is>
@@ -63606,22 +63606,22 @@
         </is>
       </c>
       <c r="P231" t="n">
-        <v>13.7</v>
+        <v>16.3</v>
       </c>
       <c r="Q231" t="n">
-        <v>33.7</v>
+        <v>40</v>
       </c>
       <c r="R231" t="n">
-        <v>28.2</v>
+        <v>22.6</v>
       </c>
       <c r="S231" t="n">
-        <v>59.8</v>
+        <v>40.2</v>
       </c>
       <c r="T231" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U231" t="n">
-        <v>0</v>
+        <v>46.5</v>
       </c>
       <c r="V231" t="inlineStr">
         <is>
@@ -63635,7 +63635,7 @@
       </c>
       <c r="X231" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y231" t="inlineStr">
@@ -63660,7 +63660,7 @@
       </c>
       <c r="AC231" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD231" t="inlineStr"/>
@@ -63677,134 +63677,134 @@
       </c>
       <c r="AH231" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI231" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Last 7 games: 8/26, 1 HR</t>
         </is>
       </c>
       <c r="AL231" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.6% barrel, 7.8 HR allowed</t>
+          <t>switch hitter; pitcher baseline 7.8% barrel, 15.7 HR allowed</t>
         </is>
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN231" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="AO231" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>33.61</t>
         </is>
       </c>
       <c r="AP231" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.52</t>
         </is>
       </c>
       <c r="AQ231" t="inlineStr">
         <is>
-          <t>97.0729</t>
+          <t>97.8176</t>
         </is>
       </c>
       <c r="AR231" t="inlineStr">
         <is>
-          <t>0.194</t>
+          <t>0.3568</t>
         </is>
       </c>
       <c r="AS231" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>0.1003</t>
         </is>
       </c>
       <c r="AT231" t="inlineStr">
         <is>
-          <t>0.198</t>
+          <t>0.3062</t>
         </is>
       </c>
       <c r="AU231" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>70.76</t>
         </is>
       </c>
       <c r="AV231" t="inlineStr">
         <is>
-          <t>51.6</t>
+          <t>14.23</t>
         </is>
       </c>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>18.01</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>0.0837</t>
         </is>
       </c>
       <c r="BA231" t="inlineStr">
         <is>
-          <t>7.61</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="BB231" t="inlineStr">
         <is>
-          <t>34.94</t>
+          <t>34.4</t>
         </is>
       </c>
       <c r="BC231" t="inlineStr">
         <is>
-          <t>88.08</t>
+          <t>87.33</t>
         </is>
       </c>
       <c r="BD231" t="inlineStr">
         <is>
-          <t>0.3902</t>
+          <t>0.4319</t>
         </is>
       </c>
       <c r="BE231" t="inlineStr">
         <is>
-          <t>0.1497</t>
+          <t>0.1953</t>
         </is>
       </c>
       <c r="BF231" t="inlineStr">
         <is>
-          <t>28.36</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BG231" t="inlineStr"/>
       <c r="BH231" t="inlineStr"/>
       <c r="BI231" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ231" t="inlineStr"/>
@@ -63815,27 +63815,27 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>807712</t>
+          <t>699302</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Luke Keaschall</t>
+          <t>Hector Rodriguez</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>2026-08-23T00:40:00Z</t>
+          <t>2026-08-23T00:10:00Z</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
@@ -63850,12 +63850,12 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>Casey Mize</t>
+          <t>Michael Soroka</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>663554</t>
+          <t>647336</t>
         </is>
       </c>
       <c r="K232" t="inlineStr">
@@ -63878,26 +63878,26 @@
       </c>
       <c r="O232" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P232" t="n">
-        <v>11.6</v>
+        <v>13.7</v>
       </c>
       <c r="Q232" t="n">
-        <v>39</v>
+        <v>33.7</v>
       </c>
       <c r="R232" t="n">
-        <v>22.6</v>
+        <v>28.2</v>
       </c>
       <c r="S232" t="n">
         <v>59.8</v>
       </c>
       <c r="T232" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U232" t="n">
-        <v>59.3</v>
+        <v>0</v>
       </c>
       <c r="V232" t="inlineStr">
         <is>
@@ -63936,7 +63936,7 @@
       </c>
       <c r="AC232" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD232" t="inlineStr"/>
@@ -63953,134 +63953,134 @@
       </c>
       <c r="AH232" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI232" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK232" t="inlineStr">
         <is>
-          <t>Contact streak: 11/28 over last 7 games</t>
+          <t>Last 7 games: 2/21, 0 HR</t>
         </is>
       </c>
       <c r="AL232" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.2% barrel, 11.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.6% barrel, 7.8 HR allowed</t>
         </is>
       </c>
       <c r="AM232" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN232" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AO232" t="inlineStr">
         <is>
-          <t>29.94</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="AP232" t="inlineStr">
         <is>
-          <t>85.36</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AQ232" t="inlineStr">
         <is>
-          <t>96.7655</t>
+          <t>97.0729</t>
         </is>
       </c>
       <c r="AR232" t="inlineStr">
         <is>
-          <t>0.3591</t>
+          <t>0.194</t>
         </is>
       </c>
       <c r="AS232" t="inlineStr">
         <is>
-          <t>0.1111</t>
+          <t>0.037</t>
         </is>
       </c>
       <c r="AT232" t="inlineStr">
         <is>
-          <t>0.3149</t>
+          <t>0.198</t>
         </is>
       </c>
       <c r="AU232" t="inlineStr">
         <is>
-          <t>68.64</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AV232" t="inlineStr">
         <is>
-          <t>7.59</t>
+          <t>51.6</t>
         </is>
       </c>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>26.97</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ232" t="inlineStr">
         <is>
-          <t>0.115</t>
+          <t>0.029</t>
         </is>
       </c>
       <c r="BA232" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>7.61</t>
         </is>
       </c>
       <c r="BB232" t="inlineStr">
         <is>
-          <t>38.58</t>
+          <t>34.94</t>
         </is>
       </c>
       <c r="BC232" t="inlineStr">
         <is>
-          <t>89.16</t>
+          <t>88.08</t>
         </is>
       </c>
       <c r="BD232" t="inlineStr">
         <is>
-          <t>0.3763</t>
+          <t>0.3902</t>
         </is>
       </c>
       <c r="BE232" t="inlineStr">
         <is>
-          <t>0.1455</t>
+          <t>0.1497</t>
         </is>
       </c>
       <c r="BF232" t="inlineStr">
         <is>
-          <t>30.46</t>
+          <t>28.36</t>
         </is>
       </c>
       <c r="BG232" t="inlineStr"/>
       <c r="BH232" t="inlineStr"/>
       <c r="BI232" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BJ232" t="inlineStr"/>
@@ -64091,27 +64091,27 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>641680</t>
+          <t>807712</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Jonah Heim</t>
+          <t>Luke Keaschall</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>2026-08-22T23:10:00Z</t>
+          <t>2026-08-23T00:40:00Z</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
@@ -64126,12 +64126,12 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>Hunter Brown</t>
+          <t>Casey Mize</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>686613</t>
+          <t>663554</t>
         </is>
       </c>
       <c r="K233" t="inlineStr">
@@ -64140,7 +64140,7 @@
         </is>
       </c>
       <c r="L233" t="n">
-        <v>32.3</v>
+        <v>32.4</v>
       </c>
       <c r="M233" t="inlineStr">
         <is>
@@ -64154,26 +64154,26 @@
       </c>
       <c r="O233" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P233" t="n">
-        <v>24</v>
+        <v>11.6</v>
       </c>
       <c r="Q233" t="n">
-        <v>21.5</v>
+        <v>39</v>
       </c>
       <c r="R233" t="n">
-        <v>27.6</v>
+        <v>22.6</v>
       </c>
       <c r="S233" t="n">
         <v>59.8</v>
       </c>
       <c r="T233" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U233" t="n">
-        <v>0</v>
+        <v>59.3</v>
       </c>
       <c r="V233" t="inlineStr">
         <is>
@@ -64229,134 +64229,134 @@
       </c>
       <c r="AH233" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AI233" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AJ233" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AI233" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AJ233" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK233" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/19, 0 HR</t>
+          <t>Contact streak: 11/28 over last 7 games</t>
         </is>
       </c>
       <c r="AL233" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.2% barrel, 11.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.2% barrel, 11.2 HR allowed</t>
         </is>
       </c>
       <c r="AM233" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN233" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="AO233" t="inlineStr">
         <is>
-          <t>33.24</t>
+          <t>29.94</t>
         </is>
       </c>
       <c r="AP233" t="inlineStr">
         <is>
-          <t>87.82</t>
+          <t>85.36</t>
         </is>
       </c>
       <c r="AQ233" t="inlineStr">
         <is>
-          <t>97.8947</t>
+          <t>96.7655</t>
         </is>
       </c>
       <c r="AR233" t="inlineStr">
         <is>
-          <t>0.3684</t>
+          <t>0.3591</t>
         </is>
       </c>
       <c r="AS233" t="inlineStr">
         <is>
-          <t>0.1403</t>
+          <t>0.1111</t>
         </is>
       </c>
       <c r="AT233" t="inlineStr">
         <is>
-          <t>0.2914</t>
+          <t>0.3149</t>
         </is>
       </c>
       <c r="AU233" t="inlineStr">
         <is>
-          <t>69.84</t>
+          <t>68.64</t>
         </is>
       </c>
       <c r="AV233" t="inlineStr">
         <is>
-          <t>9.45</t>
+          <t>7.59</t>
         </is>
       </c>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>40.49</t>
+          <t>38.26</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>28.39</t>
+          <t>26.97</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="AZ233" t="inlineStr">
         <is>
-          <t>0.1603</t>
+          <t>0.115</t>
         </is>
       </c>
       <c r="BA233" t="inlineStr">
         <is>
-          <t>6.18</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="BB233" t="inlineStr">
         <is>
-          <t>35.63</t>
+          <t>38.58</t>
         </is>
       </c>
       <c r="BC233" t="inlineStr">
         <is>
-          <t>85.96</t>
+          <t>89.16</t>
         </is>
       </c>
       <c r="BD233" t="inlineStr">
         <is>
-          <t>0.3397</t>
+          <t>0.3763</t>
         </is>
       </c>
       <c r="BE233" t="inlineStr">
         <is>
-          <t>0.1304</t>
+          <t>0.1455</t>
         </is>
       </c>
       <c r="BF233" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>30.46</t>
         </is>
       </c>
       <c r="BG233" t="inlineStr"/>
       <c r="BH233" t="inlineStr"/>
       <c r="BI233" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ233" t="inlineStr"/>
@@ -64367,27 +64367,27 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>703601</t>
+          <t>641680</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Max Clark</t>
+          <t>Jonah Heim</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>2026-08-22T23:15:00Z</t>
+          <t>2026-08-22T23:10:00Z</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
@@ -64397,17 +64397,17 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>Michael Wacha</t>
+          <t>Hunter Brown</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>608379</t>
+          <t>686613</t>
         </is>
       </c>
       <c r="K234" t="inlineStr">
@@ -64416,7 +64416,7 @@
         </is>
       </c>
       <c r="L234" t="n">
-        <v>32.2</v>
+        <v>32.3</v>
       </c>
       <c r="M234" t="inlineStr">
         <is>
@@ -64434,22 +64434,22 @@
         </is>
       </c>
       <c r="P234" t="n">
-        <v>13.5</v>
+        <v>24</v>
       </c>
       <c r="Q234" t="n">
-        <v>39.3</v>
+        <v>21.5</v>
       </c>
       <c r="R234" t="n">
-        <v>23.2</v>
+        <v>27.6</v>
       </c>
       <c r="S234" t="n">
-        <v>47.9</v>
+        <v>59.8</v>
       </c>
       <c r="T234" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U234" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="V234" t="inlineStr">
         <is>
@@ -64463,7 +64463,7 @@
       </c>
       <c r="X234" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y234" t="inlineStr">
@@ -64488,7 +64488,7 @@
       </c>
       <c r="AC234" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD234" t="inlineStr"/>
@@ -64505,12 +64505,12 @@
       </c>
       <c r="AH234" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI234" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ234" t="inlineStr">
@@ -64520,12 +64520,12 @@
       </c>
       <c r="AK234" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 0 HR</t>
+          <t>Last 7 games: 1/19, 0 HR</t>
         </is>
       </c>
       <c r="AL234" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.2% barrel, 19.2 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.2% barrel, 11.4 HR allowed</t>
         </is>
       </c>
       <c r="AM234" t="inlineStr">
@@ -64535,104 +64535,104 @@
       </c>
       <c r="AN234" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>6.66</t>
         </is>
       </c>
       <c r="AO234" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>33.24</t>
         </is>
       </c>
       <c r="AP234" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>87.82</t>
         </is>
       </c>
       <c r="AQ234" t="inlineStr">
         <is>
-          <t>97.4351</t>
+          <t>97.8947</t>
         </is>
       </c>
       <c r="AR234" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.3684</t>
         </is>
       </c>
       <c r="AS234" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>0.1403</t>
         </is>
       </c>
       <c r="AT234" t="inlineStr">
         <is>
-          <t>0.301</t>
+          <t>0.2914</t>
         </is>
       </c>
       <c r="AU234" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>69.84</t>
         </is>
       </c>
       <c r="AV234" t="inlineStr">
         <is>
-          <t>26.9</t>
+          <t>9.45</t>
         </is>
       </c>
       <c r="AW234" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>40.49</t>
         </is>
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>28.39</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="AZ234" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>0.1603</t>
         </is>
       </c>
       <c r="BA234" t="inlineStr">
         <is>
-          <t>7.19</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="BB234" t="inlineStr">
         <is>
-          <t>36.35</t>
+          <t>35.63</t>
         </is>
       </c>
       <c r="BC234" t="inlineStr">
         <is>
-          <t>88.34</t>
+          <t>85.96</t>
         </is>
       </c>
       <c r="BD234" t="inlineStr">
         <is>
-          <t>0.4182</t>
+          <t>0.3397</t>
         </is>
       </c>
       <c r="BE234" t="inlineStr">
         <is>
-          <t>0.1661</t>
+          <t>0.1304</t>
         </is>
       </c>
       <c r="BF234" t="inlineStr">
         <is>
-          <t>28.88</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="BG234" t="inlineStr"/>
       <c r="BH234" t="inlineStr"/>
       <c r="BI234" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ234" t="inlineStr"/>
@@ -64643,27 +64643,27 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>643289</t>
+          <t>703601</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Mauricio Dubon</t>
+          <t>Max Clark</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>2026-08-22T18:10:00Z</t>
+          <t>2026-08-22T23:15:00Z</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
@@ -64673,17 +64673,17 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>Logan Henderson</t>
+          <t>Michael Wacha</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>701656</t>
+          <t>608379</t>
         </is>
       </c>
       <c r="K235" t="inlineStr">
@@ -64692,7 +64692,7 @@
         </is>
       </c>
       <c r="L235" t="n">
-        <v>32.1</v>
+        <v>32.2</v>
       </c>
       <c r="M235" t="inlineStr">
         <is>
@@ -64706,26 +64706,26 @@
       </c>
       <c r="O235" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P235" t="n">
-        <v>11.1</v>
+        <v>13.5</v>
       </c>
       <c r="Q235" t="n">
-        <v>35</v>
+        <v>39.3</v>
       </c>
       <c r="R235" t="n">
-        <v>27.6</v>
+        <v>23.2</v>
       </c>
       <c r="S235" t="n">
-        <v>71.7</v>
+        <v>47.9</v>
       </c>
       <c r="T235" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U235" t="n">
-        <v>27.7</v>
+        <v>19.5</v>
       </c>
       <c r="V235" t="inlineStr">
         <is>
@@ -64739,7 +64739,7 @@
       </c>
       <c r="X235" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y235" t="inlineStr">
@@ -64764,7 +64764,7 @@
       </c>
       <c r="AC235" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD235" t="inlineStr"/>
@@ -64781,12 +64781,12 @@
       </c>
       <c r="AH235" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI235" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ235" t="inlineStr">
@@ -64796,12 +64796,12 @@
       </c>
       <c r="AK235" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/23, 0 HR</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AL235" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.6% barrel, 7.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.2% barrel, 19.2 HR allowed</t>
         </is>
       </c>
       <c r="AM235" t="inlineStr">
@@ -64811,104 +64811,104 @@
       </c>
       <c r="AN235" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="AO235" t="inlineStr">
         <is>
-          <t>29.31</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="AP235" t="inlineStr">
         <is>
-          <t>86.18</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AQ235" t="inlineStr">
         <is>
-          <t>96.3935</t>
+          <t>97.4351</t>
         </is>
       </c>
       <c r="AR235" t="inlineStr">
         <is>
-          <t>0.3667</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AS235" t="inlineStr">
         <is>
-          <t>0.1036</t>
+          <t>0.079</t>
         </is>
       </c>
       <c r="AT235" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>0.301</t>
         </is>
       </c>
       <c r="AU235" t="inlineStr">
         <is>
-          <t>68.73</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AV235" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>26.9</t>
         </is>
       </c>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>32.17</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>25.09</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ235" t="inlineStr">
         <is>
-          <t>0.1217</t>
+          <t>0.137</t>
         </is>
       </c>
       <c r="BA235" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>7.19</t>
         </is>
       </c>
       <c r="BB235" t="inlineStr">
         <is>
-          <t>36.09</t>
+          <t>36.35</t>
         </is>
       </c>
       <c r="BC235" t="inlineStr">
         <is>
-          <t>88.38</t>
+          <t>88.34</t>
         </is>
       </c>
       <c r="BD235" t="inlineStr">
         <is>
-          <t>0.352</t>
+          <t>0.4182</t>
         </is>
       </c>
       <c r="BE235" t="inlineStr">
         <is>
-          <t>0.1393</t>
+          <t>0.1661</t>
         </is>
       </c>
       <c r="BF235" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>28.88</t>
         </is>
       </c>
       <c r="BG235" t="inlineStr"/>
       <c r="BH235" t="inlineStr"/>
       <c r="BI235" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ235" t="inlineStr"/>
@@ -64919,27 +64919,27 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>673237</t>
+          <t>643289</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Yainer Diaz</t>
+          <t>Mauricio Dubon</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>2026-08-22T23:10:00Z</t>
+          <t>2026-08-22T18:10:00Z</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
@@ -64949,22 +64949,22 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>Jacob Lopez</t>
+          <t>Logan Henderson</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>682052</t>
+          <t>701656</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L236" t="n">
@@ -64982,26 +64982,26 @@
       </c>
       <c r="O236" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P236" t="n">
-        <v>27.9</v>
+        <v>11.1</v>
       </c>
       <c r="Q236" t="n">
-        <v>21.9</v>
+        <v>35</v>
       </c>
       <c r="R236" t="n">
         <v>27.6</v>
       </c>
       <c r="S236" t="n">
-        <v>40.2</v>
+        <v>71.7</v>
       </c>
       <c r="T236" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U236" t="n">
-        <v>17.3</v>
+        <v>27.7</v>
       </c>
       <c r="V236" t="inlineStr">
         <is>
@@ -65015,7 +65015,7 @@
       </c>
       <c r="X236" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y236" t="inlineStr">
@@ -65057,12 +65057,12 @@
       </c>
       <c r="AH236" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI236" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ236" t="inlineStr">
@@ -65072,119 +65072,119 @@
       </c>
       <c r="AK236" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/17, 0 HR</t>
+          <t>Last 7 games: 7/23, 0 HR</t>
         </is>
       </c>
       <c r="AL236" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.7% barrel, 15.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.6% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AM236" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN236" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AO236" t="inlineStr">
         <is>
-          <t>37.02</t>
+          <t>29.31</t>
         </is>
       </c>
       <c r="AP236" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>86.18</t>
         </is>
       </c>
       <c r="AQ236" t="inlineStr">
         <is>
-          <t>99.4468</t>
+          <t>96.3935</t>
         </is>
       </c>
       <c r="AR236" t="inlineStr">
         <is>
-          <t>0.4195</t>
+          <t>0.3667</t>
         </is>
       </c>
       <c r="AS236" t="inlineStr">
         <is>
-          <t>0.1501</t>
+          <t>0.1036</t>
         </is>
       </c>
       <c r="AT236" t="inlineStr">
         <is>
-          <t>0.3113</t>
+          <t>0.299</t>
         </is>
       </c>
       <c r="AU236" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>68.73</t>
         </is>
       </c>
       <c r="AV236" t="inlineStr">
         <is>
-          <t>21.39</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>36.42</t>
+          <t>32.17</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>19.03</t>
+          <t>25.09</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="AZ236" t="inlineStr">
         <is>
-          <t>0.1449</t>
+          <t>0.1217</t>
         </is>
       </c>
       <c r="BA236" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="BB236" t="inlineStr">
         <is>
-          <t>30.19</t>
+          <t>36.09</t>
         </is>
       </c>
       <c r="BC236" t="inlineStr">
         <is>
-          <t>85.29</t>
+          <t>88.38</t>
         </is>
       </c>
       <c r="BD236" t="inlineStr">
         <is>
-          <t>0.3424</t>
+          <t>0.352</t>
         </is>
       </c>
       <c r="BE236" t="inlineStr">
         <is>
-          <t>0.1338</t>
+          <t>0.1393</t>
         </is>
       </c>
       <c r="BF236" t="inlineStr">
         <is>
-          <t>32.48</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BG236" t="inlineStr"/>
       <c r="BH236" t="inlineStr"/>
       <c r="BI236" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ236" t="inlineStr"/>
@@ -65195,27 +65195,27 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>678011</t>
+          <t>673237</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Anthony Seigler</t>
+          <t>Yainer Diaz</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>2026-08-22T23:15:00Z</t>
+          <t>2026-08-22T23:10:00Z</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
@@ -65230,17 +65230,17 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>Blade Tidwell</t>
+          <t>Jacob Lopez</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>694918</t>
+          <t>682052</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L237" t="n">
@@ -65262,22 +65262,22 @@
         </is>
       </c>
       <c r="P237" t="n">
-        <v>20.2</v>
+        <v>27.9</v>
       </c>
       <c r="Q237" t="n">
-        <v>25.9</v>
+        <v>21.9</v>
       </c>
       <c r="R237" t="n">
-        <v>28.7</v>
+        <v>27.6</v>
       </c>
       <c r="S237" t="n">
         <v>40.2</v>
       </c>
       <c r="T237" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="U237" t="n">
-        <v>50</v>
+        <v>17.3</v>
       </c>
       <c r="V237" t="inlineStr">
         <is>
@@ -65328,139 +65328,139 @@
       </c>
       <c r="AG237" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AH237" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI237" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AJ237" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AH237" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI237" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ237" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK237" t="inlineStr">
         <is>
-          <t>Recent form unavailable</t>
+          <t>Last 7 games: 4/17, 0 HR</t>
         </is>
       </c>
       <c r="AL237" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.5% barrel, 2.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.7% barrel, 15.0 HR allowed</t>
         </is>
       </c>
       <c r="AM237" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN237" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AO237" t="inlineStr">
         <is>
-          <t>36.38</t>
+          <t>37.02</t>
         </is>
       </c>
       <c r="AP237" t="inlineStr">
         <is>
-          <t>88.11</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AQ237" t="inlineStr">
         <is>
-          <t>97.283</t>
+          <t>99.4468</t>
         </is>
       </c>
       <c r="AR237" t="inlineStr">
         <is>
-          <t>0.3677</t>
+          <t>0.4195</t>
         </is>
       </c>
       <c r="AS237" t="inlineStr">
         <is>
-          <t>0.1258</t>
+          <t>0.1501</t>
         </is>
       </c>
       <c r="AT237" t="inlineStr">
         <is>
-          <t>0.3079</t>
+          <t>0.3113</t>
         </is>
       </c>
       <c r="AU237" t="inlineStr">
         <is>
-          <t>67.08</t>
+          <t>72.41</t>
         </is>
       </c>
       <c r="AV237" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>21.39</t>
         </is>
       </c>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>33.93</t>
+          <t>36.42</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>27.8</t>
+          <t>19.03</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>11.6</t>
         </is>
       </c>
       <c r="AZ237" t="inlineStr">
         <is>
-          <t>0.1105</t>
+          <t>0.1449</t>
         </is>
       </c>
       <c r="BA237" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>5.69</t>
         </is>
       </c>
       <c r="BB237" t="inlineStr">
         <is>
-          <t>36.64</t>
+          <t>30.19</t>
         </is>
       </c>
       <c r="BC237" t="inlineStr">
         <is>
-          <t>87.78</t>
+          <t>85.29</t>
         </is>
       </c>
       <c r="BD237" t="inlineStr">
         <is>
-          <t>0.3849</t>
+          <t>0.3424</t>
         </is>
       </c>
       <c r="BE237" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>0.1338</t>
         </is>
       </c>
       <c r="BF237" t="inlineStr">
         <is>
-          <t>21.73</t>
+          <t>32.48</t>
         </is>
       </c>
       <c r="BG237" t="inlineStr"/>
       <c r="BH237" t="inlineStr"/>
       <c r="BI237" t="inlineStr">
         <is>
-          <t>Fenway Park</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ237" t="inlineStr"/>

--- a/outputs/daily/hr_rankings_2026-08-22_full.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-22_full.xlsx
@@ -1616,7 +1616,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>63.3</v>
+        <v>63.4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>35</v>
       </c>
       <c r="R5" t="n">
-        <v>67.09999999999999</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="S5" t="n">
         <v>96.59999999999999</v>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2214,34 +2214,30 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 2</t>
-        </is>
-      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -3248,7 +3244,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>59.6</v>
+        <v>59.7</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3272,7 +3268,7 @@
         <v>38</v>
       </c>
       <c r="R11" t="n">
-        <v>67.09999999999999</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="S11" t="n">
         <v>94.90000000000001</v>
@@ -3463,7 +3459,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4080,7 +4076,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>59</v>
+        <v>59.1</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4104,7 +4100,7 @@
         <v>35</v>
       </c>
       <c r="R14" t="n">
-        <v>67.09999999999999</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="S14" t="n">
         <v>93.2</v>
@@ -4295,7 +4291,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -4360,7 +4356,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>58.2</v>
+        <v>58.3</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4384,7 +4380,7 @@
         <v>38</v>
       </c>
       <c r="R15" t="n">
-        <v>67.09999999999999</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="S15" t="n">
         <v>93.2</v>
@@ -4575,7 +4571,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -4616,7 +4612,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -4850,7 +4846,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -5200,7 +5196,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>57.5</v>
+        <v>57.6</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5224,7 +5220,7 @@
         <v>35</v>
       </c>
       <c r="R18" t="n">
-        <v>67.09999999999999</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="S18" t="n">
         <v>100</v>
@@ -5415,7 +5411,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -5456,7 +5452,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -5690,7 +5686,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -5736,7 +5732,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -5802,34 +5798,30 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 4</t>
-        </is>
-      </c>
+      <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -5974,7 +5966,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -6020,7 +6012,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -6086,34 +6078,30 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 9</t>
-        </is>
-      </c>
+      <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6258,7 +6246,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -6880,7 +6868,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>55.9</v>
+        <v>56</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -6904,7 +6892,7 @@
         <v>35</v>
       </c>
       <c r="R24" t="n">
-        <v>67.09999999999999</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="S24" t="n">
         <v>94.90000000000001</v>
@@ -7095,7 +7083,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI24" t="inlineStr">
@@ -8292,7 +8280,7 @@
         <v>38</v>
       </c>
       <c r="R29" t="n">
-        <v>67.09999999999999</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="S29" t="n">
         <v>96.59999999999999</v>
@@ -8483,7 +8471,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI29" t="inlineStr">
@@ -9352,7 +9340,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -9416,28 +9404,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W33" t="inlineStr"/>
-      <c r="X33" t="inlineStr"/>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="Y33" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9582,7 +9574,7 @@
       </c>
       <c r="BG33" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH33" t="inlineStr">
@@ -11836,7 +11828,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -11902,34 +11894,30 @@
       </c>
       <c r="W42" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 3 vs RotoWire 2</t>
-        </is>
-      </c>
+      <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -12074,7 +12062,7 @@
       </c>
       <c r="BG42" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH42" t="inlineStr">
@@ -12184,28 +12172,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W43" t="inlineStr"/>
-      <c r="X43" t="inlineStr"/>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="Y43" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB43" t="inlineStr"/>
       <c r="AC43" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -13728,7 +13720,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -13794,34 +13786,30 @@
       </c>
       <c r="W49" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 3</t>
-        </is>
-      </c>
+      <c r="AB49" t="inlineStr"/>
       <c r="AC49" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -13966,7 +13954,7 @@
       </c>
       <c r="BG49" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH49" t="inlineStr">
@@ -14312,7 +14300,7 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>51.8</v>
+        <v>51.9</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
@@ -14336,7 +14324,7 @@
         <v>38</v>
       </c>
       <c r="R51" t="n">
-        <v>67.09999999999999</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="S51" t="n">
         <v>86.40000000000001</v>
@@ -14527,7 +14515,7 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI51" t="inlineStr">
@@ -15916,7 +15904,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -16150,7 +16138,7 @@
       </c>
       <c r="BG57" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH57" t="inlineStr">
@@ -17024,7 +17012,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -17258,7 +17246,7 @@
       </c>
       <c r="BG61" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH61" t="inlineStr">
@@ -17604,7 +17592,7 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>50.1</v>
+        <v>50.2</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
@@ -17628,7 +17616,7 @@
         <v>38</v>
       </c>
       <c r="R63" t="n">
-        <v>67.09999999999999</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="S63" t="n">
         <v>100</v>
@@ -17819,7 +17807,7 @@
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI63" t="inlineStr">
@@ -20875,52 +20863,52 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>605137</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Josh Bell</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-08-23T00:40:00Z</t>
+          <t>2026-08-22T18:10:00Z</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Casey Mize</t>
+          <t>Martín Pérez</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>663554</t>
+          <t>527048</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L75" t="n">
@@ -20938,62 +20926,58 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P75" t="n">
-        <v>45</v>
+        <v>39.4</v>
       </c>
       <c r="Q75" t="n">
-        <v>37.8</v>
+        <v>38</v>
       </c>
       <c r="R75" t="n">
-        <v>22.6</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="S75" t="n">
-        <v>90.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T75" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U75" t="n">
-        <v>44.1</v>
+        <v>29.2</v>
       </c>
       <c r="V75" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W75" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X75" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y75" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr"/>
       <c r="AC75" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -21013,12 +20997,12 @@
       </c>
       <c r="AH75" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ75" t="inlineStr">
@@ -21028,119 +21012,127 @@
       </c>
       <c r="AK75" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/24, 1 HR</t>
+          <t>Last 7 games: 5/26, 1 HR</t>
         </is>
       </c>
       <c r="AL75" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.2% barrel, 11.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.1% barrel, 9.5 HR allowed</t>
         </is>
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN75" t="inlineStr">
         <is>
-          <t>10.56</t>
+          <t>10.37</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>43.36</t>
+          <t>44.58</t>
         </is>
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>90.05</t>
+          <t>89.29</t>
         </is>
       </c>
       <c r="AQ75" t="inlineStr">
         <is>
-          <t>100.9179</t>
+          <t>101.0756</t>
         </is>
       </c>
       <c r="AR75" t="inlineStr">
         <is>
-          <t>0.4556</t>
+          <t>0.4033</t>
         </is>
       </c>
       <c r="AS75" t="inlineStr">
         <is>
-          <t>0.2031</t>
+          <t>0.1681</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr">
         <is>
-          <t>0.3387</t>
+          <t>0.3167</t>
         </is>
       </c>
       <c r="AU75" t="inlineStr">
         <is>
-          <t>72.33</t>
+          <t>73.09</t>
         </is>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>31.34</t>
         </is>
       </c>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>41.29</t>
+          <t>33.75</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>26.57</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>0.1751</t>
+          <t>0.1565</t>
         </is>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.14</t>
         </is>
       </c>
       <c r="BB75" t="inlineStr">
         <is>
-          <t>38.58</t>
+          <t>37.86</t>
         </is>
       </c>
       <c r="BC75" t="inlineStr">
         <is>
-          <t>89.16</t>
+          <t>88.13</t>
         </is>
       </c>
       <c r="BD75" t="inlineStr">
         <is>
-          <t>0.3763</t>
+          <t>0.4171</t>
         </is>
       </c>
       <c r="BE75" t="inlineStr">
         <is>
-          <t>0.1455</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="BF75" t="inlineStr">
         <is>
-          <t>30.46</t>
-        </is>
-      </c>
-      <c r="BG75" t="inlineStr"/>
-      <c r="BH75" t="inlineStr"/>
+          <t>24.2</t>
+        </is>
+      </c>
+      <c r="BG75" t="inlineStr">
+        <is>
+          <t>Out To CF</t>
+        </is>
+      </c>
+      <c r="BH75" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
       <c r="BI75" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ75" t="inlineStr"/>
@@ -21151,56 +21143,56 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>605137</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>Josh Bell</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-08-22T18:10:00Z</t>
+          <t>2026-08-23T00:40:00Z</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Martín Pérez</t>
+          <t>Casey Mize</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>527048</t>
+          <t>663554</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>48.8</v>
+        <v>48.9</v>
       </c>
       <c r="M76" t="inlineStr">
         <is>
@@ -21214,58 +21206,62 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P76" t="n">
-        <v>39.4</v>
+        <v>45</v>
       </c>
       <c r="Q76" t="n">
-        <v>38</v>
+        <v>37.8</v>
       </c>
       <c r="R76" t="n">
-        <v>67.09999999999999</v>
+        <v>22.6</v>
       </c>
       <c r="S76" t="n">
-        <v>76.2</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T76" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U76" t="n">
-        <v>29.2</v>
+        <v>44.1</v>
       </c>
       <c r="V76" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W76" t="inlineStr">
+      <c r="Z76" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X76" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y76" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC76" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -21285,12 +21281,12 @@
       </c>
       <c r="AH76" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ76" t="inlineStr">
@@ -21300,127 +21296,119 @@
       </c>
       <c r="AK76" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 1 HR</t>
+          <t>Last 7 games: 7/24, 1 HR</t>
         </is>
       </c>
       <c r="AL76" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.1% barrel, 9.5 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.2% barrel, 11.2 HR allowed</t>
         </is>
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN76" t="inlineStr">
         <is>
-          <t>10.37</t>
+          <t>10.56</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>44.58</t>
+          <t>43.36</t>
         </is>
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>89.29</t>
+          <t>90.05</t>
         </is>
       </c>
       <c r="AQ76" t="inlineStr">
         <is>
-          <t>101.0756</t>
+          <t>100.9179</t>
         </is>
       </c>
       <c r="AR76" t="inlineStr">
         <is>
-          <t>0.4033</t>
+          <t>0.4556</t>
         </is>
       </c>
       <c r="AS76" t="inlineStr">
         <is>
-          <t>0.1681</t>
+          <t>0.2031</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr">
         <is>
-          <t>0.3167</t>
+          <t>0.3387</t>
         </is>
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>73.09</t>
+          <t>72.33</t>
         </is>
       </c>
       <c r="AV76" t="inlineStr">
         <is>
-          <t>31.34</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>41.29</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>26.57</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>0.1565</t>
+          <t>0.1751</t>
         </is>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
-          <t>8.14</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="BB76" t="inlineStr">
         <is>
-          <t>37.86</t>
+          <t>38.58</t>
         </is>
       </c>
       <c r="BC76" t="inlineStr">
         <is>
-          <t>88.13</t>
+          <t>89.16</t>
         </is>
       </c>
       <c r="BD76" t="inlineStr">
         <is>
-          <t>0.4171</t>
+          <t>0.3763</t>
         </is>
       </c>
       <c r="BE76" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.1455</t>
         </is>
       </c>
       <c r="BF76" t="inlineStr">
         <is>
-          <t>24.2</t>
-        </is>
-      </c>
-      <c r="BG76" t="inlineStr">
-        <is>
-          <t>Out To CF</t>
-        </is>
-      </c>
-      <c r="BH76" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
+          <t>30.46</t>
+        </is>
+      </c>
+      <c r="BG76" t="inlineStr"/>
+      <c r="BH76" t="inlineStr"/>
       <c r="BI76" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ76" t="inlineStr"/>
@@ -21431,52 +21419,52 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>664040</t>
+          <t>573262</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Brandon Lowe</t>
+          <t>Mike Yastrzemski</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-08-22T23:15:00Z</t>
+          <t>2026-08-22T18:10:00Z</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Tarik Skubal</t>
+          <t>Logan Henderson</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>669373</t>
+          <t>701656</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L77" t="n">
@@ -21494,62 +21482,58 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P77" t="n">
-        <v>52.4</v>
+        <v>35.8</v>
       </c>
       <c r="Q77" t="n">
-        <v>28.8</v>
+        <v>35</v>
       </c>
       <c r="R77" t="n">
-        <v>27.6</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="S77" t="n">
-        <v>90.40000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="T77" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U77" t="n">
-        <v>66.90000000000001</v>
+        <v>44.5</v>
       </c>
       <c r="V77" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W77" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X77" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y77" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr"/>
       <c r="AC77" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -21569,27 +21553,27 @@
       </c>
       <c r="AH77" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/17, 1 HR</t>
         </is>
       </c>
       <c r="AL77" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.5% barrel, 13.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.6% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AM77" t="inlineStr">
@@ -21599,104 +21583,112 @@
       </c>
       <c r="AN77" t="inlineStr">
         <is>
-          <t>12.37</t>
+          <t>7.59</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>46.74</t>
+          <t>43.23</t>
         </is>
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>91.17</t>
+          <t>90.73</t>
         </is>
       </c>
       <c r="AQ77" t="inlineStr">
         <is>
-          <t>101.5242</t>
+          <t>99.7769</t>
         </is>
       </c>
       <c r="AR77" t="inlineStr">
         <is>
-          <t>0.4479</t>
+          <t>0.3861</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr">
         <is>
-          <t>0.203</t>
+          <t>0.1491</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr">
         <is>
-          <t>0.3287</t>
+          <t>0.3185</t>
         </is>
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>73.66</t>
+          <t>71.31</t>
         </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
-          <t>39.81</t>
+          <t>8.44</t>
         </is>
       </c>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>46.86</t>
+          <t>46.04</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>32.99</t>
+          <t>31.12</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
-          <t>28.2</t>
+          <t>11.4</t>
         </is>
       </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>0.2252</t>
+          <t>0.1623</t>
         </is>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
-          <t>7.54</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="BB77" t="inlineStr">
         <is>
-          <t>35.38</t>
+          <t>36.09</t>
         </is>
       </c>
       <c r="BC77" t="inlineStr">
         <is>
-          <t>86.94</t>
+          <t>88.38</t>
         </is>
       </c>
       <c r="BD77" t="inlineStr">
         <is>
-          <t>0.3433</t>
+          <t>0.352</t>
         </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
-          <t>0.1233</t>
+          <t>0.1393</t>
         </is>
       </c>
       <c r="BF77" t="inlineStr">
         <is>
-          <t>26.32</t>
-        </is>
-      </c>
-      <c r="BG77" t="inlineStr"/>
-      <c r="BH77" t="inlineStr"/>
+          <t>29.67</t>
+        </is>
+      </c>
+      <c r="BG77" t="inlineStr">
+        <is>
+          <t>Out To CF</t>
+        </is>
+      </c>
+      <c r="BH77" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
       <c r="BI77" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ77" t="inlineStr"/>
@@ -21707,56 +21699,56 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>573262</t>
+          <t>664040</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Mike Yastrzemski</t>
+          <t>Brandon Lowe</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-22T18:10:00Z</t>
+          <t>2026-08-22T23:15:00Z</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Logan Henderson</t>
+          <t>Tarik Skubal</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>701656</t>
+          <t>669373</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
@@ -21770,58 +21762,62 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P78" t="n">
-        <v>35.8</v>
+        <v>52.4</v>
       </c>
       <c r="Q78" t="n">
-        <v>35</v>
+        <v>28.8</v>
       </c>
       <c r="R78" t="n">
-        <v>67.09999999999999</v>
+        <v>27.6</v>
       </c>
       <c r="S78" t="n">
-        <v>64.3</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T78" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U78" t="n">
-        <v>44.5</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="V78" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W78" t="inlineStr">
+      <c r="Z78" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X78" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y78" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC78" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -21841,27 +21837,27 @@
       </c>
       <c r="AH78" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/17, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL78" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.6% barrel, 7.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.5% barrel, 13.8 HR allowed</t>
         </is>
       </c>
       <c r="AM78" t="inlineStr">
@@ -21871,112 +21867,104 @@
       </c>
       <c r="AN78" t="inlineStr">
         <is>
-          <t>7.59</t>
+          <t>12.37</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>43.23</t>
+          <t>46.74</t>
         </is>
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>90.73</t>
+          <t>91.17</t>
         </is>
       </c>
       <c r="AQ78" t="inlineStr">
         <is>
-          <t>99.7769</t>
+          <t>101.5242</t>
         </is>
       </c>
       <c r="AR78" t="inlineStr">
         <is>
-          <t>0.3861</t>
+          <t>0.4479</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr">
         <is>
-          <t>0.1491</t>
+          <t>0.203</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr">
         <is>
-          <t>0.3185</t>
+          <t>0.3287</t>
         </is>
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>71.31</t>
+          <t>73.66</t>
         </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
-          <t>8.44</t>
+          <t>39.81</t>
         </is>
       </c>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>46.04</t>
+          <t>46.86</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>31.12</t>
+          <t>32.99</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
-          <t>11.4</t>
+          <t>28.2</t>
         </is>
       </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>0.1623</t>
+          <t>0.2252</t>
         </is>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>7.54</t>
         </is>
       </c>
       <c r="BB78" t="inlineStr">
         <is>
-          <t>36.09</t>
+          <t>35.38</t>
         </is>
       </c>
       <c r="BC78" t="inlineStr">
         <is>
-          <t>88.38</t>
+          <t>86.94</t>
         </is>
       </c>
       <c r="BD78" t="inlineStr">
         <is>
-          <t>0.352</t>
+          <t>0.3433</t>
         </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
-          <t>0.1393</t>
+          <t>0.1233</t>
         </is>
       </c>
       <c r="BF78" t="inlineStr">
         <is>
-          <t>29.67</t>
-        </is>
-      </c>
-      <c r="BG78" t="inlineStr">
-        <is>
-          <t>Out To CF</t>
-        </is>
-      </c>
-      <c r="BH78" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
+          <t>26.32</t>
+        </is>
+      </c>
+      <c r="BG78" t="inlineStr"/>
+      <c r="BH78" t="inlineStr"/>
       <c r="BI78" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ78" t="inlineStr"/>
@@ -21987,27 +21975,27 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>691781</t>
+          <t>663586</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Brady House</t>
+          <t>Austin Riley</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-08-22T20:10:00Z</t>
+          <t>2026-08-22T18:10:00Z</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -22017,17 +22005,17 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Eury Pérez</t>
+          <t>Logan Henderson</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>691587</t>
+          <t>701656</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -22050,26 +22038,26 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P79" t="n">
-        <v>39.8</v>
+        <v>53.9</v>
       </c>
       <c r="Q79" t="n">
-        <v>43.1</v>
+        <v>35</v>
       </c>
       <c r="R79" t="n">
-        <v>35</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="S79" t="n">
-        <v>96.59999999999999</v>
+        <v>52.4</v>
       </c>
       <c r="T79" t="n">
         <v>50</v>
       </c>
       <c r="U79" t="n">
-        <v>39.8</v>
+        <v>10.8</v>
       </c>
       <c r="V79" t="inlineStr">
         <is>
@@ -22078,34 +22066,30 @@
       </c>
       <c r="W79" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X79" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y79" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 3 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB79" t="inlineStr"/>
       <c r="AC79" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -22130,137 +22114,137 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/19, 1 HR</t>
+          <t>Last 7 games: 5/26, 0 HR</t>
         </is>
       </c>
       <c r="AL79" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.1% barrel, 12.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.6% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN79" t="inlineStr">
         <is>
-          <t>9.06</t>
+          <t>13.17</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>46.93</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>89.52</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="AQ79" t="inlineStr">
         <is>
-          <t>101.6965</t>
+          <t>103.0149</t>
         </is>
       </c>
       <c r="AR79" t="inlineStr">
         <is>
-          <t>0.419</t>
+          <t>0.4188</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr">
         <is>
-          <t>0.1602</t>
+          <t>0.1963</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr">
         <is>
-          <t>0.3169</t>
+          <t>0.309</t>
         </is>
       </c>
       <c r="AU79" t="inlineStr">
         <is>
-          <t>73.31</t>
+          <t>75.76</t>
         </is>
       </c>
       <c r="AV79" t="inlineStr">
         <is>
-          <t>30.95</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>33.8</t>
+          <t>39.73</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>31.01</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>15.3</t>
         </is>
       </c>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>0.1526</t>
         </is>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="BB79" t="inlineStr">
         <is>
-          <t>41.81</t>
+          <t>36.09</t>
         </is>
       </c>
       <c r="BC79" t="inlineStr">
         <is>
-          <t>88.96</t>
+          <t>88.38</t>
         </is>
       </c>
       <c r="BD79" t="inlineStr">
         <is>
-          <t>0.3618</t>
+          <t>0.352</t>
         </is>
       </c>
       <c r="BE79" t="inlineStr">
         <is>
-          <t>0.1553</t>
+          <t>0.1393</t>
         </is>
       </c>
       <c r="BF79" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BG79" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH79" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI79" t="inlineStr">
         <is>
-          <t>loanDepot park</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ79" t="inlineStr"/>
@@ -22271,47 +22255,47 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>686469</t>
+          <t>691781</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Vinnie Pasquantino</t>
+          <t>Brady House</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-22T23:15:00Z</t>
+          <t>2026-08-22T20:10:00Z</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Drew Anderson</t>
+          <t>Eury Pérez</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>623454</t>
+          <t>691587</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -22334,65 +22318,61 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P80" t="n">
-        <v>37.8</v>
+        <v>39.8</v>
       </c>
       <c r="Q80" t="n">
-        <v>36.8</v>
+        <v>43.1</v>
       </c>
       <c r="R80" t="n">
-        <v>23.2</v>
+        <v>35</v>
       </c>
       <c r="S80" t="n">
-        <v>90.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T80" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U80" t="n">
-        <v>81.7</v>
+        <v>39.8</v>
       </c>
       <c r="V80" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W80" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X80" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y80" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr"/>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD80" t="inlineStr"/>
@@ -22409,134 +22389,142 @@
       </c>
       <c r="AH80" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/19, 1 HR</t>
         </is>
       </c>
       <c r="AL80" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.3% barrel, 11.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.1% barrel, 12.7 HR allowed</t>
         </is>
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN80" t="inlineStr">
         <is>
-          <t>8.49</t>
+          <t>9.06</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>42.39</t>
+          <t>46.93</t>
         </is>
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>89.92</t>
+          <t>89.52</t>
         </is>
       </c>
       <c r="AQ80" t="inlineStr">
         <is>
-          <t>100.2351</t>
+          <t>101.6965</t>
         </is>
       </c>
       <c r="AR80" t="inlineStr">
         <is>
-          <t>0.4273</t>
+          <t>0.419</t>
         </is>
       </c>
       <c r="AS80" t="inlineStr">
         <is>
-          <t>0.1721</t>
+          <t>0.1602</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr">
         <is>
-          <t>0.3291</t>
+          <t>0.3169</t>
         </is>
       </c>
       <c r="AU80" t="inlineStr">
         <is>
-          <t>70.96</t>
+          <t>73.31</t>
         </is>
       </c>
       <c r="AV80" t="inlineStr">
         <is>
-          <t>14.68</t>
+          <t>30.95</t>
         </is>
       </c>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>43.91</t>
+          <t>33.8</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>27.81</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
-          <t>15.2</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>0.1571</t>
+          <t>0.137</t>
         </is>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>9.14</t>
         </is>
       </c>
       <c r="BB80" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>41.81</t>
         </is>
       </c>
       <c r="BC80" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.96</t>
         </is>
       </c>
       <c r="BD80" t="inlineStr">
         <is>
-          <t>0.354</t>
+          <t>0.3618</t>
         </is>
       </c>
       <c r="BE80" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>0.1553</t>
         </is>
       </c>
       <c r="BF80" t="inlineStr">
         <is>
-          <t>24.6</t>
-        </is>
-      </c>
-      <c r="BG80" t="inlineStr"/>
-      <c r="BH80" t="inlineStr"/>
+          <t>30.45</t>
+        </is>
+      </c>
+      <c r="BG80" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH80" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI80" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>loanDepot park</t>
         </is>
       </c>
       <c r="BJ80" t="inlineStr"/>
@@ -22547,47 +22535,47 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>663586</t>
+          <t>686469</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Austin Riley</t>
+          <t>Vinnie Pasquantino</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-08-22T18:10:00Z</t>
+          <t>2026-08-22T23:15:00Z</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Logan Henderson</t>
+          <t>Drew Anderson</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>701656</t>
+          <t>623454</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -22596,7 +22584,7 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
@@ -22610,61 +22598,65 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P81" t="n">
-        <v>53.9</v>
+        <v>37.8</v>
       </c>
       <c r="Q81" t="n">
-        <v>35</v>
+        <v>36.8</v>
       </c>
       <c r="R81" t="n">
-        <v>67.09999999999999</v>
+        <v>23.2</v>
       </c>
       <c r="S81" t="n">
-        <v>52.4</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T81" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U81" t="n">
-        <v>10.8</v>
+        <v>81.7</v>
       </c>
       <c r="V81" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W81" t="inlineStr">
+      <c r="Z81" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X81" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y81" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD81" t="inlineStr"/>
@@ -22681,7 +22673,7 @@
       </c>
       <c r="AH81" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AI81" t="inlineStr">
@@ -22691,17 +22683,17 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL81" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.6% barrel, 7.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 11.0 HR allowed</t>
         </is>
       </c>
       <c r="AM81" t="inlineStr">
@@ -22711,112 +22703,104 @@
       </c>
       <c r="AN81" t="inlineStr">
         <is>
-          <t>13.17</t>
+          <t>8.49</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>42.39</t>
         </is>
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>89.92</t>
         </is>
       </c>
       <c r="AQ81" t="inlineStr">
         <is>
-          <t>103.0149</t>
+          <t>100.2351</t>
         </is>
       </c>
       <c r="AR81" t="inlineStr">
         <is>
-          <t>0.4188</t>
+          <t>0.4273</t>
         </is>
       </c>
       <c r="AS81" t="inlineStr">
         <is>
-          <t>0.1963</t>
+          <t>0.1721</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr">
         <is>
-          <t>0.309</t>
+          <t>0.3291</t>
         </is>
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>75.76</t>
+          <t>70.96</t>
         </is>
       </c>
       <c r="AV81" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>14.68</t>
         </is>
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>39.73</t>
+          <t>43.91</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>31.01</t>
+          <t>27.81</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
-          <t>15.3</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>0.1526</t>
+          <t>0.1571</t>
         </is>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="BB81" t="inlineStr">
         <is>
-          <t>36.09</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="BC81" t="inlineStr">
         <is>
-          <t>88.38</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="BD81" t="inlineStr">
         <is>
-          <t>0.352</t>
+          <t>0.354</t>
         </is>
       </c>
       <c r="BE81" t="inlineStr">
         <is>
-          <t>0.1393</t>
+          <t>0.137</t>
         </is>
       </c>
       <c r="BF81" t="inlineStr">
         <is>
-          <t>29.67</t>
-        </is>
-      </c>
-      <c r="BG81" t="inlineStr">
-        <is>
-          <t>Out To CF</t>
-        </is>
-      </c>
-      <c r="BH81" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
+          <t>24.6</t>
+        </is>
+      </c>
+      <c r="BG81" t="inlineStr"/>
+      <c r="BH81" t="inlineStr"/>
       <c r="BI81" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ81" t="inlineStr"/>
@@ -23746,34 +23730,30 @@
       </c>
       <c r="W85" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X85" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y85" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 2 vs RotoWire 3</t>
-        </is>
-      </c>
+      <c r="AB85" t="inlineStr"/>
       <c r="AC85" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -24860,28 +24840,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W89" t="inlineStr"/>
-      <c r="X89" t="inlineStr"/>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="Y89" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB89" t="inlineStr"/>
       <c r="AC89" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -28402,34 +28386,30 @@
       </c>
       <c r="W102" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X102" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X102" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y102" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 1 vs RotoWire 4</t>
-        </is>
-      </c>
+      <c r="AB102" t="inlineStr"/>
       <c r="AC102" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -29448,7 +29428,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -29682,7 +29662,7 @@
       </c>
       <c r="BG106" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH106" t="inlineStr">
@@ -31148,28 +31128,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W112" t="inlineStr"/>
-      <c r="X112" t="inlineStr"/>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X112" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="Y112" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB112" t="inlineStr"/>
       <c r="AC112" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -36584,7 +36568,7 @@
         <v>38</v>
       </c>
       <c r="R132" t="n">
-        <v>67.09999999999999</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="S132" t="n">
         <v>64.3</v>
@@ -36775,7 +36759,7 @@
       </c>
       <c r="BH132" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI132" t="inlineStr">
@@ -38196,7 +38180,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -38430,7 +38414,7 @@
       </c>
       <c r="BG138" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH138" t="inlineStr">
@@ -39316,7 +39300,7 @@
         <v>34.1</v>
       </c>
       <c r="R142" t="n">
-        <v>67.09999999999999</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="S142" t="n">
         <v>86.40000000000001</v>
@@ -39507,7 +39491,7 @@
       </c>
       <c r="BH142" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI142" t="inlineStr">
@@ -40351,47 +40335,47 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>621493</t>
+          <t>800325</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Taylor Ward</t>
+          <t>Luis Lara</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-08-22T23:15:00Z</t>
+          <t>2026-08-22T18:10:00Z</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>David Peterson</t>
+          <t>Martín Pérez</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>656849</t>
+          <t>527048</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -40414,65 +40398,61 @@
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P146" t="n">
-        <v>31.9</v>
+        <v>22.4</v>
       </c>
       <c r="Q146" t="n">
-        <v>35.9</v>
+        <v>37</v>
       </c>
       <c r="R146" t="n">
-        <v>25.4</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="S146" t="n">
-        <v>88.7</v>
+        <v>52.4</v>
       </c>
       <c r="T146" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U146" t="n">
-        <v>5.1</v>
+        <v>41.7</v>
       </c>
       <c r="V146" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X146" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z146" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W146" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X146" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y146" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z146" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB146" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB146" t="inlineStr"/>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD146" t="inlineStr"/>
@@ -40489,27 +40469,27 @@
       </c>
       <c r="AH146" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI146" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK146" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/26, 0 HR</t>
+          <t>Last 7 games: 8/29, 1 HR</t>
         </is>
       </c>
       <c r="AL146" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.4% barrel, 11.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.1% barrel, 9.5 HR allowed</t>
         </is>
       </c>
       <c r="AM146" t="inlineStr">
@@ -40519,104 +40499,112 @@
       </c>
       <c r="AN146" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="AO146" t="inlineStr">
         <is>
-          <t>39.48</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="AP146" t="inlineStr">
         <is>
-          <t>89.19</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AQ146" t="inlineStr">
         <is>
-          <t>99.3862</t>
+          <t>98.8151</t>
         </is>
       </c>
       <c r="AR146" t="inlineStr">
         <is>
-          <t>0.3947</t>
+          <t>0.366</t>
         </is>
       </c>
       <c r="AS146" t="inlineStr">
         <is>
-          <t>0.1539</t>
+          <t>0.092</t>
         </is>
       </c>
       <c r="AT146" t="inlineStr">
         <is>
-          <t>0.3379</t>
+          <t>0.319</t>
         </is>
       </c>
       <c r="AU146" t="inlineStr">
         <is>
-          <t>68.8</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="AV146" t="inlineStr">
         <is>
-          <t>4.16</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>33.1</t>
+          <t>32.1</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>30.01</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
         <is>
-          <t>15.7</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>0.1406</t>
+          <t>0.108</t>
         </is>
       </c>
       <c r="BA146" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>8.14</t>
         </is>
       </c>
       <c r="BB146" t="inlineStr">
         <is>
-          <t>42.64</t>
+          <t>37.86</t>
         </is>
       </c>
       <c r="BC146" t="inlineStr">
         <is>
-          <t>89.69</t>
+          <t>88.13</t>
         </is>
       </c>
       <c r="BD146" t="inlineStr">
         <is>
-          <t>0.414</t>
+          <t>0.4171</t>
         </is>
       </c>
       <c r="BE146" t="inlineStr">
         <is>
-          <t>0.1405</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="BF146" t="inlineStr">
         <is>
-          <t>19.71</t>
-        </is>
-      </c>
-      <c r="BG146" t="inlineStr"/>
-      <c r="BH146" t="inlineStr"/>
+          <t>24.2</t>
+        </is>
+      </c>
+      <c r="BG146" t="inlineStr">
+        <is>
+          <t>Out To CF</t>
+        </is>
+      </c>
+      <c r="BH146" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
       <c r="BI146" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ146" t="inlineStr"/>
@@ -40627,22 +40615,22 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>668939</t>
+          <t>621493</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Adley Rutschman</t>
+          <t>Taylor Ward</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -40657,22 +40645,22 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Blade Tidwell</t>
+          <t>David Peterson</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>694918</t>
+          <t>656849</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L147" t="n">
@@ -40694,22 +40682,22 @@
         </is>
       </c>
       <c r="P147" t="n">
-        <v>33.1</v>
+        <v>31.9</v>
       </c>
       <c r="Q147" t="n">
-        <v>25.9</v>
+        <v>35.9</v>
       </c>
       <c r="R147" t="n">
-        <v>28.7</v>
+        <v>25.4</v>
       </c>
       <c r="S147" t="n">
-        <v>92.09999999999999</v>
+        <v>88.7</v>
       </c>
       <c r="T147" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="U147" t="n">
-        <v>30.3</v>
+        <v>5.1</v>
       </c>
       <c r="V147" t="inlineStr">
         <is>
@@ -40723,7 +40711,7 @@
       </c>
       <c r="X147" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y147" t="inlineStr">
@@ -40765,27 +40753,27 @@
       </c>
       <c r="AH147" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI147" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 1 HR</t>
+          <t>Last 7 games: 4/26, 0 HR</t>
         </is>
       </c>
       <c r="AL147" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.5% barrel, 2.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.4% barrel, 11.0 HR allowed</t>
         </is>
       </c>
       <c r="AM147" t="inlineStr">
@@ -40795,104 +40783,104 @@
       </c>
       <c r="AN147" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>8.03</t>
         </is>
       </c>
       <c r="AO147" t="inlineStr">
         <is>
-          <t>40.14</t>
+          <t>39.48</t>
         </is>
       </c>
       <c r="AP147" t="inlineStr">
         <is>
-          <t>88.98</t>
+          <t>89.19</t>
         </is>
       </c>
       <c r="AQ147" t="inlineStr">
         <is>
-          <t>99.3995</t>
+          <t>99.3862</t>
         </is>
       </c>
       <c r="AR147" t="inlineStr">
         <is>
-          <t>0.4219</t>
+          <t>0.3947</t>
         </is>
       </c>
       <c r="AS147" t="inlineStr">
         <is>
-          <t>0.1641</t>
+          <t>0.1539</t>
         </is>
       </c>
       <c r="AT147" t="inlineStr">
         <is>
-          <t>0.339</t>
+          <t>0.3379</t>
         </is>
       </c>
       <c r="AU147" t="inlineStr">
         <is>
-          <t>70.42</t>
+          <t>68.8</t>
         </is>
       </c>
       <c r="AV147" t="inlineStr">
         <is>
-          <t>12.42</t>
+          <t>4.16</t>
         </is>
       </c>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>39.03</t>
+          <t>33.1</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>28.87</t>
+          <t>30.01</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>15.7</t>
         </is>
       </c>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>0.167</t>
+          <t>0.1406</t>
         </is>
       </c>
       <c r="BA147" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="BB147" t="inlineStr">
         <is>
-          <t>36.64</t>
+          <t>42.64</t>
         </is>
       </c>
       <c r="BC147" t="inlineStr">
         <is>
-          <t>87.78</t>
+          <t>89.69</t>
         </is>
       </c>
       <c r="BD147" t="inlineStr">
         <is>
-          <t>0.3849</t>
+          <t>0.414</t>
         </is>
       </c>
       <c r="BE147" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>0.1405</t>
         </is>
       </c>
       <c r="BF147" t="inlineStr">
         <is>
-          <t>21.73</t>
+          <t>19.71</t>
         </is>
       </c>
       <c r="BG147" t="inlineStr"/>
       <c r="BH147" t="inlineStr"/>
       <c r="BI147" t="inlineStr">
         <is>
-          <t>Fenway Park</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ147" t="inlineStr"/>
@@ -40903,56 +40891,56 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>800325</t>
+          <t>668939</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Luis Lara</t>
+          <t>Adley Rutschman</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-08-22T18:10:00Z</t>
+          <t>2026-08-22T23:15:00Z</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Martín Pérez</t>
+          <t>Blade Tidwell</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>527048</t>
+          <t>694918</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L148" t="n">
-        <v>42.5</v>
+        <v>42.6</v>
       </c>
       <c r="M148" t="inlineStr">
         <is>
@@ -40966,61 +40954,65 @@
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P148" t="n">
-        <v>22.4</v>
+        <v>33.1</v>
       </c>
       <c r="Q148" t="n">
-        <v>37</v>
+        <v>25.9</v>
       </c>
       <c r="R148" t="n">
-        <v>67.09999999999999</v>
+        <v>28.7</v>
       </c>
       <c r="S148" t="n">
-        <v>52.4</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T148" t="n">
         <v>75</v>
       </c>
       <c r="U148" t="n">
-        <v>41.7</v>
+        <v>30.3</v>
       </c>
       <c r="V148" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X148" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W148" t="inlineStr">
+      <c r="Z148" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X148" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y148" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z148" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB148" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB148" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC148" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD148" t="inlineStr"/>
@@ -41037,12 +41029,12 @@
       </c>
       <c r="AH148" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI148" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ148" t="inlineStr">
@@ -41052,12 +41044,12 @@
       </c>
       <c r="AK148" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/29, 1 HR</t>
+          <t>Last 7 games: 5/25, 1 HR</t>
         </is>
       </c>
       <c r="AL148" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.1% barrel, 9.5 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.5% barrel, 2.6 HR allowed</t>
         </is>
       </c>
       <c r="AM148" t="inlineStr">
@@ -41067,112 +41059,104 @@
       </c>
       <c r="AN148" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>7.36</t>
         </is>
       </c>
       <c r="AO148" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>40.14</t>
         </is>
       </c>
       <c r="AP148" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.98</t>
         </is>
       </c>
       <c r="AQ148" t="inlineStr">
         <is>
-          <t>98.8151</t>
+          <t>99.3995</t>
         </is>
       </c>
       <c r="AR148" t="inlineStr">
         <is>
-          <t>0.366</t>
+          <t>0.4219</t>
         </is>
       </c>
       <c r="AS148" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>0.1641</t>
         </is>
       </c>
       <c r="AT148" t="inlineStr">
         <is>
-          <t>0.319</t>
+          <t>0.339</t>
         </is>
       </c>
       <c r="AU148" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>70.42</t>
         </is>
       </c>
       <c r="AV148" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>12.42</t>
         </is>
       </c>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>32.1</t>
+          <t>39.03</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>28.87</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>0.167</t>
         </is>
       </c>
       <c r="BA148" t="inlineStr">
         <is>
-          <t>8.14</t>
+          <t>6.51</t>
         </is>
       </c>
       <c r="BB148" t="inlineStr">
         <is>
-          <t>37.86</t>
+          <t>36.64</t>
         </is>
       </c>
       <c r="BC148" t="inlineStr">
         <is>
-          <t>88.13</t>
+          <t>87.78</t>
         </is>
       </c>
       <c r="BD148" t="inlineStr">
         <is>
-          <t>0.4171</t>
+          <t>0.3849</t>
         </is>
       </c>
       <c r="BE148" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.125</t>
         </is>
       </c>
       <c r="BF148" t="inlineStr">
         <is>
-          <t>24.2</t>
-        </is>
-      </c>
-      <c r="BG148" t="inlineStr">
-        <is>
-          <t>Out To CF</t>
-        </is>
-      </c>
-      <c r="BH148" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
+          <t>21.73</t>
+        </is>
+      </c>
+      <c r="BG148" t="inlineStr"/>
+      <c r="BH148" t="inlineStr"/>
       <c r="BI148" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Fenway Park</t>
         </is>
       </c>
       <c r="BJ148" t="inlineStr"/>
@@ -43416,7 +43400,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -43482,34 +43466,30 @@
       </c>
       <c r="W157" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X157" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z157" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X157" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y157" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z157" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB157" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 8 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AB157" t="inlineStr"/>
       <c r="AC157" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -43654,7 +43634,7 @@
       </c>
       <c r="BG157" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH157" t="inlineStr">
@@ -47784,7 +47764,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -47850,34 +47830,30 @@
       </c>
       <c r="W173" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X173" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y173" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z173" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X173" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y173" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z173" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA173" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB173" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB173" t="inlineStr"/>
       <c r="AC173" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -48022,7 +47998,7 @@
       </c>
       <c r="BG173" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH173" t="inlineStr">
@@ -48871,42 +48847,54 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>650333</t>
+          <t>643289</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Luis Arraez</t>
+          <t>Mauricio Dubón</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>2026-08-22T22:05:00Z</t>
+          <t>2026-08-22T18:10:00Z</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr"/>
-      <c r="J177" t="inlineStr"/>
-      <c r="K177" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Logan Henderson</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>701656</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L177" t="n">
         <v>38.8</v>
       </c>
@@ -48922,65 +48910,61 @@
       </c>
       <c r="O177" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P177" t="n">
-        <v>7.7</v>
+        <v>11.1</v>
       </c>
       <c r="Q177" t="n">
-        <v>41.2</v>
+        <v>35</v>
       </c>
       <c r="R177" t="n">
-        <v>34.3</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="S177" t="n">
-        <v>90.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T177" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U177" t="n">
-        <v>63.3</v>
+        <v>27.7</v>
       </c>
       <c r="V177" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W177" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X177" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y177" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z177" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W177" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X177" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y177" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z177" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA177" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB177" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB177" t="inlineStr"/>
       <c r="AC177" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD177" t="inlineStr"/>
@@ -48997,27 +48981,27 @@
       </c>
       <c r="AH177" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI177" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
         <is>
-          <t>Contact streak: 14/31 over last 7 games</t>
+          <t>Last 7 games: 7/23, 0 HR</t>
         </is>
       </c>
       <c r="AL177" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.6% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AM177" t="inlineStr">
@@ -49027,80 +49011,112 @@
       </c>
       <c r="AN177" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AO177" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>29.31</t>
         </is>
       </c>
       <c r="AP177" t="inlineStr">
         <is>
-          <t>86.59</t>
+          <t>86.18</t>
         </is>
       </c>
       <c r="AQ177" t="inlineStr">
         <is>
-          <t>94.0058</t>
+          <t>96.3935</t>
         </is>
       </c>
       <c r="AR177" t="inlineStr">
         <is>
-          <t>0.3777</t>
+          <t>0.3667</t>
         </is>
       </c>
       <c r="AS177" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.1036</t>
         </is>
       </c>
       <c r="AT177" t="inlineStr">
         <is>
-          <t>0.3072</t>
+          <t>0.299</t>
         </is>
       </c>
       <c r="AU177" t="inlineStr">
         <is>
-          <t>62.99</t>
+          <t>68.73</t>
         </is>
       </c>
       <c r="AV177" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>30.24</t>
+          <t>32.17</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>28.52</t>
+          <t>25.09</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>0.1154</t>
-        </is>
-      </c>
-      <c r="BA177" t="inlineStr"/>
-      <c r="BB177" t="inlineStr"/>
-      <c r="BC177" t="inlineStr"/>
-      <c r="BD177" t="inlineStr"/>
-      <c r="BE177" t="inlineStr"/>
-      <c r="BF177" t="inlineStr"/>
-      <c r="BG177" t="inlineStr"/>
-      <c r="BH177" t="inlineStr"/>
+          <t>0.1217</t>
+        </is>
+      </c>
+      <c r="BA177" t="inlineStr">
+        <is>
+          <t>8.6</t>
+        </is>
+      </c>
+      <c r="BB177" t="inlineStr">
+        <is>
+          <t>36.09</t>
+        </is>
+      </c>
+      <c r="BC177" t="inlineStr">
+        <is>
+          <t>88.38</t>
+        </is>
+      </c>
+      <c r="BD177" t="inlineStr">
+        <is>
+          <t>0.352</t>
+        </is>
+      </c>
+      <c r="BE177" t="inlineStr">
+        <is>
+          <t>0.1393</t>
+        </is>
+      </c>
+      <c r="BF177" t="inlineStr">
+        <is>
+          <t>29.67</t>
+        </is>
+      </c>
+      <c r="BG177" t="inlineStr">
+        <is>
+          <t>Out To CF</t>
+        </is>
+      </c>
+      <c r="BH177" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
       <c r="BI177" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ177" t="inlineStr"/>
@@ -49111,27 +49127,27 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>691720</t>
+          <t>650333</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Kyle Karros</t>
+          <t>Luis Arraez</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>2026-08-23T00:10:00Z</t>
+          <t>2026-08-22T22:05:00Z</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -49141,24 +49157,12 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>Tanner Bibee</t>
-        </is>
-      </c>
-      <c r="J178" t="inlineStr">
-        <is>
-          <t>676440</t>
-        </is>
-      </c>
-      <c r="K178" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr"/>
       <c r="L178" t="n">
         <v>38.8</v>
       </c>
@@ -49174,26 +49178,26 @@
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P178" t="n">
-        <v>24.2</v>
+        <v>7.7</v>
       </c>
       <c r="Q178" t="n">
-        <v>43.8</v>
+        <v>41.2</v>
       </c>
       <c r="R178" t="n">
-        <v>38.7</v>
+        <v>34.3</v>
       </c>
       <c r="S178" t="n">
-        <v>59.8</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T178" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="U178" t="n">
-        <v>32.9</v>
+        <v>63.3</v>
       </c>
       <c r="V178" t="inlineStr">
         <is>
@@ -49207,7 +49211,7 @@
       </c>
       <c r="X178" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y178" t="inlineStr">
@@ -49232,7 +49236,7 @@
       </c>
       <c r="AC178" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD178" t="inlineStr"/>
@@ -49249,12 +49253,12 @@
       </c>
       <c r="AH178" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AI178" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AJ178" t="inlineStr">
@@ -49264,12 +49268,12 @@
       </c>
       <c r="AK178" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/23, 1 HR</t>
+          <t>Contact streak: 14/31 over last 7 games</t>
         </is>
       </c>
       <c r="AL178" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.2% barrel, 25.6 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM178" t="inlineStr">
@@ -49279,104 +49283,80 @@
       </c>
       <c r="AN178" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AO178" t="inlineStr">
         <is>
-          <t>39.09</t>
+          <t>19.08</t>
         </is>
       </c>
       <c r="AP178" t="inlineStr">
         <is>
-          <t>89.02</t>
+          <t>86.59</t>
         </is>
       </c>
       <c r="AQ178" t="inlineStr">
         <is>
-          <t>99.598</t>
+          <t>94.0058</t>
         </is>
       </c>
       <c r="AR178" t="inlineStr">
         <is>
-          <t>0.3614</t>
+          <t>0.3777</t>
         </is>
       </c>
       <c r="AS178" t="inlineStr">
         <is>
-          <t>0.1201</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AT178" t="inlineStr">
         <is>
-          <t>0.3147</t>
+          <t>0.3072</t>
         </is>
       </c>
       <c r="AU178" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>62.99</t>
         </is>
       </c>
       <c r="AV178" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>30.24</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>24.13</t>
+          <t>28.52</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="AZ178" t="inlineStr">
         <is>
-          <t>0.1252</t>
-        </is>
-      </c>
-      <c r="BA178" t="inlineStr">
-        <is>
-          <t>8.24</t>
-        </is>
-      </c>
-      <c r="BB178" t="inlineStr">
-        <is>
-          <t>38.49</t>
-        </is>
-      </c>
-      <c r="BC178" t="inlineStr">
-        <is>
-          <t>89.13</t>
-        </is>
-      </c>
-      <c r="BD178" t="inlineStr">
-        <is>
-          <t>0.4116</t>
-        </is>
-      </c>
-      <c r="BE178" t="inlineStr">
-        <is>
-          <t>0.1674</t>
-        </is>
-      </c>
-      <c r="BF178" t="inlineStr">
-        <is>
-          <t>27.62</t>
-        </is>
-      </c>
+          <t>0.1154</t>
+        </is>
+      </c>
+      <c r="BA178" t="inlineStr"/>
+      <c r="BB178" t="inlineStr"/>
+      <c r="BC178" t="inlineStr"/>
+      <c r="BD178" t="inlineStr"/>
+      <c r="BE178" t="inlineStr"/>
+      <c r="BF178" t="inlineStr"/>
       <c r="BG178" t="inlineStr"/>
       <c r="BH178" t="inlineStr"/>
       <c r="BI178" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BJ178" t="inlineStr"/>
@@ -49387,47 +49367,47 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>643289</t>
+          <t>691720</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Mauricio Dubón</t>
+          <t>Kyle Karros</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>2026-08-22T18:10:00Z</t>
+          <t>2026-08-23T00:10:00Z</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>Logan Henderson</t>
+          <t>Tanner Bibee</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>701656</t>
+          <t>676440</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
@@ -49436,72 +49416,76 @@
         </is>
       </c>
       <c r="L179" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>Longshot</t>
+        </is>
+      </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>Watch List</t>
+        </is>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>Projected Lineup</t>
+        </is>
+      </c>
+      <c r="P179" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="Q179" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="R179" t="n">
         <v>38.7</v>
       </c>
-      <c r="M179" t="inlineStr">
-        <is>
-          <t>Longshot</t>
-        </is>
-      </c>
-      <c r="N179" t="inlineStr">
-        <is>
-          <t>Watch List</t>
-        </is>
-      </c>
-      <c r="O179" t="inlineStr">
-        <is>
-          <t>No major boost</t>
-        </is>
-      </c>
-      <c r="P179" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="Q179" t="n">
-        <v>35</v>
-      </c>
-      <c r="R179" t="n">
-        <v>67.09999999999999</v>
-      </c>
       <c r="S179" t="n">
-        <v>76.2</v>
+        <v>59.8</v>
       </c>
       <c r="T179" t="n">
         <v>50</v>
       </c>
       <c r="U179" t="n">
-        <v>27.7</v>
+        <v>32.9</v>
       </c>
       <c r="V179" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W179" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X179" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y179" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W179" t="inlineStr">
+      <c r="Z179" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X179" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y179" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z179" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB179" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB179" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC179" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -49521,7 +49505,7 @@
       </c>
       <c r="AH179" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI179" t="inlineStr">
@@ -49531,17 +49515,17 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/23, 0 HR</t>
+          <t>Last 7 games: 5/23, 1 HR</t>
         </is>
       </c>
       <c r="AL179" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.6% barrel, 7.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.2% barrel, 25.6 HR allowed</t>
         </is>
       </c>
       <c r="AM179" t="inlineStr">
@@ -49551,112 +49535,104 @@
       </c>
       <c r="AN179" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="AO179" t="inlineStr">
         <is>
-          <t>29.31</t>
+          <t>39.09</t>
         </is>
       </c>
       <c r="AP179" t="inlineStr">
         <is>
-          <t>86.18</t>
+          <t>89.02</t>
         </is>
       </c>
       <c r="AQ179" t="inlineStr">
         <is>
-          <t>96.3935</t>
+          <t>99.598</t>
         </is>
       </c>
       <c r="AR179" t="inlineStr">
         <is>
-          <t>0.3667</t>
+          <t>0.3614</t>
         </is>
       </c>
       <c r="AS179" t="inlineStr">
         <is>
-          <t>0.1036</t>
+          <t>0.1201</t>
         </is>
       </c>
       <c r="AT179" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>0.3147</t>
         </is>
       </c>
       <c r="AU179" t="inlineStr">
         <is>
-          <t>68.73</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="AV179" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>32.17</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>25.09</t>
+          <t>24.13</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AZ179" t="inlineStr">
         <is>
-          <t>0.1217</t>
+          <t>0.1252</t>
         </is>
       </c>
       <c r="BA179" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.24</t>
         </is>
       </c>
       <c r="BB179" t="inlineStr">
         <is>
-          <t>36.09</t>
+          <t>38.49</t>
         </is>
       </c>
       <c r="BC179" t="inlineStr">
         <is>
-          <t>88.38</t>
+          <t>89.13</t>
         </is>
       </c>
       <c r="BD179" t="inlineStr">
         <is>
-          <t>0.352</t>
+          <t>0.4116</t>
         </is>
       </c>
       <c r="BE179" t="inlineStr">
         <is>
-          <t>0.1393</t>
+          <t>0.1674</t>
         </is>
       </c>
       <c r="BF179" t="inlineStr">
         <is>
-          <t>29.67</t>
-        </is>
-      </c>
-      <c r="BG179" t="inlineStr">
-        <is>
-          <t>Out To CF</t>
-        </is>
-      </c>
-      <c r="BH179" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
+          <t>27.62</t>
+        </is>
+      </c>
+      <c r="BG179" t="inlineStr"/>
+      <c r="BH179" t="inlineStr"/>
       <c r="BI179" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ179" t="inlineStr"/>
@@ -49692,7 +49668,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -49926,7 +49902,7 @@
       </c>
       <c r="BG180" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH180" t="inlineStr">
@@ -52976,7 +52952,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -53042,34 +53018,30 @@
       </c>
       <c r="W192" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X192" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y192" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z192" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X192" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y192" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z192" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA192" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB192" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB192" t="inlineStr"/>
       <c r="AC192" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -53214,7 +53186,7 @@
       </c>
       <c r="BG192" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH192" t="inlineStr">
@@ -54867,24 +54839,24 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>806198</t>
+          <t>805347</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Cooper Pratt</t>
+          <t>Jim Jarvis</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
       <c r="F199" t="inlineStr">
         <is>
           <t>2026-08-22T18:10:00Z</t>
@@ -54902,17 +54874,17 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>Martín Pérez</t>
+          <t>Logan Henderson</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>527048</t>
+          <t>701656</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L199" t="n">
@@ -54934,22 +54906,22 @@
         </is>
       </c>
       <c r="P199" t="n">
-        <v>12.9</v>
+        <v>14.4</v>
       </c>
       <c r="Q199" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="R199" t="n">
-        <v>67.09999999999999</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="S199" t="n">
         <v>44.8</v>
       </c>
       <c r="T199" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U199" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="V199" t="inlineStr">
         <is>
@@ -55001,12 +54973,12 @@
       </c>
       <c r="AH199" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI199" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ199" t="inlineStr">
@@ -55016,12 +54988,12 @@
       </c>
       <c r="AK199" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/24, 0 HR</t>
+          <t>Last 7 games: 1/17, 0 HR</t>
         </is>
       </c>
       <c r="AL199" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.1% barrel, 9.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.6% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AM199" t="inlineStr">
@@ -55031,97 +55003,97 @@
       </c>
       <c r="AN199" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="AO199" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>36.7</t>
         </is>
       </c>
       <c r="AP199" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AQ199" t="inlineStr">
         <is>
-          <t>96.7673</t>
+          <t>98.6045</t>
         </is>
       </c>
       <c r="AR199" t="inlineStr">
         <is>
-          <t>0.346</t>
+          <t>0.308</t>
         </is>
       </c>
       <c r="AS199" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>0.071</t>
         </is>
       </c>
       <c r="AT199" t="inlineStr">
         <is>
-          <t>0.311</t>
+          <t>0.272</t>
         </is>
       </c>
       <c r="AU199" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AV199" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>32.1</t>
+          <t>26.7</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>0.093</t>
         </is>
       </c>
       <c r="BA199" t="inlineStr">
         <is>
-          <t>8.14</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="BB199" t="inlineStr">
         <is>
-          <t>37.86</t>
+          <t>36.09</t>
         </is>
       </c>
       <c r="BC199" t="inlineStr">
         <is>
-          <t>88.13</t>
+          <t>88.38</t>
         </is>
       </c>
       <c r="BD199" t="inlineStr">
         <is>
-          <t>0.4171</t>
+          <t>0.352</t>
         </is>
       </c>
       <c r="BE199" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.1393</t>
         </is>
       </c>
       <c r="BF199" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BG199" t="inlineStr">
@@ -55131,7 +55103,7 @@
       </c>
       <c r="BH199" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI199" t="inlineStr">
@@ -55147,24 +55119,24 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>805347</t>
+          <t>806198</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Jim Jarvis</t>
+          <t>Cooper Pratt</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
           <t>ATL</t>
         </is>
       </c>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F200" t="inlineStr">
         <is>
           <t>2026-08-22T18:10:00Z</t>
@@ -55182,21 +55154,21 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>Logan Henderson</t>
+          <t>Martín Pérez</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>701656</t>
+          <t>527048</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L200" t="n">
-        <v>36.7</v>
+        <v>36.8</v>
       </c>
       <c r="M200" t="inlineStr">
         <is>
@@ -55214,22 +55186,22 @@
         </is>
       </c>
       <c r="P200" t="n">
-        <v>14.4</v>
+        <v>12.9</v>
       </c>
       <c r="Q200" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="R200" t="n">
-        <v>67.09999999999999</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="S200" t="n">
         <v>44.8</v>
       </c>
       <c r="T200" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U200" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="V200" t="inlineStr">
         <is>
@@ -55281,12 +55253,12 @@
       </c>
       <c r="AH200" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI200" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ200" t="inlineStr">
@@ -55296,12 +55268,12 @@
       </c>
       <c r="AK200" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/17, 0 HR</t>
+          <t>Last 7 games: 3/24, 0 HR</t>
         </is>
       </c>
       <c r="AL200" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.6% barrel, 7.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.1% barrel, 9.5 HR allowed</t>
         </is>
       </c>
       <c r="AM200" t="inlineStr">
@@ -55311,97 +55283,97 @@
       </c>
       <c r="AN200" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="AO200" t="inlineStr">
         <is>
-          <t>36.7</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="AP200" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AQ200" t="inlineStr">
         <is>
-          <t>98.6045</t>
+          <t>96.7673</t>
         </is>
       </c>
       <c r="AR200" t="inlineStr">
         <is>
-          <t>0.308</t>
+          <t>0.346</t>
         </is>
       </c>
       <c r="AS200" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>0.095</t>
         </is>
       </c>
       <c r="AT200" t="inlineStr">
         <is>
-          <t>0.272</t>
+          <t>0.311</t>
         </is>
       </c>
       <c r="AU200" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="AV200" t="inlineStr">
         <is>
-          <t>12.4</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>26.7</t>
+          <t>32.1</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ200" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>0.091</t>
         </is>
       </c>
       <c r="BA200" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.14</t>
         </is>
       </c>
       <c r="BB200" t="inlineStr">
         <is>
-          <t>36.09</t>
+          <t>37.86</t>
         </is>
       </c>
       <c r="BC200" t="inlineStr">
         <is>
-          <t>88.38</t>
+          <t>88.13</t>
         </is>
       </c>
       <c r="BD200" t="inlineStr">
         <is>
-          <t>0.352</t>
+          <t>0.4171</t>
         </is>
       </c>
       <c r="BE200" t="inlineStr">
         <is>
-          <t>0.1393</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="BF200" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="BG200" t="inlineStr">
@@ -55411,7 +55383,7 @@
       </c>
       <c r="BH200" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI200" t="inlineStr">
@@ -55518,34 +55490,30 @@
       </c>
       <c r="W201" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X201" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y201" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z201" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X201" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y201" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z201" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA201" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB201" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 9</t>
-        </is>
-      </c>
+      <c r="AB201" t="inlineStr"/>
       <c r="AC201" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -60152,7 +60120,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -60386,7 +60354,7 @@
       </c>
       <c r="BG218" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH218" t="inlineStr">
@@ -62316,7 +62284,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -62382,34 +62350,30 @@
       </c>
       <c r="W226" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X226" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y226" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z226" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X226" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y226" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z226" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA226" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB226" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 9 vs RotoWire 8</t>
-        </is>
-      </c>
+      <c r="AB226" t="inlineStr"/>
       <c r="AC226" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -62554,7 +62518,7 @@
       </c>
       <c r="BG226" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH226" t="inlineStr">
@@ -66806,34 +66770,30 @@
       </c>
       <c r="W242" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X242" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y242" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z242" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X242" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y242" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z242" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA242" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB242" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 8 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AB242" t="inlineStr"/>
       <c r="AC242" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -71956,7 +71916,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -72190,7 +72150,7 @@
       </c>
       <c r="BG261" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH261" t="inlineStr">
@@ -73694,7 +73654,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>63.3</v>
+        <v>63.4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -73718,7 +73678,7 @@
         <v>35</v>
       </c>
       <c r="R5" t="n">
-        <v>67.09999999999999</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="S5" t="n">
         <v>96.59999999999999</v>
@@ -73909,7 +73869,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -74292,34 +74252,30 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 2</t>
-        </is>
-      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -75326,7 +75282,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>59.6</v>
+        <v>59.7</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -75350,7 +75306,7 @@
         <v>38</v>
       </c>
       <c r="R11" t="n">
-        <v>67.09999999999999</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="S11" t="n">
         <v>94.90000000000001</v>
@@ -75541,7 +75497,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -76158,7 +76114,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>59</v>
+        <v>59.1</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -76182,7 +76138,7 @@
         <v>35</v>
       </c>
       <c r="R14" t="n">
-        <v>67.09999999999999</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="S14" t="n">
         <v>93.2</v>
@@ -76373,7 +76329,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -76438,7 +76394,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>58.2</v>
+        <v>58.3</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -76462,7 +76418,7 @@
         <v>38</v>
       </c>
       <c r="R15" t="n">
-        <v>67.09999999999999</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="S15" t="n">
         <v>93.2</v>
@@ -76653,7 +76609,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -76694,7 +76650,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -76928,7 +76884,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -77278,7 +77234,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>57.5</v>
+        <v>57.6</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -77302,7 +77258,7 @@
         <v>35</v>
       </c>
       <c r="R18" t="n">
-        <v>67.09999999999999</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="S18" t="n">
         <v>100</v>
@@ -77493,7 +77449,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -77534,7 +77490,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -77768,7 +77724,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -77814,7 +77770,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -77880,34 +77836,30 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 4</t>
-        </is>
-      </c>
+      <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -78052,7 +78004,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -78098,7 +78050,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -78164,34 +78116,30 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 9</t>
-        </is>
-      </c>
+      <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -78336,7 +78284,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">

--- a/outputs/daily/hr_rankings_2026-08-22_full.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-22_full.xlsx
@@ -1592,7 +1592,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -4052,7 +4052,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4612,7 +4612,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -4636,7 +4636,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>58</v>
+        <v>58.1</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4669,7 +4669,7 @@
         <v>80</v>
       </c>
       <c r="U16" t="n">
-        <v>64.8</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -4721,12 +4721,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -5172,7 +5172,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -5452,7 +5452,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -5732,7 +5732,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -6012,7 +6012,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -6844,7 +6844,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -8232,7 +8232,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -9315,47 +9315,47 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>665489</t>
+          <t>642350</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Vladimir Guerrero Jr.</t>
+          <t>Jose Siri</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-22T17:35:00Z</t>
+          <t>2026-08-22T23:05:00Z</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Ryan Weathers</t>
+          <t>Cody Bradford</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>677960</t>
+          <t>674003</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -9378,61 +9378,65 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>39.5</v>
+        <v>51.2</v>
       </c>
       <c r="Q33" t="n">
-        <v>45.5</v>
+        <v>60.9</v>
       </c>
       <c r="R33" t="n">
-        <v>48.2</v>
+        <v>27.6</v>
       </c>
       <c r="S33" t="n">
-        <v>100</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T33" t="n">
         <v>78</v>
       </c>
       <c r="U33" t="n">
-        <v>46.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="V33" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W33" t="inlineStr">
+      <c r="Z33" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr"/>
@@ -9449,142 +9453,134 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Last 7 games: 9/29, 1 HR</t>
+          <t>Last 7 games: 2/11, 0 HR</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 14.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.2% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>8.42</t>
+          <t>16.08</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>45.31</t>
+          <t>39.6</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>90.74</t>
+          <t>87.63</t>
         </is>
       </c>
       <c r="AQ33" t="inlineStr">
         <is>
-          <t>102.9852</t>
+          <t>99.9834</t>
         </is>
       </c>
       <c r="AR33" t="inlineStr">
         <is>
-          <t>0.4311</t>
+          <t>0.397</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr">
         <is>
-          <t>0.1444</t>
+          <t>0.2092</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr">
         <is>
-          <t>0.3483</t>
+          <t>0.2855</t>
         </is>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>76.35</t>
+          <t>73.22</t>
         </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>63.54</t>
+          <t>35.64</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>35.6</t>
+          <t>30.57</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>19.38</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>11.8</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>0.1176</t>
+          <t>0.1586</t>
         </is>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>8.76</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>89.46</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="BD33" t="inlineStr">
         <is>
-          <t>0.4173</t>
+          <t>0.511</t>
         </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
-          <t>0.1708</t>
+          <t>0.213</t>
         </is>
       </c>
       <c r="BF33" t="inlineStr">
         <is>
-          <t>25.2</t>
-        </is>
-      </c>
-      <c r="BG33" t="inlineStr">
-        <is>
-          <t>In From LF</t>
-        </is>
-      </c>
-      <c r="BH33" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
+          <t>34.0</t>
+        </is>
+      </c>
+      <c r="BG33" t="inlineStr"/>
+      <c r="BH33" t="inlineStr"/>
       <c r="BI33" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ33" t="inlineStr"/>
@@ -9595,27 +9591,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>642350</t>
+          <t>666160</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Jose Siri</t>
+          <t>Mickey Moniak</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-22T23:05:00Z</t>
+          <t>2026-08-23T00:10:00Z</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -9625,26 +9621,26 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Cody Bradford</t>
+          <t>Tanner Bibee</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>674003</t>
+          <t>676440</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>54.6</v>
+        <v>53.9</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -9658,26 +9654,26 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>51.2</v>
+        <v>48.7</v>
       </c>
       <c r="Q34" t="n">
-        <v>60.9</v>
+        <v>43.8</v>
       </c>
       <c r="R34" t="n">
-        <v>27.6</v>
+        <v>38.7</v>
       </c>
       <c r="S34" t="n">
-        <v>81.90000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T34" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U34" t="n">
-        <v>9.300000000000001</v>
+        <v>28.1</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
@@ -9691,7 +9687,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
@@ -9716,7 +9712,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr"/>
@@ -9733,134 +9729,134 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/11, 0 HR</t>
+          <t>Last 7 games: 5/27, 1 HR</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.2% barrel, 1.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.2% barrel, 25.6 HR allowed</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher allows elevated contact</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>16.08</t>
+          <t>11.56</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>39.6</t>
+          <t>42.92</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>87.63</t>
+          <t>89.49</t>
         </is>
       </c>
       <c r="AQ34" t="inlineStr">
         <is>
-          <t>99.9834</t>
+          <t>100.3022</t>
         </is>
       </c>
       <c r="AR34" t="inlineStr">
         <is>
-          <t>0.397</t>
+          <t>0.4375</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr">
         <is>
-          <t>0.2092</t>
+          <t>0.2056</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr">
         <is>
-          <t>0.2855</t>
+          <t>0.3055</t>
         </is>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>73.22</t>
+          <t>74.19</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>35.64</t>
+          <t>43.81</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>30.57</t>
+          <t>45.89</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>38.17</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>0.1586</t>
+          <t>0.2634</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>8.24</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>38.49</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>89.13</t>
         </is>
       </c>
       <c r="BD34" t="inlineStr">
         <is>
-          <t>0.511</t>
+          <t>0.4116</t>
         </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
-          <t>0.213</t>
+          <t>0.1674</t>
         </is>
       </c>
       <c r="BF34" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>27.62</t>
         </is>
       </c>
       <c r="BG34" t="inlineStr"/>
       <c r="BH34" t="inlineStr"/>
       <c r="BI34" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ34" t="inlineStr"/>
@@ -9871,27 +9867,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>666160</t>
+          <t>596019</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Mickey Moniak</t>
+          <t>Francisco Lindor</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-23T00:10:00Z</t>
+          <t>2026-08-22T23:10:00Z</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -9901,17 +9897,17 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Tanner Bibee</t>
+          <t>Luis Castillo</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>676440</t>
+          <t>622491</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -9920,7 +9916,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>53.9</v>
+        <v>53.6</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -9934,26 +9930,26 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>48.7</v>
+        <v>46.1</v>
       </c>
       <c r="Q35" t="n">
-        <v>43.8</v>
+        <v>52.6</v>
       </c>
       <c r="R35" t="n">
-        <v>38.7</v>
+        <v>27.6</v>
       </c>
       <c r="S35" t="n">
-        <v>92.09999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="T35" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U35" t="n">
-        <v>28.1</v>
+        <v>30.3</v>
       </c>
       <c r="V35" t="inlineStr">
         <is>
@@ -9967,7 +9963,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
@@ -10014,7 +10010,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
@@ -10024,119 +10020,119 @@
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/27, 1 HR</t>
+          <t>Last 7 games: 5/25, 1 HR</t>
         </is>
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.2% barrel, 25.6 HR allowed</t>
+          <t>switch hitter; pitcher baseline 10.1% barrel, 20.2 HR allowed</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>11.56</t>
+          <t>9.18</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>42.92</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>89.49</t>
+          <t>91.13</t>
         </is>
       </c>
       <c r="AQ35" t="inlineStr">
         <is>
-          <t>100.3022</t>
+          <t>100.2887</t>
         </is>
       </c>
       <c r="AR35" t="inlineStr">
         <is>
-          <t>0.4375</t>
+          <t>0.4512</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr">
         <is>
-          <t>0.2056</t>
+          <t>0.1982</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr">
         <is>
-          <t>0.3055</t>
+          <t>0.345</t>
         </is>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>74.19</t>
+          <t>72.02</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>43.81</t>
+          <t>22.32</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>45.89</t>
+          <t>45.88</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>38.17</t>
+          <t>30.51</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>0.2634</t>
+          <t>0.1885</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>8.24</t>
+          <t>10.05</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>38.49</t>
+          <t>43.18</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
         <is>
-          <t>89.13</t>
+          <t>90.09</t>
         </is>
       </c>
       <c r="BD35" t="inlineStr">
         <is>
-          <t>0.4116</t>
+          <t>0.4425</t>
         </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
-          <t>0.1674</t>
+          <t>0.1814</t>
         </is>
       </c>
       <c r="BF35" t="inlineStr">
         <is>
-          <t>27.62</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="BG35" t="inlineStr"/>
       <c r="BH35" t="inlineStr"/>
       <c r="BI35" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ35" t="inlineStr"/>
@@ -10147,27 +10143,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>596019</t>
+          <t>665833</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Francisco Lindor</t>
+          <t>Oneil Cruz</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-22T23:10:00Z</t>
+          <t>2026-08-22T23:15:00Z</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -10177,22 +10173,22 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Luis Castillo</t>
+          <t>Tarik Skubal</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>622491</t>
+          <t>669373</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L36" t="n">
@@ -10210,26 +10206,26 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Elite Power, Strong Barrel</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>46.1</v>
+        <v>75</v>
       </c>
       <c r="Q36" t="n">
-        <v>52.6</v>
+        <v>28.8</v>
       </c>
       <c r="R36" t="n">
         <v>27.6</v>
       </c>
       <c r="S36" t="n">
-        <v>95.5</v>
+        <v>71.7</v>
       </c>
       <c r="T36" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U36" t="n">
-        <v>30.3</v>
+        <v>65.5</v>
       </c>
       <c r="V36" t="inlineStr">
         <is>
@@ -10243,7 +10239,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
@@ -10290,129 +10286,129 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL36" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 10.1% barrel, 20.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.5% barrel, 13.8 HR allowed</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>9.18</t>
+          <t>17.51</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>57.72</t>
         </is>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>91.13</t>
+          <t>95.8</t>
         </is>
       </c>
       <c r="AQ36" t="inlineStr">
         <is>
-          <t>100.2887</t>
+          <t>107.1338</t>
         </is>
       </c>
       <c r="AR36" t="inlineStr">
         <is>
-          <t>0.4512</t>
+          <t>0.4817</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr">
         <is>
-          <t>0.1982</t>
+          <t>0.2371</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr">
         <is>
-          <t>0.345</t>
+          <t>0.3527</t>
         </is>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>72.02</t>
+          <t>78.45</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>22.32</t>
+          <t>76.94</t>
         </is>
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>40.09</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>30.51</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>0.1885</t>
+          <t>0.2102</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>10.05</t>
+          <t>7.54</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
         <is>
-          <t>43.18</t>
+          <t>35.38</t>
         </is>
       </c>
       <c r="BC36" t="inlineStr">
         <is>
-          <t>90.09</t>
+          <t>86.94</t>
         </is>
       </c>
       <c r="BD36" t="inlineStr">
         <is>
-          <t>0.4425</t>
+          <t>0.3433</t>
         </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
-          <t>0.1814</t>
+          <t>0.1233</t>
         </is>
       </c>
       <c r="BF36" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>26.32</t>
         </is>
       </c>
       <c r="BG36" t="inlineStr"/>
       <c r="BH36" t="inlineStr"/>
       <c r="BI36" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ36" t="inlineStr"/>
@@ -10423,47 +10419,47 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>665833</t>
+          <t>665489</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Oneil Cruz</t>
+          <t>Vladimir Guerrero Jr.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-22T23:15:00Z</t>
+          <t>2026-08-22T17:35:00Z</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Tarik Skubal</t>
+          <t>Ryan Weathers</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>669373</t>
+          <t>677960</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -10472,7 +10468,7 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>53.6</v>
+        <v>53.3</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -10486,62 +10482,58 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>75</v>
+        <v>39.5</v>
       </c>
       <c r="Q37" t="n">
-        <v>28.8</v>
+        <v>45.5</v>
       </c>
       <c r="R37" t="n">
-        <v>27.6</v>
+        <v>48.2</v>
       </c>
       <c r="S37" t="n">
-        <v>71.7</v>
+        <v>100</v>
       </c>
       <c r="T37" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U37" t="n">
-        <v>65.5</v>
+        <v>22.4</v>
       </c>
       <c r="V37" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10561,134 +10553,142 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 7/26, 0 HR</t>
         </is>
       </c>
       <c r="AL37" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.5% barrel, 13.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 14.7 HR allowed</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>17.51</t>
+          <t>8.42</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>57.72</t>
+          <t>45.31</t>
         </is>
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>95.8</t>
+          <t>90.74</t>
         </is>
       </c>
       <c r="AQ37" t="inlineStr">
         <is>
-          <t>107.1338</t>
+          <t>102.9852</t>
         </is>
       </c>
       <c r="AR37" t="inlineStr">
         <is>
-          <t>0.4817</t>
+          <t>0.4311</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr">
         <is>
-          <t>0.2371</t>
+          <t>0.1444</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr">
         <is>
-          <t>0.3527</t>
+          <t>0.3483</t>
         </is>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>78.45</t>
+          <t>76.35</t>
         </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
-          <t>76.94</t>
+          <t>63.54</t>
         </is>
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>40.09</t>
+          <t>35.6</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>19.38</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>11.8</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>0.2102</t>
+          <t>0.1176</t>
         </is>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
-          <t>7.54</t>
+          <t>8.76</t>
         </is>
       </c>
       <c r="BB37" t="inlineStr">
         <is>
-          <t>35.38</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="BC37" t="inlineStr">
         <is>
-          <t>86.94</t>
+          <t>89.46</t>
         </is>
       </c>
       <c r="BD37" t="inlineStr">
         <is>
-          <t>0.3433</t>
+          <t>0.4173</t>
         </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
-          <t>0.1233</t>
+          <t>0.1708</t>
         </is>
       </c>
       <c r="BF37" t="inlineStr">
         <is>
-          <t>26.32</t>
-        </is>
-      </c>
-      <c r="BG37" t="inlineStr"/>
-      <c r="BH37" t="inlineStr"/>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="BG37" t="inlineStr">
+        <is>
+          <t>In From LF</t>
+        </is>
+      </c>
+      <c r="BH37" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
       <c r="BI37" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ37" t="inlineStr"/>
@@ -11803,52 +11803,52 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>672386</t>
+          <t>687605</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Alejandro Kirk</t>
+          <t>Andrew Pinckney</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-22T17:35:00Z</t>
+          <t>2026-08-22T20:10:00Z</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Ryan Weathers</t>
+          <t>Eury Pérez</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>677960</t>
+          <t>691587</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L42" t="n">
@@ -11866,26 +11866,26 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Elite Power, Strong Barrel</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>27.5</v>
+        <v>78.8</v>
       </c>
       <c r="Q42" t="n">
-        <v>45.5</v>
+        <v>43.1</v>
       </c>
       <c r="R42" t="n">
-        <v>48.2</v>
+        <v>35</v>
       </c>
       <c r="S42" t="n">
-        <v>96.59999999999999</v>
+        <v>44.8</v>
       </c>
       <c r="T42" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U42" t="n">
-        <v>100</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="V42" t="inlineStr">
         <is>
@@ -11899,7 +11899,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
@@ -11920,7 +11920,7 @@
       <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD42" t="inlineStr"/>
@@ -11937,142 +11937,142 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Last 7 games: 2/11, 0 HR</t>
         </is>
       </c>
       <c r="AL42" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 14.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.1% barrel, 12.7 HR allowed</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>41.63</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>88.72</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="AQ42" t="inlineStr">
         <is>
-          <t>100.0105</t>
+          <t>104.4172</t>
         </is>
       </c>
       <c r="AR42" t="inlineStr">
         <is>
-          <t>0.4002</t>
+          <t>0.483</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr">
         <is>
-          <t>0.1351</t>
+          <t>0.235</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr">
         <is>
-          <t>0.324</t>
+          <t>0.378</t>
         </is>
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
-          <t>19.86</t>
+          <t>61.1</t>
         </is>
       </c>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>26.56</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>0.1453</t>
+          <t>0.384</t>
         </is>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
-          <t>8.76</t>
+          <t>9.14</t>
         </is>
       </c>
       <c r="BB42" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>41.81</t>
         </is>
       </c>
       <c r="BC42" t="inlineStr">
         <is>
-          <t>89.46</t>
+          <t>88.96</t>
         </is>
       </c>
       <c r="BD42" t="inlineStr">
         <is>
-          <t>0.4173</t>
+          <t>0.3618</t>
         </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
-          <t>0.1708</t>
+          <t>0.1553</t>
         </is>
       </c>
       <c r="BF42" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>30.45</t>
         </is>
       </c>
       <c r="BG42" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI42" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>loanDepot park</t>
         </is>
       </c>
       <c r="BJ42" t="inlineStr"/>
@@ -12083,56 +12083,56 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>687605</t>
+          <t>543807</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Andrew Pinckney</t>
+          <t>George Springer</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-22T20:10:00Z</t>
+          <t>2026-08-22T17:35:00Z</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Eury Pérez</t>
+          <t>Ryan Weathers</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>691587</t>
+          <t>677960</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>52.8</v>
+        <v>52.6</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
@@ -12146,26 +12146,26 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Elite Power, Strong Barrel</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P43" t="n">
-        <v>78.8</v>
+        <v>38.6</v>
       </c>
       <c r="Q43" t="n">
-        <v>43.1</v>
+        <v>45.5</v>
       </c>
       <c r="R43" t="n">
-        <v>35</v>
+        <v>48.2</v>
       </c>
       <c r="S43" t="n">
-        <v>44.8</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T43" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U43" t="n">
-        <v>9.300000000000001</v>
+        <v>27</v>
       </c>
       <c r="V43" t="inlineStr">
         <is>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
@@ -12200,7 +12200,7 @@
       <c r="AB43" t="inlineStr"/>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD43" t="inlineStr"/>
@@ -12217,12 +12217,12 @@
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ43" t="inlineStr">
@@ -12232,127 +12232,127 @@
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/11, 0 HR</t>
+          <t>Last 7 games: 6/20, 0 HR</t>
         </is>
       </c>
       <c r="AL43" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.1% barrel, 12.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 14.7 HR allowed</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>EV profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>9.48</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>88.67</t>
         </is>
       </c>
       <c r="AQ43" t="inlineStr">
         <is>
-          <t>104.4172</t>
+          <t>100.034</t>
         </is>
       </c>
       <c r="AR43" t="inlineStr">
         <is>
-          <t>0.483</t>
+          <t>0.4289</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>0.1806</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr">
         <is>
-          <t>0.378</t>
+          <t>0.3326</t>
         </is>
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>74.9</t>
+          <t>73.24</t>
         </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
-          <t>61.1</t>
+          <t>34.74</t>
         </is>
       </c>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>40.74</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>26.58</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>0.384</t>
+          <t>0.1817</t>
         </is>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>8.76</t>
         </is>
       </c>
       <c r="BB43" t="inlineStr">
         <is>
-          <t>41.81</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="BC43" t="inlineStr">
         <is>
-          <t>88.96</t>
+          <t>89.46</t>
         </is>
       </c>
       <c r="BD43" t="inlineStr">
         <is>
-          <t>0.3618</t>
+          <t>0.4173</t>
         </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
-          <t>0.1553</t>
+          <t>0.1708</t>
         </is>
       </c>
       <c r="BF43" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="BG43" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI43" t="inlineStr">
         <is>
-          <t>loanDepot park</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ43" t="inlineStr"/>
@@ -13695,52 +13695,52 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>543807</t>
+          <t>669394</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>George Springer</t>
+          <t>Jake Burger</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-22T17:35:00Z</t>
+          <t>2026-08-22T23:05:00Z</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Ryan Weathers</t>
+          <t>Ryan Johnson</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>677960</t>
+          <t>696270</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L49" t="n">
@@ -13758,58 +13758,62 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>38.6</v>
+        <v>47.8</v>
       </c>
       <c r="Q49" t="n">
-        <v>45.5</v>
+        <v>50.2</v>
       </c>
       <c r="R49" t="n">
-        <v>48.2</v>
+        <v>27.6</v>
       </c>
       <c r="S49" t="n">
-        <v>94.90000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T49" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U49" t="n">
-        <v>16.1</v>
+        <v>53.3</v>
       </c>
       <c r="V49" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W49" t="inlineStr">
+      <c r="Z49" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC49" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -13829,142 +13833,134 @@
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/22, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL49" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 14.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.4% barrel, 12.4 HR allowed</t>
         </is>
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>9.48</t>
+          <t>11.73</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>46.89</t>
         </is>
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>88.67</t>
+          <t>89.98</t>
         </is>
       </c>
       <c r="AQ49" t="inlineStr">
         <is>
-          <t>100.034</t>
+          <t>102.6591</t>
         </is>
       </c>
       <c r="AR49" t="inlineStr">
         <is>
-          <t>0.4289</t>
+          <t>0.4199</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr">
         <is>
-          <t>0.1806</t>
+          <t>0.1851</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr">
         <is>
-          <t>0.3326</t>
+          <t>0.3072</t>
         </is>
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>73.24</t>
+          <t>75.37</t>
         </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
-          <t>34.74</t>
+          <t>58.07</t>
         </is>
       </c>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>40.74</t>
+          <t>41.88</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>26.58</t>
+          <t>27.76</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>0.1817</t>
+          <t>0.1816</t>
         </is>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
-          <t>8.76</t>
+          <t>10.39</t>
         </is>
       </c>
       <c r="BB49" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>36.84</t>
         </is>
       </c>
       <c r="BC49" t="inlineStr">
         <is>
-          <t>89.46</t>
+          <t>87.82</t>
         </is>
       </c>
       <c r="BD49" t="inlineStr">
         <is>
-          <t>0.4173</t>
+          <t>0.4535</t>
         </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
-          <t>0.1708</t>
+          <t>0.1945</t>
         </is>
       </c>
       <c r="BF49" t="inlineStr">
         <is>
-          <t>25.2</t>
-        </is>
-      </c>
-      <c r="BG49" t="inlineStr">
-        <is>
-          <t>In From LF</t>
-        </is>
-      </c>
-      <c r="BH49" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
+          <t>33.95</t>
+        </is>
+      </c>
+      <c r="BG49" t="inlineStr"/>
+      <c r="BH49" t="inlineStr"/>
       <c r="BI49" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ49" t="inlineStr"/>
@@ -13975,56 +13971,56 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>669394</t>
+          <t>683734</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Jake Burger</t>
+          <t>Andrew Vaughn</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-22T23:05:00Z</t>
+          <t>2026-08-22T18:10:00Z</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Ryan Johnson</t>
+          <t>Martín Pérez</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>696270</t>
+          <t>527048</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>52</v>
+        <v>51.9</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
@@ -14038,62 +14034,58 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>47.8</v>
+        <v>35</v>
       </c>
       <c r="Q50" t="n">
-        <v>50.2</v>
+        <v>38</v>
       </c>
       <c r="R50" t="n">
-        <v>27.6</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="S50" t="n">
-        <v>92.09999999999999</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T50" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U50" t="n">
-        <v>53.3</v>
+        <v>39.1</v>
       </c>
       <c r="V50" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W50" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y50" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr"/>
       <c r="AC50" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -14113,134 +14105,142 @@
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 8/21 over last 7 games</t>
         </is>
       </c>
       <c r="AL50" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.4% barrel, 12.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.1% barrel, 9.5 HR allowed</t>
         </is>
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN50" t="inlineStr">
         <is>
-          <t>11.73</t>
+          <t>7.59</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>46.89</t>
+          <t>44.41</t>
         </is>
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>89.98</t>
+          <t>90.41</t>
         </is>
       </c>
       <c r="AQ50" t="inlineStr">
         <is>
-          <t>102.6591</t>
+          <t>100.217</t>
         </is>
       </c>
       <c r="AR50" t="inlineStr">
         <is>
-          <t>0.4199</t>
+          <t>0.4195</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr">
         <is>
-          <t>0.1851</t>
+          <t>0.1479</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr">
         <is>
-          <t>0.3072</t>
+          <t>0.3434</t>
         </is>
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>75.37</t>
+          <t>70.53</t>
         </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
-          <t>58.07</t>
+          <t>13.64</t>
         </is>
       </c>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>41.88</t>
+          <t>36.31</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>27.76</t>
+          <t>24.41</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>0.1816</t>
+          <t>0.1535</t>
         </is>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
-          <t>10.39</t>
+          <t>8.14</t>
         </is>
       </c>
       <c r="BB50" t="inlineStr">
         <is>
-          <t>36.84</t>
+          <t>37.86</t>
         </is>
       </c>
       <c r="BC50" t="inlineStr">
         <is>
-          <t>87.82</t>
+          <t>88.13</t>
         </is>
       </c>
       <c r="BD50" t="inlineStr">
         <is>
-          <t>0.4535</t>
+          <t>0.4171</t>
         </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
-          <t>0.1945</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="BF50" t="inlineStr">
         <is>
-          <t>33.95</t>
-        </is>
-      </c>
-      <c r="BG50" t="inlineStr"/>
-      <c r="BH50" t="inlineStr"/>
+          <t>24.2</t>
+        </is>
+      </c>
+      <c r="BG50" t="inlineStr">
+        <is>
+          <t>Out To CF</t>
+        </is>
+      </c>
+      <c r="BH50" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
       <c r="BI50" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ50" t="inlineStr"/>
@@ -14251,47 +14251,47 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>683734</t>
+          <t>672386</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Andrew Vaughn</t>
+          <t>Alejandro Kirk</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-22T18:10:00Z</t>
+          <t>2026-08-22T17:35:00Z</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Martín Pérez</t>
+          <t>Ryan Weathers</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>527048</t>
+          <t>677960</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -14300,7 +14300,7 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>51.9</v>
+        <v>51.8</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
@@ -14314,26 +14314,26 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>35</v>
+        <v>27.5</v>
       </c>
       <c r="Q51" t="n">
-        <v>38</v>
+        <v>45.5</v>
       </c>
       <c r="R51" t="n">
-        <v>67.59999999999999</v>
+        <v>48.2</v>
       </c>
       <c r="S51" t="n">
-        <v>86.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T51" t="n">
         <v>78</v>
       </c>
       <c r="U51" t="n">
-        <v>39.1</v>
+        <v>81.2</v>
       </c>
       <c r="V51" t="inlineStr">
         <is>
@@ -14347,7 +14347,7 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
@@ -14385,27 +14385,27 @@
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Contact streak: 8/21 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL51" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.1% barrel, 9.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 14.7 HR allowed</t>
         </is>
       </c>
       <c r="AM51" t="inlineStr">
@@ -14415,112 +14415,112 @@
       </c>
       <c r="AN51" t="inlineStr">
         <is>
-          <t>7.59</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>44.41</t>
+          <t>41.63</t>
         </is>
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>90.41</t>
+          <t>88.72</t>
         </is>
       </c>
       <c r="AQ51" t="inlineStr">
         <is>
-          <t>100.217</t>
+          <t>100.0105</t>
         </is>
       </c>
       <c r="AR51" t="inlineStr">
         <is>
-          <t>0.4195</t>
+          <t>0.4002</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr">
         <is>
-          <t>0.1479</t>
+          <t>0.1351</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr">
         <is>
-          <t>0.3434</t>
+          <t>0.324</t>
         </is>
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>70.53</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
-          <t>13.64</t>
+          <t>19.86</t>
         </is>
       </c>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>36.31</t>
+          <t>26.56</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>24.41</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>0.1535</t>
+          <t>0.1453</t>
         </is>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
-          <t>8.14</t>
+          <t>8.76</t>
         </is>
       </c>
       <c r="BB51" t="inlineStr">
         <is>
-          <t>37.86</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="BC51" t="inlineStr">
         <is>
-          <t>88.13</t>
+          <t>89.46</t>
         </is>
       </c>
       <c r="BD51" t="inlineStr">
         <is>
-          <t>0.4171</t>
+          <t>0.4173</t>
         </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.1708</t>
         </is>
       </c>
       <c r="BF51" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="BG51" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI51" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ51" t="inlineStr"/>
@@ -15879,32 +15879,32 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>663757</t>
+          <t>641933</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Trent Grisham</t>
+          <t>Tyler O'Neill</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-22T17:35:00Z</t>
+          <t>2026-08-22T23:05:00Z</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -15914,21 +15914,21 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Dylan Cease</t>
+          <t>Shane McClanahan</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>656302</t>
+          <t>663556</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>51.1</v>
+        <v>51</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
@@ -15942,61 +15942,65 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P57" t="n">
-        <v>48.6</v>
+        <v>47.3</v>
       </c>
       <c r="Q57" t="n">
-        <v>20.3</v>
+        <v>43.4</v>
       </c>
       <c r="R57" t="n">
-        <v>48.2</v>
+        <v>32.1</v>
       </c>
       <c r="S57" t="n">
-        <v>93.2</v>
+        <v>88.7</v>
       </c>
       <c r="T57" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U57" t="n">
-        <v>54.7</v>
+        <v>14.6</v>
       </c>
       <c r="V57" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W57" t="inlineStr">
+      <c r="Z57" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y57" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD57" t="inlineStr"/>
@@ -16013,142 +16017,134 @@
       </c>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/23, 0 HR</t>
         </is>
       </c>
       <c r="AL57" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.0% barrel, 12.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 8.0 HR allowed</t>
         </is>
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN57" t="inlineStr">
         <is>
-          <t>11.19</t>
+          <t>11.25</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>46.26</t>
+          <t>41.97</t>
         </is>
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>90.89</t>
+          <t>89.22</t>
         </is>
       </c>
       <c r="AQ57" t="inlineStr">
         <is>
-          <t>100.9592</t>
+          <t>100.334</t>
         </is>
       </c>
       <c r="AR57" t="inlineStr">
         <is>
-          <t>0.4567</t>
+          <t>0.4355</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr">
         <is>
-          <t>0.208</t>
+          <t>0.2114</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr">
         <is>
-          <t>0.3497</t>
+          <t>0.325</t>
         </is>
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>70.72</t>
+          <t>72.81</t>
         </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
-          <t>8.81</t>
+          <t>23.68</t>
         </is>
       </c>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>46.68</t>
+          <t>44.95</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>31.05</t>
+          <t>39.28</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>0.2066</t>
+          <t>0.1748</t>
         </is>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="BB57" t="inlineStr">
         <is>
-          <t>33.93</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="BC57" t="inlineStr">
         <is>
-          <t>86.73</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="BD57" t="inlineStr">
         <is>
-          <t>0.3009</t>
+          <t>0.405</t>
         </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
-          <t>0.1086</t>
+          <t>0.164</t>
         </is>
       </c>
       <c r="BF57" t="inlineStr">
         <is>
-          <t>25.47</t>
-        </is>
-      </c>
-      <c r="BG57" t="inlineStr">
-        <is>
-          <t>In From LF</t>
-        </is>
-      </c>
-      <c r="BH57" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
+          <t>27.7</t>
+        </is>
+      </c>
+      <c r="BG57" t="inlineStr"/>
+      <c r="BH57" t="inlineStr"/>
       <c r="BI57" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ57" t="inlineStr"/>
@@ -16159,27 +16155,27 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>641933</t>
+          <t>701807</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Tyler O'Neill</t>
+          <t>Carson Benge</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-08-22T23:05:00Z</t>
+          <t>2026-08-22T23:10:00Z</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -16189,22 +16185,22 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Shane McClanahan</t>
+          <t>Luis Castillo</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>663556</t>
+          <t>622491</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L58" t="n">
@@ -16222,26 +16218,26 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P58" t="n">
-        <v>47.3</v>
+        <v>33.7</v>
       </c>
       <c r="Q58" t="n">
-        <v>43.4</v>
+        <v>54.7</v>
       </c>
       <c r="R58" t="n">
-        <v>32.1</v>
+        <v>27.6</v>
       </c>
       <c r="S58" t="n">
-        <v>88.7</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T58" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U58" t="n">
-        <v>14.6</v>
+        <v>54.7</v>
       </c>
       <c r="V58" t="inlineStr">
         <is>
@@ -16255,7 +16251,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr">
@@ -16280,7 +16276,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD58" t="inlineStr"/>
@@ -16297,134 +16293,134 @@
       </c>
       <c r="AH58" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/23, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL58" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 8.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.1% barrel, 20.2 HR allowed</t>
         </is>
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN58" t="inlineStr">
         <is>
-          <t>11.25</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>41.97</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>89.22</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AQ58" t="inlineStr">
         <is>
-          <t>100.334</t>
+          <t>99.9721</t>
         </is>
       </c>
       <c r="AR58" t="inlineStr">
         <is>
-          <t>0.4355</t>
+          <t>0.437</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr">
         <is>
-          <t>0.2114</t>
+          <t>0.158</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>72.81</t>
+          <t>70.9</t>
         </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
-          <t>23.68</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>44.95</t>
+          <t>32.4</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>39.28</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>0.1748</t>
+          <t>0.145</t>
         </is>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>10.05</t>
         </is>
       </c>
       <c r="BB58" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>43.18</t>
         </is>
       </c>
       <c r="BC58" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>90.09</t>
         </is>
       </c>
       <c r="BD58" t="inlineStr">
         <is>
-          <t>0.405</t>
+          <t>0.4425</t>
         </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>0.1814</t>
         </is>
       </c>
       <c r="BF58" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="BG58" t="inlineStr"/>
       <c r="BH58" t="inlineStr"/>
       <c r="BI58" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ58" t="inlineStr"/>
@@ -16435,27 +16431,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>701807</t>
+          <t>575929</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Carson Benge</t>
+          <t>Willson Contreras</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-22T23:10:00Z</t>
+          <t>2026-08-22T23:15:00Z</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -16470,12 +16466,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Luis Castillo</t>
+          <t>Blade Tidwell</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>622491</t>
+          <t>694918</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -16484,7 +16480,7 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>51</v>
+        <v>50.9</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
@@ -16498,26 +16494,26 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>33.7</v>
+        <v>59.1</v>
       </c>
       <c r="Q59" t="n">
-        <v>54.7</v>
+        <v>26.2</v>
       </c>
       <c r="R59" t="n">
-        <v>27.6</v>
+        <v>28.7</v>
       </c>
       <c r="S59" t="n">
         <v>90.40000000000001</v>
       </c>
       <c r="T59" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U59" t="n">
-        <v>54.7</v>
+        <v>72.7</v>
       </c>
       <c r="V59" t="inlineStr">
         <is>
@@ -16556,7 +16552,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD59" t="inlineStr"/>
@@ -16573,7 +16569,7 @@
       </c>
       <c r="AH59" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI59" t="inlineStr">
@@ -16593,7 +16589,7 @@
       </c>
       <c r="AL59" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.1% barrel, 20.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.5% barrel, 2.6 HR allowed</t>
         </is>
       </c>
       <c r="AM59" t="inlineStr">
@@ -16603,104 +16599,104 @@
       </c>
       <c r="AN59" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>14.32</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>46.13</t>
         </is>
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>90.18</t>
         </is>
       </c>
       <c r="AQ59" t="inlineStr">
         <is>
-          <t>99.9721</t>
+          <t>102.9905</t>
         </is>
       </c>
       <c r="AR59" t="inlineStr">
         <is>
-          <t>0.437</t>
+          <t>0.4999</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr">
         <is>
-          <t>0.158</t>
+          <t>0.2401</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.3776</t>
         </is>
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>70.9</t>
+          <t>76.77</t>
         </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>68.73</t>
         </is>
       </c>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>32.4</t>
+          <t>44.98</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>29.54</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>0.2362</t>
         </is>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
-          <t>10.05</t>
+          <t>6.51</t>
         </is>
       </c>
       <c r="BB59" t="inlineStr">
         <is>
-          <t>43.18</t>
+          <t>36.64</t>
         </is>
       </c>
       <c r="BC59" t="inlineStr">
         <is>
-          <t>90.09</t>
+          <t>87.78</t>
         </is>
       </c>
       <c r="BD59" t="inlineStr">
         <is>
-          <t>0.4425</t>
+          <t>0.3849</t>
         </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
-          <t>0.1814</t>
+          <t>0.125</t>
         </is>
       </c>
       <c r="BF59" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>21.73</t>
         </is>
       </c>
       <c r="BG59" t="inlineStr"/>
       <c r="BH59" t="inlineStr"/>
       <c r="BI59" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Fenway Park</t>
         </is>
       </c>
       <c r="BJ59" t="inlineStr"/>
@@ -16711,32 +16707,32 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>575929</t>
+          <t>671277</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Willson Contreras</t>
+          <t>Luis García Jr.</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-22T23:15:00Z</t>
+          <t>2026-08-22T17:35:00Z</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -16746,12 +16742,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Blade Tidwell</t>
+          <t>Dylan Cease</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>694918</t>
+          <t>656302</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -16760,7 +16756,7 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
@@ -16774,62 +16770,58 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P60" t="n">
-        <v>59.1</v>
+        <v>49.6</v>
       </c>
       <c r="Q60" t="n">
-        <v>26.2</v>
+        <v>20.3</v>
       </c>
       <c r="R60" t="n">
-        <v>28.7</v>
+        <v>48.2</v>
       </c>
       <c r="S60" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T60" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U60" t="n">
-        <v>72.7</v>
+        <v>36.3</v>
       </c>
       <c r="V60" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W60" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y60" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr"/>
       <c r="AC60" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -16849,7 +16841,7 @@
       </c>
       <c r="AH60" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI60" t="inlineStr">
@@ -16859,17 +16851,17 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/25, 1 HR</t>
         </is>
       </c>
       <c r="AL60" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.5% barrel, 2.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM60" t="inlineStr">
@@ -16879,104 +16871,112 @@
       </c>
       <c r="AN60" t="inlineStr">
         <is>
-          <t>14.32</t>
+          <t>11.17</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>46.13</t>
+          <t>46.08</t>
         </is>
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>90.18</t>
+          <t>91.18</t>
         </is>
       </c>
       <c r="AQ60" t="inlineStr">
         <is>
-          <t>102.9905</t>
+          <t>101.8604</t>
         </is>
       </c>
       <c r="AR60" t="inlineStr">
         <is>
-          <t>0.4999</t>
+          <t>0.4889</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr">
         <is>
-          <t>0.2401</t>
+          <t>0.2051</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr">
         <is>
-          <t>0.3776</t>
+          <t>0.3453</t>
         </is>
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>76.77</t>
+          <t>73.66</t>
         </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
-          <t>68.73</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>44.98</t>
+          <t>40.66</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>29.54</t>
+          <t>22.68</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>0.2362</t>
+          <t>0.2314</t>
         </is>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="BB60" t="inlineStr">
         <is>
-          <t>36.64</t>
+          <t>33.93</t>
         </is>
       </c>
       <c r="BC60" t="inlineStr">
         <is>
-          <t>87.78</t>
+          <t>86.73</t>
         </is>
       </c>
       <c r="BD60" t="inlineStr">
         <is>
-          <t>0.3849</t>
+          <t>0.3009</t>
         </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>0.1086</t>
         </is>
       </c>
       <c r="BF60" t="inlineStr">
         <is>
-          <t>21.73</t>
-        </is>
-      </c>
-      <c r="BG60" t="inlineStr"/>
-      <c r="BH60" t="inlineStr"/>
+          <t>25.47</t>
+        </is>
+      </c>
+      <c r="BG60" t="inlineStr">
+        <is>
+          <t>In From LF</t>
+        </is>
+      </c>
+      <c r="BH60" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
       <c r="BI60" t="inlineStr">
         <is>
-          <t>Fenway Park</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ60" t="inlineStr"/>
@@ -16987,47 +16987,47 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>671277</t>
+          <t>676724</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Luis García Jr.</t>
+          <t>Jared Young</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-22T17:35:00Z</t>
+          <t>2026-08-22T23:10:00Z</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Dylan Cease</t>
+          <t>Luis Castillo</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>656302</t>
+          <t>622491</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -17036,7 +17036,7 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>50.8</v>
+        <v>50.7</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
@@ -17050,58 +17050,62 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P61" t="n">
-        <v>49.6</v>
+        <v>41.6</v>
       </c>
       <c r="Q61" t="n">
-        <v>20.3</v>
+        <v>54.7</v>
       </c>
       <c r="R61" t="n">
-        <v>48.2</v>
+        <v>27.6</v>
       </c>
       <c r="S61" t="n">
-        <v>94.90000000000001</v>
+        <v>71.7</v>
       </c>
       <c r="T61" t="n">
         <v>80</v>
       </c>
       <c r="U61" t="n">
-        <v>36.3</v>
+        <v>50.3</v>
       </c>
       <c r="V61" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W61" t="inlineStr">
+      <c r="Z61" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y61" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC61" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -17121,12 +17125,12 @@
       </c>
       <c r="AH61" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ61" t="inlineStr">
@@ -17136,12 +17140,12 @@
       </c>
       <c r="AK61" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 1 HR</t>
+          <t>Contact streak: 8/24 over last 7 games</t>
         </is>
       </c>
       <c r="AL61" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.0% barrel, 12.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.1% barrel, 20.2 HR allowed</t>
         </is>
       </c>
       <c r="AM61" t="inlineStr">
@@ -17151,112 +17155,104 @@
       </c>
       <c r="AN61" t="inlineStr">
         <is>
-          <t>11.17</t>
+          <t>9.96</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>46.08</t>
+          <t>44.69</t>
         </is>
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>91.18</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="AQ61" t="inlineStr">
         <is>
-          <t>101.8604</t>
+          <t>101.1371</t>
         </is>
       </c>
       <c r="AR61" t="inlineStr">
         <is>
-          <t>0.4889</t>
+          <t>0.4238</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr">
         <is>
-          <t>0.2051</t>
+          <t>0.1892</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr">
         <is>
-          <t>0.3453</t>
+          <t>0.3156</t>
         </is>
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>73.66</t>
+          <t>73.44</t>
         </is>
       </c>
       <c r="AV61" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>33.88</t>
         </is>
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>40.66</t>
+          <t>39.02</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>22.68</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>0.2314</t>
+          <t>0.2117</t>
         </is>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>10.05</t>
         </is>
       </c>
       <c r="BB61" t="inlineStr">
         <is>
-          <t>33.93</t>
+          <t>43.18</t>
         </is>
       </c>
       <c r="BC61" t="inlineStr">
         <is>
-          <t>86.73</t>
+          <t>90.09</t>
         </is>
       </c>
       <c r="BD61" t="inlineStr">
         <is>
-          <t>0.3009</t>
+          <t>0.4425</t>
         </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
-          <t>0.1086</t>
+          <t>0.1814</t>
         </is>
       </c>
       <c r="BF61" t="inlineStr">
         <is>
-          <t>25.47</t>
-        </is>
-      </c>
-      <c r="BG61" t="inlineStr">
-        <is>
-          <t>In From LF</t>
-        </is>
-      </c>
-      <c r="BH61" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
+          <t>28.0</t>
+        </is>
+      </c>
+      <c r="BG61" t="inlineStr"/>
+      <c r="BH61" t="inlineStr"/>
       <c r="BI61" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ61" t="inlineStr"/>
@@ -17267,56 +17263,56 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>676724</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Jared Young</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-22T23:10:00Z</t>
+          <t>2026-08-22T18:10:00Z</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Luis Castillo</t>
+          <t>Martín Pérez</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>622491</t>
+          <t>527048</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>50.7</v>
+        <v>50.2</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
@@ -17330,62 +17326,58 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P62" t="n">
-        <v>41.6</v>
+        <v>37.2</v>
       </c>
       <c r="Q62" t="n">
-        <v>54.7</v>
+        <v>38</v>
       </c>
       <c r="R62" t="n">
-        <v>27.6</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="S62" t="n">
-        <v>71.7</v>
+        <v>100</v>
       </c>
       <c r="T62" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U62" t="n">
-        <v>50.3</v>
+        <v>2.7</v>
       </c>
       <c r="V62" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W62" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y62" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr"/>
       <c r="AC62" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -17405,27 +17397,27 @@
       </c>
       <c r="AH62" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
         <is>
-          <t>Contact streak: 8/24 over last 7 games</t>
+          <t>Last 7 games: 4/29, 0 HR</t>
         </is>
       </c>
       <c r="AL62" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.1% barrel, 20.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.1% barrel, 9.5 HR allowed</t>
         </is>
       </c>
       <c r="AM62" t="inlineStr">
@@ -17435,104 +17427,112 @@
       </c>
       <c r="AN62" t="inlineStr">
         <is>
-          <t>9.96</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>44.69</t>
+          <t>43.83</t>
         </is>
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>88.59</t>
+          <t>90.61</t>
         </is>
       </c>
       <c r="AQ62" t="inlineStr">
         <is>
-          <t>101.1371</t>
+          <t>100.4505</t>
         </is>
       </c>
       <c r="AR62" t="inlineStr">
         <is>
-          <t>0.4238</t>
+          <t>0.4304</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr">
         <is>
-          <t>0.1892</t>
+          <t>0.1733</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr">
         <is>
-          <t>0.3156</t>
+          <t>0.3406</t>
         </is>
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>73.44</t>
+          <t>70.11</t>
         </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
-          <t>33.88</t>
+          <t>12.99</t>
         </is>
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>39.02</t>
+          <t>27.44</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>24.27</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>0.2117</t>
+          <t>0.1673</t>
         </is>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
-          <t>10.05</t>
+          <t>8.14</t>
         </is>
       </c>
       <c r="BB62" t="inlineStr">
         <is>
-          <t>43.18</t>
+          <t>37.86</t>
         </is>
       </c>
       <c r="BC62" t="inlineStr">
         <is>
-          <t>90.09</t>
+          <t>88.13</t>
         </is>
       </c>
       <c r="BD62" t="inlineStr">
         <is>
-          <t>0.4425</t>
+          <t>0.4171</t>
         </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
-          <t>0.1814</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="BF62" t="inlineStr">
         <is>
-          <t>28.0</t>
-        </is>
-      </c>
-      <c r="BG62" t="inlineStr"/>
-      <c r="BH62" t="inlineStr"/>
+          <t>24.2</t>
+        </is>
+      </c>
+      <c r="BG62" t="inlineStr">
+        <is>
+          <t>Out To CF</t>
+        </is>
+      </c>
+      <c r="BH62" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
       <c r="BI62" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ62" t="inlineStr"/>
@@ -17543,56 +17543,56 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>665019</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Kody Clemens</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-22T18:10:00Z</t>
+          <t>2026-08-23T00:40:00Z</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Martín Pérez</t>
+          <t>Casey Mize</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>527048</t>
+          <t>663554</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>50.2</v>
+        <v>50.1</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
@@ -17606,58 +17606,62 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>37.2</v>
+        <v>52.9</v>
       </c>
       <c r="Q63" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="R63" t="n">
-        <v>67.59999999999999</v>
+        <v>22.6</v>
       </c>
       <c r="S63" t="n">
-        <v>100</v>
+        <v>71.7</v>
       </c>
       <c r="T63" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U63" t="n">
-        <v>2.7</v>
+        <v>52.3</v>
       </c>
       <c r="V63" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W63" t="inlineStr">
+      <c r="Z63" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y63" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC63" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -17677,142 +17681,134 @@
       </c>
       <c r="AH63" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/29, 0 HR</t>
+          <t>Contact streak: 9/26 over last 7 games</t>
         </is>
       </c>
       <c r="AL63" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.1% barrel, 9.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.2% barrel, 11.2 HR allowed</t>
         </is>
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>lift-pull EV profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN63" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>12.07</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>43.83</t>
+          <t>46.83</t>
         </is>
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>90.61</t>
+          <t>92.13</t>
         </is>
       </c>
       <c r="AQ63" t="inlineStr">
         <is>
-          <t>100.4505</t>
+          <t>101.5156</t>
         </is>
       </c>
       <c r="AR63" t="inlineStr">
         <is>
-          <t>0.4304</t>
+          <t>0.4559</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr">
         <is>
-          <t>0.1733</t>
+          <t>0.2083</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr">
         <is>
-          <t>0.3406</t>
+          <t>0.3303</t>
         </is>
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>70.11</t>
+          <t>72.06</t>
         </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
-          <t>12.99</t>
+          <t>14.21</t>
         </is>
       </c>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>27.44</t>
+          <t>46.08</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>24.27</t>
+          <t>33.32</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>0.1673</t>
+          <t>0.2287</t>
         </is>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
-          <t>8.14</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="BB63" t="inlineStr">
         <is>
-          <t>37.86</t>
+          <t>38.58</t>
         </is>
       </c>
       <c r="BC63" t="inlineStr">
         <is>
-          <t>88.13</t>
+          <t>89.16</t>
         </is>
       </c>
       <c r="BD63" t="inlineStr">
         <is>
-          <t>0.4171</t>
+          <t>0.3763</t>
         </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.1455</t>
         </is>
       </c>
       <c r="BF63" t="inlineStr">
         <is>
-          <t>24.2</t>
-        </is>
-      </c>
-      <c r="BG63" t="inlineStr">
-        <is>
-          <t>Out To CF</t>
-        </is>
-      </c>
-      <c r="BH63" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
+          <t>30.46</t>
+        </is>
+      </c>
+      <c r="BG63" t="inlineStr"/>
+      <c r="BH63" t="inlineStr"/>
       <c r="BI63" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ63" t="inlineStr"/>
@@ -17823,27 +17819,27 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>665019</t>
+          <t>677800</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Kody Clemens</t>
+          <t>Wilyer Abreu</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-23T00:40:00Z</t>
+          <t>2026-08-22T23:15:00Z</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -17853,17 +17849,17 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Casey Mize</t>
+          <t>Blade Tidwell</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>663554</t>
+          <t>694918</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -17872,7 +17868,7 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>50.1</v>
+        <v>50</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
@@ -17890,22 +17886,22 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>52.9</v>
+        <v>54.5</v>
       </c>
       <c r="Q64" t="n">
-        <v>39</v>
+        <v>26.2</v>
       </c>
       <c r="R64" t="n">
-        <v>22.6</v>
+        <v>28.7</v>
       </c>
       <c r="S64" t="n">
-        <v>71.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T64" t="n">
         <v>80</v>
       </c>
       <c r="U64" t="n">
-        <v>52.3</v>
+        <v>55.9</v>
       </c>
       <c r="V64" t="inlineStr">
         <is>
@@ -17919,7 +17915,7 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr">
@@ -17961,12 +17957,12 @@
       </c>
       <c r="AH64" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ64" t="inlineStr">
@@ -17976,119 +17972,119 @@
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>Contact streak: 9/26 over last 7 games</t>
+          <t>Contact streak: 10/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL64" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.2% barrel, 11.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.5% barrel, 2.6 HR allowed</t>
         </is>
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>lift-pull EV profile; pitcher allows elevated contact</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN64" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>12.65</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>46.83</t>
+          <t>44.69</t>
         </is>
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>92.13</t>
+          <t>90.17</t>
         </is>
       </c>
       <c r="AQ64" t="inlineStr">
         <is>
-          <t>101.5156</t>
+          <t>101.4905</t>
         </is>
       </c>
       <c r="AR64" t="inlineStr">
         <is>
-          <t>0.4559</t>
+          <t>0.4848</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr">
         <is>
-          <t>0.2083</t>
+          <t>0.2285</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr">
         <is>
-          <t>0.3303</t>
+          <t>0.3511</t>
         </is>
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>72.06</t>
+          <t>73.89</t>
         </is>
       </c>
       <c r="AV64" t="inlineStr">
         <is>
-          <t>14.21</t>
+          <t>38.73</t>
         </is>
       </c>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>46.08</t>
+          <t>38.67</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>33.32</t>
+          <t>36.82</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>0.2287</t>
+          <t>0.2157</t>
         </is>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>6.51</t>
         </is>
       </c>
       <c r="BB64" t="inlineStr">
         <is>
-          <t>38.58</t>
+          <t>36.64</t>
         </is>
       </c>
       <c r="BC64" t="inlineStr">
         <is>
-          <t>89.16</t>
+          <t>87.78</t>
         </is>
       </c>
       <c r="BD64" t="inlineStr">
         <is>
-          <t>0.3763</t>
+          <t>0.3849</t>
         </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
-          <t>0.1455</t>
+          <t>0.125</t>
         </is>
       </c>
       <c r="BF64" t="inlineStr">
         <is>
-          <t>30.46</t>
+          <t>21.73</t>
         </is>
       </c>
       <c r="BG64" t="inlineStr"/>
       <c r="BH64" t="inlineStr"/>
       <c r="BI64" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Fenway Park</t>
         </is>
       </c>
       <c r="BJ64" t="inlineStr"/>
@@ -18099,47 +18095,47 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>677800</t>
+          <t>663757</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Wilyer Abreu</t>
+          <t>Trent Grisham</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-22T23:15:00Z</t>
+          <t>2026-08-22T17:35:00Z</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Blade Tidwell</t>
+          <t>Dylan Cease</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>694918</t>
+          <t>656302</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -18148,7 +18144,7 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>50</v>
+        <v>49.8</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
@@ -18162,62 +18158,58 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>54.5</v>
+        <v>48.6</v>
       </c>
       <c r="Q65" t="n">
-        <v>26.2</v>
+        <v>20.3</v>
       </c>
       <c r="R65" t="n">
-        <v>28.7</v>
+        <v>48.2</v>
       </c>
       <c r="S65" t="n">
-        <v>81.90000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T65" t="n">
         <v>80</v>
       </c>
       <c r="U65" t="n">
-        <v>55.9</v>
+        <v>28.9</v>
       </c>
       <c r="V65" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W65" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X65" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y65" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr"/>
       <c r="AC65" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -18237,12 +18229,12 @@
       </c>
       <c r="AH65" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ65" t="inlineStr">
@@ -18252,119 +18244,127 @@
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>Contact streak: 10/27 over last 7 games</t>
+          <t>Last 7 games: 4/21, 1 HR</t>
         </is>
       </c>
       <c r="AL65" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.5% barrel, 2.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN65" t="inlineStr">
         <is>
-          <t>12.65</t>
+          <t>11.19</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>44.69</t>
+          <t>46.26</t>
         </is>
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>90.17</t>
+          <t>90.89</t>
         </is>
       </c>
       <c r="AQ65" t="inlineStr">
         <is>
-          <t>101.4905</t>
+          <t>100.9592</t>
         </is>
       </c>
       <c r="AR65" t="inlineStr">
         <is>
-          <t>0.4848</t>
+          <t>0.4567</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr">
         <is>
-          <t>0.2285</t>
+          <t>0.208</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr">
         <is>
-          <t>0.3511</t>
+          <t>0.3497</t>
         </is>
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>73.89</t>
+          <t>70.72</t>
         </is>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
-          <t>38.73</t>
+          <t>8.81</t>
         </is>
       </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>38.67</t>
+          <t>46.68</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>36.82</t>
+          <t>31.05</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>0.2157</t>
+          <t>0.2066</t>
         </is>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="BB65" t="inlineStr">
         <is>
-          <t>36.64</t>
+          <t>33.93</t>
         </is>
       </c>
       <c r="BC65" t="inlineStr">
         <is>
-          <t>87.78</t>
+          <t>86.73</t>
         </is>
       </c>
       <c r="BD65" t="inlineStr">
         <is>
-          <t>0.3849</t>
+          <t>0.3009</t>
         </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>0.1086</t>
         </is>
       </c>
       <c r="BF65" t="inlineStr">
         <is>
-          <t>21.73</t>
-        </is>
-      </c>
-      <c r="BG65" t="inlineStr"/>
-      <c r="BH65" t="inlineStr"/>
+          <t>25.47</t>
+        </is>
+      </c>
+      <c r="BG65" t="inlineStr">
+        <is>
+          <t>In From LF</t>
+        </is>
+      </c>
+      <c r="BH65" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
       <c r="BI65" t="inlineStr">
         <is>
-          <t>Fenway Park</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ65" t="inlineStr"/>
@@ -20888,7 +20888,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -21444,7 +21444,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -22000,7 +22000,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -28851,52 +28851,52 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>677594</t>
+          <t>671218</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Julio Rodriguez</t>
+          <t>Heliot Ramos</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-08-22T23:15:00Z</t>
+          <t>2026-08-22T17:35:00Z</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>David Peterson</t>
+          <t>Dylan Cease</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>656849</t>
+          <t>656302</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L104" t="n">
@@ -28914,62 +28914,58 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P104" t="n">
-        <v>46.6</v>
+        <v>48.9</v>
       </c>
       <c r="Q104" t="n">
-        <v>35.9</v>
+        <v>20.3</v>
       </c>
       <c r="R104" t="n">
-        <v>25.4</v>
+        <v>48.2</v>
       </c>
       <c r="S104" t="n">
-        <v>81.90000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T104" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U104" t="n">
-        <v>10.1</v>
+        <v>10.6</v>
       </c>
       <c r="V104" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X104" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W104" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X104" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y104" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr"/>
       <c r="AC104" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -28989,12 +28985,12 @@
       </c>
       <c r="AH104" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI104" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ104" t="inlineStr">
@@ -29004,119 +29000,127 @@
       </c>
       <c r="AK104" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/32, 0 HR</t>
+          <t>Last 7 games: 4/21, 0 HR</t>
         </is>
       </c>
       <c r="AL104" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.4% barrel, 11.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.0% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM104" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN104" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>12.02</t>
         </is>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>44.43</t>
+          <t>48.52</t>
         </is>
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>90.47</t>
+          <t>92.01</t>
         </is>
       </c>
       <c r="AQ104" t="inlineStr">
         <is>
-          <t>102.6394</t>
+          <t>102.8875</t>
         </is>
       </c>
       <c r="AR104" t="inlineStr">
         <is>
-          <t>0.4692</t>
+          <t>0.4317</t>
         </is>
       </c>
       <c r="AS104" t="inlineStr">
         <is>
-          <t>0.1964</t>
+          <t>0.1792</t>
         </is>
       </c>
       <c r="AT104" t="inlineStr">
         <is>
-          <t>0.3482</t>
+          <t>0.3214</t>
         </is>
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>76.68</t>
+          <t>72.92</t>
         </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
-          <t>67.62</t>
+          <t>31.56</t>
         </is>
       </c>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>38.63</t>
+          <t>33.17</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>22.46</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>12.6</t>
         </is>
       </c>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>0.1755</t>
+          <t>0.1475</t>
         </is>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="BB104" t="inlineStr">
         <is>
-          <t>42.64</t>
+          <t>33.93</t>
         </is>
       </c>
       <c r="BC104" t="inlineStr">
         <is>
-          <t>89.69</t>
+          <t>86.73</t>
         </is>
       </c>
       <c r="BD104" t="inlineStr">
         <is>
-          <t>0.414</t>
+          <t>0.3009</t>
         </is>
       </c>
       <c r="BE104" t="inlineStr">
         <is>
-          <t>0.1405</t>
+          <t>0.1086</t>
         </is>
       </c>
       <c r="BF104" t="inlineStr">
         <is>
-          <t>19.71</t>
-        </is>
-      </c>
-      <c r="BG104" t="inlineStr"/>
-      <c r="BH104" t="inlineStr"/>
+          <t>25.47</t>
+        </is>
+      </c>
+      <c r="BG104" t="inlineStr">
+        <is>
+          <t>In From LF</t>
+        </is>
+      </c>
+      <c r="BH104" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
       <c r="BI104" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ104" t="inlineStr"/>
@@ -29127,27 +29131,27 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>668723</t>
+          <t>677594</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Ryan Vilade</t>
+          <t>Julio Rodriguez</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-08-22T23:05:00Z</t>
+          <t>2026-08-22T23:15:00Z</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -29157,26 +29161,26 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Brandon Young</t>
+          <t>David Peterson</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>687064</t>
+          <t>656849</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L105" t="n">
-        <v>46.7</v>
+        <v>46.8</v>
       </c>
       <c r="M105" t="inlineStr">
         <is>
@@ -29190,26 +29194,26 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P105" t="n">
-        <v>43.7</v>
+        <v>46.6</v>
       </c>
       <c r="Q105" t="n">
-        <v>43.6</v>
+        <v>35.9</v>
       </c>
       <c r="R105" t="n">
-        <v>32.1</v>
+        <v>25.4</v>
       </c>
       <c r="S105" t="n">
-        <v>59.8</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T105" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U105" t="n">
-        <v>81.7</v>
+        <v>10.1</v>
       </c>
       <c r="V105" t="inlineStr">
         <is>
@@ -29223,7 +29227,7 @@
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y105" t="inlineStr">
@@ -29265,27 +29269,27 @@
       </c>
       <c r="AH105" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI105" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/32, 0 HR</t>
         </is>
       </c>
       <c r="AL105" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.9% barrel, 14.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.4% barrel, 11.0 HR allowed</t>
         </is>
       </c>
       <c r="AM105" t="inlineStr">
@@ -29295,104 +29299,104 @@
       </c>
       <c r="AN105" t="inlineStr">
         <is>
-          <t>8.51</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>49.45</t>
+          <t>44.43</t>
         </is>
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>91.42</t>
+          <t>90.47</t>
         </is>
       </c>
       <c r="AQ105" t="inlineStr">
         <is>
-          <t>102.4749</t>
+          <t>102.6394</t>
         </is>
       </c>
       <c r="AR105" t="inlineStr">
         <is>
-          <t>0.4047</t>
+          <t>0.4692</t>
         </is>
       </c>
       <c r="AS105" t="inlineStr">
         <is>
-          <t>0.1653</t>
+          <t>0.1964</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr">
         <is>
-          <t>0.3153</t>
+          <t>0.3482</t>
         </is>
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>75.77</t>
+          <t>76.68</t>
         </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
-          <t>57.72</t>
+          <t>67.62</t>
         </is>
       </c>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>38.63</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>24.89</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>0.1561</t>
+          <t>0.1755</t>
         </is>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="BB105" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>42.64</t>
         </is>
       </c>
       <c r="BC105" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>89.69</t>
         </is>
       </c>
       <c r="BD105" t="inlineStr">
         <is>
-          <t>0.4201</t>
+          <t>0.414</t>
         </is>
       </c>
       <c r="BE105" t="inlineStr">
         <is>
-          <t>0.1672</t>
+          <t>0.1405</t>
         </is>
       </c>
       <c r="BF105" t="inlineStr">
         <is>
-          <t>27.43</t>
+          <t>19.71</t>
         </is>
       </c>
       <c r="BG105" t="inlineStr"/>
       <c r="BH105" t="inlineStr"/>
       <c r="BI105" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ105" t="inlineStr"/>
@@ -29403,47 +29407,47 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>671218</t>
+          <t>668723</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Heliot Ramos</t>
+          <t>Ryan Vilade</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-08-22T17:35:00Z</t>
+          <t>2026-08-22T23:05:00Z</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Dylan Cease</t>
+          <t>Brandon Young</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>656302</t>
+          <t>687064</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -29452,7 +29456,7 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>46.6</v>
+        <v>46.7</v>
       </c>
       <c r="M106" t="inlineStr">
         <is>
@@ -29466,58 +29470,62 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P106" t="n">
-        <v>48.9</v>
+        <v>43.7</v>
       </c>
       <c r="Q106" t="n">
-        <v>20.3</v>
+        <v>43.6</v>
       </c>
       <c r="R106" t="n">
-        <v>48.2</v>
+        <v>32.1</v>
       </c>
       <c r="S106" t="n">
-        <v>96.59999999999999</v>
+        <v>59.8</v>
       </c>
       <c r="T106" t="n">
         <v>50</v>
       </c>
       <c r="U106" t="n">
-        <v>7</v>
+        <v>81.7</v>
       </c>
       <c r="V106" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X106" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W106" t="inlineStr">
+      <c r="Z106" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X106" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y106" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB106" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC106" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -29537,142 +29545,134 @@
       </c>
       <c r="AH106" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI106" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL106" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.0% barrel, 12.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.9% barrel, 14.1 HR allowed</t>
         </is>
       </c>
       <c r="AM106" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN106" t="inlineStr">
         <is>
-          <t>12.02</t>
+          <t>8.51</t>
         </is>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>48.52</t>
+          <t>49.45</t>
         </is>
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>92.01</t>
+          <t>91.42</t>
         </is>
       </c>
       <c r="AQ106" t="inlineStr">
         <is>
-          <t>102.8875</t>
+          <t>102.4749</t>
         </is>
       </c>
       <c r="AR106" t="inlineStr">
         <is>
-          <t>0.4317</t>
+          <t>0.4047</t>
         </is>
       </c>
       <c r="AS106" t="inlineStr">
         <is>
-          <t>0.1792</t>
+          <t>0.1653</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr">
         <is>
-          <t>0.3214</t>
+          <t>0.3153</t>
         </is>
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>72.92</t>
+          <t>75.77</t>
         </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
-          <t>31.56</t>
+          <t>57.72</t>
         </is>
       </c>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>33.17</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>22.46</t>
+          <t>24.89</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>0.1475</t>
+          <t>0.1561</t>
         </is>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="BB106" t="inlineStr">
         <is>
-          <t>33.93</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="BC106" t="inlineStr">
         <is>
-          <t>86.73</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="BD106" t="inlineStr">
         <is>
-          <t>0.3009</t>
+          <t>0.4201</t>
         </is>
       </c>
       <c r="BE106" t="inlineStr">
         <is>
-          <t>0.1086</t>
+          <t>0.1672</t>
         </is>
       </c>
       <c r="BF106" t="inlineStr">
         <is>
-          <t>25.47</t>
-        </is>
-      </c>
-      <c r="BG106" t="inlineStr">
-        <is>
-          <t>In From LF</t>
-        </is>
-      </c>
-      <c r="BH106" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
+          <t>27.43</t>
+        </is>
+      </c>
+      <c r="BG106" t="inlineStr"/>
+      <c r="BH106" t="inlineStr"/>
       <c r="BI106" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ106" t="inlineStr"/>
@@ -36520,7 +36520,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -38155,54 +38155,42 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>665862</t>
+          <t>607208</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Jazz Chisholm Jr.</t>
+          <t>Trea Turner</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-08-22T17:35:00Z</t>
+          <t>2026-08-22T22:05:00Z</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>Dylan Cease</t>
-        </is>
-      </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>656302</t>
-        </is>
-      </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
       <c r="L138" t="n">
         <v>43.2</v>
       </c>
@@ -38218,61 +38206,65 @@
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P138" t="n">
-        <v>43.7</v>
+        <v>27.1</v>
       </c>
       <c r="Q138" t="n">
-        <v>20.3</v>
+        <v>41.2</v>
       </c>
       <c r="R138" t="n">
-        <v>48.2</v>
+        <v>34.3</v>
       </c>
       <c r="S138" t="n">
-        <v>64.3</v>
+        <v>95.5</v>
       </c>
       <c r="T138" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U138" t="n">
-        <v>10.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="V138" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X138" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W138" t="inlineStr">
+      <c r="Z138" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X138" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y138" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z138" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB138" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB138" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC138" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD138" t="inlineStr"/>
@@ -38289,12 +38281,12 @@
       </c>
       <c r="AH138" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ138" t="inlineStr">
@@ -38304,12 +38296,12 @@
       </c>
       <c r="AK138" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 0 HR</t>
+          <t>Last 7 games: 5/27, 0 HR</t>
         </is>
       </c>
       <c r="AL138" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.0% barrel, 12.6 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM138" t="inlineStr">
@@ -38319,112 +38311,80 @@
       </c>
       <c r="AN138" t="inlineStr">
         <is>
-          <t>10.87</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="AO138" t="inlineStr">
         <is>
-          <t>42.53</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="AP138" t="inlineStr">
         <is>
-          <t>90.26</t>
+          <t>88.74</t>
         </is>
       </c>
       <c r="AQ138" t="inlineStr">
         <is>
-          <t>100.4918</t>
+          <t>99.4026</t>
         </is>
       </c>
       <c r="AR138" t="inlineStr">
         <is>
-          <t>0.3991</t>
+          <t>0.382</t>
         </is>
       </c>
       <c r="AS138" t="inlineStr">
         <is>
-          <t>0.1826</t>
+          <t>0.1281</t>
         </is>
       </c>
       <c r="AT138" t="inlineStr">
         <is>
-          <t>0.3061</t>
+          <t>0.3042</t>
         </is>
       </c>
       <c r="AU138" t="inlineStr">
         <is>
-          <t>73.41</t>
+          <t>71.45</t>
         </is>
       </c>
       <c r="AV138" t="inlineStr">
         <is>
-          <t>34.63</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>52.33</t>
+          <t>35.17</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>30.61</t>
+          <t>25.13</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>0.1921</t>
-        </is>
-      </c>
-      <c r="BA138" t="inlineStr">
-        <is>
-          <t>6.01</t>
-        </is>
-      </c>
-      <c r="BB138" t="inlineStr">
-        <is>
-          <t>33.93</t>
-        </is>
-      </c>
-      <c r="BC138" t="inlineStr">
-        <is>
-          <t>86.73</t>
-        </is>
-      </c>
-      <c r="BD138" t="inlineStr">
-        <is>
-          <t>0.3009</t>
-        </is>
-      </c>
-      <c r="BE138" t="inlineStr">
-        <is>
-          <t>0.1086</t>
-        </is>
-      </c>
-      <c r="BF138" t="inlineStr">
-        <is>
-          <t>25.47</t>
-        </is>
-      </c>
-      <c r="BG138" t="inlineStr">
-        <is>
-          <t>In From LF</t>
-        </is>
-      </c>
-      <c r="BH138" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
+          <t>0.1488</t>
+        </is>
+      </c>
+      <c r="BA138" t="inlineStr"/>
+      <c r="BB138" t="inlineStr"/>
+      <c r="BC138" t="inlineStr"/>
+      <c r="BD138" t="inlineStr"/>
+      <c r="BE138" t="inlineStr"/>
+      <c r="BF138" t="inlineStr"/>
+      <c r="BG138" t="inlineStr"/>
+      <c r="BH138" t="inlineStr"/>
       <c r="BI138" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BJ138" t="inlineStr"/>
@@ -38435,27 +38395,27 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>607208</t>
+          <t>694249</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Trea Turner</t>
+          <t>Cole Carrigg</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-08-22T22:05:00Z</t>
+          <t>2026-08-23T00:10:00Z</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -38468,9 +38428,21 @@
           <t>2</t>
         </is>
       </c>
-      <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Tanner Bibee</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>676440</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L139" t="n">
         <v>43.2</v>
       </c>
@@ -38486,26 +38458,26 @@
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P139" t="n">
-        <v>27.1</v>
+        <v>19.5</v>
       </c>
       <c r="Q139" t="n">
-        <v>41.2</v>
+        <v>42.4</v>
       </c>
       <c r="R139" t="n">
-        <v>34.3</v>
+        <v>38.7</v>
       </c>
       <c r="S139" t="n">
         <v>95.5</v>
       </c>
       <c r="T139" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="U139" t="n">
-        <v>9.800000000000001</v>
+        <v>13.3</v>
       </c>
       <c r="V139" t="inlineStr">
         <is>
@@ -38544,7 +38516,7 @@
       </c>
       <c r="AC139" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD139" t="inlineStr"/>
@@ -38566,7 +38538,7 @@
       </c>
       <c r="AI139" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ139" t="inlineStr">
@@ -38576,12 +38548,12 @@
       </c>
       <c r="AK139" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/27, 0 HR</t>
+          <t>Last 7 games: 5/24, 0 HR</t>
         </is>
       </c>
       <c r="AL139" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.2% barrel, 25.6 HR allowed</t>
         </is>
       </c>
       <c r="AM139" t="inlineStr">
@@ -38591,80 +38563,104 @@
       </c>
       <c r="AN139" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AO139" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>31.8</t>
         </is>
       </c>
       <c r="AP139" t="inlineStr">
         <is>
-          <t>88.74</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AQ139" t="inlineStr">
         <is>
-          <t>99.4026</t>
+          <t>97.9672</t>
         </is>
       </c>
       <c r="AR139" t="inlineStr">
         <is>
-          <t>0.382</t>
+          <t>0.385</t>
         </is>
       </c>
       <c r="AS139" t="inlineStr">
         <is>
-          <t>0.1281</t>
+          <t>0.125</t>
         </is>
       </c>
       <c r="AT139" t="inlineStr">
         <is>
-          <t>0.3042</t>
+          <t>0.326</t>
         </is>
       </c>
       <c r="AU139" t="inlineStr">
         <is>
-          <t>71.45</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AV139" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>37.9</t>
         </is>
       </c>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>35.17</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>25.13</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
         <is>
-          <t>16.4</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>0.1488</t>
-        </is>
-      </c>
-      <c r="BA139" t="inlineStr"/>
-      <c r="BB139" t="inlineStr"/>
-      <c r="BC139" t="inlineStr"/>
-      <c r="BD139" t="inlineStr"/>
-      <c r="BE139" t="inlineStr"/>
-      <c r="BF139" t="inlineStr"/>
+          <t>0.188</t>
+        </is>
+      </c>
+      <c r="BA139" t="inlineStr">
+        <is>
+          <t>8.24</t>
+        </is>
+      </c>
+      <c r="BB139" t="inlineStr">
+        <is>
+          <t>38.49</t>
+        </is>
+      </c>
+      <c r="BC139" t="inlineStr">
+        <is>
+          <t>89.13</t>
+        </is>
+      </c>
+      <c r="BD139" t="inlineStr">
+        <is>
+          <t>0.4116</t>
+        </is>
+      </c>
+      <c r="BE139" t="inlineStr">
+        <is>
+          <t>0.1674</t>
+        </is>
+      </c>
+      <c r="BF139" t="inlineStr">
+        <is>
+          <t>27.62</t>
+        </is>
+      </c>
       <c r="BG139" t="inlineStr"/>
       <c r="BH139" t="inlineStr"/>
       <c r="BI139" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ139" t="inlineStr"/>
@@ -38675,47 +38671,47 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>694249</t>
+          <t>665862</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Cole Carrigg</t>
+          <t>Jazz Chisholm Jr.</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-08-23T00:10:00Z</t>
+          <t>2026-08-22T17:35:00Z</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Tanner Bibee</t>
+          <t>Dylan Cease</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>676440</t>
+          <t>656302</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -38724,7 +38720,7 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>43.2</v>
+        <v>43.1</v>
       </c>
       <c r="M140" t="inlineStr">
         <is>
@@ -38738,65 +38734,61 @@
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P140" t="n">
-        <v>19.5</v>
+        <v>43.7</v>
       </c>
       <c r="Q140" t="n">
-        <v>42.4</v>
+        <v>20.3</v>
       </c>
       <c r="R140" t="n">
-        <v>38.7</v>
+        <v>48.2</v>
       </c>
       <c r="S140" t="n">
-        <v>95.5</v>
+        <v>64.3</v>
       </c>
       <c r="T140" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U140" t="n">
-        <v>13.3</v>
+        <v>8.5</v>
       </c>
       <c r="V140" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X140" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z140" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W140" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X140" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y140" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z140" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB140" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB140" t="inlineStr"/>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD140" t="inlineStr"/>
@@ -38813,12 +38805,12 @@
       </c>
       <c r="AH140" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ140" t="inlineStr">
@@ -38828,12 +38820,12 @@
       </c>
       <c r="AK140" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 0 HR</t>
+          <t>Last 7 games: 3/17, 0 HR</t>
         </is>
       </c>
       <c r="AL140" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.2% barrel, 25.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM140" t="inlineStr">
@@ -38843,104 +38835,112 @@
       </c>
       <c r="AN140" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>10.87</t>
         </is>
       </c>
       <c r="AO140" t="inlineStr">
         <is>
-          <t>31.8</t>
+          <t>42.53</t>
         </is>
       </c>
       <c r="AP140" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>90.26</t>
         </is>
       </c>
       <c r="AQ140" t="inlineStr">
         <is>
-          <t>97.9672</t>
+          <t>100.4918</t>
         </is>
       </c>
       <c r="AR140" t="inlineStr">
         <is>
-          <t>0.385</t>
+          <t>0.3991</t>
         </is>
       </c>
       <c r="AS140" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>0.1826</t>
         </is>
       </c>
       <c r="AT140" t="inlineStr">
         <is>
-          <t>0.326</t>
+          <t>0.3061</t>
         </is>
       </c>
       <c r="AU140" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>73.41</t>
         </is>
       </c>
       <c r="AV140" t="inlineStr">
         <is>
-          <t>37.9</t>
+          <t>34.63</t>
         </is>
       </c>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>52.33</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>30.61</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>0.1921</t>
         </is>
       </c>
       <c r="BA140" t="inlineStr">
         <is>
-          <t>8.24</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="BB140" t="inlineStr">
         <is>
-          <t>38.49</t>
+          <t>33.93</t>
         </is>
       </c>
       <c r="BC140" t="inlineStr">
         <is>
-          <t>89.13</t>
+          <t>86.73</t>
         </is>
       </c>
       <c r="BD140" t="inlineStr">
         <is>
-          <t>0.4116</t>
+          <t>0.3009</t>
         </is>
       </c>
       <c r="BE140" t="inlineStr">
         <is>
-          <t>0.1674</t>
+          <t>0.1086</t>
         </is>
       </c>
       <c r="BF140" t="inlineStr">
         <is>
-          <t>27.62</t>
-        </is>
-      </c>
-      <c r="BG140" t="inlineStr"/>
-      <c r="BH140" t="inlineStr"/>
+          <t>25.47</t>
+        </is>
+      </c>
+      <c r="BG140" t="inlineStr">
+        <is>
+          <t>In From LF</t>
+        </is>
+      </c>
+      <c r="BH140" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
       <c r="BI140" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ140" t="inlineStr"/>
@@ -39252,7 +39252,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -40360,7 +40360,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -43400,7 +43400,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -47764,7 +47764,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -48872,7 +48872,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -49668,7 +49668,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -49725,7 +49725,7 @@
         <v>80</v>
       </c>
       <c r="U180" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="V180" t="inlineStr">
         <is>
@@ -49782,7 +49782,7 @@
       </c>
       <c r="AI180" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ180" t="inlineStr">
@@ -49792,7 +49792,7 @@
       </c>
       <c r="AK180" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/18, 0 HR</t>
+          <t>Last 7 games: 2/16, 0 HR</t>
         </is>
       </c>
       <c r="AL180" t="inlineStr">
@@ -51583,52 +51583,52 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>691458</t>
+          <t>703520</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Blaze Jordan</t>
+          <t>Brett Bateman</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>2026-08-22T22:05:00Z</t>
+          <t>2026-08-22T17:35:00Z</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>Andrew Painter</t>
+          <t>Ryan Weathers</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>691725</t>
+          <t>677960</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L187" t="n">
@@ -51646,65 +51646,61 @@
       </c>
       <c r="O187" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P187" t="n">
-        <v>33.4</v>
+        <v>1.2</v>
       </c>
       <c r="Q187" t="n">
-        <v>41.4</v>
+        <v>45.5</v>
       </c>
       <c r="R187" t="n">
-        <v>34.3</v>
+        <v>48.2</v>
       </c>
       <c r="S187" t="n">
-        <v>47.9</v>
+        <v>93.2</v>
       </c>
       <c r="T187" t="n">
         <v>50</v>
       </c>
       <c r="U187" t="n">
-        <v>14.1</v>
+        <v>37.6</v>
       </c>
       <c r="V187" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W187" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X187" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y187" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z187" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W187" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X187" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y187" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z187" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA187" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB187" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB187" t="inlineStr"/>
       <c r="AC187" t="inlineStr">
         <is>
-          <t>H:2026 P:2026</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD187" t="inlineStr"/>
@@ -51721,12 +51717,12 @@
       </c>
       <c r="AH187" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI187" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ187" t="inlineStr">
@@ -51736,12 +51732,12 @@
       </c>
       <c r="AK187" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/28, 0 HR</t>
+          <t>Contact streak: 10/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL187" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.4% barrel, 17.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.8% barrel, 14.7 HR allowed</t>
         </is>
       </c>
       <c r="AM187" t="inlineStr">
@@ -51751,104 +51747,112 @@
       </c>
       <c r="AN187" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO187" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="AP187" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="AQ187" t="inlineStr">
         <is>
-          <t>99.8323</t>
+          <t>92.6696</t>
         </is>
       </c>
       <c r="AR187" t="inlineStr">
         <is>
-          <t>0.407</t>
+          <t>0.301</t>
         </is>
       </c>
       <c r="AS187" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AT187" t="inlineStr">
         <is>
-          <t>0.308</t>
+          <t>0.262</t>
         </is>
       </c>
       <c r="AU187" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>68.1</t>
         </is>
       </c>
       <c r="AV187" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ187" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>0.094</t>
         </is>
       </c>
       <c r="BA187" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.76</t>
         </is>
       </c>
       <c r="BB187" t="inlineStr">
         <is>
-          <t>35.5</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="BC187" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>89.46</t>
         </is>
       </c>
       <c r="BD187" t="inlineStr">
         <is>
-          <t>0.445</t>
+          <t>0.4173</t>
         </is>
       </c>
       <c r="BE187" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>0.1708</t>
         </is>
       </c>
       <c r="BF187" t="inlineStr">
         <is>
-          <t>27.1</t>
-        </is>
-      </c>
-      <c r="BG187" t="inlineStr"/>
-      <c r="BH187" t="inlineStr"/>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="BG187" t="inlineStr">
+        <is>
+          <t>In From LF</t>
+        </is>
+      </c>
+      <c r="BH187" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
       <c r="BI187" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ187" t="inlineStr"/>
@@ -51859,27 +51863,27 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>701358</t>
+          <t>691458</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Cam Smith</t>
+          <t>Blaze Jordan</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>2026-08-22T23:10:00Z</t>
+          <t>2026-08-22T22:05:00Z</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -51894,17 +51898,17 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>Jacob Lopez</t>
+          <t>Andrew Painter</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>682052</t>
+          <t>691725</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L188" t="n">
@@ -51922,26 +51926,26 @@
       </c>
       <c r="O188" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P188" t="n">
-        <v>42.2</v>
+        <v>33.4</v>
       </c>
       <c r="Q188" t="n">
-        <v>21.9</v>
+        <v>41.4</v>
       </c>
       <c r="R188" t="n">
-        <v>27.6</v>
+        <v>34.3</v>
       </c>
       <c r="S188" t="n">
         <v>47.9</v>
       </c>
       <c r="T188" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U188" t="n">
-        <v>18.3</v>
+        <v>14.1</v>
       </c>
       <c r="V188" t="inlineStr">
         <is>
@@ -51980,7 +51984,7 @@
       </c>
       <c r="AC188" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026</t>
         </is>
       </c>
       <c r="AD188" t="inlineStr"/>
@@ -51997,134 +52001,134 @@
       </c>
       <c r="AH188" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI188" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK188" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/20, 1 HR</t>
+          <t>Last 7 games: 6/28, 0 HR</t>
         </is>
       </c>
       <c r="AL188" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.7% barrel, 15.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.4% barrel, 17.0 HR allowed</t>
         </is>
       </c>
       <c r="AM188" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN188" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="AO188" t="inlineStr">
         <is>
-          <t>43.46</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="AP188" t="inlineStr">
         <is>
-          <t>88.88</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AQ188" t="inlineStr">
         <is>
-          <t>101.626</t>
+          <t>99.8323</t>
         </is>
       </c>
       <c r="AR188" t="inlineStr">
         <is>
-          <t>0.4173</t>
+          <t>0.407</t>
         </is>
       </c>
       <c r="AS188" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>0.146</t>
         </is>
       </c>
       <c r="AT188" t="inlineStr">
         <is>
-          <t>0.3194</t>
+          <t>0.308</t>
         </is>
       </c>
       <c r="AU188" t="inlineStr">
         <is>
-          <t>76.74</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AV188" t="inlineStr">
         <is>
-          <t>67.97</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>37.98</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>25.21</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr">
         <is>
-          <t>14.6</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ188" t="inlineStr">
         <is>
-          <t>0.1591</t>
+          <t>0.121</t>
         </is>
       </c>
       <c r="BA188" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="BB188" t="inlineStr">
         <is>
-          <t>30.19</t>
+          <t>35.5</t>
         </is>
       </c>
       <c r="BC188" t="inlineStr">
         <is>
-          <t>85.29</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="BD188" t="inlineStr">
         <is>
-          <t>0.3424</t>
+          <t>0.445</t>
         </is>
       </c>
       <c r="BE188" t="inlineStr">
         <is>
-          <t>0.1338</t>
+          <t>0.178</t>
         </is>
       </c>
       <c r="BF188" t="inlineStr">
         <is>
-          <t>32.48</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="BG188" t="inlineStr"/>
       <c r="BH188" t="inlineStr"/>
       <c r="BI188" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BJ188" t="inlineStr"/>
@@ -52135,27 +52139,27 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>693304</t>
+          <t>701358</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Nick Gonzales</t>
+          <t>Cam Smith</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>2026-08-22T23:15:00Z</t>
+          <t>2026-08-22T23:10:00Z</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -52165,17 +52169,17 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>Tarik Skubal</t>
+          <t>Jacob Lopez</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>669373</t>
+          <t>682052</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
@@ -52198,26 +52202,26 @@
       </c>
       <c r="O189" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P189" t="n">
-        <v>16</v>
+        <v>42.2</v>
       </c>
       <c r="Q189" t="n">
-        <v>28.8</v>
+        <v>21.9</v>
       </c>
       <c r="R189" t="n">
         <v>27.6</v>
       </c>
       <c r="S189" t="n">
-        <v>88.7</v>
+        <v>47.9</v>
       </c>
       <c r="T189" t="n">
         <v>78</v>
       </c>
       <c r="U189" t="n">
-        <v>43.4</v>
+        <v>18.3</v>
       </c>
       <c r="V189" t="inlineStr">
         <is>
@@ -52231,7 +52235,7 @@
       </c>
       <c r="X189" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y189" t="inlineStr">
@@ -52273,134 +52277,134 @@
       </c>
       <c r="AH189" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI189" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
         <is>
-          <t>Contact streak: 9/22 over last 7 games</t>
+          <t>Last 7 games: 2/20, 1 HR</t>
         </is>
       </c>
       <c r="AL189" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.5% barrel, 13.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.7% barrel, 15.0 HR allowed</t>
         </is>
       </c>
       <c r="AM189" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN189" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="AO189" t="inlineStr">
         <is>
-          <t>36.14</t>
+          <t>43.46</t>
         </is>
       </c>
       <c r="AP189" t="inlineStr">
         <is>
-          <t>87.05</t>
+          <t>88.88</t>
         </is>
       </c>
       <c r="AQ189" t="inlineStr">
         <is>
-          <t>98.2813</t>
+          <t>101.626</t>
         </is>
       </c>
       <c r="AR189" t="inlineStr">
         <is>
-          <t>0.3813</t>
+          <t>0.4173</t>
         </is>
       </c>
       <c r="AS189" t="inlineStr">
         <is>
-          <t>0.1063</t>
+          <t>0.176</t>
         </is>
       </c>
       <c r="AT189" t="inlineStr">
         <is>
-          <t>0.3141</t>
+          <t>0.3194</t>
         </is>
       </c>
       <c r="AU189" t="inlineStr">
         <is>
-          <t>70.71</t>
+          <t>76.74</t>
         </is>
       </c>
       <c r="AV189" t="inlineStr">
         <is>
-          <t>12.66</t>
+          <t>67.97</t>
         </is>
       </c>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>37.64</t>
+          <t>37.98</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>25.21</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>14.6</t>
         </is>
       </c>
       <c r="AZ189" t="inlineStr">
         <is>
-          <t>0.0957</t>
+          <t>0.1591</t>
         </is>
       </c>
       <c r="BA189" t="inlineStr">
         <is>
-          <t>7.54</t>
+          <t>5.69</t>
         </is>
       </c>
       <c r="BB189" t="inlineStr">
         <is>
-          <t>35.38</t>
+          <t>30.19</t>
         </is>
       </c>
       <c r="BC189" t="inlineStr">
         <is>
-          <t>86.94</t>
+          <t>85.29</t>
         </is>
       </c>
       <c r="BD189" t="inlineStr">
         <is>
-          <t>0.3433</t>
+          <t>0.3424</t>
         </is>
       </c>
       <c r="BE189" t="inlineStr">
         <is>
-          <t>0.1233</t>
+          <t>0.1338</t>
         </is>
       </c>
       <c r="BF189" t="inlineStr">
         <is>
-          <t>26.32</t>
+          <t>32.48</t>
         </is>
       </c>
       <c r="BG189" t="inlineStr"/>
       <c r="BH189" t="inlineStr"/>
       <c r="BI189" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ189" t="inlineStr"/>
@@ -52411,27 +52415,27 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>592663</t>
+          <t>693304</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>J.T. Realmuto</t>
+          <t>Nick Gonzales</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>2026-08-22T22:05:00Z</t>
+          <t>2026-08-22T23:15:00Z</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -52441,14 +52445,26 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr"/>
-      <c r="J190" t="inlineStr"/>
-      <c r="K190" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>Tarik Skubal</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>669373</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="L190" t="n">
-        <v>37.7</v>
+        <v>38</v>
       </c>
       <c r="M190" t="inlineStr">
         <is>
@@ -52462,26 +52478,26 @@
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P190" t="n">
-        <v>30.5</v>
+        <v>16</v>
       </c>
       <c r="Q190" t="n">
-        <v>41.2</v>
+        <v>28.8</v>
       </c>
       <c r="R190" t="n">
-        <v>34.3</v>
+        <v>27.6</v>
       </c>
       <c r="S190" t="n">
-        <v>47.9</v>
+        <v>88.7</v>
       </c>
       <c r="T190" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="U190" t="n">
-        <v>9.300000000000001</v>
+        <v>43.4</v>
       </c>
       <c r="V190" t="inlineStr">
         <is>
@@ -52495,7 +52511,7 @@
       </c>
       <c r="X190" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y190" t="inlineStr">
@@ -52520,7 +52536,7 @@
       </c>
       <c r="AC190" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD190" t="inlineStr"/>
@@ -52537,7 +52553,7 @@
       </c>
       <c r="AH190" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI190" t="inlineStr">
@@ -52552,12 +52568,12 @@
       </c>
       <c r="AK190" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/22, 0 HR</t>
+          <t>Contact streak: 9/22 over last 7 games</t>
         </is>
       </c>
       <c r="AL190" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.5% barrel, 13.8 HR allowed</t>
         </is>
       </c>
       <c r="AM190" t="inlineStr">
@@ -52567,80 +52583,104 @@
       </c>
       <c r="AN190" t="inlineStr">
         <is>
-          <t>5.79</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="AO190" t="inlineStr">
         <is>
-          <t>41.86</t>
+          <t>36.14</t>
         </is>
       </c>
       <c r="AP190" t="inlineStr">
         <is>
-          <t>89.79</t>
+          <t>87.05</t>
         </is>
       </c>
       <c r="AQ190" t="inlineStr">
         <is>
-          <t>100.1831</t>
+          <t>98.2813</t>
         </is>
       </c>
       <c r="AR190" t="inlineStr">
         <is>
-          <t>0.3935</t>
+          <t>0.3813</t>
         </is>
       </c>
       <c r="AS190" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>0.1063</t>
         </is>
       </c>
       <c r="AT190" t="inlineStr">
         <is>
-          <t>0.3202</t>
+          <t>0.3141</t>
         </is>
       </c>
       <c r="AU190" t="inlineStr">
         <is>
-          <t>72.84</t>
+          <t>70.71</t>
         </is>
       </c>
       <c r="AV190" t="inlineStr">
         <is>
-          <t>32.15</t>
+          <t>12.66</t>
         </is>
       </c>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>41.25</t>
+          <t>37.64</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="AZ190" t="inlineStr">
         <is>
-          <t>0.1263</t>
-        </is>
-      </c>
-      <c r="BA190" t="inlineStr"/>
-      <c r="BB190" t="inlineStr"/>
-      <c r="BC190" t="inlineStr"/>
-      <c r="BD190" t="inlineStr"/>
-      <c r="BE190" t="inlineStr"/>
-      <c r="BF190" t="inlineStr"/>
+          <t>0.0957</t>
+        </is>
+      </c>
+      <c r="BA190" t="inlineStr">
+        <is>
+          <t>7.54</t>
+        </is>
+      </c>
+      <c r="BB190" t="inlineStr">
+        <is>
+          <t>35.38</t>
+        </is>
+      </c>
+      <c r="BC190" t="inlineStr">
+        <is>
+          <t>86.94</t>
+        </is>
+      </c>
+      <c r="BD190" t="inlineStr">
+        <is>
+          <t>0.3433</t>
+        </is>
+      </c>
+      <c r="BE190" t="inlineStr">
+        <is>
+          <t>0.1233</t>
+        </is>
+      </c>
+      <c r="BF190" t="inlineStr">
+        <is>
+          <t>26.32</t>
+        </is>
+      </c>
       <c r="BG190" t="inlineStr"/>
       <c r="BH190" t="inlineStr"/>
       <c r="BI190" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ190" t="inlineStr"/>
@@ -52651,27 +52691,27 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>676439</t>
+          <t>592663</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Hunter Feduccia</t>
+          <t>J.T. Realmuto</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>2026-08-22T23:15:00Z</t>
+          <t>2026-08-22T22:05:00Z</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -52681,24 +52721,12 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr">
-        <is>
-          <t>Jared Jones</t>
-        </is>
-      </c>
-      <c r="J191" t="inlineStr">
-        <is>
-          <t>683003</t>
-        </is>
-      </c>
-      <c r="K191" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr"/>
+      <c r="J191" t="inlineStr"/>
+      <c r="K191" t="inlineStr"/>
       <c r="L191" t="n">
         <v>37.7</v>
       </c>
@@ -52714,26 +52742,26 @@
       </c>
       <c r="O191" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P191" t="n">
-        <v>30.3</v>
+        <v>30.5</v>
       </c>
       <c r="Q191" t="n">
-        <v>42.6</v>
+        <v>41.2</v>
       </c>
       <c r="R191" t="n">
-        <v>27.6</v>
+        <v>34.3</v>
       </c>
       <c r="S191" t="n">
-        <v>40.2</v>
+        <v>47.9</v>
       </c>
       <c r="T191" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U191" t="n">
-        <v>10.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="V191" t="inlineStr">
         <is>
@@ -52747,7 +52775,7 @@
       </c>
       <c r="X191" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y191" t="inlineStr">
@@ -52772,7 +52800,7 @@
       </c>
       <c r="AC191" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD191" t="inlineStr"/>
@@ -52789,12 +52817,12 @@
       </c>
       <c r="AH191" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI191" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ191" t="inlineStr">
@@ -52804,12 +52832,12 @@
       </c>
       <c r="AK191" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/16, 0 HR</t>
+          <t>Last 7 games: 4/22, 0 HR</t>
         </is>
       </c>
       <c r="AL191" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.6% barrel, 11.0 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM191" t="inlineStr">
@@ -52819,104 +52847,80 @@
       </c>
       <c r="AN191" t="inlineStr">
         <is>
-          <t>8.55</t>
+          <t>5.79</t>
         </is>
       </c>
       <c r="AO191" t="inlineStr">
         <is>
-          <t>37.63</t>
+          <t>41.86</t>
         </is>
       </c>
       <c r="AP191" t="inlineStr">
         <is>
-          <t>89.49</t>
+          <t>89.79</t>
         </is>
       </c>
       <c r="AQ191" t="inlineStr">
         <is>
-          <t>99.0908</t>
+          <t>100.1831</t>
         </is>
       </c>
       <c r="AR191" t="inlineStr">
         <is>
-          <t>0.3601</t>
+          <t>0.3935</t>
         </is>
       </c>
       <c r="AS191" t="inlineStr">
         <is>
-          <t>0.1304</t>
+          <t>0.137</t>
         </is>
       </c>
       <c r="AT191" t="inlineStr">
         <is>
-          <t>0.3058</t>
+          <t>0.3202</t>
         </is>
       </c>
       <c r="AU191" t="inlineStr">
         <is>
-          <t>70.71</t>
+          <t>72.84</t>
         </is>
       </c>
       <c r="AV191" t="inlineStr">
         <is>
-          <t>12.7</t>
+          <t>32.15</t>
         </is>
       </c>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>31.89</t>
+          <t>41.25</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="AZ191" t="inlineStr">
         <is>
-          <t>0.0983</t>
-        </is>
-      </c>
-      <c r="BA191" t="inlineStr">
-        <is>
-          <t>8.6</t>
-        </is>
-      </c>
-      <c r="BB191" t="inlineStr">
-        <is>
-          <t>39.1</t>
-        </is>
-      </c>
-      <c r="BC191" t="inlineStr">
-        <is>
-          <t>89.6</t>
-        </is>
-      </c>
-      <c r="BD191" t="inlineStr">
-        <is>
-          <t>0.392</t>
-        </is>
-      </c>
-      <c r="BE191" t="inlineStr">
-        <is>
-          <t>0.173</t>
-        </is>
-      </c>
-      <c r="BF191" t="inlineStr">
-        <is>
-          <t>27.0</t>
-        </is>
-      </c>
+          <t>0.1263</t>
+        </is>
+      </c>
+      <c r="BA191" t="inlineStr"/>
+      <c r="BB191" t="inlineStr"/>
+      <c r="BC191" t="inlineStr"/>
+      <c r="BD191" t="inlineStr"/>
+      <c r="BE191" t="inlineStr"/>
+      <c r="BF191" t="inlineStr"/>
       <c r="BG191" t="inlineStr"/>
       <c r="BH191" t="inlineStr"/>
       <c r="BI191" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BJ191" t="inlineStr"/>
@@ -52927,56 +52931,56 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>703520</t>
+          <t>676439</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Brett Bateman</t>
+          <t>Hunter Feduccia</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>2026-08-22T17:35:00Z</t>
+          <t>2026-08-22T23:15:00Z</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>Ryan Weathers</t>
+          <t>Jared Jones</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>677960</t>
+          <t>683003</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L192" t="n">
-        <v>37.6</v>
+        <v>37.7</v>
       </c>
       <c r="M192" t="inlineStr">
         <is>
@@ -52990,61 +52994,65 @@
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P192" t="n">
-        <v>1.2</v>
+        <v>30.3</v>
       </c>
       <c r="Q192" t="n">
-        <v>45.5</v>
+        <v>42.6</v>
       </c>
       <c r="R192" t="n">
-        <v>48.2</v>
+        <v>27.6</v>
       </c>
       <c r="S192" t="n">
-        <v>93.2</v>
+        <v>40.2</v>
       </c>
       <c r="T192" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U192" t="n">
-        <v>30.4</v>
+        <v>10.1</v>
       </c>
       <c r="V192" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W192" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X192" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y192" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W192" t="inlineStr">
+      <c r="Z192" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X192" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y192" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z192" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA192" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB192" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB192" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC192" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD192" t="inlineStr"/>
@@ -53061,12 +53069,12 @@
       </c>
       <c r="AH192" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI192" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ192" t="inlineStr">
@@ -53076,12 +53084,12 @@
       </c>
       <c r="AK192" t="inlineStr">
         <is>
-          <t>Contact streak: 10/31 over last 7 games</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AL192" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.8% barrel, 14.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.6% barrel, 11.0 HR allowed</t>
         </is>
       </c>
       <c r="AM192" t="inlineStr">
@@ -53091,112 +53099,104 @@
       </c>
       <c r="AN192" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.55</t>
         </is>
       </c>
       <c r="AO192" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>37.63</t>
         </is>
       </c>
       <c r="AP192" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>89.49</t>
         </is>
       </c>
       <c r="AQ192" t="inlineStr">
         <is>
-          <t>92.6696</t>
+          <t>99.0908</t>
         </is>
       </c>
       <c r="AR192" t="inlineStr">
         <is>
-          <t>0.301</t>
+          <t>0.3601</t>
         </is>
       </c>
       <c r="AS192" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.1304</t>
         </is>
       </c>
       <c r="AT192" t="inlineStr">
         <is>
-          <t>0.262</t>
+          <t>0.3058</t>
         </is>
       </c>
       <c r="AU192" t="inlineStr">
         <is>
-          <t>68.1</t>
+          <t>70.71</t>
         </is>
       </c>
       <c r="AV192" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>12.7</t>
         </is>
       </c>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>31.89</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="AZ192" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>0.0983</t>
         </is>
       </c>
       <c r="BA192" t="inlineStr">
         <is>
-          <t>8.76</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="BB192" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="BC192" t="inlineStr">
         <is>
-          <t>89.46</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="BD192" t="inlineStr">
         <is>
-          <t>0.4173</t>
+          <t>0.392</t>
         </is>
       </c>
       <c r="BE192" t="inlineStr">
         <is>
-          <t>0.1708</t>
+          <t>0.173</t>
         </is>
       </c>
       <c r="BF192" t="inlineStr">
         <is>
-          <t>25.2</t>
-        </is>
-      </c>
-      <c r="BG192" t="inlineStr">
-        <is>
-          <t>In From LF</t>
-        </is>
-      </c>
-      <c r="BH192" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
+          <t>27.0</t>
+        </is>
+      </c>
+      <c r="BG192" t="inlineStr"/>
+      <c r="BH192" t="inlineStr"/>
       <c r="BI192" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ192" t="inlineStr"/>
@@ -54864,7 +54864,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -55144,7 +55144,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -60120,7 +60120,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -62284,7 +62284,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -71916,7 +71916,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -72030,7 +72030,7 @@
       </c>
       <c r="AI261" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AJ261" t="inlineStr">
@@ -72040,7 +72040,7 @@
       </c>
       <c r="AK261" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/11, 0 HR</t>
+          <t>Last 7 games: 1/9, 0 HR</t>
         </is>
       </c>
       <c r="AL261" t="inlineStr">
@@ -73630,7 +73630,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -75258,7 +75258,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -76090,7 +76090,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -76370,7 +76370,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -76650,7 +76650,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -76674,7 +76674,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>58</v>
+        <v>58.1</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -76707,7 +76707,7 @@
         <v>80</v>
       </c>
       <c r="U16" t="n">
-        <v>64.8</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -76759,12 +76759,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -77210,7 +77210,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -77490,7 +77490,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -77770,7 +77770,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -78050,7 +78050,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">

--- a/outputs/daily/hr_rankings_2026-08-22_full.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-22_full.xlsx
@@ -5476,7 +5476,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>56.8</v>
+        <v>56.9</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         <v>80</v>
       </c>
       <c r="U19" t="n">
-        <v>40.9</v>
+        <v>43.7</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -5707,12 +5707,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>672960</t>
+          <t>663662</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kazuma Okamoto</t>
+          <t>Daz Cameron</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -5737,7 +5737,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -5774,7 +5774,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>49.3</v>
+        <v>59.7</v>
       </c>
       <c r="Q20" t="n">
         <v>45.5</v>
@@ -5783,13 +5783,13 @@
         <v>48.2</v>
       </c>
       <c r="S20" t="n">
-        <v>86.40000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="T20" t="n">
         <v>78</v>
       </c>
       <c r="U20" t="n">
-        <v>61.5</v>
+        <v>54.9</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
@@ -5803,7 +5803,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -5824,7 +5824,7 @@
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr"/>
@@ -5836,27 +5836,27 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 4/11 over last 4 games</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
@@ -5866,72 +5866,72 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>19.63</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>27.13</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>88.19</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>101.4012</t>
+          <t>99.5682</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.426</t>
+          <t>0.5447</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>0.208</t>
+          <t>0.2722</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>0.314</t>
+          <t>0.3449</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>34.6</t>
+          <t>32.84</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>32.8</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>0.208</t>
+          <t>0.2835</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
@@ -5987,12 +5987,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>663662</t>
+          <t>672960</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Daz Cameron</t>
+          <t>Kazuma Okamoto</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -6017,7 +6017,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -6036,7 +6036,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>56.6</v>
+        <v>56.5</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>59.7</v>
+        <v>49.3</v>
       </c>
       <c r="Q21" t="n">
         <v>45.5</v>
@@ -6063,13 +6063,13 @@
         <v>48.2</v>
       </c>
       <c r="S21" t="n">
-        <v>64.3</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T21" t="n">
         <v>78</v>
       </c>
       <c r="U21" t="n">
-        <v>54.9</v>
+        <v>59.1</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -6083,7 +6083,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -6104,7 +6104,7 @@
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr"/>
@@ -6116,27 +6116,27 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Contact streak: 4/11 over last 3 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
@@ -6146,72 +6146,72 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>19.63</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>27.13</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>88.19</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>99.5682</t>
+          <t>101.4012</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.5447</t>
+          <t>0.426</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>0.2722</t>
+          <t>0.208</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>0.3449</t>
+          <t>0.314</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>32.84</t>
+          <t>34.6</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>32.8</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>0.2835</t>
+          <t>0.208</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
@@ -15879,52 +15879,52 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>641933</t>
+          <t>671277</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Tyler O'Neill</t>
+          <t>Luis García Jr.</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-22T23:05:00Z</t>
+          <t>2026-08-22T17:35:00Z</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Shane McClanahan</t>
+          <t>Dylan Cease</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>663556</t>
+          <t>656302</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L57" t="n">
@@ -15942,65 +15942,61 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P57" t="n">
-        <v>47.3</v>
+        <v>49.6</v>
       </c>
       <c r="Q57" t="n">
-        <v>43.4</v>
+        <v>20.3</v>
       </c>
       <c r="R57" t="n">
-        <v>32.1</v>
+        <v>48.2</v>
       </c>
       <c r="S57" t="n">
-        <v>88.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T57" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U57" t="n">
-        <v>14.6</v>
+        <v>41.2</v>
       </c>
       <c r="V57" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W57" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y57" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr"/>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD57" t="inlineStr"/>
@@ -16017,134 +16013,142 @@
       </c>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/23, 0 HR</t>
+          <t>Last 7 games: 6/22, 1 HR</t>
         </is>
       </c>
       <c r="AL57" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 8.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN57" t="inlineStr">
         <is>
-          <t>11.25</t>
+          <t>11.17</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>41.97</t>
+          <t>46.08</t>
         </is>
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>89.22</t>
+          <t>91.18</t>
         </is>
       </c>
       <c r="AQ57" t="inlineStr">
         <is>
-          <t>100.334</t>
+          <t>101.8604</t>
         </is>
       </c>
       <c r="AR57" t="inlineStr">
         <is>
-          <t>0.4355</t>
+          <t>0.4889</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr">
         <is>
-          <t>0.2114</t>
+          <t>0.2051</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>0.3453</t>
         </is>
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>72.81</t>
+          <t>73.66</t>
         </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
-          <t>23.68</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>44.95</t>
+          <t>40.66</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>39.28</t>
+          <t>22.68</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>0.1748</t>
+          <t>0.2314</t>
         </is>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="BB57" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>33.93</t>
         </is>
       </c>
       <c r="BC57" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>86.73</t>
         </is>
       </c>
       <c r="BD57" t="inlineStr">
         <is>
-          <t>0.405</t>
+          <t>0.3009</t>
         </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>0.1086</t>
         </is>
       </c>
       <c r="BF57" t="inlineStr">
         <is>
-          <t>27.7</t>
-        </is>
-      </c>
-      <c r="BG57" t="inlineStr"/>
-      <c r="BH57" t="inlineStr"/>
+          <t>25.47</t>
+        </is>
+      </c>
+      <c r="BG57" t="inlineStr">
+        <is>
+          <t>In From LF</t>
+        </is>
+      </c>
+      <c r="BH57" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
       <c r="BI57" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ57" t="inlineStr"/>
@@ -16155,27 +16159,27 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>701807</t>
+          <t>641933</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Carson Benge</t>
+          <t>Tyler O'Neill</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-08-22T23:10:00Z</t>
+          <t>2026-08-22T23:05:00Z</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -16185,22 +16189,22 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Luis Castillo</t>
+          <t>Shane McClanahan</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>622491</t>
+          <t>663556</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L58" t="n">
@@ -16218,26 +16222,26 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P58" t="n">
-        <v>33.7</v>
+        <v>47.3</v>
       </c>
       <c r="Q58" t="n">
-        <v>54.7</v>
+        <v>43.4</v>
       </c>
       <c r="R58" t="n">
-        <v>27.6</v>
+        <v>32.1</v>
       </c>
       <c r="S58" t="n">
-        <v>90.40000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="T58" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U58" t="n">
-        <v>54.7</v>
+        <v>14.6</v>
       </c>
       <c r="V58" t="inlineStr">
         <is>
@@ -16251,7 +16255,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr">
@@ -16276,7 +16280,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD58" t="inlineStr"/>
@@ -16293,134 +16297,134 @@
       </c>
       <c r="AH58" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/23, 0 HR</t>
         </is>
       </c>
       <c r="AL58" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.1% barrel, 20.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 8.0 HR allowed</t>
         </is>
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN58" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>11.25</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.97</t>
         </is>
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>89.22</t>
         </is>
       </c>
       <c r="AQ58" t="inlineStr">
         <is>
-          <t>99.9721</t>
+          <t>100.334</t>
         </is>
       </c>
       <c r="AR58" t="inlineStr">
         <is>
-          <t>0.437</t>
+          <t>0.4355</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr">
         <is>
-          <t>0.158</t>
+          <t>0.2114</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.325</t>
         </is>
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>70.9</t>
+          <t>72.81</t>
         </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>23.68</t>
         </is>
       </c>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>32.4</t>
+          <t>44.95</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>39.28</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>0.1748</t>
         </is>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
-          <t>10.05</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="BB58" t="inlineStr">
         <is>
-          <t>43.18</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="BC58" t="inlineStr">
         <is>
-          <t>90.09</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="BD58" t="inlineStr">
         <is>
-          <t>0.4425</t>
+          <t>0.405</t>
         </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
-          <t>0.1814</t>
+          <t>0.164</t>
         </is>
       </c>
       <c r="BF58" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="BG58" t="inlineStr"/>
       <c r="BH58" t="inlineStr"/>
       <c r="BI58" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ58" t="inlineStr"/>
@@ -16431,27 +16435,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>575929</t>
+          <t>701807</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Willson Contreras</t>
+          <t>Carson Benge</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-22T23:15:00Z</t>
+          <t>2026-08-22T23:10:00Z</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -16466,12 +16470,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Blade Tidwell</t>
+          <t>Luis Castillo</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>694918</t>
+          <t>622491</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -16480,7 +16484,7 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>50.9</v>
+        <v>51</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
@@ -16494,26 +16498,26 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>59.1</v>
+        <v>33.7</v>
       </c>
       <c r="Q59" t="n">
-        <v>26.2</v>
+        <v>54.7</v>
       </c>
       <c r="R59" t="n">
-        <v>28.7</v>
+        <v>27.6</v>
       </c>
       <c r="S59" t="n">
         <v>90.40000000000001</v>
       </c>
       <c r="T59" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U59" t="n">
-        <v>72.7</v>
+        <v>54.7</v>
       </c>
       <c r="V59" t="inlineStr">
         <is>
@@ -16552,7 +16556,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD59" t="inlineStr"/>
@@ -16569,7 +16573,7 @@
       </c>
       <c r="AH59" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI59" t="inlineStr">
@@ -16589,7 +16593,7 @@
       </c>
       <c r="AL59" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.5% barrel, 2.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.1% barrel, 20.2 HR allowed</t>
         </is>
       </c>
       <c r="AM59" t="inlineStr">
@@ -16599,104 +16603,104 @@
       </c>
       <c r="AN59" t="inlineStr">
         <is>
-          <t>14.32</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>46.13</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>90.18</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AQ59" t="inlineStr">
         <is>
-          <t>102.9905</t>
+          <t>99.9721</t>
         </is>
       </c>
       <c r="AR59" t="inlineStr">
         <is>
-          <t>0.4999</t>
+          <t>0.437</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr">
         <is>
-          <t>0.2401</t>
+          <t>0.158</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr">
         <is>
-          <t>0.3776</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>76.77</t>
+          <t>70.9</t>
         </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
-          <t>68.73</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>44.98</t>
+          <t>32.4</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>29.54</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>0.2362</t>
+          <t>0.145</t>
         </is>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>10.05</t>
         </is>
       </c>
       <c r="BB59" t="inlineStr">
         <is>
-          <t>36.64</t>
+          <t>43.18</t>
         </is>
       </c>
       <c r="BC59" t="inlineStr">
         <is>
-          <t>87.78</t>
+          <t>90.09</t>
         </is>
       </c>
       <c r="BD59" t="inlineStr">
         <is>
-          <t>0.3849</t>
+          <t>0.4425</t>
         </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>0.1814</t>
         </is>
       </c>
       <c r="BF59" t="inlineStr">
         <is>
-          <t>21.73</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="BG59" t="inlineStr"/>
       <c r="BH59" t="inlineStr"/>
       <c r="BI59" t="inlineStr">
         <is>
-          <t>Fenway Park</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ59" t="inlineStr"/>
@@ -16707,32 +16711,32 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>671277</t>
+          <t>575929</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Luis García Jr.</t>
+          <t>Willson Contreras</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-22T17:35:00Z</t>
+          <t>2026-08-22T23:15:00Z</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -16742,12 +16746,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Dylan Cease</t>
+          <t>Blade Tidwell</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>656302</t>
+          <t>694918</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -16756,7 +16760,7 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>50.8</v>
+        <v>50.9</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
@@ -16770,58 +16774,62 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P60" t="n">
-        <v>49.6</v>
+        <v>59.1</v>
       </c>
       <c r="Q60" t="n">
-        <v>20.3</v>
+        <v>26.2</v>
       </c>
       <c r="R60" t="n">
-        <v>48.2</v>
+        <v>28.7</v>
       </c>
       <c r="S60" t="n">
-        <v>94.90000000000001</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T60" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U60" t="n">
-        <v>36.3</v>
+        <v>72.7</v>
       </c>
       <c r="V60" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W60" t="inlineStr">
+      <c r="Z60" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y60" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC60" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -16841,7 +16849,7 @@
       </c>
       <c r="AH60" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI60" t="inlineStr">
@@ -16851,17 +16859,17 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL60" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.0% barrel, 12.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.5% barrel, 2.6 HR allowed</t>
         </is>
       </c>
       <c r="AM60" t="inlineStr">
@@ -16871,112 +16879,104 @@
       </c>
       <c r="AN60" t="inlineStr">
         <is>
-          <t>11.17</t>
+          <t>14.32</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>46.08</t>
+          <t>46.13</t>
         </is>
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>91.18</t>
+          <t>90.18</t>
         </is>
       </c>
       <c r="AQ60" t="inlineStr">
         <is>
-          <t>101.8604</t>
+          <t>102.9905</t>
         </is>
       </c>
       <c r="AR60" t="inlineStr">
         <is>
-          <t>0.4889</t>
+          <t>0.4999</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr">
         <is>
-          <t>0.2051</t>
+          <t>0.2401</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr">
         <is>
-          <t>0.3453</t>
+          <t>0.3776</t>
         </is>
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>73.66</t>
+          <t>76.77</t>
         </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>68.73</t>
         </is>
       </c>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>40.66</t>
+          <t>44.98</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>22.68</t>
+          <t>29.54</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>0.2314</t>
+          <t>0.2362</t>
         </is>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>6.51</t>
         </is>
       </c>
       <c r="BB60" t="inlineStr">
         <is>
-          <t>33.93</t>
+          <t>36.64</t>
         </is>
       </c>
       <c r="BC60" t="inlineStr">
         <is>
-          <t>86.73</t>
+          <t>87.78</t>
         </is>
       </c>
       <c r="BD60" t="inlineStr">
         <is>
-          <t>0.3009</t>
+          <t>0.3849</t>
         </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
-          <t>0.1086</t>
+          <t>0.125</t>
         </is>
       </c>
       <c r="BF60" t="inlineStr">
         <is>
-          <t>25.47</t>
-        </is>
-      </c>
-      <c r="BG60" t="inlineStr">
-        <is>
-          <t>In From LF</t>
-        </is>
-      </c>
-      <c r="BH60" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
+          <t>21.73</t>
+        </is>
+      </c>
+      <c r="BG60" t="inlineStr"/>
+      <c r="BH60" t="inlineStr"/>
       <c r="BI60" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Fenway Park</t>
         </is>
       </c>
       <c r="BJ60" t="inlineStr"/>
@@ -28851,52 +28851,52 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>671218</t>
+          <t>677594</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Heliot Ramos</t>
+          <t>Julio Rodriguez</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-08-22T17:35:00Z</t>
+          <t>2026-08-22T23:15:00Z</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Dylan Cease</t>
+          <t>David Peterson</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>656302</t>
+          <t>656849</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L104" t="n">
@@ -28914,58 +28914,62 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P104" t="n">
-        <v>48.9</v>
+        <v>46.6</v>
       </c>
       <c r="Q104" t="n">
-        <v>20.3</v>
+        <v>35.9</v>
       </c>
       <c r="R104" t="n">
-        <v>48.2</v>
+        <v>25.4</v>
       </c>
       <c r="S104" t="n">
-        <v>96.59999999999999</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T104" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U104" t="n">
-        <v>10.6</v>
+        <v>10.1</v>
       </c>
       <c r="V104" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X104" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W104" t="inlineStr">
+      <c r="Z104" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X104" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y104" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB104" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC104" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -28985,12 +28989,12 @@
       </c>
       <c r="AH104" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI104" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AJ104" t="inlineStr">
@@ -29000,127 +29004,119 @@
       </c>
       <c r="AK104" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 0 HR</t>
+          <t>Last 7 games: 6/32, 0 HR</t>
         </is>
       </c>
       <c r="AL104" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.0% barrel, 12.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.4% barrel, 11.0 HR allowed</t>
         </is>
       </c>
       <c r="AM104" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN104" t="inlineStr">
         <is>
-          <t>12.02</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>48.52</t>
+          <t>44.43</t>
         </is>
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>92.01</t>
+          <t>90.47</t>
         </is>
       </c>
       <c r="AQ104" t="inlineStr">
         <is>
-          <t>102.8875</t>
+          <t>102.6394</t>
         </is>
       </c>
       <c r="AR104" t="inlineStr">
         <is>
-          <t>0.4317</t>
+          <t>0.4692</t>
         </is>
       </c>
       <c r="AS104" t="inlineStr">
         <is>
-          <t>0.1792</t>
+          <t>0.1964</t>
         </is>
       </c>
       <c r="AT104" t="inlineStr">
         <is>
-          <t>0.3214</t>
+          <t>0.3482</t>
         </is>
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>72.92</t>
+          <t>76.68</t>
         </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
-          <t>31.56</t>
+          <t>67.62</t>
         </is>
       </c>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>33.17</t>
+          <t>38.63</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>22.46</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>0.1475</t>
+          <t>0.1755</t>
         </is>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="BB104" t="inlineStr">
         <is>
-          <t>33.93</t>
+          <t>42.64</t>
         </is>
       </c>
       <c r="BC104" t="inlineStr">
         <is>
-          <t>86.73</t>
+          <t>89.69</t>
         </is>
       </c>
       <c r="BD104" t="inlineStr">
         <is>
-          <t>0.3009</t>
+          <t>0.414</t>
         </is>
       </c>
       <c r="BE104" t="inlineStr">
         <is>
-          <t>0.1086</t>
+          <t>0.1405</t>
         </is>
       </c>
       <c r="BF104" t="inlineStr">
         <is>
-          <t>25.47</t>
-        </is>
-      </c>
-      <c r="BG104" t="inlineStr">
-        <is>
-          <t>In From LF</t>
-        </is>
-      </c>
-      <c r="BH104" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
+          <t>19.71</t>
+        </is>
+      </c>
+      <c r="BG104" t="inlineStr"/>
+      <c r="BH104" t="inlineStr"/>
       <c r="BI104" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ104" t="inlineStr"/>
@@ -29131,56 +29127,56 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>677594</t>
+          <t>671218</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Julio Rodriguez</t>
+          <t>Heliot Ramos</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-08-22T23:15:00Z</t>
+          <t>2026-08-22T17:35:00Z</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>David Peterson</t>
+          <t>Dylan Cease</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>656849</t>
+          <t>656302</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L105" t="n">
-        <v>46.8</v>
+        <v>46.7</v>
       </c>
       <c r="M105" t="inlineStr">
         <is>
@@ -29194,62 +29190,58 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P105" t="n">
-        <v>46.6</v>
+        <v>48.9</v>
       </c>
       <c r="Q105" t="n">
-        <v>35.9</v>
+        <v>20.3</v>
       </c>
       <c r="R105" t="n">
-        <v>25.4</v>
+        <v>48.2</v>
       </c>
       <c r="S105" t="n">
-        <v>81.90000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T105" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U105" t="n">
-        <v>10.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="V105" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X105" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W105" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X105" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y105" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr"/>
       <c r="AC105" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -29269,12 +29261,12 @@
       </c>
       <c r="AH105" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI105" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ105" t="inlineStr">
@@ -29284,119 +29276,127 @@
       </c>
       <c r="AK105" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/32, 0 HR</t>
+          <t>Last 7 games: 4/22, 0 HR</t>
         </is>
       </c>
       <c r="AL105" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.4% barrel, 11.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.0% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN105" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>12.02</t>
         </is>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>44.43</t>
+          <t>48.52</t>
         </is>
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>90.47</t>
+          <t>92.01</t>
         </is>
       </c>
       <c r="AQ105" t="inlineStr">
         <is>
-          <t>102.6394</t>
+          <t>102.8875</t>
         </is>
       </c>
       <c r="AR105" t="inlineStr">
         <is>
-          <t>0.4692</t>
+          <t>0.4317</t>
         </is>
       </c>
       <c r="AS105" t="inlineStr">
         <is>
-          <t>0.1964</t>
+          <t>0.1792</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr">
         <is>
-          <t>0.3482</t>
+          <t>0.3214</t>
         </is>
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>76.68</t>
+          <t>72.92</t>
         </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
-          <t>67.62</t>
+          <t>31.56</t>
         </is>
       </c>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>38.63</t>
+          <t>33.17</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>22.46</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>12.6</t>
         </is>
       </c>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>0.1755</t>
+          <t>0.1475</t>
         </is>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="BB105" t="inlineStr">
         <is>
-          <t>42.64</t>
+          <t>33.93</t>
         </is>
       </c>
       <c r="BC105" t="inlineStr">
         <is>
-          <t>89.69</t>
+          <t>86.73</t>
         </is>
       </c>
       <c r="BD105" t="inlineStr">
         <is>
-          <t>0.414</t>
+          <t>0.3009</t>
         </is>
       </c>
       <c r="BE105" t="inlineStr">
         <is>
-          <t>0.1405</t>
+          <t>0.1086</t>
         </is>
       </c>
       <c r="BF105" t="inlineStr">
         <is>
-          <t>19.71</t>
-        </is>
-      </c>
-      <c r="BG105" t="inlineStr"/>
-      <c r="BH105" t="inlineStr"/>
+          <t>25.47</t>
+        </is>
+      </c>
+      <c r="BG105" t="inlineStr">
+        <is>
+          <t>In From LF</t>
+        </is>
+      </c>
+      <c r="BH105" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
       <c r="BI105" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ105" t="inlineStr"/>
@@ -43099,47 +43099,47 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>702616</t>
+          <t>807727</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Jackson Holliday</t>
+          <t>Charles McAdoo</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-08-22T23:05:00Z</t>
+          <t>2026-08-22T17:35:00Z</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Shane McClanahan</t>
+          <t>Ryan Weathers</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>663556</t>
+          <t>677960</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
@@ -43148,7 +43148,7 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>41.5</v>
+        <v>41.6</v>
       </c>
       <c r="M156" t="inlineStr">
         <is>
@@ -43162,65 +43162,61 @@
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P156" t="n">
-        <v>25.6</v>
+        <v>21.7</v>
       </c>
       <c r="Q156" t="n">
-        <v>43.4</v>
+        <v>45.5</v>
       </c>
       <c r="R156" t="n">
-        <v>32.1</v>
+        <v>48.2</v>
       </c>
       <c r="S156" t="n">
-        <v>92.09999999999999</v>
+        <v>52.4</v>
       </c>
       <c r="T156" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U156" t="n">
-        <v>8.800000000000001</v>
+        <v>39.1</v>
       </c>
       <c r="V156" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W156" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X156" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z156" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W156" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X156" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y156" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z156" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB156" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB156" t="inlineStr"/>
       <c r="AC156" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD156" t="inlineStr"/>
@@ -43237,12 +43233,12 @@
       </c>
       <c r="AH156" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI156" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ156" t="inlineStr">
@@ -43252,12 +43248,12 @@
       </c>
       <c r="AK156" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/28, 0 HR</t>
+          <t>Contact streak: 8/21 over last 7 games</t>
         </is>
       </c>
       <c r="AL156" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 8.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 14.7 HR allowed</t>
         </is>
       </c>
       <c r="AM156" t="inlineStr">
@@ -43267,104 +43263,112 @@
       </c>
       <c r="AN156" t="inlineStr">
         <is>
-          <t>7.31</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AO156" t="inlineStr">
         <is>
-          <t>35.69</t>
+          <t>31.7</t>
         </is>
       </c>
       <c r="AP156" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AQ156" t="inlineStr">
         <is>
-          <t>98.0892</t>
+          <t>97.3928</t>
         </is>
       </c>
       <c r="AR156" t="inlineStr">
         <is>
-          <t>0.376</t>
+          <t>0.358</t>
         </is>
       </c>
       <c r="AS156" t="inlineStr">
         <is>
-          <t>0.1371</t>
+          <t>0.121</t>
         </is>
       </c>
       <c r="AT156" t="inlineStr">
         <is>
-          <t>0.3119</t>
+          <t>0.275</t>
         </is>
       </c>
       <c r="AU156" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AV156" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>33.7</t>
         </is>
       </c>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>34.43</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>24.82</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>0.1323</t>
+          <t>0.141</t>
         </is>
       </c>
       <c r="BA156" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.76</t>
         </is>
       </c>
       <c r="BB156" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="BC156" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>89.46</t>
         </is>
       </c>
       <c r="BD156" t="inlineStr">
         <is>
-          <t>0.405</t>
+          <t>0.4173</t>
         </is>
       </c>
       <c r="BE156" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>0.1708</t>
         </is>
       </c>
       <c r="BF156" t="inlineStr">
         <is>
-          <t>27.7</t>
-        </is>
-      </c>
-      <c r="BG156" t="inlineStr"/>
-      <c r="BH156" t="inlineStr"/>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="BG156" t="inlineStr">
+        <is>
+          <t>In From LF</t>
+        </is>
+      </c>
+      <c r="BH156" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
       <c r="BI156" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ156" t="inlineStr"/>
@@ -43375,47 +43379,47 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>807727</t>
+          <t>702616</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Charles McAdoo</t>
+          <t>Jackson Holliday</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>2026-08-22T17:35:00Z</t>
+          <t>2026-08-22T23:05:00Z</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Ryan Weathers</t>
+          <t>Shane McClanahan</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>677960</t>
+          <t>663556</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -43424,7 +43428,7 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>41.4</v>
+        <v>41.5</v>
       </c>
       <c r="M157" t="inlineStr">
         <is>
@@ -43438,61 +43442,65 @@
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P157" t="n">
-        <v>21.7</v>
+        <v>25.6</v>
       </c>
       <c r="Q157" t="n">
-        <v>45.5</v>
+        <v>43.4</v>
       </c>
       <c r="R157" t="n">
-        <v>48.2</v>
+        <v>32.1</v>
       </c>
       <c r="S157" t="n">
-        <v>52.4</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T157" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U157" t="n">
-        <v>34.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="V157" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X157" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W157" t="inlineStr">
+      <c r="Z157" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X157" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y157" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z157" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB157" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC157" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD157" t="inlineStr"/>
@@ -43509,12 +43517,12 @@
       </c>
       <c r="AH157" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI157" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ157" t="inlineStr">
@@ -43524,12 +43532,12 @@
       </c>
       <c r="AK157" t="inlineStr">
         <is>
-          <t>Contact streak: 8/23 over last 7 games</t>
+          <t>Last 7 games: 5/28, 0 HR</t>
         </is>
       </c>
       <c r="AL157" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 14.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 8.0 HR allowed</t>
         </is>
       </c>
       <c r="AM157" t="inlineStr">
@@ -43539,112 +43547,104 @@
       </c>
       <c r="AN157" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.31</t>
         </is>
       </c>
       <c r="AO157" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>35.69</t>
         </is>
       </c>
       <c r="AP157" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="AQ157" t="inlineStr">
         <is>
-          <t>97.3928</t>
+          <t>98.0892</t>
         </is>
       </c>
       <c r="AR157" t="inlineStr">
         <is>
-          <t>0.358</t>
+          <t>0.376</t>
         </is>
       </c>
       <c r="AS157" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>0.1371</t>
         </is>
       </c>
       <c r="AT157" t="inlineStr">
         <is>
-          <t>0.275</t>
+          <t>0.3119</t>
         </is>
       </c>
       <c r="AU157" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>70.6</t>
         </is>
       </c>
       <c r="AV157" t="inlineStr">
         <is>
-          <t>33.7</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>34.43</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>24.82</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>0.1323</t>
         </is>
       </c>
       <c r="BA157" t="inlineStr">
         <is>
-          <t>8.76</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="BB157" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="BC157" t="inlineStr">
         <is>
-          <t>89.46</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="BD157" t="inlineStr">
         <is>
-          <t>0.4173</t>
+          <t>0.405</t>
         </is>
       </c>
       <c r="BE157" t="inlineStr">
         <is>
-          <t>0.1708</t>
+          <t>0.164</t>
         </is>
       </c>
       <c r="BF157" t="inlineStr">
         <is>
-          <t>25.2</t>
-        </is>
-      </c>
-      <c r="BG157" t="inlineStr">
-        <is>
-          <t>In From LF</t>
-        </is>
-      </c>
-      <c r="BH157" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
+          <t>27.7</t>
+        </is>
+      </c>
+      <c r="BG157" t="inlineStr"/>
+      <c r="BH157" t="inlineStr"/>
       <c r="BI157" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ157" t="inlineStr"/>
@@ -46907,52 +46907,52 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>691594</t>
+          <t>676391</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Javier Sanoja</t>
+          <t>Ernie Clement</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>2026-08-22T20:10:00Z</t>
+          <t>2026-08-22T17:35:00Z</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>Jake Irvin</t>
+          <t>Ryan Weathers</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>663623</t>
+          <t>677960</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L170" t="n">
@@ -46970,26 +46970,26 @@
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t>Hot Hitter/Streak</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P170" t="n">
-        <v>9.6</v>
+        <v>5.5</v>
       </c>
       <c r="Q170" t="n">
-        <v>64.40000000000001</v>
+        <v>45.5</v>
       </c>
       <c r="R170" t="n">
-        <v>35</v>
+        <v>48.2</v>
       </c>
       <c r="S170" t="n">
-        <v>52.4</v>
+        <v>76.2</v>
       </c>
       <c r="T170" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U170" t="n">
-        <v>77.40000000000001</v>
+        <v>39.1</v>
       </c>
       <c r="V170" t="inlineStr">
         <is>
@@ -47003,7 +47003,7 @@
       </c>
       <c r="X170" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y170" t="inlineStr">
@@ -47041,142 +47041,142 @@
       </c>
       <c r="AH170" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI170" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK170" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 8/21 over last 7 games</t>
         </is>
       </c>
       <c r="AL170" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 12.2% barrel, 19.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 14.7 HR allowed</t>
         </is>
       </c>
       <c r="AM170" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN170" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="AO170" t="inlineStr">
         <is>
-          <t>32.06</t>
+          <t>22.08</t>
         </is>
       </c>
       <c r="AP170" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>85.13</t>
         </is>
       </c>
       <c r="AQ170" t="inlineStr">
         <is>
-          <t>97.3605</t>
+          <t>94.7039</t>
         </is>
       </c>
       <c r="AR170" t="inlineStr">
         <is>
-          <t>0.3343</t>
+          <t>0.3415</t>
         </is>
       </c>
       <c r="AS170" t="inlineStr">
         <is>
-          <t>0.0795</t>
+          <t>0.0867</t>
         </is>
       </c>
       <c r="AT170" t="inlineStr">
         <is>
-          <t>0.2792</t>
+          <t>0.2757</t>
         </is>
       </c>
       <c r="AU170" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>67.46</t>
         </is>
       </c>
       <c r="AV170" t="inlineStr">
         <is>
-          <t>6.74</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>37.17</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>27.83</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AZ170" t="inlineStr">
         <is>
-          <t>0.1474</t>
+          <t>0.1189</t>
         </is>
       </c>
       <c r="BA170" t="inlineStr">
         <is>
-          <t>12.21</t>
+          <t>8.76</t>
         </is>
       </c>
       <c r="BB170" t="inlineStr">
         <is>
-          <t>44.79</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="BC170" t="inlineStr">
         <is>
-          <t>89.28</t>
+          <t>89.46</t>
         </is>
       </c>
       <c r="BD170" t="inlineStr">
         <is>
-          <t>0.4742</t>
+          <t>0.4173</t>
         </is>
       </c>
       <c r="BE170" t="inlineStr">
         <is>
-          <t>0.2197</t>
+          <t>0.1708</t>
         </is>
       </c>
       <c r="BF170" t="inlineStr">
         <is>
-          <t>30.07</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="BG170" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH170" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI170" t="inlineStr">
         <is>
-          <t>loanDepot park</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ170" t="inlineStr"/>
@@ -47187,47 +47187,47 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>608070</t>
+          <t>691594</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>Javier Sanoja</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-08-23T00:10:00Z</t>
+          <t>2026-08-22T20:10:00Z</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>Gabriel Hughes</t>
+          <t>Jake Irvin</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>687312</t>
+          <t>663623</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
@@ -47250,65 +47250,61 @@
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P171" t="n">
-        <v>29.6</v>
+        <v>9.6</v>
       </c>
       <c r="Q171" t="n">
-        <v>14</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="R171" t="n">
-        <v>38.7</v>
+        <v>35</v>
       </c>
       <c r="S171" t="n">
-        <v>92.09999999999999</v>
+        <v>52.4</v>
       </c>
       <c r="T171" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U171" t="n">
-        <v>20.9</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="V171" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W171" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X171" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y171" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z171" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W171" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X171" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y171" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z171" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA171" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB171" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB171" t="inlineStr"/>
       <c r="AC171" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD171" t="inlineStr"/>
@@ -47325,134 +47321,142 @@
       </c>
       <c r="AH171" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI171" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL171" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 4.3% barrel, 3.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 12.2% barrel, 19.8 HR allowed</t>
         </is>
       </c>
       <c r="AM171" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN171" t="inlineStr">
         <is>
-          <t>5.53</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="AO171" t="inlineStr">
         <is>
-          <t>40.08</t>
+          <t>32.06</t>
         </is>
       </c>
       <c r="AP171" t="inlineStr">
         <is>
-          <t>89.11</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="AQ171" t="inlineStr">
         <is>
-          <t>99.6485</t>
+          <t>97.3605</t>
         </is>
       </c>
       <c r="AR171" t="inlineStr">
         <is>
-          <t>0.4292</t>
+          <t>0.3343</t>
         </is>
       </c>
       <c r="AS171" t="inlineStr">
         <is>
-          <t>0.1473</t>
+          <t>0.0795</t>
         </is>
       </c>
       <c r="AT171" t="inlineStr">
         <is>
-          <t>0.3462</t>
+          <t>0.2792</t>
         </is>
       </c>
       <c r="AU171" t="inlineStr">
         <is>
-          <t>70.34</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AV171" t="inlineStr">
         <is>
-          <t>13.47</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>50.62</t>
+          <t>37.17</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>29.41</t>
+          <t>19.11</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AZ171" t="inlineStr">
         <is>
-          <t>0.1654</t>
+          <t>0.1474</t>
         </is>
       </c>
       <c r="BA171" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>12.21</t>
         </is>
       </c>
       <c r="BB171" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>44.79</t>
         </is>
       </c>
       <c r="BC171" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>89.28</t>
         </is>
       </c>
       <c r="BD171" t="inlineStr">
         <is>
-          <t>0.338</t>
+          <t>0.4742</t>
         </is>
       </c>
       <c r="BE171" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>0.2197</t>
         </is>
       </c>
       <c r="BF171" t="inlineStr">
         <is>
-          <t>25.0</t>
-        </is>
-      </c>
-      <c r="BG171" t="inlineStr"/>
-      <c r="BH171" t="inlineStr"/>
+          <t>30.07</t>
+        </is>
+      </c>
+      <c r="BG171" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH171" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI171" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>loanDepot park</t>
         </is>
       </c>
       <c r="BJ171" t="inlineStr"/>
@@ -47463,27 +47467,27 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>656775</t>
+          <t>608070</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Cedric Mullins</t>
+          <t>Jose Ramirez</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>2026-08-22T23:05:00Z</t>
+          <t>2026-08-23T00:10:00Z</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -47493,17 +47497,17 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>Brandon Young</t>
+          <t>Gabriel Hughes</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>687064</t>
+          <t>687312</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
@@ -47512,7 +47516,7 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>39.5</v>
+        <v>39.6</v>
       </c>
       <c r="M172" t="inlineStr">
         <is>
@@ -47526,26 +47530,26 @@
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P172" t="n">
-        <v>19.2</v>
+        <v>29.6</v>
       </c>
       <c r="Q172" t="n">
-        <v>43.6</v>
+        <v>14</v>
       </c>
       <c r="R172" t="n">
-        <v>32.1</v>
+        <v>38.7</v>
       </c>
       <c r="S172" t="n">
-        <v>71.7</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T172" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U172" t="n">
-        <v>12</v>
+        <v>20.9</v>
       </c>
       <c r="V172" t="inlineStr">
         <is>
@@ -47559,7 +47563,7 @@
       </c>
       <c r="X172" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y172" t="inlineStr">
@@ -47584,7 +47588,7 @@
       </c>
       <c r="AC172" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD172" t="inlineStr"/>
@@ -47601,12 +47605,12 @@
       </c>
       <c r="AH172" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI172" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ172" t="inlineStr">
@@ -47616,12 +47620,12 @@
       </c>
       <c r="AK172" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/20, 0 HR</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AL172" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.9% barrel, 14.1 HR allowed</t>
+          <t>switch hitter; pitcher baseline 4.3% barrel, 3.0 HR allowed</t>
         </is>
       </c>
       <c r="AM172" t="inlineStr">
@@ -47631,104 +47635,104 @@
       </c>
       <c r="AN172" t="inlineStr">
         <is>
-          <t>4.52</t>
+          <t>5.53</t>
         </is>
       </c>
       <c r="AO172" t="inlineStr">
         <is>
-          <t>32.68</t>
+          <t>40.08</t>
         </is>
       </c>
       <c r="AP172" t="inlineStr">
         <is>
-          <t>87.96</t>
+          <t>89.11</t>
         </is>
       </c>
       <c r="AQ172" t="inlineStr">
         <is>
-          <t>97.8022</t>
+          <t>99.6485</t>
         </is>
       </c>
       <c r="AR172" t="inlineStr">
         <is>
-          <t>0.3148</t>
+          <t>0.4292</t>
         </is>
       </c>
       <c r="AS172" t="inlineStr">
         <is>
-          <t>0.1225</t>
+          <t>0.1473</t>
         </is>
       </c>
       <c r="AT172" t="inlineStr">
         <is>
-          <t>0.2658</t>
+          <t>0.3462</t>
         </is>
       </c>
       <c r="AU172" t="inlineStr">
         <is>
-          <t>70.89</t>
+          <t>70.34</t>
         </is>
       </c>
       <c r="AV172" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>13.47</t>
         </is>
       </c>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>44.69</t>
+          <t>50.62</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>32.01</t>
+          <t>29.41</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="AZ172" t="inlineStr">
         <is>
-          <t>0.1547</t>
+          <t>0.1654</t>
         </is>
       </c>
       <c r="BA172" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="BB172" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="BC172" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="BD172" t="inlineStr">
         <is>
-          <t>0.4201</t>
+          <t>0.338</t>
         </is>
       </c>
       <c r="BE172" t="inlineStr">
         <is>
-          <t>0.1672</t>
+          <t>0.106</t>
         </is>
       </c>
       <c r="BF172" t="inlineStr">
         <is>
-          <t>27.43</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="BG172" t="inlineStr"/>
       <c r="BH172" t="inlineStr"/>
       <c r="BI172" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ172" t="inlineStr"/>
@@ -47739,32 +47743,32 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>676391</t>
+          <t>656775</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Ernie Clement</t>
+          <t>Cedric Mullins</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2026-08-22T17:35:00Z</t>
+          <t>2026-08-22T23:05:00Z</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -47774,21 +47778,21 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>Ryan Weathers</t>
+          <t>Brandon Young</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>677960</t>
+          <t>687064</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L173" t="n">
-        <v>39.4</v>
+        <v>39.5</v>
       </c>
       <c r="M173" t="inlineStr">
         <is>
@@ -47802,58 +47806,62 @@
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P173" t="n">
-        <v>5.5</v>
+        <v>19.2</v>
       </c>
       <c r="Q173" t="n">
-        <v>45.5</v>
+        <v>43.6</v>
       </c>
       <c r="R173" t="n">
-        <v>48.2</v>
+        <v>32.1</v>
       </c>
       <c r="S173" t="n">
-        <v>76.2</v>
+        <v>71.7</v>
       </c>
       <c r="T173" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U173" t="n">
-        <v>34.2</v>
+        <v>12</v>
       </c>
       <c r="V173" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W173" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X173" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y173" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W173" t="inlineStr">
+      <c r="Z173" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X173" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y173" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z173" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB173" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB173" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC173" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -47873,12 +47881,12 @@
       </c>
       <c r="AH173" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI173" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ173" t="inlineStr">
@@ -47888,12 +47896,12 @@
       </c>
       <c r="AK173" t="inlineStr">
         <is>
-          <t>Contact streak: 8/23 over last 7 games</t>
+          <t>Last 7 games: 4/20, 0 HR</t>
         </is>
       </c>
       <c r="AL173" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 14.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.9% barrel, 14.1 HR allowed</t>
         </is>
       </c>
       <c r="AM173" t="inlineStr">
@@ -47903,72 +47911,72 @@
       </c>
       <c r="AN173" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>4.52</t>
         </is>
       </c>
       <c r="AO173" t="inlineStr">
         <is>
-          <t>22.08</t>
+          <t>32.68</t>
         </is>
       </c>
       <c r="AP173" t="inlineStr">
         <is>
-          <t>85.13</t>
+          <t>87.96</t>
         </is>
       </c>
       <c r="AQ173" t="inlineStr">
         <is>
-          <t>94.7039</t>
+          <t>97.8022</t>
         </is>
       </c>
       <c r="AR173" t="inlineStr">
         <is>
-          <t>0.3415</t>
+          <t>0.3148</t>
         </is>
       </c>
       <c r="AS173" t="inlineStr">
         <is>
-          <t>0.0867</t>
+          <t>0.1225</t>
         </is>
       </c>
       <c r="AT173" t="inlineStr">
         <is>
-          <t>0.2757</t>
+          <t>0.2658</t>
         </is>
       </c>
       <c r="AU173" t="inlineStr">
         <is>
-          <t>67.46</t>
+          <t>70.89</t>
         </is>
       </c>
       <c r="AV173" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>44.69</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>27.83</t>
+          <t>32.01</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>0.1189</t>
+          <t>0.1547</t>
         </is>
       </c>
       <c r="BA173" t="inlineStr">
         <is>
-          <t>8.76</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="BB173" t="inlineStr">
@@ -47978,37 +47986,29 @@
       </c>
       <c r="BC173" t="inlineStr">
         <is>
-          <t>89.46</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="BD173" t="inlineStr">
         <is>
-          <t>0.4173</t>
+          <t>0.4201</t>
         </is>
       </c>
       <c r="BE173" t="inlineStr">
         <is>
-          <t>0.1708</t>
+          <t>0.1672</t>
         </is>
       </c>
       <c r="BF173" t="inlineStr">
         <is>
-          <t>25.2</t>
-        </is>
-      </c>
-      <c r="BG173" t="inlineStr">
-        <is>
-          <t>In From LF</t>
-        </is>
-      </c>
-      <c r="BH173" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
+          <t>27.43</t>
+        </is>
+      </c>
+      <c r="BG173" t="inlineStr"/>
+      <c r="BH173" t="inlineStr"/>
       <c r="BI173" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ173" t="inlineStr"/>
@@ -58439,56 +58439,56 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>665750</t>
+          <t>806146</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Leody Taveras</t>
+          <t>George Lombard Jr.</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>2026-08-22T23:05:00Z</t>
+          <t>2026-08-22T17:35:00Z</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>Shane McClanahan</t>
+          <t>Dylan Cease</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>663556</t>
+          <t>656302</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L212" t="n">
-        <v>35.4</v>
+        <v>35.5</v>
       </c>
       <c r="M212" t="inlineStr">
         <is>
@@ -58502,65 +58502,61 @@
       </c>
       <c r="O212" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P212" t="n">
-        <v>18.9</v>
+        <v>19.6</v>
       </c>
       <c r="Q212" t="n">
-        <v>42.6</v>
+        <v>20.3</v>
       </c>
       <c r="R212" t="n">
-        <v>32.1</v>
+        <v>48.2</v>
       </c>
       <c r="S212" t="n">
-        <v>40.2</v>
+        <v>76.2</v>
       </c>
       <c r="T212" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U212" t="n">
-        <v>34.2</v>
+        <v>34.5</v>
       </c>
       <c r="V212" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W212" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X212" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y212" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z212" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W212" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X212" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y212" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z212" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA212" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB212" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB212" t="inlineStr"/>
       <c r="AC212" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD212" t="inlineStr"/>
@@ -58577,12 +58573,12 @@
       </c>
       <c r="AH212" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI212" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ212" t="inlineStr">
@@ -58592,12 +58588,12 @@
       </c>
       <c r="AK212" t="inlineStr">
         <is>
-          <t>Contact streak: 8/23 over last 7 games</t>
+          <t>Contact streak: 7/20 over last 7 games</t>
         </is>
       </c>
       <c r="AL212" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.7% barrel, 8.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.0% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM212" t="inlineStr">
@@ -58607,104 +58603,112 @@
       </c>
       <c r="AN212" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="AO212" t="inlineStr">
         <is>
-          <t>33.1</t>
+          <t>35.1</t>
         </is>
       </c>
       <c r="AP212" t="inlineStr">
         <is>
-          <t>88.08</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AQ212" t="inlineStr">
         <is>
-          <t>99.0534</t>
+          <t>97.5738</t>
         </is>
       </c>
       <c r="AR212" t="inlineStr">
         <is>
-          <t>0.3251</t>
+          <t>0.358</t>
         </is>
       </c>
       <c r="AS212" t="inlineStr">
         <is>
-          <t>0.1124</t>
+          <t>0.105</t>
         </is>
       </c>
       <c r="AT212" t="inlineStr">
         <is>
-          <t>0.2663</t>
+          <t>0.303</t>
         </is>
       </c>
       <c r="AU212" t="inlineStr">
         <is>
-          <t>72.39</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AV212" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>32.4</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>24.31</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ212" t="inlineStr">
         <is>
-          <t>0.1221</t>
+          <t>0.135</t>
         </is>
       </c>
       <c r="BA212" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="BB212" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>33.93</t>
         </is>
       </c>
       <c r="BC212" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>86.73</t>
         </is>
       </c>
       <c r="BD212" t="inlineStr">
         <is>
-          <t>0.405</t>
+          <t>0.3009</t>
         </is>
       </c>
       <c r="BE212" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>0.1086</t>
         </is>
       </c>
       <c r="BF212" t="inlineStr">
         <is>
-          <t>27.7</t>
-        </is>
-      </c>
-      <c r="BG212" t="inlineStr"/>
-      <c r="BH212" t="inlineStr"/>
+          <t>25.47</t>
+        </is>
+      </c>
+      <c r="BG212" t="inlineStr">
+        <is>
+          <t>In From LF</t>
+        </is>
+      </c>
+      <c r="BH212" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
       <c r="BI212" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ212" t="inlineStr"/>
@@ -58715,27 +58719,27 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>514888</t>
+          <t>665750</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Jose Altuve</t>
+          <t>Leody Taveras</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>2026-08-22T23:10:00Z</t>
+          <t>2026-08-22T23:05:00Z</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
@@ -58745,17 +58749,17 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>Jacob Lopez</t>
+          <t>Shane McClanahan</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>682052</t>
+          <t>663556</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
@@ -58778,26 +58782,26 @@
       </c>
       <c r="O213" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P213" t="n">
-        <v>13.6</v>
+        <v>18.9</v>
       </c>
       <c r="Q213" t="n">
-        <v>21.9</v>
+        <v>42.6</v>
       </c>
       <c r="R213" t="n">
-        <v>27.6</v>
+        <v>32.1</v>
       </c>
       <c r="S213" t="n">
-        <v>90.40000000000001</v>
+        <v>40.2</v>
       </c>
       <c r="T213" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U213" t="n">
-        <v>36</v>
+        <v>34.2</v>
       </c>
       <c r="V213" t="inlineStr">
         <is>
@@ -58811,7 +58815,7 @@
       </c>
       <c r="X213" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y213" t="inlineStr">
@@ -58836,7 +58840,7 @@
       </c>
       <c r="AC213" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD213" t="inlineStr"/>
@@ -58853,12 +58857,12 @@
       </c>
       <c r="AH213" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI213" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ213" t="inlineStr">
@@ -58868,119 +58872,119 @@
       </c>
       <c r="AK213" t="inlineStr">
         <is>
-          <t>Contact streak: 9/25 over last 7 games</t>
+          <t>Contact streak: 8/23 over last 7 games</t>
         </is>
       </c>
       <c r="AL213" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.7% barrel, 15.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.7% barrel, 8.0 HR allowed</t>
         </is>
       </c>
       <c r="AM213" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN213" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="AO213" t="inlineStr">
         <is>
-          <t>31.11</t>
+          <t>33.1</t>
         </is>
       </c>
       <c r="AP213" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>88.08</t>
         </is>
       </c>
       <c r="AQ213" t="inlineStr">
         <is>
-          <t>96.9181</t>
+          <t>99.0534</t>
         </is>
       </c>
       <c r="AR213" t="inlineStr">
         <is>
-          <t>0.3455</t>
+          <t>0.3251</t>
         </is>
       </c>
       <c r="AS213" t="inlineStr">
         <is>
-          <t>0.1183</t>
+          <t>0.1124</t>
         </is>
       </c>
       <c r="AT213" t="inlineStr">
         <is>
-          <t>0.2825</t>
+          <t>0.2663</t>
         </is>
       </c>
       <c r="AU213" t="inlineStr">
         <is>
-          <t>69.07</t>
+          <t>72.39</t>
         </is>
       </c>
       <c r="AV213" t="inlineStr">
         <is>
-          <t>10.13</t>
+          <t>24.32</t>
         </is>
       </c>
       <c r="AW213" t="inlineStr">
         <is>
-          <t>45.92</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>24.31</t>
         </is>
       </c>
       <c r="AY213" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="AZ213" t="inlineStr">
         <is>
-          <t>0.1574</t>
+          <t>0.1221</t>
         </is>
       </c>
       <c r="BA213" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="BB213" t="inlineStr">
         <is>
-          <t>30.19</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="BC213" t="inlineStr">
         <is>
-          <t>85.29</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="BD213" t="inlineStr">
         <is>
-          <t>0.3424</t>
+          <t>0.405</t>
         </is>
       </c>
       <c r="BE213" t="inlineStr">
         <is>
-          <t>0.1338</t>
+          <t>0.164</t>
         </is>
       </c>
       <c r="BF213" t="inlineStr">
         <is>
-          <t>32.48</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="BG213" t="inlineStr"/>
       <c r="BH213" t="inlineStr"/>
       <c r="BI213" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ213" t="inlineStr"/>
@@ -58991,27 +58995,27 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>680574</t>
+          <t>514888</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Matt McLain</t>
+          <t>Jose Altuve</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>2026-08-23T00:10:00Z</t>
+          <t>2026-08-22T23:10:00Z</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
@@ -59021,22 +59025,22 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>Michael Soroka</t>
+          <t>Jacob Lopez</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>647336</t>
+          <t>682052</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L214" t="n">
@@ -59054,26 +59058,26 @@
       </c>
       <c r="O214" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P214" t="n">
-        <v>34.6</v>
+        <v>13.6</v>
       </c>
       <c r="Q214" t="n">
-        <v>33.7</v>
+        <v>21.9</v>
       </c>
       <c r="R214" t="n">
-        <v>28.2</v>
+        <v>27.6</v>
       </c>
       <c r="S214" t="n">
-        <v>40.2</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T214" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U214" t="n">
-        <v>31.6</v>
+        <v>36</v>
       </c>
       <c r="V214" t="inlineStr">
         <is>
@@ -59087,7 +59091,7 @@
       </c>
       <c r="X214" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y214" t="inlineStr">
@@ -59129,134 +59133,134 @@
       </c>
       <c r="AH214" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI214" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK214" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 1 HR</t>
+          <t>Contact streak: 9/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL214" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.6% barrel, 7.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.7% barrel, 15.0 HR allowed</t>
         </is>
       </c>
       <c r="AM214" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN214" t="inlineStr">
         <is>
-          <t>9.55</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="AO214" t="inlineStr">
         <is>
-          <t>38.53</t>
+          <t>31.11</t>
         </is>
       </c>
       <c r="AP214" t="inlineStr">
         <is>
-          <t>88.31</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="AQ214" t="inlineStr">
         <is>
-          <t>99.0888</t>
+          <t>96.9181</t>
         </is>
       </c>
       <c r="AR214" t="inlineStr">
         <is>
-          <t>0.3876</t>
+          <t>0.3455</t>
         </is>
       </c>
       <c r="AS214" t="inlineStr">
         <is>
-          <t>0.1602</t>
+          <t>0.1183</t>
         </is>
       </c>
       <c r="AT214" t="inlineStr">
         <is>
-          <t>0.3117</t>
+          <t>0.2825</t>
         </is>
       </c>
       <c r="AU214" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>69.07</t>
         </is>
       </c>
       <c r="AV214" t="inlineStr">
         <is>
-          <t>9.96</t>
+          <t>10.13</t>
         </is>
       </c>
       <c r="AW214" t="inlineStr">
         <is>
-          <t>35.57</t>
+          <t>45.92</t>
         </is>
       </c>
       <c r="AX214" t="inlineStr">
         <is>
-          <t>32.31</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="AY214" t="inlineStr">
         <is>
-          <t>12.9</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="AZ214" t="inlineStr">
         <is>
-          <t>0.1461</t>
+          <t>0.1574</t>
         </is>
       </c>
       <c r="BA214" t="inlineStr">
         <is>
-          <t>7.61</t>
+          <t>5.69</t>
         </is>
       </c>
       <c r="BB214" t="inlineStr">
         <is>
-          <t>34.94</t>
+          <t>30.19</t>
         </is>
       </c>
       <c r="BC214" t="inlineStr">
         <is>
-          <t>88.08</t>
+          <t>85.29</t>
         </is>
       </c>
       <c r="BD214" t="inlineStr">
         <is>
-          <t>0.3902</t>
+          <t>0.3424</t>
         </is>
       </c>
       <c r="BE214" t="inlineStr">
         <is>
-          <t>0.1497</t>
+          <t>0.1338</t>
         </is>
       </c>
       <c r="BF214" t="inlineStr">
         <is>
-          <t>28.36</t>
+          <t>32.48</t>
         </is>
       </c>
       <c r="BG214" t="inlineStr"/>
       <c r="BH214" t="inlineStr"/>
       <c r="BI214" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ214" t="inlineStr"/>
@@ -59267,27 +59271,27 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>680700</t>
+          <t>680574</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Richie Palacios</t>
+          <t>Matt McLain</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>2026-08-22T23:05:00Z</t>
+          <t>2026-08-23T00:10:00Z</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
@@ -59297,17 +59301,17 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>Brandon Young</t>
+          <t>Michael Soroka</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>687064</t>
+          <t>647336</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
@@ -59316,7 +59320,7 @@
         </is>
       </c>
       <c r="L215" t="n">
-        <v>35.3</v>
+        <v>35.4</v>
       </c>
       <c r="M215" t="inlineStr">
         <is>
@@ -59330,26 +59334,26 @@
       </c>
       <c r="O215" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P215" t="n">
-        <v>15.1</v>
+        <v>34.6</v>
       </c>
       <c r="Q215" t="n">
-        <v>43.6</v>
+        <v>33.7</v>
       </c>
       <c r="R215" t="n">
-        <v>32.1</v>
+        <v>28.2</v>
       </c>
       <c r="S215" t="n">
-        <v>47.9</v>
+        <v>40.2</v>
       </c>
       <c r="T215" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U215" t="n">
-        <v>22.9</v>
+        <v>31.6</v>
       </c>
       <c r="V215" t="inlineStr">
         <is>
@@ -59363,7 +59367,7 @@
       </c>
       <c r="X215" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y215" t="inlineStr">
@@ -59405,27 +59409,27 @@
       </c>
       <c r="AH215" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI215" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/22, 0 HR</t>
+          <t>Last 7 games: 5/24, 1 HR</t>
         </is>
       </c>
       <c r="AL215" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.9% barrel, 14.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.6% barrel, 7.8 HR allowed</t>
         </is>
       </c>
       <c r="AM215" t="inlineStr">
@@ -59435,104 +59439,104 @@
       </c>
       <c r="AN215" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>9.55</t>
         </is>
       </c>
       <c r="AO215" t="inlineStr">
         <is>
-          <t>32.97</t>
+          <t>38.53</t>
         </is>
       </c>
       <c r="AP215" t="inlineStr">
         <is>
-          <t>87.38</t>
+          <t>88.31</t>
         </is>
       </c>
       <c r="AQ215" t="inlineStr">
         <is>
-          <t>97.0638</t>
+          <t>99.0888</t>
         </is>
       </c>
       <c r="AR215" t="inlineStr">
         <is>
-          <t>0.3709</t>
+          <t>0.3876</t>
         </is>
       </c>
       <c r="AS215" t="inlineStr">
         <is>
-          <t>0.1011</t>
+          <t>0.1602</t>
         </is>
       </c>
       <c r="AT215" t="inlineStr">
         <is>
-          <t>0.3264</t>
+          <t>0.3117</t>
         </is>
       </c>
       <c r="AU215" t="inlineStr">
         <is>
-          <t>68.77</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AV215" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>9.96</t>
         </is>
       </c>
       <c r="AW215" t="inlineStr">
         <is>
-          <t>35.62</t>
+          <t>35.57</t>
         </is>
       </c>
       <c r="AX215" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>32.31</t>
         </is>
       </c>
       <c r="AY215" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>12.9</t>
         </is>
       </c>
       <c r="AZ215" t="inlineStr">
         <is>
-          <t>0.1162</t>
+          <t>0.1461</t>
         </is>
       </c>
       <c r="BA215" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>7.61</t>
         </is>
       </c>
       <c r="BB215" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>34.94</t>
         </is>
       </c>
       <c r="BC215" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>88.08</t>
         </is>
       </c>
       <c r="BD215" t="inlineStr">
         <is>
-          <t>0.4201</t>
+          <t>0.3902</t>
         </is>
       </c>
       <c r="BE215" t="inlineStr">
         <is>
-          <t>0.1672</t>
+          <t>0.1497</t>
         </is>
       </c>
       <c r="BF215" t="inlineStr">
         <is>
-          <t>27.43</t>
+          <t>28.36</t>
         </is>
       </c>
       <c r="BG215" t="inlineStr"/>
       <c r="BH215" t="inlineStr"/>
       <c r="BI215" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BJ215" t="inlineStr"/>
@@ -59543,27 +59547,27 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>680779</t>
+          <t>680700</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Henry Davis</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>2026-08-22T23:15:00Z</t>
+          <t>2026-08-22T23:05:00Z</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
@@ -59573,26 +59577,26 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>Tarik Skubal</t>
+          <t>Brandon Young</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>669373</t>
+          <t>687064</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L216" t="n">
-        <v>35.2</v>
+        <v>35.3</v>
       </c>
       <c r="M216" t="inlineStr">
         <is>
@@ -59610,22 +59614,22 @@
         </is>
       </c>
       <c r="P216" t="n">
-        <v>34.7</v>
+        <v>15.1</v>
       </c>
       <c r="Q216" t="n">
-        <v>28.8</v>
+        <v>43.6</v>
       </c>
       <c r="R216" t="n">
-        <v>27.6</v>
+        <v>32.1</v>
       </c>
       <c r="S216" t="n">
-        <v>40.2</v>
+        <v>47.9</v>
       </c>
       <c r="T216" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U216" t="n">
-        <v>0</v>
+        <v>22.9</v>
       </c>
       <c r="V216" t="inlineStr">
         <is>
@@ -59639,7 +59643,7 @@
       </c>
       <c r="X216" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y216" t="inlineStr">
@@ -59681,12 +59685,12 @@
       </c>
       <c r="AH216" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI216" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ216" t="inlineStr">
@@ -59696,12 +59700,12 @@
       </c>
       <c r="AK216" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/17, 0 HR</t>
+          <t>Last 7 games: 6/22, 0 HR</t>
         </is>
       </c>
       <c r="AL216" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.5% barrel, 13.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.9% barrel, 14.1 HR allowed</t>
         </is>
       </c>
       <c r="AM216" t="inlineStr">
@@ -59711,104 +59715,104 @@
       </c>
       <c r="AN216" t="inlineStr">
         <is>
-          <t>9.54</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="AO216" t="inlineStr">
         <is>
-          <t>38.52</t>
+          <t>32.97</t>
         </is>
       </c>
       <c r="AP216" t="inlineStr">
         <is>
-          <t>89.58</t>
+          <t>87.38</t>
         </is>
       </c>
       <c r="AQ216" t="inlineStr">
         <is>
-          <t>100.3588</t>
+          <t>97.0638</t>
         </is>
       </c>
       <c r="AR216" t="inlineStr">
         <is>
-          <t>0.3505</t>
+          <t>0.3709</t>
         </is>
       </c>
       <c r="AS216" t="inlineStr">
         <is>
-          <t>0.1466</t>
+          <t>0.1011</t>
         </is>
       </c>
       <c r="AT216" t="inlineStr">
         <is>
-          <t>0.2881</t>
+          <t>0.3264</t>
         </is>
       </c>
       <c r="AU216" t="inlineStr">
         <is>
-          <t>74.18</t>
+          <t>68.77</t>
         </is>
       </c>
       <c r="AV216" t="inlineStr">
         <is>
-          <t>42.63</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="AW216" t="inlineStr">
         <is>
-          <t>50.23</t>
+          <t>35.62</t>
         </is>
       </c>
       <c r="AX216" t="inlineStr">
         <is>
-          <t>26.14</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="AY216" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="AZ216" t="inlineStr">
         <is>
-          <t>0.1236</t>
+          <t>0.1162</t>
         </is>
       </c>
       <c r="BA216" t="inlineStr">
         <is>
-          <t>7.54</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="BB216" t="inlineStr">
         <is>
-          <t>35.38</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="BC216" t="inlineStr">
         <is>
-          <t>86.94</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="BD216" t="inlineStr">
         <is>
-          <t>0.3433</t>
+          <t>0.4201</t>
         </is>
       </c>
       <c r="BE216" t="inlineStr">
         <is>
-          <t>0.1233</t>
+          <t>0.1672</t>
         </is>
       </c>
       <c r="BF216" t="inlineStr">
         <is>
-          <t>26.32</t>
+          <t>27.43</t>
         </is>
       </c>
       <c r="BG216" t="inlineStr"/>
       <c r="BH216" t="inlineStr"/>
       <c r="BI216" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ216" t="inlineStr"/>
@@ -59819,27 +59823,27 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>593428</t>
+          <t>680779</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Xander Bogaerts</t>
+          <t>Henry Davis</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>2026-08-23T00:40:00Z</t>
+          <t>2026-08-22T23:15:00Z</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
@@ -59849,22 +59853,22 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>Dean Kremer</t>
+          <t>Tarik Skubal</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>665152</t>
+          <t>669373</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L217" t="n">
@@ -59882,26 +59886,26 @@
       </c>
       <c r="O217" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P217" t="n">
-        <v>28.5</v>
+        <v>34.7</v>
       </c>
       <c r="Q217" t="n">
-        <v>41.7</v>
+        <v>28.8</v>
       </c>
       <c r="R217" t="n">
-        <v>22.6</v>
+        <v>27.6</v>
       </c>
       <c r="S217" t="n">
-        <v>47.9</v>
+        <v>40.2</v>
       </c>
       <c r="T217" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U217" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="V217" t="inlineStr">
         <is>
@@ -59915,7 +59919,7 @@
       </c>
       <c r="X217" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y217" t="inlineStr">
@@ -59957,134 +59961,134 @@
       </c>
       <c r="AH217" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI217" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/19, 1 HR</t>
+          <t>Last 7 games: 2/17, 0 HR</t>
         </is>
       </c>
       <c r="AL217" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.8% barrel, 15.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.5% barrel, 13.8 HR allowed</t>
         </is>
       </c>
       <c r="AM217" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN217" t="inlineStr">
         <is>
-          <t>6.48</t>
+          <t>9.54</t>
         </is>
       </c>
       <c r="AO217" t="inlineStr">
         <is>
-          <t>40.18</t>
+          <t>38.52</t>
         </is>
       </c>
       <c r="AP217" t="inlineStr">
         <is>
-          <t>88.86</t>
+          <t>89.58</t>
         </is>
       </c>
       <c r="AQ217" t="inlineStr">
         <is>
-          <t>100.0019</t>
+          <t>100.3588</t>
         </is>
       </c>
       <c r="AR217" t="inlineStr">
         <is>
-          <t>0.3857</t>
+          <t>0.3505</t>
         </is>
       </c>
       <c r="AS217" t="inlineStr">
         <is>
-          <t>0.1348</t>
+          <t>0.1466</t>
         </is>
       </c>
       <c r="AT217" t="inlineStr">
         <is>
-          <t>0.3235</t>
+          <t>0.2881</t>
         </is>
       </c>
       <c r="AU217" t="inlineStr">
         <is>
-          <t>72.38</t>
+          <t>74.18</t>
         </is>
       </c>
       <c r="AV217" t="inlineStr">
         <is>
-          <t>28.43</t>
+          <t>42.63</t>
         </is>
       </c>
       <c r="AW217" t="inlineStr">
         <is>
-          <t>44.29</t>
+          <t>50.23</t>
         </is>
       </c>
       <c r="AX217" t="inlineStr">
         <is>
-          <t>23.27</t>
+          <t>26.14</t>
         </is>
       </c>
       <c r="AY217" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ217" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>0.1236</t>
         </is>
       </c>
       <c r="BA217" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>7.54</t>
         </is>
       </c>
       <c r="BB217" t="inlineStr">
         <is>
-          <t>34.4</t>
+          <t>35.38</t>
         </is>
       </c>
       <c r="BC217" t="inlineStr">
         <is>
-          <t>87.33</t>
+          <t>86.94</t>
         </is>
       </c>
       <c r="BD217" t="inlineStr">
         <is>
-          <t>0.4319</t>
+          <t>0.3433</t>
         </is>
       </c>
       <c r="BE217" t="inlineStr">
         <is>
-          <t>0.1953</t>
+          <t>0.1233</t>
         </is>
       </c>
       <c r="BF217" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>26.32</t>
         </is>
       </c>
       <c r="BG217" t="inlineStr"/>
       <c r="BH217" t="inlineStr"/>
       <c r="BI217" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ217" t="inlineStr"/>
@@ -60095,47 +60099,47 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>806146</t>
+          <t>593428</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>George Lombard Jr.</t>
+          <t>Xander Bogaerts</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>2026-08-22T17:35:00Z</t>
+          <t>2026-08-23T00:40:00Z</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>Dylan Cease</t>
+          <t>Dean Kremer</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>656302</t>
+          <t>665152</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
@@ -60144,7 +60148,7 @@
         </is>
       </c>
       <c r="L218" t="n">
-        <v>35.1</v>
+        <v>35.2</v>
       </c>
       <c r="M218" t="inlineStr">
         <is>
@@ -60158,61 +60162,65 @@
       </c>
       <c r="O218" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P218" t="n">
-        <v>19.6</v>
+        <v>28.5</v>
       </c>
       <c r="Q218" t="n">
-        <v>20.3</v>
+        <v>41.7</v>
       </c>
       <c r="R218" t="n">
-        <v>48.2</v>
+        <v>22.6</v>
       </c>
       <c r="S218" t="n">
-        <v>76.2</v>
+        <v>47.9</v>
       </c>
       <c r="T218" t="n">
         <v>50</v>
       </c>
       <c r="U218" t="n">
-        <v>27.7</v>
+        <v>24</v>
       </c>
       <c r="V218" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W218" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X218" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y218" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W218" t="inlineStr">
+      <c r="Z218" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X218" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y218" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z218" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA218" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB218" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB218" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC218" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD218" t="inlineStr"/>
@@ -60229,142 +60237,134 @@
       </c>
       <c r="AH218" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI218" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK218" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/23, 0 HR</t>
+          <t>Last 7 games: 3/19, 1 HR</t>
         </is>
       </c>
       <c r="AL218" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.0% barrel, 12.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.8% barrel, 15.7 HR allowed</t>
         </is>
       </c>
       <c r="AM218" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN218" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>6.48</t>
         </is>
       </c>
       <c r="AO218" t="inlineStr">
         <is>
-          <t>35.1</t>
+          <t>40.18</t>
         </is>
       </c>
       <c r="AP218" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>88.86</t>
         </is>
       </c>
       <c r="AQ218" t="inlineStr">
         <is>
-          <t>97.5738</t>
+          <t>100.0019</t>
         </is>
       </c>
       <c r="AR218" t="inlineStr">
         <is>
-          <t>0.358</t>
+          <t>0.3857</t>
         </is>
       </c>
       <c r="AS218" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>0.1348</t>
         </is>
       </c>
       <c r="AT218" t="inlineStr">
         <is>
-          <t>0.303</t>
+          <t>0.3235</t>
         </is>
       </c>
       <c r="AU218" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>72.38</t>
         </is>
       </c>
       <c r="AV218" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>28.43</t>
         </is>
       </c>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>32.4</t>
+          <t>44.29</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>23.27</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="AZ218" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>0.114</t>
         </is>
       </c>
       <c r="BA218" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="BB218" t="inlineStr">
         <is>
-          <t>33.93</t>
+          <t>34.4</t>
         </is>
       </c>
       <c r="BC218" t="inlineStr">
         <is>
-          <t>86.73</t>
+          <t>87.33</t>
         </is>
       </c>
       <c r="BD218" t="inlineStr">
         <is>
-          <t>0.3009</t>
+          <t>0.4319</t>
         </is>
       </c>
       <c r="BE218" t="inlineStr">
         <is>
-          <t>0.1086</t>
+          <t>0.1953</t>
         </is>
       </c>
       <c r="BF218" t="inlineStr">
         <is>
-          <t>25.47</t>
-        </is>
-      </c>
-      <c r="BG218" t="inlineStr">
-        <is>
-          <t>In From LF</t>
-        </is>
-      </c>
-      <c r="BH218" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
+          <t>34.56</t>
+        </is>
+      </c>
+      <c r="BG218" t="inlineStr"/>
+      <c r="BH218" t="inlineStr"/>
       <c r="BI218" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ218" t="inlineStr"/>
@@ -77514,7 +77514,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>56.8</v>
+        <v>56.9</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -77547,7 +77547,7 @@
         <v>80</v>
       </c>
       <c r="U19" t="n">
-        <v>40.9</v>
+        <v>43.7</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -77604,7 +77604,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -77745,12 +77745,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>672960</t>
+          <t>663662</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kazuma Okamoto</t>
+          <t>Daz Cameron</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -77775,7 +77775,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -77812,7 +77812,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>49.3</v>
+        <v>59.7</v>
       </c>
       <c r="Q20" t="n">
         <v>45.5</v>
@@ -77821,13 +77821,13 @@
         <v>48.2</v>
       </c>
       <c r="S20" t="n">
-        <v>86.40000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="T20" t="n">
         <v>78</v>
       </c>
       <c r="U20" t="n">
-        <v>61.5</v>
+        <v>54.9</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
@@ -77841,7 +77841,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -77862,7 +77862,7 @@
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr"/>
@@ -77874,27 +77874,27 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 4/11 over last 4 games</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
@@ -77904,72 +77904,72 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>19.63</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>27.13</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>88.19</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>101.4012</t>
+          <t>99.5682</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.426</t>
+          <t>0.5447</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>0.208</t>
+          <t>0.2722</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>0.314</t>
+          <t>0.3449</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>34.6</t>
+          <t>32.84</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>32.8</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>0.208</t>
+          <t>0.2835</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
@@ -78025,12 +78025,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>663662</t>
+          <t>672960</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Daz Cameron</t>
+          <t>Kazuma Okamoto</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -78055,7 +78055,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -78074,7 +78074,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>56.6</v>
+        <v>56.5</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -78092,7 +78092,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>59.7</v>
+        <v>49.3</v>
       </c>
       <c r="Q21" t="n">
         <v>45.5</v>
@@ -78101,13 +78101,13 @@
         <v>48.2</v>
       </c>
       <c r="S21" t="n">
-        <v>64.3</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T21" t="n">
         <v>78</v>
       </c>
       <c r="U21" t="n">
-        <v>54.9</v>
+        <v>59.1</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -78121,7 +78121,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -78142,7 +78142,7 @@
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr"/>
@@ -78154,27 +78154,27 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Contact streak: 4/11 over last 3 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
@@ -78184,72 +78184,72 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>19.63</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>27.13</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>88.19</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>99.5682</t>
+          <t>101.4012</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.5447</t>
+          <t>0.426</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>0.2722</t>
+          <t>0.208</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>0.3449</t>
+          <t>0.314</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>32.84</t>
+          <t>34.6</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>32.8</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>0.2835</t>
+          <t>0.208</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
